--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -16805,7 +16805,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetMasterTable" displayName="AssetMasterTable" ref="A5:X115" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssetMasterTable" displayName="AssetMasterTable" ref="A5:X241" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="24">
     <tableColumn id="1" name="AssetID"/>
     <tableColumn id="2" name="中文名"/>
@@ -17095,22 +17095,22 @@
     </row>
     <row r="6" spans="1:9" ht="42" customHeight="1">
       <c r="A6" s="8">
-        <f>=COUNTA(资产主表!$A$6:$A$240)</f>
+        <f>=COUNTA(资产主表!$A$6:$A$241)</f>
         <v>235</v>
       </c>
       <c r="B6" s="6" t="s"/>
       <c r="C6" s="8">
-        <f>=COUNTIF(资产主表!$K$6:$K$240,"已完成")+COUNTIF(资产主表!$K$6:$K$240,"原型已接入")+COUNTIF(资产主表!$K$6:$K$240,"正式美术已接入")+COUNTIF(资产主表!$K$6:$K$240,"已优化并正式接入")+COUNTIF(资产主表!$K$6:$K$240,"Blender源已完成")+COUNTIF(资产主表!$K$6:$K$240,"已导入；优化完成")</f>
+        <f>=COUNTIF(资产主表!$K$6:$K$241,"已完成")+COUNTIF(资产主表!$K$6:$K$241,"原型已接入")+COUNTIF(资产主表!$K$6:$K$241,"正式美术已接入")+COUNTIF(资产主表!$K$6:$K$241,"已优化并正式接入")+COUNTIF(资产主表!$K$6:$K$241,"Blender源已完成")+COUNTIF(资产主表!$K$6:$K$241,"已导入；优化完成")</f>
         <v>164</v>
       </c>
       <c r="D6" s="6" t="s"/>
       <c r="E6" s="8">
-        <f>=COUNTIF(资产主表!$K$6:$K$240,"待制作")+COUNTIF(资产主表!$K$6:$K$240,"程序占位")</f>
+        <f>=COUNTIF(资产主表!$K$6:$K$241,"待制作")+COUNTIF(资产主表!$K$6:$K$241,"程序占位")</f>
         <v>60</v>
       </c>
       <c r="F6" s="6" t="s"/>
       <c r="G6" s="8">
-        <f>=COUNTIF(资产主表!$S$6:$S$240,"重复")</f>
+        <f>=COUNTIF(资产主表!$S$6:$S$241,"重复")</f>
         <v>0</v>
       </c>
       <c r="H6" s="6" t="s"/>
@@ -17167,11 +17167,11 @@
         <v>273</v>
       </c>
       <c r="B10" s="12">
-        <f>=COUNTIF(资产主表!$C$6:$C$240,A10)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$241,A10)</f>
         <v>101</v>
       </c>
       <c r="C10" s="12">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$240=A10)*((资产主表!$K$6:$K$240="已完成")+(资产主表!$K$6:$K$240="原型已接入")+(资产主表!$K$6:$K$240="正式美术已接入")+(资产主表!$K$6:$K$240="已优化并正式接入")+(资产主表!$K$6:$K$240="Blender源已完成")+(资产主表!$K$6:$K$240="已导入；优化完成")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$241=A10)*((资产主表!$K$6:$K$241="已完成")+(资产主表!$K$6:$K$241="原型已接入")+(资产主表!$K$6:$K$241="正式美术已接入")+(资产主表!$K$6:$K$241="已优化并正式接入")+(资产主表!$K$6:$K$241="Blender源已完成")+(资产主表!$K$6:$K$241="已导入；优化完成")))</f>
         <v>39</v>
       </c>
       <c r="D10" s="12" t="s"/>
@@ -17187,11 +17187,11 @@
         <v>274</v>
       </c>
       <c r="B11" s="12">
-        <f>=COUNTIF(资产主表!$C$6:$C$240,A11)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$241,A11)</f>
         <v>20</v>
       </c>
       <c r="C11" s="12">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$240=A11)*((资产主表!$K$6:$K$240="已完成")+(资产主表!$K$6:$K$240="原型已接入")+(资产主表!$K$6:$K$240="正式美术已接入")+(资产主表!$K$6:$K$240="已优化并正式接入")+(资产主表!$K$6:$K$240="Blender源已完成")+(资产主表!$K$6:$K$240="已导入；优化完成")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$241=A11)*((资产主表!$K$6:$K$241="已完成")+(资产主表!$K$6:$K$241="原型已接入")+(资产主表!$K$6:$K$241="正式美术已接入")+(资产主表!$K$6:$K$241="已优化并正式接入")+(资产主表!$K$6:$K$241="Blender源已完成")+(资产主表!$K$6:$K$241="已导入；优化完成")))</f>
         <v>11</v>
       </c>
       <c r="D11" s="12" t="s"/>
@@ -17207,11 +17207,11 @@
         <v>275</v>
       </c>
       <c r="B12" s="12">
-        <f>=COUNTIF(资产主表!$C$6:$C$240,A12)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$241,A12)</f>
         <v>114</v>
       </c>
       <c r="C12" s="12">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$240=A12)*((资产主表!$K$6:$K$240="已完成")+(资产主表!$K$6:$K$240="原型已接入")+(资产主表!$K$6:$K$240="正式美术已接入")+(资产主表!$K$6:$K$240="已优化并正式接入")+(资产主表!$K$6:$K$240="Blender源已完成")+(资产主表!$K$6:$K$240="已导入；优化完成")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$241=A12)*((资产主表!$K$6:$K$241="已完成")+(资产主表!$K$6:$K$241="原型已接入")+(资产主表!$K$6:$K$241="正式美术已接入")+(资产主表!$K$6:$K$241="已优化并正式接入")+(资产主表!$K$6:$K$241="Blender源已完成")+(资产主表!$K$6:$K$241="已导入；优化完成")))</f>
         <v>114</v>
       </c>
       <c r="D12" s="12" t="s"/>
@@ -17684,7 +17684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="Y240"/>
+  <dimension ref="Y241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -17878,7 +17878,7 @@
         <v>场景|biome_kit|base_world|root|顶视|default</v>
       </c>
       <c r="S6" s="25" t="str">
-        <f t="array" ref="S6">=IF(COUNTIF($R$6:$R$240,R6)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S6">=IF(COUNTIF($R$6:$R$241,R6)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T6" s="25" t="s"/>
@@ -17949,7 +17949,7 @@
         <v>场景|biome_kit|iron_frontier|root|顶视|default</v>
       </c>
       <c r="S7" s="25" t="str">
-        <f t="array" ref="S7">=IF(COUNTIF($R$6:$R$240,R7)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S7">=IF(COUNTIF($R$6:$R$241,R7)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T7" s="25" t="s"/>
@@ -18020,7 +18020,7 @@
         <v>场景|biome_kit|rust_foundry|root|顶视|default</v>
       </c>
       <c r="S8" s="25" t="str">
-        <f t="array" ref="S8">=IF(COUNTIF($R$6:$R$240,R8)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S8">=IF(COUNTIF($R$6:$R$241,R8)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T8" s="25" t="s"/>
@@ -18091,7 +18091,7 @@
         <v>场景|biome_kit|spore_depths|root|顶视|default</v>
       </c>
       <c r="S9" s="25" t="str">
-        <f t="array" ref="S9">=IF(COUNTIF($R$6:$R$240,R9)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S9">=IF(COUNTIF($R$6:$R$241,R9)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T9" s="25" t="s"/>
@@ -18162,7 +18162,7 @@
         <v>场景|biome_kit|abyss_archive|root|顶视|default</v>
       </c>
       <c r="S10" s="25" t="str">
-        <f t="array" ref="S10">=IF(COUNTIF($R$6:$R$240,R10)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S10">=IF(COUNTIF($R$6:$R$241,R10)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T10" s="25" t="s"/>
@@ -18233,7 +18233,7 @@
         <v>场景|biome_kit|training_range|root|顶视|default</v>
       </c>
       <c r="S11" s="25" t="str">
-        <f t="array" ref="S11">=IF(COUNTIF($R$6:$R$240,R11)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S11">=IF(COUNTIF($R$6:$R$241,R11)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T11" s="25" t="s"/>
@@ -18304,7 +18304,7 @@
         <v>场景|room_dressing|room_combat|root|顶视|default</v>
       </c>
       <c r="S12" s="25" t="str">
-        <f t="array" ref="S12">=IF(COUNTIF($R$6:$R$240,R12)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S12">=IF(COUNTIF($R$6:$R$241,R12)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T12" s="25" t="s"/>
@@ -18375,7 +18375,7 @@
         <v>场景|room_dressing|room_elite|root|顶视|default</v>
       </c>
       <c r="S13" s="25" t="str">
-        <f t="array" ref="S13">=IF(COUNTIF($R$6:$R$240,R13)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S13">=IF(COUNTIF($R$6:$R$241,R13)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T13" s="25" t="s"/>
@@ -18446,7 +18446,7 @@
         <v>场景|room_dressing|room_boss|root|顶视|default</v>
       </c>
       <c r="S14" s="25" t="str">
-        <f t="array" ref="S14">=IF(COUNTIF($R$6:$R$240,R14)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S14">=IF(COUNTIF($R$6:$R$241,R14)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T14" s="25" t="s"/>
@@ -18517,7 +18517,7 @@
         <v>场景|room_dressing|room_event|root|顶视|default</v>
       </c>
       <c r="S15" s="25" t="str">
-        <f t="array" ref="S15">=IF(COUNTIF($R$6:$R$240,R15)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S15">=IF(COUNTIF($R$6:$R$241,R15)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T15" s="25" t="s"/>
@@ -18588,7 +18588,7 @@
         <v>场景|room_dressing|room_extraction|root|顶视|default</v>
       </c>
       <c r="S16" s="25" t="str">
-        <f t="array" ref="S16">=IF(COUNTIF($R$6:$R$240,R16)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S16">=IF(COUNTIF($R$6:$R$241,R16)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T16" s="25" t="s"/>
@@ -18659,7 +18659,7 @@
         <v>场景|room_dressing|room_merchant|root|顶视|default</v>
       </c>
       <c r="S17" s="25" t="str">
-        <f t="array" ref="S17">=IF(COUNTIF($R$6:$R$240,R17)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S17">=IF(COUNTIF($R$6:$R$241,R17)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T17" s="25" t="s"/>
@@ -18730,7 +18730,7 @@
         <v>场景|room_dressing|room_scavenge|root|顶视|default</v>
       </c>
       <c r="S18" s="25" t="str">
-        <f t="array" ref="S18">=IF(COUNTIF($R$6:$R$240,R18)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S18">=IF(COUNTIF($R$6:$R$241,R18)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T18" s="25" t="s"/>
@@ -18801,7 +18801,7 @@
         <v>场景|room_dressing|room_storage|root|顶视|default</v>
       </c>
       <c r="S19" s="25" t="str">
-        <f t="array" ref="S19">=IF(COUNTIF($R$6:$R$240,R19)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S19">=IF(COUNTIF($R$6:$R$241,R19)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T19" s="25" t="s"/>
@@ -18872,7 +18872,7 @@
         <v>场景|room_dressing|room_trap|root|顶视|default</v>
       </c>
       <c r="S20" s="25" t="str">
-        <f t="array" ref="S20">=IF(COUNTIF($R$6:$R$240,R20)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S20">=IF(COUNTIF($R$6:$R$241,R20)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T20" s="25" t="s"/>
@@ -18943,7 +18943,7 @@
         <v>场景|room_dressing|room_upgrade|root|顶视|default</v>
       </c>
       <c r="S21" s="25" t="str">
-        <f t="array" ref="S21">=IF(COUNTIF($R$6:$R$240,R21)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S21">=IF(COUNTIF($R$6:$R$241,R21)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T21" s="25" t="s"/>
@@ -19014,7 +19014,7 @@
         <v>场景|room_dressing|room_spawn|root|顶视|default</v>
       </c>
       <c r="S22" s="25" t="str">
-        <f t="array" ref="S22">=IF(COUNTIF($R$6:$R$240,R22)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S22">=IF(COUNTIF($R$6:$R$241,R22)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T22" s="25" t="s"/>
@@ -19085,7 +19085,7 @@
         <v>场景|room_dressing|room_stairs|root|顶视|default</v>
       </c>
       <c r="S23" s="25" t="str">
-        <f t="array" ref="S23">=IF(COUNTIF($R$6:$R$240,R23)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S23">=IF(COUNTIF($R$6:$R$241,R23)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T23" s="25" t="s"/>
@@ -19156,7 +19156,7 @@
         <v>场景道具|facility|base_divination|root|顶视|default</v>
       </c>
       <c r="S24" s="25" t="str">
-        <f t="array" ref="S24">=IF(COUNTIF($R$6:$R$240,R24)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S24">=IF(COUNTIF($R$6:$R$241,R24)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T24" s="25" t="s"/>
@@ -19227,7 +19227,7 @@
         <v>场景道具|facility|base_vault|root|顶视|default</v>
       </c>
       <c r="S25" s="25" t="str">
-        <f t="array" ref="S25">=IF(COUNTIF($R$6:$R$240,R25)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S25">=IF(COUNTIF($R$6:$R$241,R25)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T25" s="25" t="s"/>
@@ -19298,7 +19298,7 @@
         <v>场景道具|facility|base_monster_archive|root|顶视|default</v>
       </c>
       <c r="S26" s="25" t="str">
-        <f t="array" ref="S26">=IF(COUNTIF($R$6:$R$240,R26)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S26">=IF(COUNTIF($R$6:$R$241,R26)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T26" s="25" t="s"/>
@@ -19369,7 +19369,7 @@
         <v>场景道具|facility|base_card_collection|root|顶视|default</v>
       </c>
       <c r="S27" s="25" t="str">
-        <f t="array" ref="S27">=IF(COUNTIF($R$6:$R$240,R27)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S27">=IF(COUNTIF($R$6:$R$241,R27)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T27" s="25" t="s"/>
@@ -19440,7 +19440,7 @@
         <v>场景道具|facility|base_terminal|root|顶视|default</v>
       </c>
       <c r="S28" s="25" t="str">
-        <f t="array" ref="S28">=IF(COUNTIF($R$6:$R$240,R28)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S28">=IF(COUNTIF($R$6:$R$241,R28)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T28" s="25" t="s"/>
@@ -19511,7 +19511,7 @@
         <v>场景道具|facility|dungeon_gate|root|顶视|default</v>
       </c>
       <c r="S29" s="25" t="str">
-        <f t="array" ref="S29">=IF(COUNTIF($R$6:$R$240,R29)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S29">=IF(COUNTIF($R$6:$R$241,R29)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T29" s="25" t="s"/>
@@ -19582,7 +19582,7 @@
         <v>场景道具|facility|workbench|root|顶视|default</v>
       </c>
       <c r="S30" s="25" t="str">
-        <f t="array" ref="S30">=IF(COUNTIF($R$6:$R$240,R30)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S30">=IF(COUNTIF($R$6:$R$241,R30)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T30" s="25" t="s"/>
@@ -19653,7 +19653,7 @@
         <v>场景道具|facility|door|root|顶视|default</v>
       </c>
       <c r="S31" s="25" t="str">
-        <f t="array" ref="S31">=IF(COUNTIF($R$6:$R$240,R31)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S31">=IF(COUNTIF($R$6:$R$241,R31)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T31" s="25" t="s"/>
@@ -19730,7 +19730,7 @@
         <v>场景|environment_module_3d|base99_floor_full_replacement_v021|full_floor_visual_replacement|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S32" s="28" t="str">
-        <f t="array" ref="S32">=IF(COUNTIF($R$6:$R$240,R32)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S32">=IF(COUNTIF($R$6:$R$241,R32)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T32" s="28" t="s">
@@ -19809,7 +19809,7 @@
         <v>场景|environment_module_3d|base99_loft_floor_finish_v020|loft_floor_finish_overlay|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S33" s="21" t="str">
-        <f t="array" ref="S33">=IF(COUNTIF($R$6:$R$240,R33)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S33">=IF(COUNTIF($R$6:$R$241,R33)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T33" s="21" t="s">
@@ -19888,7 +19888,7 @@
         <v>场景|environment_module_3d|base99_floor_visual_layout_v021|floor_visual_assembly|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S34" s="21" t="str">
-        <f t="array" ref="S34">=IF(COUNTIF($R$6:$R$240,R34)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S34">=IF(COUNTIF($R$6:$R$241,R34)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T34" s="21" t="s">
@@ -19967,7 +19967,7 @@
         <v>场景|base|base_world|root_3d|俯视3d|default</v>
       </c>
       <c r="S35" s="21" t="str">
-        <f t="array" ref="S35">=IF(COUNTIF($R$6:$R$240,R35)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S35">=IF(COUNTIF($R$6:$R$241,R35)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T35" s="21" t="s">
@@ -20046,7 +20046,7 @@
         <v>场景道具|facility|base_facility_module|root_3d|俯视3d|default</v>
       </c>
       <c r="S36" s="28" t="str">
-        <f t="array" ref="S36">=IF(COUNTIF($R$6:$R$240,R36)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S36">=IF(COUNTIF($R$6:$R$241,R36)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T36" s="28" t="s">
@@ -20125,7 +20125,7 @@
         <v>场景道具|door|dungeon_gate|root_3d|俯视3d|default</v>
       </c>
       <c r="S37" s="21" t="str">
-        <f t="array" ref="S37">=IF(COUNTIF($R$6:$R$240,R37)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S37">=IF(COUNTIF($R$6:$R$241,R37)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T37" s="21" t="s">
@@ -20204,7 +20204,7 @@
         <v>场景|review_board|base_world|preview_3d|俯视3d|default</v>
       </c>
       <c r="S38" s="21" t="str">
-        <f t="array" ref="S38">=IF(COUNTIF($R$6:$R$240,R38)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S38">=IF(COUNTIF($R$6:$R$241,R38)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T38" s="21" t="s">
@@ -20281,7 +20281,7 @@
         <v>场景|room|dungeon_runtime|root_3d|俯视3d|default</v>
       </c>
       <c r="S39" s="28" t="str">
-        <f t="array" ref="S39">=IF(COUNTIF($R$6:$R$240,R39)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S39">=IF(COUNTIF($R$6:$R$241,R39)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T39" s="28" t="s">
@@ -20360,7 +20360,7 @@
         <v>场景|biome|iron_frontier|theme_3d|俯视3d|default</v>
       </c>
       <c r="S40" s="21" t="str">
-        <f t="array" ref="S40">=IF(COUNTIF($R$6:$R$240,R40)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S40">=IF(COUNTIF($R$6:$R$241,R40)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T40" s="21" t="s">
@@ -20439,7 +20439,7 @@
         <v>场景|biome|rust_foundry|theme_3d|俯视3d|default</v>
       </c>
       <c r="S41" s="21" t="str">
-        <f t="array" ref="S41">=IF(COUNTIF($R$6:$R$240,R41)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S41">=IF(COUNTIF($R$6:$R$241,R41)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T41" s="21" t="s">
@@ -20518,7 +20518,7 @@
         <v>场景|biome|spore_depths|theme_3d|俯视3d|default</v>
       </c>
       <c r="S42" s="21" t="str">
-        <f t="array" ref="S42">=IF(COUNTIF($R$6:$R$240,R42)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S42">=IF(COUNTIF($R$6:$R$241,R42)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T42" s="21" t="s">
@@ -20597,7 +20597,7 @@
         <v>场景|biome|abyss_archive|theme_3d|俯视3d|default</v>
       </c>
       <c r="S43" s="21" t="str">
-        <f t="array" ref="S43">=IF(COUNTIF($R$6:$R$240,R43)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S43">=IF(COUNTIF($R$6:$R$241,R43)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T43" s="21" t="s">
@@ -20676,7 +20676,7 @@
         <v>场景道具|light|wasteland_light|root_3d|俯视3d|default</v>
       </c>
       <c r="S44" s="28" t="str">
-        <f t="array" ref="S44">=IF(COUNTIF($R$6:$R$240,R44)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S44">=IF(COUNTIF($R$6:$R$241,R44)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T44" s="28" t="s">
@@ -20755,7 +20755,7 @@
         <v>场景道具|furniture|room_furniture|root_3d|俯视3d|default</v>
       </c>
       <c r="S45" s="21" t="str">
-        <f t="array" ref="S45">=IF(COUNTIF($R$6:$R$240,R45)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S45">=IF(COUNTIF($R$6:$R$241,R45)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T45" s="21" t="s">
@@ -20834,7 +20834,7 @@
         <v>场景道具|container|search_container|root_3d|俯视3d|closed_opened</v>
       </c>
       <c r="S46" s="21" t="str">
-        <f t="array" ref="S46">=IF(COUNTIF($R$6:$R$240,R46)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S46">=IF(COUNTIF($R$6:$R$241,R46)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T46" s="21" t="s">
@@ -20913,7 +20913,7 @@
         <v>场景道具|facility|service_station|root_3d|俯视3d|default</v>
       </c>
       <c r="S47" s="21" t="str">
-        <f t="array" ref="S47">=IF(COUNTIF($R$6:$R$240,R47)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S47">=IF(COUNTIF($R$6:$R$241,R47)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T47" s="21" t="s">
@@ -20992,7 +20992,7 @@
         <v>场景道具|facility|extraction_beacon|root_3d|俯视3d|locked_active_done</v>
       </c>
       <c r="S48" s="21" t="str">
-        <f t="array" ref="S48">=IF(COUNTIF($R$6:$R$240,R48)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S48">=IF(COUNTIF($R$6:$R$241,R48)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T48" s="21" t="s">
@@ -21069,7 +21069,7 @@
         <v>场景|training_range|training_range|root_3d|俯视3d|default</v>
       </c>
       <c r="S49" s="21" t="str">
-        <f t="array" ref="S49">=IF(COUNTIF($R$6:$R$240,R49)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S49">=IF(COUNTIF($R$6:$R$241,R49)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T49" s="21" t="s">
@@ -21148,7 +21148,7 @@
         <v>场景|review_board|dungeon_runtime|preview_3d|俯视3d|default</v>
       </c>
       <c r="S50" s="21" t="str">
-        <f t="array" ref="S50">=IF(COUNTIF($R$6:$R$240,R50)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S50">=IF(COUNTIF($R$6:$R$241,R50)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T50" s="21" t="s">
@@ -21227,7 +21227,7 @@
         <v>场景|review_board|training_range|preview_3d|俯视3d|default</v>
       </c>
       <c r="S51" s="21" t="str">
-        <f t="array" ref="S51">=IF(COUNTIF($R$6:$R$240,R51)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S51">=IF(COUNTIF($R$6:$R$241,R51)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T51" s="21" t="s">
@@ -21306,7 +21306,7 @@
         <v>场景道具|facility|room_light_switch|root_3d|俯视3d|default</v>
       </c>
       <c r="S52" s="28" t="str">
-        <f t="array" ref="S52">=IF(COUNTIF($R$6:$R$240,R52)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S52">=IF(COUNTIF($R$6:$R$241,R52)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T52" s="28" t="s">
@@ -21385,7 +21385,7 @@
         <v>场景|room_kit|tower_descent|root_3d|俯视3d|godot_runtime</v>
       </c>
       <c r="S53" s="28" t="str">
-        <f t="array" ref="S53">=IF(COUNTIF($R$6:$R$240,R53)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S53">=IF(COUNTIF($R$6:$R$241,R53)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T53" s="28" t="s">
@@ -21464,7 +21464,7 @@
         <v>场景|room_kit|tower_descent|floor_tile_5m|俯视3d|godot_runtime</v>
       </c>
       <c r="S54" s="28" t="str">
-        <f t="array" ref="S54">=IF(COUNTIF($R$6:$R$240,R54)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S54">=IF(COUNTIF($R$6:$R$241,R54)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T54" s="28" t="s">
@@ -21523,17 +21523,25 @@
       <c r="L55" s="28" t="s">
         <v>361</v>
       </c>
-      <c r="M55" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="N55" s="28" t="s">
-        <v>713</v>
-      </c>
-      <c r="O55" s="28" t="s">
-        <v>714</v>
-      </c>
-      <c r="P55" s="28" t="s">
-        <v>715</v>
+      <c r="M55" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v004</t>
+        </is>
+      </c>
+      <c r="N55" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GLB / 可视包络 5×11.9×0.4675m（结构阻挡 0.30m）/ 12m逻辑碰撞 / 共享Mesh / 可旋转</t>
+        </is>
+      </c>
+      <c r="O55" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/art/environments/tower_descent_3d/components/env_tower_wall_solid_5m_top3d.glb</t>
+        </is>
+      </c>
+      <c r="P55" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/art/environments/tower_descent_3d/source/wall_height12/env_tower_wall_solid_5m_source_v004.blend; assets/art/environments/tower_descent_3d/source/wall_height12/export_env_tower_wall_solid_5m_v004.py; assets/art/environments/tower_zones/battle/source/common_components/v007/env_battle_common_components_source_v007.blend; assets/art/props/dungeon_3d/prp_tower_wall_solid_5m.tscn; src/world3d/TowerGeometry3D.gd</t>
+        </is>
       </c>
       <c r="Q55" s="28" t="s">
         <v>716</v>
@@ -21543,26 +21551,36 @@
         <v>场景|room_kit|tower_descent|wall_solid_5m|俯视3d|godot_runtime</v>
       </c>
       <c r="S55" s="28" t="str">
-        <f t="array" ref="S55">=IF(COUNTIF($R$6:$R$240,R55)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S55">=IF(COUNTIF($R$6:$R$241,R55)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
-      <c r="T55" s="28" t="s">
-        <v>717</v>
+      <c r="T55" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0bca134eef74148f0df444d72afff769974863cab6fec4ca885b773186649fb9</t>
+        </is>
       </c>
       <c r="U55" s="28" t="s">
         <v>486</v>
       </c>
       <c r="V55" s="29">
-        <v>46277</v>
-      </c>
-      <c r="W55" s="28" t="s">
-        <v>695</v>
+        <v>46284</v>
+      </c>
+      <c r="W55" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blender 派生（自 v007 通用实墙组件）</t>
+        </is>
       </c>
       <c r="X55" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="Y55" s="28" t="s">
-        <v>718</v>
+      <c r="Y55" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-02：南北向水平共享墙统一注册相机抬升判定，楼梯南侧墙纳入同一规则；墙体始终不透明，取消运行时墙体透明度改写。
+2026-08-03：东西向5m房间连接通道的无门南侧实墙增加独立camera_lower_wall碰撞标记；南北向通道的东/西墙保持不触发。真实98层侧门通道相机回归通过。
+2026-08-03：水平通道按每5m左右各一块动态生成9m实墙实例；墙体可视覆盖与连续碰撞严格等长，东西向通道南墙继续承担相机抬升判定。
+2026-08-03：动态水平通道按实墙Mesh包围盒底面自动贴合楼面；GLB几何保持Y=0..9m，可视原点不再误用碰撞盒4.5m中心。新增墙底高度与9m墙高自动回归。
+2026-09-19：可视网格换为 v004（自 battle/common_components v007「wall_standard_5m_通用包」派生，派生脚本 assets/art/environments/tower_descent_3d/source/wall_height12/export_env_tower_wall_solid_5m_v004.py）。Blender 内对根节点烘焙 180° 偏航后 transform_apply，使装饰面落在 Godot +Z（与 prp_tower_* A 套 forward_axis="+Z" 对齐）；先三角化再删朝下面（去 1095 面）、join 成单 Mesh，丢掉无几何的 03_清漆反光_紫粉点缀 槽，只留 01/02/04 三个共享色盘角色。稳定路径 GLB 原地覆盖（文件名去版本号），节点名统一 ENV_TOWER_WALL_SOLID_5M，根变换为单位矩阵（该 GLB 被 TowerDescent3D 直接 preload，根变换会直接决定走廊墙位置）。阻挡不动：结构碰撞仍 0.30m 代理，可视包络 5×11.9×0.4675m（正面装甲凸到 +Z 0.3175）。</t>
+        </is>
       </c>
     </row>
     <row r="56" spans="1:25">
@@ -21622,7 +21640,7 @@
         <v>场景|room_kit|tower_descent|wall_parapet_5m|俯视3d|godot_runtime</v>
       </c>
       <c r="S56" s="28" t="str">
-        <f t="array" ref="S56">=IF(COUNTIF($R$6:$R$240,R56)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S56">=IF(COUNTIF($R$6:$R$241,R56)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T56" s="28" t="s">
@@ -21701,7 +21719,7 @@
         <v>场景|room_kit|tower_descent|wall_door_5m|俯视3d|godot_runtime</v>
       </c>
       <c r="S57" s="28" t="str">
-        <f t="array" ref="S57">=IF(COUNTIF($R$6:$R$240,R57)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S57">=IF(COUNTIF($R$6:$R$241,R57)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T57" s="28" t="s">
@@ -21780,7 +21798,7 @@
         <v>场景|room_kit|stairwell_generic_12m|stairwell_generic_12m|俯视3d|godot_runtime</v>
       </c>
       <c r="S58" s="28" t="str">
-        <f t="array" ref="S58">=IF(COUNTIF($R$6:$R$240,R58)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S58">=IF(COUNTIF($R$6:$R$241,R58)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T58" s="28" t="s">
@@ -21859,7 +21877,7 @@
         <v>场景|room_kit|stairwell_rooftop_12m|stairwell_rooftop_12m|俯视3d|godot_runtime</v>
       </c>
       <c r="S59" s="28" t="str">
-        <f t="array" ref="S59">=IF(COUNTIF($R$6:$R$240,R59)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S59">=IF(COUNTIF($R$6:$R$241,R59)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T59" s="28" t="s">
@@ -21936,7 +21954,7 @@
         <v>场景|boss_arena|arena_archive_95|dressing|top3d|default / 高模流式</v>
       </c>
       <c r="S60" s="21" t="str">
-        <f t="array" ref="S60">=IF(COUNTIF($R$6:$R$240,R60)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S60">=IF(COUNTIF($R$6:$R$241,R60)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T60" s="21" t="s">
@@ -22013,7 +22031,7 @@
         <v>场景|boss_arena|arena_furnace_90|dressing|top3d|default / 高模流式</v>
       </c>
       <c r="S61" s="21" t="str">
-        <f t="array" ref="S61">=IF(COUNTIF($R$6:$R$240,R61)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S61">=IF(COUNTIF($R$6:$R$241,R61)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T61" s="21" t="s">
@@ -22090,7 +22108,7 @@
         <v>场景|boss_arena|arena_choir_85|dressing|top3d|default / 高模流式</v>
       </c>
       <c r="S62" s="21" t="str">
-        <f t="array" ref="S62">=IF(COUNTIF($R$6:$R$240,R62)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S62">=IF(COUNTIF($R$6:$R$241,R62)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T62" s="21" t="s">
@@ -22167,7 +22185,7 @@
         <v>场景|environment_kit_3d|base99_modular_room|root_3d|top3d / local -z 正面|default / modular</v>
       </c>
       <c r="S63" s="21" t="str">
-        <f t="array" ref="S63">=IF(COUNTIF($R$6:$R$240,R63)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S63">=IF(COUNTIF($R$6:$R$241,R63)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T63" s="21" t="s"/>
@@ -22244,7 +22262,7 @@
         <v>场景|environment_module_3d|base99_wall_plain_5x12|wall_plain|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S64" s="21" t="str">
-        <f t="array" ref="S64">=IF(COUNTIF($R$6:$R$240,R64)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S64">=IF(COUNTIF($R$6:$R$241,R64)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T64" s="21" t="s">
@@ -22323,7 +22341,7 @@
         <v>场景|environment_module_3d|base99_wall_door_5x12|wall_door|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S65" s="21" t="str">
-        <f t="array" ref="S65">=IF(COUNTIF($R$6:$R$240,R65)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S65">=IF(COUNTIF($R$6:$R$241,R65)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T65" s="21" t="s">
@@ -22402,7 +22420,7 @@
         <v>场景|environment_module_3d|base99_floor_plain_5m|floor_plain|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S66" s="21" t="str">
-        <f t="array" ref="S66">=IF(COUNTIF($R$6:$R$240,R66)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S66">=IF(COUNTIF($R$6:$R$241,R66)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T66" s="21" t="s">
@@ -22481,7 +22499,7 @@
         <v>场景|environment_module_3d|base99_floor_rivet_5m|floor_rivet|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S67" s="21" t="str">
-        <f t="array" ref="S67">=IF(COUNTIF($R$6:$R$240,R67)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S67">=IF(COUNTIF($R$6:$R$241,R67)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T67" s="21" t="s">
@@ -22560,7 +22578,7 @@
         <v>场景|environment_module_3d|base_facility_art_layout|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S68" s="21" t="str">
-        <f t="array" ref="S68">=IF(COUNTIF($R$6:$R$240,R68)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S68">=IF(COUNTIF($R$6:$R$241,R68)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T68" s="21" t="s">
@@ -22639,7 +22657,7 @@
         <v>场景|environment_module_3d|corner_l_5m|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S69" s="21" t="str">
-        <f t="array" ref="S69">=IF(COUNTIF($R$6:$R$240,R69)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S69">=IF(COUNTIF($R$6:$R$241,R69)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T69" s="21" t="s">
@@ -22718,7 +22736,7 @@
         <v>场景|environment_module_3d|corner_l_parapet_5m|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S70" s="21" t="str">
-        <f t="array" ref="S70">=IF(COUNTIF($R$6:$R$240,R70)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S70">=IF(COUNTIF($R$6:$R$241,R70)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T70" s="21" t="s">
@@ -22797,7 +22815,7 @@
         <v>场景|environment_module_3d|corner_t_5m|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S71" s="21" t="str">
-        <f t="array" ref="S71">=IF(COUNTIF($R$6:$R$240,R71)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S71">=IF(COUNTIF($R$6:$R$241,R71)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T71" s="21" t="s">
@@ -22876,7 +22894,7 @@
         <v>场景|environment_module_3d|corner_x_5m|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S72" s="21" t="str">
-        <f t="array" ref="S72">=IF(COUNTIF($R$6:$R$240,R72)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S72">=IF(COUNTIF($R$6:$R$241,R72)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T72" s="21" t="s">
@@ -22955,7 +22973,7 @@
         <v>场景|environment_module_3d|corridor_ceiling_segment|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S73" s="21" t="str">
-        <f t="array" ref="S73">=IF(COUNTIF($R$6:$R$240,R73)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S73">=IF(COUNTIF($R$6:$R$241,R73)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T73" s="21" t="s">
@@ -23034,7 +23052,7 @@
         <v>场景|environment_module_3d|corridor_floor_segment|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S74" s="21" t="str">
-        <f t="array" ref="S74">=IF(COUNTIF($R$6:$R$240,R74)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S74">=IF(COUNTIF($R$6:$R$241,R74)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T74" s="21" t="s">
@@ -23113,7 +23131,7 @@
         <v>场景|environment_module_3d|corridor_stair_tread|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S75" s="21" t="str">
-        <f t="array" ref="S75">=IF(COUNTIF($R$6:$R$240,R75)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S75">=IF(COUNTIF($R$6:$R$241,R75)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T75" s="21" t="s">
@@ -23192,7 +23210,7 @@
         <v>场景|environment_module_3d|corridor_wall_segment|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S76" s="21" t="str">
-        <f t="array" ref="S76">=IF(COUNTIF($R$6:$R$240,R76)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S76">=IF(COUNTIF($R$6:$R$241,R76)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T76" s="21" t="s">
@@ -23271,7 +23289,7 @@
         <v>场景|environment_module_3d|room_access_step|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S77" s="21" t="str">
-        <f t="array" ref="S77">=IF(COUNTIF($R$6:$R$240,R77)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S77">=IF(COUNTIF($R$6:$R$241,R77)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T77" s="21" t="s">
@@ -23350,7 +23368,7 @@
         <v>场景|environment_module_3d|room_corner_post|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S78" s="21" t="str">
-        <f t="array" ref="S78">=IF(COUNTIF($R$6:$R$240,R78)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S78">=IF(COUNTIF($R$6:$R$241,R78)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T78" s="21" t="s">
@@ -23429,7 +23447,7 @@
         <v>场景|environment_module_3d|room_door_lintel|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S79" s="21" t="str">
-        <f t="array" ref="S79">=IF(COUNTIF($R$6:$R$240,R79)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S79">=IF(COUNTIF($R$6:$R$241,R79)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T79" s="21" t="s">
@@ -23508,7 +23526,7 @@
         <v>场景|environment_module_3d|room_facility_base_wall_door_side|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S80" s="21" t="str">
-        <f t="array" ref="S80">=IF(COUNTIF($R$6:$R$240,R80)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S80">=IF(COUNTIF($R$6:$R$241,R80)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T80" s="21" t="s">
@@ -23587,7 +23605,7 @@
         <v>场景|environment_module_3d|room_facility_base_wall_lintel|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S81" s="21" t="str">
-        <f t="array" ref="S81">=IF(COUNTIF($R$6:$R$240,R81)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S81">=IF(COUNTIF($R$6:$R$241,R81)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T81" s="21" t="s">
@@ -23666,7 +23684,7 @@
         <v>场景|environment_module_3d|room_facility_base_wall|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S82" s="21" t="str">
-        <f t="array" ref="S82">=IF(COUNTIF($R$6:$R$240,R82)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S82">=IF(COUNTIF($R$6:$R$241,R82)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T82" s="21" t="s">
@@ -23745,7 +23763,7 @@
         <v>场景|environment_module_3d|room_floor_inset|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S83" s="21" t="str">
-        <f t="array" ref="S83">=IF(COUNTIF($R$6:$R$240,R83)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S83">=IF(COUNTIF($R$6:$R$241,R83)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T83" s="21" t="s">
@@ -23824,7 +23842,7 @@
         <v>场景|environment_module_3d|room_floor_partition_horizontal|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S84" s="21" t="str">
-        <f t="array" ref="S84">=IF(COUNTIF($R$6:$R$240,R84)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S84">=IF(COUNTIF($R$6:$R$241,R84)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T84" s="21" t="s">
@@ -23903,7 +23921,7 @@
         <v>场景|environment_module_3d|room_floor_partition_vertical|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S85" s="21" t="str">
-        <f t="array" ref="S85">=IF(COUNTIF($R$6:$R$240,R85)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S85">=IF(COUNTIF($R$6:$R$241,R85)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T85" s="21" t="s">
@@ -23982,7 +24000,7 @@
         <v>场景|environment_module_3d|room_floor_seam_strip|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S86" s="21" t="str">
-        <f t="array" ref="S86">=IF(COUNTIF($R$6:$R$240,R86)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S86">=IF(COUNTIF($R$6:$R$241,R86)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T86" s="21" t="s">
@@ -24061,7 +24079,7 @@
         <v>场景|environment_module_3d|room_floor|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S87" s="21" t="str">
-        <f t="array" ref="S87">=IF(COUNTIF($R$6:$R$240,R87)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S87">=IF(COUNTIF($R$6:$R$241,R87)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T87" s="21" t="s">
@@ -24140,7 +24158,7 @@
         <v>场景|environment_module_3d|room_rooftop_descent_marker|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S88" s="21" t="str">
-        <f t="array" ref="S88">=IF(COUNTIF($R$6:$R$240,R88)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S88">=IF(COUNTIF($R$6:$R$241,R88)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T88" s="21" t="s">
@@ -24219,7 +24237,7 @@
         <v>场景|environment_module_3d|room_rooftop_facade_band|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S89" s="21" t="str">
-        <f t="array" ref="S89">=IF(COUNTIF($R$6:$R$240,R89)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S89">=IF(COUNTIF($R$6:$R$241,R89)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T89" s="21" t="s">
@@ -24298,7 +24316,7 @@
         <v>场景|environment_module_3d|room_rooftop_facade|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S90" s="21" t="str">
-        <f t="array" ref="S90">=IF(COUNTIF($R$6:$R$240,R90)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S90">=IF(COUNTIF($R$6:$R$241,R90)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T90" s="21" t="s">
@@ -24377,7 +24395,7 @@
         <v>场景|environment_module_3d|room_rooftop_rail_post|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S91" s="21" t="str">
-        <f t="array" ref="S91">=IF(COUNTIF($R$6:$R$240,R91)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S91">=IF(COUNTIF($R$6:$R$241,R91)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T91" s="21" t="s">
@@ -24456,7 +24474,7 @@
         <v>场景|environment_module_3d|room_rooftop_railing_lower|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S92" s="21" t="str">
-        <f t="array" ref="S92">=IF(COUNTIF($R$6:$R$240,R92)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S92">=IF(COUNTIF($R$6:$R$241,R92)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T92" s="21" t="s">
@@ -24535,7 +24553,7 @@
         <v>场景|environment_module_3d|room_rooftop_railing_upper|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S93" s="21" t="str">
-        <f t="array" ref="S93">=IF(COUNTIF($R$6:$R$240,R93)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S93">=IF(COUNTIF($R$6:$R$241,R93)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T93" s="21" t="s">
@@ -24614,7 +24632,7 @@
         <v>场景|environment_module_3d|room_rooftop_stair_frame_lintel|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S94" s="21" t="str">
-        <f t="array" ref="S94">=IF(COUNTIF($R$6:$R$240,R94)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S94">=IF(COUNTIF($R$6:$R$241,R94)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T94" s="21" t="s">
@@ -24693,7 +24711,7 @@
         <v>场景|environment_module_3d|room_rooftop_stair_frame_post|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S95" s="21" t="str">
-        <f t="array" ref="S95">=IF(COUNTIF($R$6:$R$240,R95)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S95">=IF(COUNTIF($R$6:$R$241,R95)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T95" s="21" t="s">
@@ -24772,7 +24790,7 @@
         <v>场景|environment_module_3d|room_stair_lobby_route_guide|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S96" s="21" t="str">
-        <f t="array" ref="S96">=IF(COUNTIF($R$6:$R$240,R96)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S96">=IF(COUNTIF($R$6:$R$241,R96)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T96" s="21" t="s">
@@ -24851,7 +24869,7 @@
         <v>场景|environment_module_3d|room_stair_lobby_threshold_guide|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S97" s="21" t="str">
-        <f t="array" ref="S97">=IF(COUNTIF($R$6:$R$240,R97)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S97">=IF(COUNTIF($R$6:$R$241,R97)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T97" s="21" t="s">
@@ -24930,7 +24948,7 @@
         <v>场景|environment_module_3d|room_vertical_access_marker_label|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S98" s="21" t="str">
-        <f t="array" ref="S98">=IF(COUNTIF($R$6:$R$240,R98)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S98">=IF(COUNTIF($R$6:$R$241,R98)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T98" s="21" t="s">
@@ -25009,7 +25027,7 @@
         <v>场景|environment_module_3d|room_wall_door_segment|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S99" s="21" t="str">
-        <f t="array" ref="S99">=IF(COUNTIF($R$6:$R$240,R99)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S99">=IF(COUNTIF($R$6:$R$241,R99)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T99" s="21" t="s">
@@ -25088,7 +25106,7 @@
         <v>场景|environment_module_3d|room_wall_segment|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S100" s="21" t="str">
-        <f t="array" ref="S100">=IF(COUNTIF($R$6:$R$240,R100)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S100">=IF(COUNTIF($R$6:$R$241,R100)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T100" s="21" t="s">
@@ -25167,7 +25185,7 @@
         <v>场景|environment_module_3d|tower_wall_parapet_door_5m|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S101" s="21" t="str">
-        <f t="array" ref="S101">=IF(COUNTIF($R$6:$R$240,R101)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S101">=IF(COUNTIF($R$6:$R$241,R101)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T101" s="21" t="s">
@@ -25246,7 +25264,7 @@
         <v>场景道具|facility|base_facility_light_grid|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S102" s="21" t="str">
-        <f t="array" ref="S102">=IF(COUNTIF($R$6:$R$240,R102)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S102">=IF(COUNTIF($R$6:$R$241,R102)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T102" s="21" t="s">
@@ -25325,7 +25343,7 @@
         <v>场景|environment_module_3d|base99_wall_window_5x12|wall_window|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S103" s="21" t="str">
-        <f t="array" ref="S103">=IF(COUNTIF($R$6:$R$240,R103)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S103">=IF(COUNTIF($R$6:$R$241,R103)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T103" s="21" t="s">
@@ -25404,7 +25422,7 @@
         <v>场景|environment_module_3d|base99_mezzanine_20x10_z7|mezzanine|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S104" s="21" t="str">
-        <f t="array" ref="S104">=IF(COUNTIF($R$6:$R$240,R104)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S104">=IF(COUNTIF($R$6:$R$241,R104)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T104" s="21" t="s">
@@ -25483,7 +25501,7 @@
         <v>场景|environment_module_3d|base99_stair_l_z7|stair_l|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S105" s="21" t="str">
-        <f t="array" ref="S105">=IF(COUNTIF($R$6:$R$240,R105)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S105">=IF(COUNTIF($R$6:$R$241,R105)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T105" s="21" t="s">
@@ -25562,7 +25580,7 @@
         <v>场景|environment_module_3d|base99_stair_exterior_h2|stair_exterior|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S106" s="21" t="str">
-        <f t="array" ref="S106">=IF(COUNTIF($R$6:$R$240,R106)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S106">=IF(COUNTIF($R$6:$R$241,R106)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T106" s="21" t="s">
@@ -25641,7 +25659,7 @@
         <v>场景|facility_visual_3d|base99_door_lift_2p2x2p5|door_leaf|top3d / local -z 正面|default / visual_only</v>
       </c>
       <c r="S107" s="21" t="str">
-        <f t="array" ref="S107">=IF(COUNTIF($R$6:$R$240,R107)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S107">=IF(COUNTIF($R$6:$R$241,R107)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T107" s="21" t="s">
@@ -25720,7 +25738,7 @@
         <v>场景|environment_kit_3d|base100_upper_shell_30x30_h12|root_3d|top3d / local -z 正面|default / prefab</v>
       </c>
       <c r="S108" s="31" t="str">
-        <f t="array" ref="S108">=IF(COUNTIF($R$6:$R$240,R108)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S108">=IF(COUNTIF($R$6:$R$241,R108)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T108" s="31" t="s">
@@ -25799,7 +25817,7 @@
         <v>场景|environment_module|base99_mezzanine_20x10_z5|platform|俯视3d|default</v>
       </c>
       <c r="S109" s="21" t="str">
-        <f t="array" ref="S109">=IF(COUNTIF($R$6:$R$240,R109)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S109">=IF(COUNTIF($R$6:$R$241,R109)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T109" s="21" t="s">
@@ -25878,7 +25896,7 @@
         <v>场景|environment_module|base99_stair_l_z5|stair|俯视3d|default</v>
       </c>
       <c r="S110" s="21" t="str">
-        <f t="array" ref="S110">=IF(COUNTIF($R$6:$R$240,R110)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S110">=IF(COUNTIF($R$6:$R$241,R110)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T110" s="21" t="s">
@@ -25957,7 +25975,7 @@
         <v>场景|environment_module|base99_stair_exterior_h4|stair_exterior|俯视3d|default</v>
       </c>
       <c r="S111" s="21" t="str">
-        <f t="array" ref="S111">=IF(COUNTIF($R$6:$R$240,R111)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S111">=IF(COUNTIF($R$6:$R$241,R111)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T111" s="21" t="s">
@@ -26036,7 +26054,7 @@
         <v>场景|environment_module|base99_mezzanine_underdeck_blocker|underdeck_blocker|俯视3d / local -z 正面|default / permanent solid enclosure</v>
       </c>
       <c r="S112" s="21" t="str">
-        <f t="array" ref="S112">=IF(COUNTIF($R$6:$R$240,R112)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S112">=IF(COUNTIF($R$6:$R$241,R112)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T112" s="21" t="s">
@@ -26113,7 +26131,7 @@
         <v>场景道具|base_facility|avatar_wardrobe|root|俯视3d|default</v>
       </c>
       <c r="S113" s="21" t="str">
-        <f t="array" ref="S113">=IF(COUNTIF($R$6:$R$240,R113)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S113">=IF(COUNTIF($R$6:$R$241,R113)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T113" s="21" t="s">
@@ -26189,7 +26207,7 @@
         <v>场景|shared_palette|palette_facility_lowlight_dopamine|root|不适用|default</v>
       </c>
       <c r="S114" s="31" t="str">
-        <f t="array" ref="S114">=IF(COUNTIF($R$6:$R$240,R114)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S114">=IF(COUNTIF($R$6:$R$241,R114)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T114" s="31" t="s">
@@ -26265,7 +26283,7 @@
         <v>场景道具|基地设施|recovery_station|root|3d|default</v>
       </c>
       <c r="S115" s="31" t="str">
-        <f t="array" ref="S115">=IF(COUNTIF($R$6:$R$240,R115)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S115">=IF(COUNTIF($R$6:$R$241,R115)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T115" s="31" t="s">
@@ -26341,7 +26359,7 @@
         <v>场景道具|门|room_door|root|3d|closed/open/locked</v>
       </c>
       <c r="S116" s="31" t="str">
-        <f t="array" ref="S116">=IF(COUNTIF($R$6:$R$240,R116)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S116">=IF(COUNTIF($R$6:$R$241,R116)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T116" s="31" t="s">
@@ -26417,7 +26435,7 @@
         <v>场景|屋顶环境|rooftop_shelter_50m|root|3d|default</v>
       </c>
       <c r="S117" s="31" t="str">
-        <f t="array" ref="S117">=IF(COUNTIF($R$6:$R$240,R117)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S117">=IF(COUNTIF($R$6:$R$241,R117)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T117" s="31" t="s">
@@ -26496,7 +26514,7 @@
         <v>场景|屋顶环境|rooftop_shelter_90x80|root|3d|default</v>
       </c>
       <c r="S118" s="31" t="str">
-        <f t="array" ref="S118">=IF(COUNTIF($R$6:$R$240,R118)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S118">=IF(COUNTIF($R$6:$R$241,R118)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T118" s="31" t="s">
@@ -26575,7 +26593,7 @@
         <v>基地资产包|建筑结构包|base99_package_east_mezzanine_structure|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S119" s="21" t="str">
-        <f t="array" ref="S119">=IF(COUNTIF($R$6:$R$240,R119)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S119">=IF(COUNTIF($R$6:$R$241,R119)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T119" s="21" t="s">
@@ -26654,7 +26672,7 @@
         <v>基地资产包|建筑结构包|base99_package_east_upper_transition_stair|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S120" s="21" t="str">
-        <f t="array" ref="S120">=IF(COUNTIF($R$6:$R$240,R120)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S120">=IF(COUNTIF($R$6:$R$241,R120)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T120" s="21" t="s">
@@ -26733,7 +26751,7 @@
         <v>基地资产包|建筑结构包|base99_package_northwest_l_stair|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S121" s="21" t="str">
-        <f t="array" ref="S121">=IF(COUNTIF($R$6:$R$240,R121)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S121">=IF(COUNTIF($R$6:$R$241,R121)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T121" s="21" t="s">
@@ -26812,7 +26830,7 @@
         <v>基地资产包|建筑结构包|base99_package_retained_wall_system|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S122" s="21" t="str">
-        <f t="array" ref="S122">=IF(COUNTIF($R$6:$R$240,R122)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S122">=IF(COUNTIF($R$6:$R$241,R122)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T122" s="21" t="s">
@@ -26891,7 +26909,7 @@
         <v>基地资产包|建筑结构包|base99_package_underdeck_sheet_blocker|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S123" s="21" t="str">
-        <f t="array" ref="S123">=IF(COUNTIF($R$6:$R$240,R123)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S123">=IF(COUNTIF($R$6:$R$241,R123)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T123" s="21" t="s">
@@ -26970,7 +26988,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_flammable_bin|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S124" s="21" t="str">
-        <f t="array" ref="S124">=IF(COUNTIF($R$6:$R$240,R124)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S124">=IF(COUNTIF($R$6:$R$241,R124)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T124" s="21" t="s">
@@ -27049,7 +27067,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_industrial_pipeline_system|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S125" s="21" t="str">
-        <f t="array" ref="S125">=IF(COUNTIF($R$6:$R$240,R125)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S125">=IF(COUNTIF($R$6:$R$241,R125)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T125" s="21" t="s">
@@ -27128,7 +27146,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_low_storage_bench|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S126" s="21" t="str">
-        <f t="array" ref="S126">=IF(COUNTIF($R$6:$R$240,R126)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S126">=IF(COUNTIF($R$6:$R$241,R126)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T126" s="21" t="s">
@@ -27207,7 +27225,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_maintenance_workstation|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S127" s="21" t="str">
-        <f t="array" ref="S127">=IF(COUNTIF($R$6:$R$240,R127)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S127">=IF(COUNTIF($R$6:$R$241,R127)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T127" s="21" t="s">
@@ -27286,7 +27304,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_personnel_security_door|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S128" s="21" t="str">
-        <f t="array" ref="S128">=IF(COUNTIF($R$6:$R$240,R128)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S128">=IF(COUNTIF($R$6:$R$241,R128)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T128" s="21" t="s">
@@ -27365,7 +27383,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_plant_group|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S129" s="21" t="str">
-        <f t="array" ref="S129">=IF(COUNTIF($R$6:$R$240,R129)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S129">=IF(COUNTIF($R$6:$R$241,R129)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T129" s="21" t="s">
@@ -27444,7 +27462,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_power_distribution|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S130" s="21" t="str">
-        <f t="array" ref="S130">=IF(COUNTIF($R$6:$R$240,R130)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S130">=IF(COUNTIF($R$6:$R$241,R130)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T130" s="21" t="s">
@@ -27523,7 +27541,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_recycle_bin|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S131" s="21" t="str">
-        <f t="array" ref="S131">=IF(COUNTIF($R$6:$R$240,R131)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S131">=IF(COUNTIF($R$6:$R$241,R131)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T131" s="21" t="s">
@@ -27602,7 +27620,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_round_pendant_light|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S132" s="21" t="str">
-        <f t="array" ref="S132">=IF(COUNTIF($R$6:$R$240,R132)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S132">=IF(COUNTIF($R$6:$R$241,R132)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T132" s="21" t="s">
@@ -27681,7 +27699,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_small_safety_devices|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S133" s="21" t="str">
-        <f t="array" ref="S133">=IF(COUNTIF($R$6:$R$240,R133)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S133">=IF(COUNTIF($R$6:$R$241,R133)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T133" s="21" t="s">
@@ -27760,7 +27778,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_supply_24h_station|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S134" s="21" t="str">
-        <f t="array" ref="S134">=IF(COUNTIF($R$6:$R$240,R134)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S134">=IF(COUNTIF($R$6:$R$241,R134)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T134" s="21" t="s">
@@ -27839,7 +27857,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_waste_bin|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S135" s="21" t="str">
-        <f t="array" ref="S135">=IF(COUNTIF($R$6:$R$240,R135)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S135">=IF(COUNTIF($R$6:$R$241,R135)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T135" s="21" t="s">
@@ -27918,7 +27936,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_work_together_poster|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S136" s="21" t="str">
-        <f t="array" ref="S136">=IF(COUNTIF($R$6:$R$240,R136)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S136">=IF(COUNTIF($R$6:$R$241,R136)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T136" s="21" t="s">
@@ -27997,7 +28015,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r01_c01|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S137" s="21" t="str">
-        <f t="array" ref="S137">=IF(COUNTIF($R$6:$R$240,R137)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S137">=IF(COUNTIF($R$6:$R$241,R137)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T137" s="21" t="s">
@@ -28076,7 +28094,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r01_c02|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S138" s="21" t="str">
-        <f t="array" ref="S138">=IF(COUNTIF($R$6:$R$240,R138)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S138">=IF(COUNTIF($R$6:$R$241,R138)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T138" s="21" t="s">
@@ -28155,7 +28173,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r01_c03|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S139" s="21" t="str">
-        <f t="array" ref="S139">=IF(COUNTIF($R$6:$R$240,R139)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S139">=IF(COUNTIF($R$6:$R$241,R139)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T139" s="21" t="s">
@@ -28234,7 +28252,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r01_c04|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S140" s="21" t="str">
-        <f t="array" ref="S140">=IF(COUNTIF($R$6:$R$240,R140)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S140">=IF(COUNTIF($R$6:$R$241,R140)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T140" s="21" t="s">
@@ -28313,7 +28331,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r01_c05|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S141" s="21" t="str">
-        <f t="array" ref="S141">=IF(COUNTIF($R$6:$R$240,R141)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S141">=IF(COUNTIF($R$6:$R$241,R141)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T141" s="21" t="s">
@@ -28392,7 +28410,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r01_c06|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S142" s="21" t="str">
-        <f t="array" ref="S142">=IF(COUNTIF($R$6:$R$240,R142)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S142">=IF(COUNTIF($R$6:$R$241,R142)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T142" s="21" t="s">
@@ -28471,7 +28489,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r02_c01|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S143" s="21" t="str">
-        <f t="array" ref="S143">=IF(COUNTIF($R$6:$R$240,R143)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S143">=IF(COUNTIF($R$6:$R$241,R143)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T143" s="21" t="s">
@@ -28550,7 +28568,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r02_c02|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S144" s="21" t="str">
-        <f t="array" ref="S144">=IF(COUNTIF($R$6:$R$240,R144)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S144">=IF(COUNTIF($R$6:$R$241,R144)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T144" s="21" t="s">
@@ -28629,7 +28647,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r02_c03|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S145" s="21" t="str">
-        <f t="array" ref="S145">=IF(COUNTIF($R$6:$R$240,R145)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S145">=IF(COUNTIF($R$6:$R$241,R145)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T145" s="21" t="s">
@@ -28708,7 +28726,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r02_c04|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S146" s="21" t="str">
-        <f t="array" ref="S146">=IF(COUNTIF($R$6:$R$240,R146)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S146">=IF(COUNTIF($R$6:$R$241,R146)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T146" s="21" t="s">
@@ -28787,7 +28805,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r02_c05|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S147" s="21" t="str">
-        <f t="array" ref="S147">=IF(COUNTIF($R$6:$R$240,R147)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S147">=IF(COUNTIF($R$6:$R$241,R147)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T147" s="21" t="s">
@@ -28866,7 +28884,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r02_c06|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S148" s="21" t="str">
-        <f t="array" ref="S148">=IF(COUNTIF($R$6:$R$240,R148)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S148">=IF(COUNTIF($R$6:$R$241,R148)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T148" s="21" t="s">
@@ -28945,7 +28963,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r03_c01|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S149" s="21" t="str">
-        <f t="array" ref="S149">=IF(COUNTIF($R$6:$R$240,R149)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S149">=IF(COUNTIF($R$6:$R$241,R149)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T149" s="21" t="s">
@@ -29024,7 +29042,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r03_c02|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S150" s="21" t="str">
-        <f t="array" ref="S150">=IF(COUNTIF($R$6:$R$240,R150)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S150">=IF(COUNTIF($R$6:$R$241,R150)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T150" s="21" t="s">
@@ -29103,7 +29121,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r03_c03|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S151" s="21" t="str">
-        <f t="array" ref="S151">=IF(COUNTIF($R$6:$R$240,R151)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S151">=IF(COUNTIF($R$6:$R$241,R151)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T151" s="21" t="s">
@@ -29182,7 +29200,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r03_c04|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S152" s="21" t="str">
-        <f t="array" ref="S152">=IF(COUNTIF($R$6:$R$240,R152)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S152">=IF(COUNTIF($R$6:$R$241,R152)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T152" s="21" t="s">
@@ -29261,7 +29279,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r03_c05|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S153" s="21" t="str">
-        <f t="array" ref="S153">=IF(COUNTIF($R$6:$R$240,R153)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S153">=IF(COUNTIF($R$6:$R$241,R153)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T153" s="21" t="s">
@@ -29340,7 +29358,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r03_c06|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S154" s="21" t="str">
-        <f t="array" ref="S154">=IF(COUNTIF($R$6:$R$240,R154)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S154">=IF(COUNTIF($R$6:$R$241,R154)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T154" s="21" t="s">
@@ -29419,7 +29437,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r04_c01|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S155" s="21" t="str">
-        <f t="array" ref="S155">=IF(COUNTIF($R$6:$R$240,R155)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S155">=IF(COUNTIF($R$6:$R$241,R155)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T155" s="21" t="s">
@@ -29498,7 +29516,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r04_c02|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S156" s="21" t="str">
-        <f t="array" ref="S156">=IF(COUNTIF($R$6:$R$240,R156)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S156">=IF(COUNTIF($R$6:$R$241,R156)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T156" s="21" t="s">
@@ -29577,7 +29595,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r04_c03|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S157" s="21" t="str">
-        <f t="array" ref="S157">=IF(COUNTIF($R$6:$R$240,R157)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S157">=IF(COUNTIF($R$6:$R$241,R157)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T157" s="21" t="s">
@@ -29656,7 +29674,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r04_c04|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S158" s="21" t="str">
-        <f t="array" ref="S158">=IF(COUNTIF($R$6:$R$240,R158)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S158">=IF(COUNTIF($R$6:$R$241,R158)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T158" s="21" t="s">
@@ -29735,7 +29753,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r04_c05|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S159" s="21" t="str">
-        <f t="array" ref="S159">=IF(COUNTIF($R$6:$R$240,R159)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S159">=IF(COUNTIF($R$6:$R$241,R159)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T159" s="21" t="s">
@@ -29814,7 +29832,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r04_c06|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S160" s="21" t="str">
-        <f t="array" ref="S160">=IF(COUNTIF($R$6:$R$240,R160)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S160">=IF(COUNTIF($R$6:$R$241,R160)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T160" s="21" t="s">
@@ -29893,7 +29911,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r05_c01|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S161" s="21" t="str">
-        <f t="array" ref="S161">=IF(COUNTIF($R$6:$R$240,R161)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S161">=IF(COUNTIF($R$6:$R$241,R161)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T161" s="21" t="s">
@@ -29972,7 +29990,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r05_c02|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S162" s="21" t="str">
-        <f t="array" ref="S162">=IF(COUNTIF($R$6:$R$240,R162)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S162">=IF(COUNTIF($R$6:$R$241,R162)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T162" s="21" t="s">
@@ -30051,7 +30069,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r05_c03|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S163" s="21" t="str">
-        <f t="array" ref="S163">=IF(COUNTIF($R$6:$R$240,R163)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S163">=IF(COUNTIF($R$6:$R$241,R163)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T163" s="21" t="s">
@@ -30130,7 +30148,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r05_c04|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S164" s="21" t="str">
-        <f t="array" ref="S164">=IF(COUNTIF($R$6:$R$240,R164)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S164">=IF(COUNTIF($R$6:$R$241,R164)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T164" s="21" t="s">
@@ -30209,7 +30227,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r05_c05|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S165" s="21" t="str">
-        <f t="array" ref="S165">=IF(COUNTIF($R$6:$R$240,R165)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S165">=IF(COUNTIF($R$6:$R$241,R165)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T165" s="21" t="s">
@@ -30288,7 +30306,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r05_c06|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S166" s="21" t="str">
-        <f t="array" ref="S166">=IF(COUNTIF($R$6:$R$240,R166)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S166">=IF(COUNTIF($R$6:$R$241,R166)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T166" s="21" t="s">
@@ -30367,7 +30385,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r06_c01|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S167" s="21" t="str">
-        <f t="array" ref="S167">=IF(COUNTIF($R$6:$R$240,R167)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S167">=IF(COUNTIF($R$6:$R$241,R167)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T167" s="21" t="s">
@@ -30446,7 +30464,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r06_c02|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S168" s="21" t="str">
-        <f t="array" ref="S168">=IF(COUNTIF($R$6:$R$240,R168)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S168">=IF(COUNTIF($R$6:$R$241,R168)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T168" s="21" t="s">
@@ -30525,7 +30543,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r06_c03|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S169" s="21" t="str">
-        <f t="array" ref="S169">=IF(COUNTIF($R$6:$R$240,R169)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S169">=IF(COUNTIF($R$6:$R$241,R169)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T169" s="21" t="s">
@@ -30604,7 +30622,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r06_c04|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S170" s="21" t="str">
-        <f t="array" ref="S170">=IF(COUNTIF($R$6:$R$240,R170)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S170">=IF(COUNTIF($R$6:$R$241,R170)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T170" s="21" t="s">
@@ -30683,7 +30701,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r06_c05|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S171" s="21" t="str">
-        <f t="array" ref="S171">=IF(COUNTIF($R$6:$R$240,R171)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S171">=IF(COUNTIF($R$6:$R$241,R171)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T171" s="21" t="s">
@@ -30762,7 +30780,7 @@
         <v>基地资产包|地面系统包|base99_package_tile_r06_c06|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S172" s="21" t="str">
-        <f t="array" ref="S172">=IF(COUNTIF($R$6:$R$240,R172)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S172">=IF(COUNTIF($R$6:$R$241,R172)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T172" s="21" t="s">
@@ -30841,7 +30859,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_backwall_function_panel_system|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S173" s="21" t="str">
-        <f t="array" ref="S173">=IF(COUNTIF($R$6:$R$240,R173)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S173">=IF(COUNTIF($R$6:$R$241,R173)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T173" s="21" t="s">
@@ -30920,7 +30938,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_backwall_services|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S174" s="21" t="str">
-        <f t="array" ref="S174">=IF(COUNTIF($R$6:$R$240,R174)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S174">=IF(COUNTIF($R$6:$R$241,R174)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T174" s="21" t="s">
@@ -30999,7 +31017,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_battery_cabinet|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S175" s="21" t="str">
-        <f t="array" ref="S175">=IF(COUNTIF($R$6:$R$240,R175)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S175">=IF(COUNTIF($R$6:$R$241,R175)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T175" s="21" t="s">
@@ -31078,7 +31096,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_bed_and_bedding|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S176" s="21" t="str">
-        <f t="array" ref="S176">=IF(COUNTIF($R$6:$R$240,R176)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S176">=IF(COUNTIF($R$6:$R$241,R176)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T176" s="21" t="s">
@@ -31157,7 +31175,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_bedside_lamp|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S177" s="21" t="str">
-        <f t="array" ref="S177">=IF(COUNTIF($R$6:$R$240,R177)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S177">=IF(COUNTIF($R$6:$R$241,R177)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T177" s="21" t="s">
@@ -31236,7 +31254,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_bedside_rug|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S178" s="21" t="str">
-        <f t="array" ref="S178">=IF(COUNTIF($R$6:$R$240,R178)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S178">=IF(COUNTIF($R$6:$R$241,R178)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T178" s="21" t="s">
@@ -31315,7 +31333,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_coffee_table|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S179" s="21" t="str">
-        <f t="array" ref="S179">=IF(COUNTIF($R$6:$R$240,R179)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S179">=IF(COUNTIF($R$6:$R$241,R179)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T179" s="21" t="s">
@@ -31394,7 +31412,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_computer_workstation|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S180" s="21" t="str">
-        <f t="array" ref="S180">=IF(COUNTIF($R$6:$R$240,R180)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S180">=IF(COUNTIF($R$6:$R$241,R180)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T180" s="21" t="s">
@@ -31473,7 +31491,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_explore_poster|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S181" s="21" t="str">
-        <f t="array" ref="S181">=IF(COUNTIF($R$6:$R$240,R181)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S181">=IF(COUNTIF($R$6:$R$241,R181)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T181" s="21" t="s">
@@ -31552,7 +31570,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_food_cabinet|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S182" s="21" t="str">
-        <f t="array" ref="S182">=IF(COUNTIF($R$6:$R$240,R182)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S182">=IF(COUNTIF($R$6:$R$241,R182)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T182" s="21" t="s">
@@ -31631,7 +31649,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_good_vibes_neon|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S183" s="21" t="str">
-        <f t="array" ref="S183">=IF(COUNTIF($R$6:$R$240,R183)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S183">=IF(COUNTIF($R$6:$R$241,R183)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T183" s="21" t="s">
@@ -31710,7 +31728,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_hanging_plant|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S184" s="21" t="str">
-        <f t="array" ref="S184">=IF(COUNTIF($R$6:$R$240,R184)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S184">=IF(COUNTIF($R$6:$R$241,R184)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T184" s="21" t="s">
@@ -31789,7 +31807,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_lounge_rug|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S185" s="21" t="str">
-        <f t="array" ref="S185">=IF(COUNTIF($R$6:$R$240,R185)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S185">=IF(COUNTIF($R$6:$R$241,R185)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T185" s="21" t="s">
@@ -31868,7 +31886,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_lounge_sofa|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S186" s="21" t="str">
-        <f t="array" ref="S186">=IF(COUNTIF($R$6:$R$240,R186)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S186">=IF(COUNTIF($R$6:$R$241,R186)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T186" s="21" t="s">
@@ -31947,7 +31965,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_medical_cabinet|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S187" s="21" t="str">
-        <f t="array" ref="S187">=IF(COUNTIF($R$6:$R$240,R187)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S187">=IF(COUNTIF($R$6:$R$241,R187)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T187" s="21" t="s">
@@ -32026,7 +32044,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_nightstand|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S188" s="21" t="str">
-        <f t="array" ref="S188">=IF(COUNTIF($R$6:$R$240,R188)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S188">=IF(COUNTIF($R$6:$R$241,R188)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T188" s="21" t="s">
@@ -32105,7 +32123,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_office_chair|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S189" s="21" t="str">
-        <f t="array" ref="S189">=IF(COUNTIF($R$6:$R$240,R189)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S189">=IF(COUNTIF($R$6:$R$241,R189)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T189" s="21" t="s">
@@ -32184,7 +32202,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_pouf_01|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S190" s="21" t="str">
-        <f t="array" ref="S190">=IF(COUNTIF($R$6:$R$240,R190)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S190">=IF(COUNTIF($R$6:$R$241,R190)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T190" s="21" t="s">
@@ -32263,7 +32281,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_pouf_02|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S191" s="21" t="str">
-        <f t="array" ref="S191">=IF(COUNTIF($R$6:$R$240,R191)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S191">=IF(COUNTIF($R$6:$R$241,R191)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T191" s="21" t="s">
@@ -32342,7 +32360,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_side_table|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S192" s="21" t="str">
-        <f t="array" ref="S192">=IF(COUNTIF($R$6:$R$240,R192)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S192">=IF(COUNTIF($R$6:$R$241,R192)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T192" s="21" t="s">
@@ -32421,7 +32439,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_stay_curious_neon|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S193" s="21" t="str">
-        <f t="array" ref="S193">=IF(COUNTIF($R$6:$R$240,R193)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S193">=IF(COUNTIF($R$6:$R$241,R193)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T193" s="21" t="s">
@@ -32500,7 +32518,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_striped_privacy_curtain|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S194" s="21" t="str">
-        <f t="array" ref="S194">=IF(COUNTIF($R$6:$R$240,R194)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S194">=IF(COUNTIF($R$6:$R$241,R194)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T194" s="21" t="s">
@@ -32579,7 +32597,7 @@
         <v>基地资产包|二楼/阁楼设施包|base99_package_loft_tool_pegboard|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S195" s="21" t="str">
-        <f t="array" ref="S195">=IF(COUNTIF($R$6:$R$240,R195)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S195">=IF(COUNTIF($R$6:$R$241,R195)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T195" s="21" t="s">
@@ -32658,7 +32676,7 @@
         <v>基地资产包|环境支持包|base99_package_corridor_emergency_light_group|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S196" s="21" t="str">
-        <f t="array" ref="S196">=IF(COUNTIF($R$6:$R$240,R196)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S196">=IF(COUNTIF($R$6:$R$241,R196)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T196" s="21" t="s">
@@ -32737,7 +32755,7 @@
         <v>基地资产包|环境支持包|base99_package_loft_lighting_support|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S197" s="21" t="str">
-        <f t="array" ref="S197">=IF(COUNTIF($R$6:$R$240,R197)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S197">=IF(COUNTIF($R$6:$R$241,R197)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T197" s="21" t="s">
@@ -32816,7 +32834,7 @@
         <v>基地资产包|环境支持包|base99_package_volumetric_dust_fx|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S198" s="21" t="str">
-        <f t="array" ref="S198">=IF(COUNTIF($R$6:$R$240,R198)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S198">=IF(COUNTIF($R$6:$R$241,R198)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T198" s="21" t="s">
@@ -32895,7 +32913,7 @@
         <v>基地资产包|环境支持包|base99_package_warehouse_pendant_light_group|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S199" s="21" t="str">
-        <f t="array" ref="S199">=IF(COUNTIF($R$6:$R$240,R199)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S199">=IF(COUNTIF($R$6:$R$241,R199)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T199" s="21" t="s">
@@ -32974,7 +32992,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_access_terminal|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S200" s="21" t="str">
-        <f t="array" ref="S200">=IF(COUNTIF($R$6:$R$240,R200)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S200">=IF(COUNTIF($R$6:$R$241,R200)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T200" s="21" t="s">
@@ -33053,7 +33071,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_base_camp_neon_sign|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S201" s="21" t="str">
-        <f t="array" ref="S201">=IF(COUNTIF($R$6:$R$240,R201)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S201">=IF(COUNTIF($R$6:$R$241,R201)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T201" s="21" t="s">
@@ -33132,7 +33150,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_base_camp_rollup_main_door|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S202" s="21" t="str">
-        <f t="array" ref="S202">=IF(COUNTIF($R$6:$R$240,R202)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S202">=IF(COUNTIF($R$6:$R$241,R202)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T202" s="21" t="s">
@@ -33211,7 +33229,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_base_status_terminal|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S203" s="21" t="str">
-        <f t="array" ref="S203">=IF(COUNTIF($R$6:$R$240,R203)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S203">=IF(COUNTIF($R$6:$R$241,R203)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T203" s="21" t="s">
@@ -33290,7 +33308,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_hologram_terminal_platform|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S204" s="21" t="str">
-        <f t="array" ref="S204">=IF(COUNTIF($R$6:$R$240,R204)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S204">=IF(COUNTIF($R$6:$R$241,R204)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T204" s="21" t="s">
@@ -33369,7 +33387,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_main_door_low_storage_cabinet|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S205" s="21" t="str">
-        <f t="array" ref="S205">=IF(COUNTIF($R$6:$R$240,R205)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S205">=IF(COUNTIF($R$6:$R$241,R205)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T205" s="21" t="s">
@@ -33448,7 +33466,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_medical_cabinet|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S206" s="21" t="str">
-        <f t="array" ref="S206">=IF(COUNTIF($R$6:$R$240,R206)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S206">=IF(COUNTIF($R$6:$R$241,R206)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T206" s="21" t="s">
@@ -33527,7 +33545,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_narrow_battery_cabinet|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S207" s="21" t="str">
-        <f t="array" ref="S207">=IF(COUNTIF($R$6:$R$240,R207)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S207">=IF(COUNTIF($R$6:$R$241,R207)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T207" s="21" t="s">
@@ -33606,7 +33624,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_narrow_emergency_cabinet|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S208" s="21" t="str">
-        <f t="array" ref="S208">=IF(COUNTIF($R$6:$R$240,R208)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S208">=IF(COUNTIF($R$6:$R$241,R208)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T208" s="21" t="s">
@@ -33685,7 +33703,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_south_industrial_wall_details|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S209" s="21" t="str">
-        <f t="array" ref="S209">=IF(COUNTIF($R$6:$R$240,R209)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S209">=IF(COUNTIF($R$6:$R$241,R209)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T209" s="21" t="s">
@@ -33764,7 +33782,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_south_upper_railing_details|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S210" s="21" t="str">
-        <f t="array" ref="S210">=IF(COUNTIF($R$6:$R$240,R210)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S210">=IF(COUNTIF($R$6:$R$241,R210)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T210" s="21" t="s">
@@ -33843,7 +33861,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_south_wall_pipeline_system|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S211" s="21" t="str">
-        <f t="array" ref="S211">=IF(COUNTIF($R$6:$R$240,R211)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S211">=IF(COUNTIF($R$6:$R$241,R211)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T211" s="21" t="s">
@@ -33922,7 +33940,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_storage_terminal|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S212" s="21" t="str">
-        <f t="array" ref="S212">=IF(COUNTIF($R$6:$R$240,R212)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S212">=IF(COUNTIF($R$6:$R$241,R212)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T212" s="21" t="s">
@@ -34001,7 +34019,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_tools_cabinet|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S213" s="21" t="str">
-        <f t="array" ref="S213">=IF(COUNTIF($R$6:$R$240,R213)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S213">=IF(COUNTIF($R$6:$R$241,R213)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T213" s="21" t="s">
@@ -34080,7 +34098,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_understair_bulletin_board|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S214" s="21" t="str">
-        <f t="array" ref="S214">=IF(COUNTIF($R$6:$R$240,R214)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S214">=IF(COUNTIF($R$6:$R$241,R214)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T214" s="21" t="s">
@@ -34159,7 +34177,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_understair_equipment_cabinet|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S215" s="21" t="str">
-        <f t="array" ref="S215">=IF(COUNTIF($R$6:$R$240,R215)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S215">=IF(COUNTIF($R$6:$R$241,R215)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T215" s="21" t="s">
@@ -34238,7 +34256,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_understair_green_bench|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S216" s="21" t="str">
-        <f t="array" ref="S216">=IF(COUNTIF($R$6:$R$240,R216)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S216">=IF(COUNTIF($R$6:$R$241,R216)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T216" s="21" t="s">
@@ -34317,7 +34335,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_understair_lighting_living_support|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S217" s="21" t="str">
-        <f t="array" ref="S217">=IF(COUNTIF($R$6:$R$240,R217)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S217">=IF(COUNTIF($R$6:$R$241,R217)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T217" s="21" t="s">
@@ -34396,7 +34414,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_understair_storage_shelf|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S218" s="21" t="str">
-        <f t="array" ref="S218">=IF(COUNTIF($R$6:$R$240,R218)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S218">=IF(COUNTIF($R$6:$R$241,R218)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T218" s="21" t="s">
@@ -34475,7 +34493,7 @@
         <v>基地资产包|阁楼下方固定设施包|base99_package_weapon_workshop_station|package_root|top3d / blender +y北|static / fixture_light</v>
       </c>
       <c r="S219" s="21" t="str">
-        <f t="array" ref="S219">=IF(COUNTIF($R$6:$R$240,R219)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S219">=IF(COUNTIF($R$6:$R$241,R219)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T219" s="21" t="s">
@@ -34554,7 +34572,7 @@
         <v>基地资产包|仓库设施包|base99_package_air_compressor|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S220" s="21" t="str">
-        <f t="array" ref="S220">=IF(COUNTIF($R$6:$R$240,R220)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S220">=IF(COUNTIF($R$6:$R$241,R220)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T220" s="21" t="s">
@@ -34633,7 +34651,7 @@
         <v>基地资产包|仓库设施包|base99_package_backup_generator|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S221" s="21" t="str">
-        <f t="array" ref="S221">=IF(COUNTIF($R$6:$R$240,R221)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S221">=IF(COUNTIF($R$6:$R$241,R221)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T221" s="21" t="s">
@@ -34712,7 +34730,7 @@
         <v>基地资产包|仓库设施包|base99_package_battery_bank|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S222" s="21" t="str">
-        <f t="array" ref="S222">=IF(COUNTIF($R$6:$R$240,R222)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S222">=IF(COUNTIF($R$6:$R$241,R222)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T222" s="21" t="s">
@@ -34791,7 +34809,7 @@
         <v>基地资产包|仓库设施包|base99_package_heavy_supply_shelf|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S223" s="21" t="str">
-        <f t="array" ref="S223">=IF(COUNTIF($R$6:$R$240,R223)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S223">=IF(COUNTIF($R$6:$R$241,R223)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T223" s="21" t="s">
@@ -34870,7 +34888,7 @@
         <v>基地资产包|仓库设施包|base99_package_hose_reel|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S224" s="21" t="str">
-        <f t="array" ref="S224">=IF(COUNTIF($R$6:$R$240,R224)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S224">=IF(COUNTIF($R$6:$R$241,R224)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T224" s="21" t="s">
@@ -34949,7 +34967,7 @@
         <v>基地资产包|仓库设施包|base99_package_industrial_water_tank|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S225" s="21" t="str">
-        <f t="array" ref="S225">=IF(COUNTIF($R$6:$R$240,R225)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S225">=IF(COUNTIF($R$6:$R$241,R225)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T225" s="21" t="s">
@@ -35028,7 +35046,7 @@
         <v>基地资产包|仓库设施包|base99_package_south_wall_information_boards|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S226" s="21" t="str">
-        <f t="array" ref="S226">=IF(COUNTIF($R$6:$R$240,R226)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S226">=IF(COUNTIF($R$6:$R$241,R226)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T226" s="21" t="s">
@@ -35107,7 +35125,7 @@
         <v>基地资产包|仓库设施包|base99_package_water_purifier|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S227" s="21" t="str">
-        <f t="array" ref="S227">=IF(COUNTIF($R$6:$R$240,R227)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S227">=IF(COUNTIF($R$6:$R$241,R227)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T227" s="21" t="s">
@@ -35186,7 +35204,7 @@
         <v>基地资产包|东侧固定设施包|base99_package_east_door_access_control|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S228" s="21" t="str">
-        <f t="array" ref="S228">=IF(COUNTIF($R$6:$R$240,R228)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S228">=IF(COUNTIF($R$6:$R$241,R228)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T228" s="21" t="s">
@@ -35265,7 +35283,7 @@
         <v>基地资产包|建筑结构包|base99_package_east_door_wall_module|package_root|top3d / blender +y北|static / wall_owned_frame</v>
       </c>
       <c r="S229" s="21" t="str">
-        <f t="array" ref="S229">=IF(COUNTIF($R$6:$R$240,R229)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S229">=IF(COUNTIF($R$6:$R$241,R229)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T229" s="21" t="s">
@@ -35344,7 +35362,7 @@
         <v>基地资产包|建筑结构包|base99_package_west_door_wall_module|package_root|top3d / blender +y北|static / wall_owned_frame</v>
       </c>
       <c r="S230" s="21" t="str">
-        <f t="array" ref="S230">=IF(COUNTIF($R$6:$R$240,R230)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S230">=IF(COUNTIF($R$6:$R$241,R230)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T230" s="21" t="s">
@@ -35423,7 +35441,7 @@
         <v>基地资产包|西侧固定设施实例|base99_placement_west_door_lift_instance|package_root|top3d / blender +y北|static / fixture_light / shared_runtime_asset</v>
       </c>
       <c r="S231" s="21" t="str">
-        <f t="array" ref="S231">=IF(COUNTIF($R$6:$R$240,R231)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S231">=IF(COUNTIF($R$6:$R$241,R231)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T231" s="21" t="s">
@@ -35502,7 +35520,7 @@
         <v>基地资产包|地面系统包|base99_package_loft_floor_finish|package_root|top3d / blender +y北|static / default</v>
       </c>
       <c r="S232" s="21" t="str">
-        <f t="array" ref="S232">=IF(COUNTIF($R$6:$R$240,R232)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S232">=IF(COUNTIF($R$6:$R$241,R232)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T232" s="21" t="s">
@@ -35581,7 +35599,7 @@
         <v>场景|environment_module_3d|base99_wall_contents_v021|wall_content_visual_bundle|top3d / blender烘焙布局|default / visual_only</v>
       </c>
       <c r="S233" s="31" t="str">
-        <f t="array" ref="S233">=IF(COUNTIF($R$6:$R$240,R233)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S233">=IF(COUNTIF($R$6:$R$241,R233)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T233" s="31" t="s">
@@ -35660,7 +35678,7 @@
         <v>场景|environment_facility_bundle|base99_remaining_facilities_v021|facility_bundle|top3d / blender烘焙布局|default / static + visual_only</v>
       </c>
       <c r="S234" s="31" t="str">
-        <f t="array" ref="S234">=IF(COUNTIF($R$6:$R$240,R234)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S234">=IF(COUNTIF($R$6:$R$241,R234)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T234" s="31" t="s">
@@ -35736,7 +35754,7 @@
         <v>场景|environment_module_3d|tower_stair_floor_lower|floor_lower|top3d / blender z-up|whitebox / default</v>
       </c>
       <c r="S235" s="31" t="str">
-        <f t="array" ref="S235">=IF(COUNTIF($R$6:$R$240,R235)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S235">=IF(COUNTIF($R$6:$R$241,R235)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="U235" s="31" t="s">
@@ -35809,7 +35827,7 @@
         <v>场景|environment_module_3d|tower_stair_floor_mid|floor_mid|top3d / blender z-up|whitebox / default</v>
       </c>
       <c r="S236" s="31" t="str">
-        <f t="array" ref="S236">=IF(COUNTIF($R$6:$R$240,R236)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S236">=IF(COUNTIF($R$6:$R$241,R236)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="U236" s="31" t="s">
@@ -35882,7 +35900,7 @@
         <v>场景|environment_module_3d|tower_stair_floor_upper|floor_upper|top3d / blender z-up|whitebox / default</v>
       </c>
       <c r="S237" s="31" t="str">
-        <f t="array" ref="S237">=IF(COUNTIF($R$6:$R$240,R237)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S237">=IF(COUNTIF($R$6:$R$241,R237)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="U237" s="31" t="s">
@@ -35955,7 +35973,7 @@
         <v>场景|environment_module_3d|tower_stair_flight_adjustable|stair_flight|top3d / blender z-up|whitebox / default</v>
       </c>
       <c r="S238" s="31" t="str">
-        <f t="array" ref="S238">=IF(COUNTIF($R$6:$R$240,R238)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S238">=IF(COUNTIF($R$6:$R$241,R238)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="U238" s="31" t="s">
@@ -36028,7 +36046,7 @@
         <v>场景|environment_module_3d|tower_corner_column_05m|corner_column|top3d / blender z-up|whitebox / default</v>
       </c>
       <c r="S239" s="31" t="str">
-        <f t="array" ref="S239">=IF(COUNTIF($R$6:$R$240,R239)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S239">=IF(COUNTIF($R$6:$R$241,R239)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="U239" s="31" t="s">
@@ -36104,7 +36122,7 @@
         <v>场景|environment_kit_3d|rooftop_reference|component_library|blender z-up / -y|reference_components</v>
       </c>
       <c r="S240" s="21" t="str">
-        <f t="array" ref="S240">=IF(COUNTIF($R$6:$R$240,R240)&gt;1,"重复","唯一")</f>
+        <f t="array" ref="S240">=IF(COUNTIF($R$6:$R$241,R240)&gt;1,"重复","唯一")</f>
         <v>唯一</v>
       </c>
       <c r="T240" s="21" t="s">
@@ -36126,38 +36144,161 @@
         <v>2439</v>
       </c>
     </row>
+    <row r="241" spans="1:25">
+      <c r="A241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENV-TOWER-DOOR-LEAF-5M</t>
+        </is>
+      </c>
+      <c r="B241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">塔楼5米门扇模块</t>
+        </is>
+      </c>
+      <c r="C241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">场景</t>
+        </is>
+      </c>
+      <c r="D241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">room_kit</t>
+        </is>
+      </c>
+      <c r="E241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tower_descent</t>
+        </is>
+      </c>
+      <c r="F241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">door_leaf_5m</t>
+        </is>
+      </c>
+      <c r="G241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENV-TOWER-DESCENT-KIT-3D</t>
+        </is>
+      </c>
+      <c r="H241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">俯视3D</t>
+        </is>
+      </c>
+      <c r="I241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godot_runtime</t>
+        </is>
+      </c>
+      <c r="J241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">普通战斗房/BOSS房/入口安全房的房间门门板（99F 基地滑升门与 start→facility 除外）</t>
+        </is>
+      </c>
+      <c r="K241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原型已接入</t>
+        </is>
+      </c>
+      <c r="L241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="M241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v001</t>
+        </is>
+      </c>
+      <c r="N241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GLB / 可视包络 2.2×2.492×0.18m（底边悬原点上方 0.008m）/ 门扇厚 0.18m / 单 Mesh 四材质角色 / 随门垂直升降 0.32m</t>
+        </is>
+      </c>
+      <c r="O241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/art/environments/tower_descent_3d/components/env_tower_door_leaf_5m_top3d.glb</t>
+        </is>
+      </c>
+      <c r="P241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/art/environments/tower_descent_3d/source/door_leaf_5m/export_env_tower_door_leaf_5m_v001.py; assets/art/props/dungeon_3d/prp_tower_door_leaf_5m.tscn; src/world3d/DungeonRoom3D.gd; src/world3d/RoomDoor3D.gd</t>
+        </is>
+      </c>
+      <c r="Q241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">门扇/门板/door_leaf/door_panel/tower_descent/door_5m</t>
+        </is>
+      </c>
+      <c r="R241" s="21" t="str">
+        <f>=LOWER(TRIM(C241)&amp;"|"&amp;TRIM(D241)&amp;"|"&amp;TRIM(E241)&amp;"|"&amp;TRIM(F241)&amp;"|"&amp;TRIM(H241)&amp;"|"&amp;TRIM(I241))</f>
+        <v>场景|room_kit|tower_descent|door_leaf_5m|俯视3d|godot_runtime</v>
+      </c>
+      <c r="S241" s="21" t="str">
+        <f t="array" ref="S241">=IF(COUNTIF($R$6:$R$241,R241)&gt;1,"重复","唯一")</f>
+        <v>唯一</v>
+      </c>
+      <c r="T241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">067fa07693c766bf8025ee2b47c451b76f3b4f2a04765a7319def325e2702bcc</t>
+        </is>
+      </c>
+      <c r="U241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codex</t>
+        </is>
+      </c>
+      <c r="V241" s="21">
+        <v>46284</v>
+      </c>
+      <c r="W241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blender 派生（自 door_5m_通用包）</t>
+        </is>
+      </c>
+      <c r="X241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="Y241" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-19：新建。自 B 套战局通用组件 source/art/whitebox/tower_zones/battle/components/common_components/v007 门扇件（包 door_5m_通用包 / 根件 ROOT_door_5m_通用组件）派生：Blender 内绕 Z 烘焙 180° 偏航后 transform_apply，使装饰面落在 Godot +Z（与 A 套 prp_tower_* forward_axis="+Z" 对齐）；先三角化再删朝下面；join 成单 Mesh，四材质角色 01/02/03/04 全保留。底边悬原点上方 8mm 是美术原始几何（关闭的门不该擦地），非几何压平。运行时替换掉战斗房原程序化深色 BoxMesh 门板；碰撞责任归 RoomDoor3D（门扇自声明 visual_only，无内嵌碰撞），升降开合由 DoorPanel.position.y 驱动。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:X240"/>
+  <autoFilter ref="A5:X241"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
   </mergeCells>
-  <conditionalFormatting sqref="S6:S240">
+  <conditionalFormatting sqref="S6:S241">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="重复">
       <formula>NOT(ISERROR(SEARCH("重复",S6)))</formula>
       <formula>"重复"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K240">
+  <conditionalFormatting sqref="K6:K241">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="已完成">
       <formula>NOT(ISERROR(SEARCH("已完成",K6)))</formula>
       <formula>"已完成"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K240">
+  <conditionalFormatting sqref="K6:K241">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="待制作">
       <formula>NOT(ISERROR(SEARCH("待制作",K6)))</formula>
       <formula>"待制作"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="C6:C240">
+    <dataValidation type="list" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="C6:C241">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
     </dataValidation>
-    <dataValidation type="list" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="K6:K240">
+    <dataValidation type="list" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="K6:K241">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation type="list" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="L6:L240">
+    <dataValidation type="list" operator="between" allowBlank="1" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="L6:L241">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -38294,8 +38435,10 @@
       <c r="D48" s="45" t="s">
         <v>2591</v>
       </c>
-      <c r="E48" s="45" t="s">
-        <v>2592</v>
+      <c r="E48" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assets/art/environments/tower_descent_3d/source/wall_height12/env_tower_wall_solid_5m_source_v004.blend（派生自 assets/art/environments/tower_zones/battle/source/common_components/v007/env_battle_common_components_source_v007.blend）</t>
+        </is>
       </c>
       <c r="F48" s="45" t="s">
         <v>2470</v>
@@ -38312,8 +38455,10 @@
       <c r="J48" s="45" t="s">
         <v>2594</v>
       </c>
-      <c r="K48" s="45" t="s">
-        <v>2595</v>
+      <c r="K48" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GLB / 可视包络 5×11.9×0.4675m（结构阻挡 0.30m）/ 12m逻辑碰撞 / 共享Mesh</t>
+        </is>
       </c>
       <c r="L48" s="45" t="s">
         <v>2579</v>
@@ -38324,11 +38469,16 @@
       <c r="N48" s="45" t="s">
         <v>742</v>
       </c>
-      <c r="O48" s="45" t="s">
-        <v>480</v>
-      </c>
-      <c r="P48" s="46" t="s">
-        <v>2596</v>
+      <c r="O48" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v004</t>
+        </is>
+      </c>
+      <c r="P48" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17：占位 BoxMesh 替换为正式美术（与 100F/98F 同源同版）。根节点=PrpTowerWallSolid5m(Node3D)，下挂 ImportedModel；Prefab 视觉专用（visual_only），结构碰撞由 DungeonRoom3D.TowerWallCollision_*_Run 与 TowerFloorStage3D.OuterBoundaryCollision_* 按 0.30m 代理生成。资产声明 preserve_authored_palette=true——塔楼 MultiMesh 不再套 WALL_SOLID_MATERIAL_A/B 单色主题，保留美术自带 PaletteUV（共享色盘角色 01_精工金属_紫色骨架 / 02_细腻哑光_青绿大面 / 04_柔和自发光_UI灯光）。原点契约 bottom_center（几何 Y=0..11.9），运行时按 -mesh.get_aabb().position.y 反算贴合楼面。
+2026-09-19：升 v004。GLB 原地覆盖稳定路径（文件名去版本号，节点名统一 ENV_TOWER_WALL_SOLID_5M，根变换为单位矩阵）。结构包络与可视包络分离：bounds_size_m 仍 5×11.9×0.30（结构阻挡），visual_bounds_size_m=5×11.9×0.4675（正面装甲凸到 +Z 0.3175，背面 -0.15）。跨套朝向：Blender 侧 +Y 为厚度轴，B 套（battle/common_components，含 v007）装饰面在 -Y，导出前烘焙 180° 使装饰面落 Godot +Z，与 A 套 prp_tower_* 的 forward_axis="+Z" 对齐。该 GLB 除本 Prefab 外还被 TowerDescent3D 直接 preload（_get_corridor_wall_module_mesh / _build_stair_approach_corridor），故根节点变换必须为单位矩阵。</t>
+        </is>
       </c>
     </row>
     <row r="49" spans="1:16">

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -30627,7 +30627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P140"/>
+  <dimension ref="A1:P143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="50" min="1" max="1"/>
@@ -38263,52 +38263,64 @@
           <t>女儿墙直段</t>
         </is>
       </c>
-      <c r="C102" s="69" t="inlineStr"/>
-      <c r="D102" s="69" t="inlineStr"/>
+      <c r="C102" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_parapet_5m.tscn</t>
+        </is>
+      </c>
+      <c r="D102" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_parapet_top3d.glb</t>
+        </is>
+      </c>
       <c r="E102" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包；导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_parapet_v001.py</t>
         </is>
       </c>
       <c r="F102" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；02_女儿墙</t>
-        </is>
-      </c>
-      <c r="G102" s="69" t="inlineStr"/>
+          <t>Godot原生场景结构Prefab；100F天台四周边界直段，由 TowerFloorStage3D 按 MultiMesh 摆 64 槽位</t>
+        </is>
+      </c>
+      <c r="G102" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H102" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>开</t>
         </is>
       </c>
       <c r="I102" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>TowerFloorStage3D</t>
         </is>
       </c>
       <c r="J102" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>BoxShape3D 5×1.80×0.50，由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）</t>
         </is>
       </c>
       <c r="K102" s="69" t="inlineStr">
         <is>
-          <t>5.000×0.500×1.800 m</t>
+          <t>GLB / 5×0.50×1.80m / 共享Mesh</t>
         </is>
       </c>
       <c r="L102" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0..1.80）；朝 +Z</t>
         </is>
       </c>
       <c r="M102" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / parapet</t>
+          <t>100F天台四周边界/64段MultiMesh</t>
         </is>
       </c>
       <c r="N102" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O102" s="69" t="inlineStr">
@@ -38318,7 +38330,10 @@
       </c>
       <c r="P102" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/02/parapet/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/02/parapet/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-19：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID。用户要求「把天台那两组围栏组件导入 Godot、做成 prefab、坐标对齐、让天台生成围栏的代码指向它们」。导出：assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_parapet_v001.py（headless Blender，把网格 rebase 到包内 根_ 空物体后丢弃变换，得到 XY 居中 / 底面 Z=0 的原点契约，再 export_scene.gltf 导 GLB）。实测 GLB 72,632 B / sha256 30d77d64…，AABB=(-2.5,-0.25,0)~(2.5,0.25,1.8)（Blender Z-up，即 5×0.50×1.80）。.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，Godot 探针实测 palette_texture_bound=true（材质角色 02_细腻哑光_青绿大面）。
+接线：TowerFloorStage3D.PARAPET_SCENE 由 prp_tower_wall_parapet_5m.tscn（塔楼 A 套 5×0.30×1.50m）改指本 prefab；ROOFTOP_PARAPET_HEIGHT 0.75 → 1.80、新增 ROOFTOP_PARAPET_THICKNESS=0.50 与按层取值的 _outer_wall_thickness()/_outer_wall_inset()（普通层仍 0.30m），并删掉历史上「1.50m 几何 × 0.5 纵向缩放凑 0.75m」的补偿——现在视觉包络 = 碰撞高度 = 1.80m（远征层被误缩半高的问题一并消掉）。每边 90−5=85m / 80−5=75m 正好整格，故直段 2×(17+15)=64 段、四角让位给 2.5m 转角件。注意旧 prefab prp_tower_wall_parapet_5m.tscn 仍被 DungeonRoom3D 引用且在 6 件 PREFAB_CONTRACT清单内，故本行是并行新身份、旧行(ENV-TOWER-WALL-PARAPET-5M)不动。
+实测（probe_rooftop_parapet_alignment，须带窗口跑：MultiMesh 实例变换存在 RenderingServer 侧，dummy 渲染器一律回读成单位阵）：直段 61 + 门洞补位墙 3 + 转角件 4 = 68 件；四条边 coverage=全长 / gap=0.000 / overlap=0.000；四个转角件各 2.500×2.500 精确落座。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract，outer_segment_count=64 / outer_corner_count=4 / outer_wall_thickness=0.5 / outer_wall_height=1.8）；ROOFTOP_RAILING_OK / TOWER_LEVEL_BLOCKS_OK / TOWER_GRID_COMPONENT_ALIGNMENT_OK / EXPEDITION_LEVEL01_FLOW_OK / TEST_LEVEL_99_FLOW_OK 全绿。</t>
         </is>
       </c>
     </row>
@@ -38403,52 +38418,64 @@
           <t>女儿墙外角</t>
         </is>
       </c>
-      <c r="C104" s="69" t="inlineStr"/>
-      <c r="D104" s="69" t="inlineStr"/>
+      <c r="C104" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_parapet_outer_2p5m.tscn</t>
+        </is>
+      </c>
+      <c r="D104" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_parapet_outer_top3d.glb</t>
+        </is>
+      </c>
       <c r="E104" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙外角_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙外角_资产包；导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_parapet_v001.py</t>
         </is>
       </c>
       <c r="F104" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；02_女儿墙</t>
-        </is>
-      </c>
-      <c r="G104" s="69" t="inlineStr"/>
+          <t>Godot原生场景结构Prefab；100F天台四角的阳角转角件，由 TowerFloorStage3D 单独实例化 4 件</t>
+        </is>
+      </c>
+      <c r="G104" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H104" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>开</t>
         </is>
       </c>
       <c r="I104" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>TowerFloorStage3D</t>
         </is>
       </c>
       <c r="J104" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>四角 2.5×2.5 槽位由四边连续的 BoundaryCollision 代理覆盖（Prefab 不再自带碰撞）</t>
         </is>
       </c>
       <c r="K104" s="69" t="inlineStr">
         <is>
-          <t>2.500×2.500×1.800 m</t>
+          <t>GLB / 2.5×2.5×1.80m 包络（两臂中心线在局部 x=-1.0 与 z=+1.0，臂厚 0.50m）/ 共享Mesh</t>
         </is>
       </c>
       <c r="L104" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0..1.80）；朝 +Z；外角两臂在局部 −X 与 +Z</t>
         </is>
       </c>
       <c r="M104" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / parapet_outer</t>
+          <t>100F天台四角（SW/SE/NE/NW）</t>
         </is>
       </c>
       <c r="N104" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O104" s="69" t="inlineStr">
@@ -38458,7 +38485,11 @@
       </c>
       <c r="P104" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/02/parapet_outer/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/02/parapet_outer/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-19：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID（asset_version 仍 v002，与参考组件库同版）。实测 GLB 70,140 B / sha256 2bc924b4…，AABB=(-1.25,-1.25,0)~(1.25,1.25,1.8)（Blender Z-up，即 2.5×2.5×1.80）；顶点按象限统计 -X-Z:540 / -X+Z:888 / +X-Z:0 / +X+Z:540，即两臂落在 −X 与 +Z 边、开口朝 +X/−Z，臂中心线 x=−1.0 / z=+1.0。.import 同样绑共享色盘后处理，palette_texture_bound=true。
+只用「外角」一件：100F 天台轮廓是 90×80m 矩形、四个角全是阳角，无内凹，所以ENV-ROOFTOP-REF-PARAPET-INNER 不在本次范围内（保持未导入）。
+放位：转角件包络 2.5×2.5，摆在该角 2.5m 让位区的中心，按角旋转 90° 整数倍——SW=(−48.75, 0, 43.75) rot 0 / SE=(38.75, 0, 43.75) rot π/2 / NE=(38.75, 0, −33.75) rot π / NW=(−48.75, 0, −33.75) rot 3π/2（俯视逆时针）。这套放位让两条臂的中心线正好落在相邻两边的 boundary 上，包络端点与相邻直段无缝相接。这替掉了原来「两根直段在角上交叉」的旧画法。碰撞仍是四边连续体，本 prefab 只产生视觉节点（visual_only / collision_owner=TowerFloorStage3D.OuterBoundaryCollision）。
+实测：probe_rooftop_parapet_alignment 四个转角件 span 尺寸均 2.500×2.500 且 position 与四个2.5m 让位区角点相等；corner_arm_centerlines / corner_open_facing 等朝向口径已写入 prefab 的metadata，供后续换件时核对。门禁 ROOFTOP_WEST_EXPANSION_CONTRACT_PASS 断言 outer_corner_count=4 与四件的位置/朝向（按 wrapf(actual-expected,-π,π) 比角）。</t>
         </is>
       </c>
     </row>
@@ -40982,7 +41013,258 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="100" customHeight="1" s="50"/>
+    <row r="141" ht="100" customHeight="1" s="50">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ENV-ROOFTOP-REF-PARAPET-DMG-A</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>女儿墙直段·破损A（崩顶）</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_parapet_dmg_a_5m.tscn</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_parapet_dmg_a_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包（程序化破损派生）；派生脚本 assets/art/environments/tower_zones/rooftop/source/author_env_rooftop_parapet_damage_v001.py</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Godot原生场景结构Prefab；100F天台四周边界直段的破损变体，由 TowerFloorStage3D 按种子随机替换部分直段槽位的可视件（外观破损、阻挡不变）</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>TowerFloorStage3D</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>BoxShape3D 5×1.80×0.50（与 intact 件同包络），由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）；破损只改外观，不改阻挡高度与缺口宽度</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>GLB / 5×0.50×1.80m / 共享Mesh</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>bottom_center（几何 Y=0..1.80）；朝 +Z</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>100F天台四周边界 / 随机破损档 A（约 1/12 概率）</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>破损口径：crown_spall / 崩顶：压顶顶部被削 3 道豁口、中段崩落，断裂面粗化；下半身与两端头带完整。
+实测 GLB 79644 B。
+父项=ENV-ROOFTOP-REF-PARAPET（同包络的派生件，不新增父库）。2026-09-19 新建。用户原话「墙壁帮我再blender里头制作3个变种，带有破损模型破损的，不同三种破损，但是需要能接起来，然后导入变成新的预制体后重新随机排列外墙」。派生做法：author_env_rooftop_parapet_damage_v001.py（headless Blender）把 intact 网格按「积木」拆成 22 块闭合倒角块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），只对与破损区相交的积木做**逐块**布尔剔料再合并。⚠️ 整件一次性布尔会静默吃掉 10 块墙身积木（512→272 顶点、4.52→1.25 m³、31.53 m² 面消失），且换个不接触的刀口也照样发生 —— 必须逐块做，这是本件最大的坑。拼接契约（用户要求的「能接起来」）：两端头带 |x|&gt;=2.05m 与 intact 件逐位相同（GLB 字节层已证：source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true）、包络 5.00×0.50×1.80、原点底面中心均与 intact 件逐值相同 ⇒ 可沿任一边、任意顺序与原件 / 彼此对接，接头无缝、槽位相位不变。色盘：破损新面 UV 已钳回色盘色块（U 0.923..0.977 / V 0.123..0.477），材质仍是02_细腻哑光_青绿大面；.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，探针实测 palette_texture_bound=true。实测：Godot 探针 probe_rooftop_parapet_damage_prefabs 四件（intact + A/B/C）包络逐值相同、端头带点云最近邻最大距离 7.07e-5 m（0.07mm；源文件逐位相同，这点偏差来自 Godot 导入对近重合重复顶点的焊接，不是几何被改）。接线：TowerFloorStage3D.PARAPET_DAMAGE_SCENES + 静态纯函数 split_outer_parapet_damage()，按种子随机分档；种子 ROOFTOP_PARAPET_DAMAGE_SEED=20260919，每段受损概率 0.25（三档均分），可用 set_outer_damage_seed() 在 _ready 前覆盖。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract 新增 _verify_rooftop_parapet_damage：槽位数 61 = 64−门洞补位 3、四批次件数之和 == 槽位数、计划 == 摆放、破损比例 ∈[0.15,0.35]、换种子必换排布、非天台层整批完好）；反向对照已做（破损概率改 0 / 改 1 / 排布忽略种子三种改坏各自变红，脚本 _scratch/task14/reverse_control_parapet_damage.py）。另：本族不像直段那样登记《资产主表》（与 102/104 行口径一致）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ENV-ROOFTOP-REF-PARAPET-DMG-B</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>女儿墙直段·破损B（贯穿）</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_parapet_dmg_b_5m.tscn</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_parapet_dmg_b_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包（程序化破损派生）；派生脚本 assets/art/environments/tower_zones/rooftop/source/author_env_rooftop_parapet_damage_v001.py</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Godot原生场景结构Prefab；100F天台四周边界直段的破损变体，由 TowerFloorStage3D 按种子随机替换部分直段槽位的可视件（外观破损、阻挡不变）</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>TowerFloorStage3D</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>BoxShape3D 5×1.80×0.50（与 intact 件同包络），由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）；破损只改外观，不改阻挡高度与缺口宽度</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>GLB / 5×0.50×1.80m / 共享Mesh</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>bottom_center（几何 Y=0..1.80）；朝 +Z</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>100F天台四周边界 / 随机破损档 A（约 1/12 概率）</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>破损口径：through_breach / 贯穿：墙身中段被打穿 2 个带放射裂纹的贯穿洞，可透视到墙外；洞缘粗化。
+实测 GLB 116652 B。
+父项=ENV-ROOFTOP-REF-PARAPET（同包络的派生件，不新增父库）。2026-09-19 新建。用户原话「墙壁帮我再blender里头制作3个变种，带有破损模型破损的，不同三种破损，但是需要能接起来，然后导入变成新的预制体后重新随机排列外墙」。派生做法：author_env_rooftop_parapet_damage_v001.py（headless Blender）把 intact 网格按「积木」拆成 22 块闭合倒角块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），只对与破损区相交的积木做**逐块**布尔剔料再合并。⚠️ 整件一次性布尔会静默吃掉 10 块墙身积木（512→272 顶点、4.52→1.25 m³、31.53 m² 面消失），且换个不接触的刀口也照样发生 —— 必须逐块做，这是本件最大的坑。拼接契约（用户要求的「能接起来」）：两端头带 |x|&gt;=2.05m 与 intact 件逐位相同（GLB 字节层已证：source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true）、包络 5.00×0.50×1.80、原点底面中心均与 intact 件逐值相同 ⇒ 可沿任一边、任意顺序与原件 / 彼此对接，接头无缝、槽位相位不变。色盘：破损新面 UV 已钳回色盘色块（U 0.923..0.977 / V 0.123..0.477），材质仍是02_细腻哑光_青绿大面；.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，探针实测 palette_texture_bound=true。实测：Godot 探针 probe_rooftop_parapet_damage_prefabs 四件（intact + A/B/C）包络逐值相同、端头带点云最近邻最大距离 7.07e-5 m（0.07mm；源文件逐位相同，这点偏差来自 Godot 导入对近重合重复顶点的焊接，不是几何被改）。接线：TowerFloorStage3D.PARAPET_DAMAGE_SCENES + 静态纯函数 split_outer_parapet_damage()，按种子随机分档；种子 ROOFTOP_PARAPET_DAMAGE_SEED=20260919，每段受损概率 0.25（三档均分），可用 set_outer_damage_seed() 在 _ready 前覆盖。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract 新增 _verify_rooftop_parapet_damage：槽位数 61 = 64−门洞补位 3、四批次件数之和 == 槽位数、计划 == 摆放、破损比例 ∈[0.15,0.35]、换种子必换排布、非天台层整批完好）；反向对照已做（破损概率改 0 / 改 1 / 排布忽略种子三种改坏各自变红，脚本 _scratch/task14/reverse_control_parapet_damage.py）。另：本族不像直段那样登记《资产主表》（与 102/104 行口径一致）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ENV-ROOFTOP-REF-PARAPET-DMG-C</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>女儿墙直段·破损C（塌脚）</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_parapet_dmg_c_5m.tscn</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_parapet_dmg_c_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包（程序化破损派生）；派生脚本 assets/art/environments/tower_zones/rooftop/source/author_env_rooftop_parapet_damage_v001.py</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Godot原生场景结构Prefab；100F天台四周边界直段的破损变体，由 TowerFloorStage3D 按种子随机替换部分直段槽位的可视件（外观破损、阻挡不变）</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>TowerFloorStage3D</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>BoxShape3D 5×1.80×0.50（与 intact 件同包络），由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）；破损只改外观，不改阻挡高度与缺口宽度</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>GLB / 5×0.50×1.80m / 共享Mesh</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>bottom_center（几何 Y=0..1.80）；朝 +Z</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>100F天台四周边界 / 随机破损档 A（约 1/12 概率）</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>破损口径：base_collapse / 塌脚：墙身中段整体塌到约 0.5m 残根、基座阳角被啃缺口，是最重的一档。
+实测 GLB 86228 B。
+父项=ENV-ROOFTOP-REF-PARAPET（同包络的派生件，不新增父库）。2026-09-19 新建。用户原话「墙壁帮我再blender里头制作3个变种，带有破损模型破损的，不同三种破损，但是需要能接起来，然后导入变成新的预制体后重新随机排列外墙」。派生做法：author_env_rooftop_parapet_damage_v001.py（headless Blender）把 intact 网格按「积木」拆成 22 块闭合倒角块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），只对与破损区相交的积木做**逐块**布尔剔料再合并。⚠️ 整件一次性布尔会静默吃掉 10 块墙身积木（512→272 顶点、4.52→1.25 m³、31.53 m² 面消失），且换个不接触的刀口也照样发生 —— 必须逐块做，这是本件最大的坑。拼接契约（用户要求的「能接起来」）：两端头带 |x|&gt;=2.05m 与 intact 件逐位相同（GLB 字节层已证：source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true）、包络 5.00×0.50×1.80、原点底面中心均与 intact 件逐值相同 ⇒ 可沿任一边、任意顺序与原件 / 彼此对接，接头无缝、槽位相位不变。色盘：破损新面 UV 已钳回色盘色块（U 0.923..0.977 / V 0.123..0.477），材质仍是02_细腻哑光_青绿大面；.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，探针实测 palette_texture_bound=true。实测：Godot 探针 probe_rooftop_parapet_damage_prefabs 四件（intact + A/B/C）包络逐值相同、端头带点云最近邻最大距离 7.07e-5 m（0.07mm；源文件逐位相同，这点偏差来自 Godot 导入对近重合重复顶点的焊接，不是几何被改）。接线：TowerFloorStage3D.PARAPET_DAMAGE_SCENES + 静态纯函数 split_outer_parapet_damage()，按种子随机分档；种子 ROOFTOP_PARAPET_DAMAGE_SEED=20260919，每段受损概率 0.25（三档均分），可用 set_outer_damage_seed() 在 _ready 前覆盖。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract 新增 _verify_rooftop_parapet_damage：槽位数 61 = 64−门洞补位 3、四批次件数之和 == 槽位数、计划 == 摆放、破损比例 ∈[0.15,0.35]、换种子必换排布、非天台层整批完好）；反向对照已做（破损概率改 0 / 改 1 / 排布忽略种子三种改坏各自变红，脚本 _scratch/task14/reverse_control_parapet_damage.py）。另：本族不像直段那样登记《资产主表》（与 102/104 行口径一致）。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
@@ -43119,7 +43401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="50" min="1" max="1"/>
@@ -43220,6 +43502,43 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>v0.1.1</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>资产升版</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>关卡场景</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>天台女儿墙两件（ENV-ROOFTOP-REF-PARAPET 女儿墙直段 / ENV-ROOFTOP-REF-PARAPET-OUTER 女儿墙外角）由「仅 Blender 源、未导入 Godot」升为运行时正式资产：从 reference_components/v002 导出 GLB，建立 prefab assets/art/props/dungeon_3d/prp_rooftop_parapet_5m.tscn 与 prp_rooftop_parapet_outer_2p5m.tscn，并把 TowerFloorStage3D 的天台周边生成从塔楼 A 套prp_tower_wall_parapet_5m.tscn（5×0.30×1.50m）改指这两件（5×0.50×1.80m）。女儿墙高度0.75m → 1.80m，视觉包络与碰撞高度统一，删掉历史 0.5 纵向缩放补偿。资产主表未增删行，总览跨度不变；只升 3D-场景通用 既有两行。</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>AssetID 与版本号不变（v002 = 参考组件库版本），仅补 prefab/GLB 路径、碰撞归属与实测记录。旧 prefab prp_tower_wall_parapet_5m.tscn 与行 ENV-TOWER-WALL-PARAPET-5M 保留不动——它仍被 DungeonRoom3D 引用且在 6 件 PREFAB_CONTRACT 清单内，不是孤儿。</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -37913,8 +37913,16 @@
           <t>完整地砖</t>
         </is>
       </c>
-      <c r="C97" s="69" t="inlineStr"/>
-      <c r="D97" s="69" t="inlineStr"/>
+      <c r="C97" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_floor_5m.tscn</t>
+        </is>
+      </c>
+      <c r="D97" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_floor_full_top3d.glb</t>
+        </is>
+      </c>
       <c r="E97" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#完整地砖_资产包</t>
@@ -37928,17 +37936,17 @@
       <c r="G97" s="69" t="inlineStr"/>
       <c r="H97" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>开</t>
         </is>
       </c>
       <c r="I97" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>TowerFloorStage3D</t>
         </is>
       </c>
       <c r="J97" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>BoxShape3D，由 TowerFloorStage3D 的 FloorSupport 按楼层轮廓铺满（Prefab 不再自带碰撞）</t>
         </is>
       </c>
       <c r="K97" s="69" t="inlineStr">
@@ -37948,17 +37956,17 @@
       </c>
       <c r="L97" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0..0.30，顶面对齐 Y=0）；+Z 为行方向</t>
         </is>
       </c>
       <c r="M97" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / floor_full</t>
+          <t>100F天台地面 / 234块5m地砖满铺（替代 POLISHED_FLOOR）</t>
         </is>
       </c>
       <c r="N97" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O97" s="69" t="inlineStr">
@@ -37968,7 +37976,8 @@
       </c>
       <c r="P97" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/01/floor_full/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/01/floor_full/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-19：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID。用户要求「天台的地板，帮我导出做一个新的 prefab，替代掉现在的地板，方法是新作一个 prefab，然后天台的生成代码从指向原来的改成这个」。导出 GLB assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_floor_full_top3d.glb（导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_ref_floor_facade_v001.py），建立 prefab assets/art/props/dungeon_3d/prp_rooftop_floor_5m.tscn；TowerFloorStage3D.ROOFTOP_FLOOR_SCENE 接管天台地面，替代原 POLISHED_FLOOR_SCENE。⚠️ 原点契约与旧地板不同：新件 bottom_center（几何 Y=0..0.30），旧件为几何中心；_build_floor 改用 _floor_visual_origin_y(mesh) = -AABB.end.y 把顶面对齐到 Y=0，不再用 -FLOOR_THICKNESS*0.5。实测 234 块 5m 地砖。Godot 契约断言 tests/verification/verify_rooftop_floor_facade_components.tscn 与 verify_rooftop_32x32_contract.tscn 通过。</t>
         </is>
       </c>
     </row>
@@ -38275,7 +38284,8 @@
       </c>
       <c r="E102" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包；导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_parapet_v001.py</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包；导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_parapet_v001.py
+2026-09-20：改由 source/author_env_rooftop_parapet_v003.py 在 source/parapet_v003_work.blend 上重建 0.80m 方案A 平整墙板，再由 source/export_env_rooftop_parapet_v001.py 导出 GLB（source/reference_components/v002 保持只读，不改动）。</t>
         </is>
       </c>
       <c r="F102" s="69" t="inlineStr">
@@ -38300,17 +38310,17 @@
       </c>
       <c r="J102" s="69" t="inlineStr">
         <is>
-          <t>BoxShape3D 5×1.80×0.50，由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）</t>
+          <t>BoxShape3D 5×0.80×0.50，由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）</t>
         </is>
       </c>
       <c r="K102" s="69" t="inlineStr">
         <is>
-          <t>GLB / 5×0.50×1.80m / 共享Mesh</t>
+          <t>GLB / 5×0.50×0.80m / 共享Mesh</t>
         </is>
       </c>
       <c r="L102" s="69" t="inlineStr">
         <is>
-          <t>bottom_center（几何 Y=0..1.80）；朝 +Z</t>
+          <t>bottom_center（几何 Y=0..0.80）；朝 +Z</t>
         </is>
       </c>
       <c r="M102" s="69" t="inlineStr">
@@ -38325,7 +38335,7 @@
       </c>
       <c r="O102" s="69" t="inlineStr">
         <is>
-          <t>v002</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="P102" s="69" t="inlineStr">
@@ -38333,7 +38343,8 @@
           <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/02/parapet/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
 2026-09-19：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID。用户要求「把天台那两组围栏组件导入 Godot、做成 prefab、坐标对齐、让天台生成围栏的代码指向它们」。导出：assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_parapet_v001.py（headless Blender，把网格 rebase 到包内 根_ 空物体后丢弃变换，得到 XY 居中 / 底面 Z=0 的原点契约，再 export_scene.gltf 导 GLB）。实测 GLB 72,632 B / sha256 30d77d64…，AABB=(-2.5,-0.25,0)~(2.5,0.25,1.8)（Blender Z-up，即 5×0.50×1.80）。.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，Godot 探针实测 palette_texture_bound=true（材质角色 02_细腻哑光_青绿大面）。
 接线：TowerFloorStage3D.PARAPET_SCENE 由 prp_tower_wall_parapet_5m.tscn（塔楼 A 套 5×0.30×1.50m）改指本 prefab；ROOFTOP_PARAPET_HEIGHT 0.75 → 1.80、新增 ROOFTOP_PARAPET_THICKNESS=0.50 与按层取值的 _outer_wall_thickness()/_outer_wall_inset()（普通层仍 0.30m），并删掉历史上「1.50m 几何 × 0.5 纵向缩放凑 0.75m」的补偿——现在视觉包络 = 碰撞高度 = 1.80m（远征层被误缩半高的问题一并消掉）。每边 90−5=85m / 80−5=75m 正好整格，故直段 2×(17+15)=64 段、四角让位给 2.5m 转角件。注意旧 prefab prp_tower_wall_parapet_5m.tscn 仍被 DungeonRoom3D 引用且在 6 件 PREFAB_CONTRACT清单内，故本行是并行新身份、旧行(ENV-TOWER-WALL-PARAPET-5M)不动。
-实测（probe_rooftop_parapet_alignment，须带窗口跑：MultiMesh 实例变换存在 RenderingServer 侧，dummy 渲染器一律回读成单位阵）：直段 61 + 门洞补位墙 3 + 转角件 4 = 68 件；四条边 coverage=全长 / gap=0.000 / overlap=0.000；四个转角件各 2.500×2.500 精确落座。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract，outer_segment_count=64 / outer_corner_count=4 / outer_wall_thickness=0.5 / outer_wall_height=1.8）；ROOFTOP_RAILING_OK / TOWER_LEVEL_BLOCKS_OK / TOWER_GRID_COMPONENT_ALIGNMENT_OK / EXPEDITION_LEVEL01_FLOW_OK / TEST_LEVEL_99_FLOW_OK 全绿。</t>
+实测（probe_rooftop_parapet_alignment，须带窗口跑：MultiMesh 实例变换存在 RenderingServer 侧，dummy 渲染器一律回读成单位阵）：直段 61 + 门洞补位墙 3 + 转角件 4 = 68 件；四条边 coverage=全长 / gap=0.000 / overlap=0.000；四个转角件各 2.500×2.500 精确落座。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract，outer_segment_count=64 / outer_corner_count=4 / outer_wall_thickness=0.5 / outer_wall_height=1.8）；ROOFTOP_RAILING_OK / TOWER_LEVEL_BLOCKS_OK / TOWER_GRID_COMPONENT_ALIGNMENT_OK / EXPEDITION_LEVEL01_FLOW_OK / TEST_LEVEL_99_FLOW_OK 全绿。
+2026-09-20：用户「改成 0.8 米的，变体也要一起改，然后中间的竖杠太密了 不好看，横杆在两边即可」。原 v002 配方是 22 块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），运行时表现为密集竖杠；本次重建为方案A 平整墙板，块数 22→3：基座带 5.0×0.50×0.10（z0..0.10）+ 墙板 5.0×0.43×0.64（z0.08..0.72）+ 压顶带 5.0×0.50×0.10（z0.70..0.80），合计**含压顶总高 0.80m**（用户选定口径）。厚度仍 0.50m ⇒ 边界内缩 _outer_wall_inset() 不变，四边/西侧碰撞位置与槽位相位不动。asset_version v002→v003；GLB 同路径覆盖重导（11,752 B）。TowerFloorStage3D.ROOFTOP_PARAPET_HEIGHT 1.80→0.80；_outer_wall_height()、OuterBoundaryCollision_* 高度、楼梯口矮墙缩放（ROOFTOP_PARAPET_HEIGHT / ROOFTOP_PARAPET_DOOR_BASE_HEIGHT = 0.80/1.50）自动跟随。⚠️ Player3D 无跳跃、无台阶攀爬，0.80m 与 1.80m 碰撞对玩法等价（都只是「走不出去」），差异仅在视觉高度、越过墙顶的相机视线与 0.80m 以上的弹道。实测 probe_rooftop_parapet_components：AABB=(5.0,0.80,0.50)、底面 Y=0、色盘已绑；门禁 ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（外墙上限高度改断言为常量口径，不再硬编码 1.8）。</t>
         </is>
       </c>
     </row>
@@ -38430,7 +38441,8 @@
       </c>
       <c r="E104" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙外角_资产包；导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_parapet_v001.py</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙外角_资产包；导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_parapet_v001.py
+2026-09-20：改由 source/author_env_rooftop_parapet_v003.py 在 source/parapet_v003_work.blend 上重建 0.80m 方案A 平整墙板，再由 source/export_env_rooftop_parapet_v001.py 导出 GLB（source/reference_components/v002 保持只读，不改动）。</t>
         </is>
       </c>
       <c r="F104" s="69" t="inlineStr">
@@ -38460,12 +38472,12 @@
       </c>
       <c r="K104" s="69" t="inlineStr">
         <is>
-          <t>GLB / 2.5×2.5×1.80m 包络（两臂中心线在局部 x=-1.0 与 z=+1.0，臂厚 0.50m）/ 共享Mesh</t>
+          <t>GLB / 2.5×2.5×0.80m 包络（两臂中心线在局部 x=-1.0 与 z=+1.0，臂厚 0.50m）/ 共享Mesh</t>
         </is>
       </c>
       <c r="L104" s="69" t="inlineStr">
         <is>
-          <t>bottom_center（几何 Y=0..1.80）；朝 +Z；外角两臂在局部 −X 与 +Z</t>
+          <t>bottom_center（几何 Y=0..0.80）；朝 +Z；外角两臂在局部 −X 与 +Z</t>
         </is>
       </c>
       <c r="M104" s="69" t="inlineStr">
@@ -38480,7 +38492,7 @@
       </c>
       <c r="O104" s="69" t="inlineStr">
         <is>
-          <t>v002</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="P104" s="69" t="inlineStr">
@@ -38489,7 +38501,8 @@
 2026-09-19：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID（asset_version 仍 v002，与参考组件库同版）。实测 GLB 70,140 B / sha256 2bc924b4…，AABB=(-1.25,-1.25,0)~(1.25,1.25,1.8)（Blender Z-up，即 2.5×2.5×1.80）；顶点按象限统计 -X-Z:540 / -X+Z:888 / +X-Z:0 / +X+Z:540，即两臂落在 −X 与 +Z 边、开口朝 +X/−Z，臂中心线 x=−1.0 / z=+1.0。.import 同样绑共享色盘后处理，palette_texture_bound=true。
 只用「外角」一件：100F 天台轮廓是 90×80m 矩形、四个角全是阳角，无内凹，所以ENV-ROOFTOP-REF-PARAPET-INNER 不在本次范围内（保持未导入）。
 放位：转角件包络 2.5×2.5，摆在该角 2.5m 让位区的中心，按角旋转 90° 整数倍——SW=(−48.75, 0, 43.75) rot 0 / SE=(38.75, 0, 43.75) rot π/2 / NE=(38.75, 0, −33.75) rot π / NW=(−48.75, 0, −33.75) rot 3π/2（俯视逆时针）。这套放位让两条臂的中心线正好落在相邻两边的 boundary 上，包络端点与相邻直段无缝相接。这替掉了原来「两根直段在角上交叉」的旧画法。碰撞仍是四边连续体，本 prefab 只产生视觉节点（visual_only / collision_owner=TowerFloorStage3D.OuterBoundaryCollision）。
-实测：probe_rooftop_parapet_alignment 四个转角件 span 尺寸均 2.500×2.500 且 position 与四个2.5m 让位区角点相等；corner_arm_centerlines / corner_open_facing 等朝向口径已写入 prefab 的metadata，供后续换件时核对。门禁 ROOFTOP_WEST_EXPANSION_CONTRACT_PASS 断言 outer_corner_count=4 与四件的位置/朝向（按 wrapf(actual-expected,-π,π) 比角）。</t>
+实测：probe_rooftop_parapet_alignment 四个转角件 span 尺寸均 2.500×2.500 且 position 与四个2.5m 让位区角点相等；corner_arm_centerlines / corner_open_facing 等朝向口径已写入 prefab 的metadata，供后续换件时核对。门禁 ROOFTOP_WEST_EXPANSION_CONTRACT_PASS 断言 outer_corner_count=4 与四件的位置/朝向（按 wrapf(actual-expected,-π,π) 比角）。
+2026-09-20：随直段一起改为 0.80m（同一套三块式配方）。asset_version v002→v003；GLB 同路径覆盖重导（21,768 B），AABB=2.5×2.5×0.80、底面中心、两臂中心线 x=−1.0 / z=+1.0 与开口朝向均不变；四角落座位置（SW/SE/NE/NW）不动。实测 probe_rooftop_parapet_alignment：转角件 4 件 span 均 2.500×2.500，四条边 coverage=全长 / gap=0.000 / overlap=0.000。</t>
         </is>
       </c>
     </row>
@@ -40394,8 +40407,16 @@
           <t>标准外墙实墙</t>
         </is>
       </c>
-      <c r="C132" s="69" t="inlineStr"/>
-      <c r="D132" s="69" t="inlineStr"/>
+      <c r="C132" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_facade_solid_5m.tscn</t>
+        </is>
+      </c>
+      <c r="D132" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_facade_solid_top3d.glb</t>
+        </is>
+      </c>
       <c r="E132" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#标准外墙实墙_资产包</t>
@@ -40409,17 +40430,17 @@
       <c r="G132" s="69" t="inlineStr"/>
       <c r="H132" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>开</t>
         </is>
       </c>
       <c r="I132" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>TowerFloorStage3D</t>
         </is>
       </c>
       <c r="J132" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>BoxShape3D 5×12×0.30，由 FacadeBoundaryCollision_{North/South/West/East} 按槽位生成（Prefab 不再自带碰撞）</t>
         </is>
       </c>
       <c r="K132" s="69" t="inlineStr">
@@ -40429,17 +40450,17 @@
       </c>
       <c r="L132" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0..11.90）；外皮与女儿墙共面</t>
         </is>
       </c>
       <c r="M132" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / facade_solid</t>
+          <t>100F天台外圈（同一圈、低一层 y=-12）/ 实墙 24 槽</t>
         </is>
       </c>
       <c r="N132" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O132" s="69" t="inlineStr">
@@ -40449,7 +40470,8 @@
       </c>
       <c r="P132" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/10/facade_solid/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/10/facade_solid/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-19：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID。用户要求「99 层的外墙 blender 组件中也有，正规导出后变成 prefab，在天台的周边调用然后围起来（其实是 99 层的外墙）——但是现在没有，所以在 100 层天台的边缘看到底下是空的」。导出 GLB env_rooftop_ref_facade_solid_top3d.glb，建立 prefab assets/art/props/dungeon_3d/prp_rooftop_facade_solid_5m.tscn。摆放口径：天台同一圈、低一层（y=-12，即 99F 楼面标高），外皮与女儿墙共面（内缩 0.15m = 厚度 0.30/2）；外立面环按「实 1 : 窗 2」每 3 槽一件实墙。TowerFloorStage3D._build_rooftop_facade_ring 生成实/窗两个 MultiMesh，并由 FacadeBoundaryCollision_{North/South/West/East} 提供 12m 高、0.30m 厚碰撞。实测整圈 68 槽（实 24 / 窗 44），四边满铺无缝；幕帘探针 y=-6 水平射线四边均命中 FacadeBoundaryCollision_*。</t>
         </is>
       </c>
     </row>
@@ -40464,8 +40486,16 @@
           <t>标准外墙窗墙</t>
         </is>
       </c>
-      <c r="C133" s="69" t="inlineStr"/>
-      <c r="D133" s="69" t="inlineStr"/>
+      <c r="C133" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_facade_window_5m.tscn</t>
+        </is>
+      </c>
+      <c r="D133" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_facade_window_top3d.glb</t>
+        </is>
+      </c>
       <c r="E133" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#标准外墙窗墙_资产包</t>
@@ -40479,17 +40509,17 @@
       <c r="G133" s="69" t="inlineStr"/>
       <c r="H133" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>开</t>
         </is>
       </c>
       <c r="I133" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>TowerFloorStage3D</t>
         </is>
       </c>
       <c r="J133" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>BoxShape3D 5×12×0.30，由 FacadeBoundaryCollision_{North/South/West/East} 按槽位生成（Prefab 不再自带碰撞）</t>
         </is>
       </c>
       <c r="K133" s="69" t="inlineStr">
@@ -40499,17 +40529,17 @@
       </c>
       <c r="L133" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0..11.90）；外皮与女儿墙共面</t>
         </is>
       </c>
       <c r="M133" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / facade_window</t>
+          <t>100F天台外圈（同一圈、低一层 y=-12）/ 窗墙 44 槽</t>
         </is>
       </c>
       <c r="N133" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O133" s="69" t="inlineStr">
@@ -40519,7 +40549,8 @@
       </c>
       <c r="P133" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/10/facade_window/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/10/facade_window/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-19：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID。与 ENV-ROOFTOP-REF-FACADE-SOLID 同批升级：窗墙件占外立面环的另外 2/3（每 3 槽 2 件）。导出 GLB env_rooftop_ref_facade_window_top3d.glb，建立 prefab assets/art/props/dungeon_3d/prp_rooftop_facade_window_5m.tscn。摆放口径同实墙：天台同一圈、低一层（y=-12），外皮与女儿墙共面（内缩 0.15m）。实测整圈 68 槽（实 24 / 窗 44），四边满铺无缝；Godot 契约断言 verify_rooftop_32x32_contract.tscn 的 [外立面环] plan==actual 通过。</t>
         </is>
       </c>
     </row>
@@ -41014,254 +41045,260 @@
       </c>
     </row>
     <row r="141" ht="100" customHeight="1" s="50">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>ENV-ROOFTOP-REF-PARAPET-DMG-A</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t>女儿墙直段·破损A（崩顶）</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>assets/art/props/dungeon_3d/prp_rooftop_parapet_dmg_a_5m.tscn</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_parapet_dmg_a_top3d.glb</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包（程序化破损派生）；派生脚本 assets/art/environments/tower_zones/rooftop/source/author_env_rooftop_parapet_damage_v001.py</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包（程序化破损派生）；派生脚本 assets/art/environments/tower_zones/rooftop/source/author_env_rooftop_parapet_damage_v001.py
+2026-09-20：派生口径升级，改由 source/author_env_rooftop_parapet_damage_v003.py 在 0.80m 三块式 base（source/parapet_v003_work.blend）上重做破损；拼缝判据脚本 source/verify_env_rooftop_parapet_damage_bands.py 同步改为「去重位置集合 + Hausdorff」。</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>Godot原生场景结构Prefab；100F天台四周边界直段的破损变体，由 TowerFloorStage3D 按种子随机替换部分直段槽位的可视件（外观破损、阻挡不变）</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>src/world3d/TowerFloorStage3D.gd</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I141" s="3" t="inlineStr">
         <is>
           <t>TowerFloorStage3D</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>BoxShape3D 5×1.80×0.50（与 intact 件同包络），由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）；破损只改外观，不改阻挡高度与缺口宽度</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>GLB / 5×0.50×1.80m / 共享Mesh</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>bottom_center（几何 Y=0..1.80）；朝 +Z</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>100F天台四周边界 / 随机破损档 A（约 1/12 概率）</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>BoxShape3D 5×0.80×0.50（与 intact 件同包络），由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）；破损只改外观，不改阻挡高度与缺口宽度</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>GLB / 5×0.50×0.80m / 共享Mesh</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>bottom_center（几何 Y=0..0.80）；朝 +Z</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>100F天台四周边界 / 随机破损档 A（每段约 1/4 受损，A/B/C 三档均分）</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
         <is>
           <t>正式美术已接入</t>
         </is>
       </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>v001</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr">
+      <c r="O141" s="3" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="P141" s="3" t="inlineStr">
         <is>
           <t>破损口径：crown_spall / 崩顶：压顶顶部被削 3 道豁口、中段崩落，断裂面粗化；下半身与两端头带完整。
 实测 GLB 79644 B。
-父项=ENV-ROOFTOP-REF-PARAPET（同包络的派生件，不新增父库）。2026-09-19 新建。用户原话「墙壁帮我再blender里头制作3个变种，带有破损模型破损的，不同三种破损，但是需要能接起来，然后导入变成新的预制体后重新随机排列外墙」。派生做法：author_env_rooftop_parapet_damage_v001.py（headless Blender）把 intact 网格按「积木」拆成 22 块闭合倒角块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），只对与破损区相交的积木做**逐块**布尔剔料再合并。⚠️ 整件一次性布尔会静默吃掉 10 块墙身积木（512→272 顶点、4.52→1.25 m³、31.53 m² 面消失），且换个不接触的刀口也照样发生 —— 必须逐块做，这是本件最大的坑。拼接契约（用户要求的「能接起来」）：两端头带 |x|&gt;=2.05m 与 intact 件逐位相同（GLB 字节层已证：source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true）、包络 5.00×0.50×1.80、原点底面中心均与 intact 件逐值相同 ⇒ 可沿任一边、任意顺序与原件 / 彼此对接，接头无缝、槽位相位不变。色盘：破损新面 UV 已钳回色盘色块（U 0.923..0.977 / V 0.123..0.477），材质仍是02_细腻哑光_青绿大面；.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，探针实测 palette_texture_bound=true。实测：Godot 探针 probe_rooftop_parapet_damage_prefabs 四件（intact + A/B/C）包络逐值相同、端头带点云最近邻最大距离 7.07e-5 m（0.07mm；源文件逐位相同，这点偏差来自 Godot 导入对近重合重复顶点的焊接，不是几何被改）。接线：TowerFloorStage3D.PARAPET_DAMAGE_SCENES + 静态纯函数 split_outer_parapet_damage()，按种子随机分档；种子 ROOFTOP_PARAPET_DAMAGE_SEED=20260919，每段受损概率 0.25（三档均分），可用 set_outer_damage_seed() 在 _ready 前覆盖。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract 新增 _verify_rooftop_parapet_damage：槽位数 61 = 64−门洞补位 3、四批次件数之和 == 槽位数、计划 == 摆放、破损比例 ∈[0.15,0.35]、换种子必换排布、非天台层整批完好）；反向对照已做（破损概率改 0 / 改 1 / 排布忽略种子三种改坏各自变红，脚本 _scratch/task14/reverse_control_parapet_damage.py）。另：本族不像直段那样登记《资产主表》（与 102/104 行口径一致）。</t>
+父项=ENV-ROOFTOP-REF-PARAPET（同包络的派生件，不新增父库）。2026-09-19 新建。用户原话「墙壁帮我再blender里头制作3个变种，带有破损模型破损的，不同三种破损，但是需要能接起来，然后导入变成新的预制体后重新随机排列外墙」。派生做法：author_env_rooftop_parapet_damage_v001.py（headless Blender）把 intact 网格按「积木」拆成 22 块闭合倒角块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），只对与破损区相交的积木做**逐块**布尔剔料再合并。⚠️ 整件一次性布尔会静默吃掉 10 块墙身积木（512→272 顶点、4.52→1.25 m³、31.53 m² 面消失），且换个不接触的刀口也照样发生 —— 必须逐块做，这是本件最大的坑。拼接契约（用户要求的「能接起来」）：两端头带 |x|&gt;=2.05m 与 intact 件逐位相同（GLB 字节层已证：source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true）、包络 5.00×0.50×1.80、原点底面中心均与 intact 件逐值相同 ⇒ 可沿任一边、任意顺序与原件 / 彼此对接，接头无缝、槽位相位不变。色盘：破损新面 UV 已钳回色盘色块（U 0.923..0.977 / V 0.123..0.477），材质仍是02_细腻哑光_青绿大面；.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，探针实测 palette_texture_bound=true。实测：Godot 探针 probe_rooftop_parapet_damage_prefabs 四件（intact + A/B/C）包络逐值相同、端头带点云最近邻最大距离 7.07e-5 m（0.07mm；源文件逐位相同，这点偏差来自 Godot 导入对近重合重复顶点的焊接，不是几何被改）。接线：TowerFloorStage3D.PARAPET_DAMAGE_SCENES + 静态纯函数 split_outer_parapet_damage()，按种子随机分档；种子 ROOFTOP_PARAPET_DAMAGE_SEED=20260919，每段受损概率 0.25（三档均分），可用 set_outer_damage_seed() 在 _ready 前覆盖。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract 新增 _verify_rooftop_parapet_damage：槽位数 61 = 64−门洞补位 3、四批次件数之和 == 槽位数、计划 == 摆放、破损比例 ∈[0.15,0.35]、换种子必换排布、非天台层整批完好）；反向对照已做（破损概率改 0 / 改 1 / 排布忽略种子三种改坏各自变红，脚本 _scratch/task14/reverse_control_parapet_damage.py）。另：本族不像直段那样登记《资产主表》（与 102/104 行口径一致）。
+2026-09-20：随直段降到 0.80m 并改 3 块式 base，破损配方同步重调（crown_spall 崩顶：压顶带被削 3 道豁口、中段崩落；下半身与两端头带完整）。asset_version v001→v002；GLB 同路径覆盖重导（38,784 B）。实测 probe_rooftop_parapet_damage_prefabs：包络 5.0×0.80×0.50、端头带去重位置 72（与 intact 同）、点云双向最近邻 5.22e-5 m ≪ 2e-4 阈值；source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK variants=3 band_bit_identical=true envelope_identical=true height_m=0.80。</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>ENV-ROOFTOP-REF-PARAPET-DMG-B</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>女儿墙直段·破损B（贯穿）</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>assets/art/props/dungeon_3d/prp_rooftop_parapet_dmg_b_5m.tscn</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_parapet_dmg_b_top3d.glb</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包（程序化破损派生）；派生脚本 assets/art/environments/tower_zones/rooftop/source/author_env_rooftop_parapet_damage_v001.py</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包（程序化破损派生）；派生脚本 assets/art/environments/tower_zones/rooftop/source/author_env_rooftop_parapet_damage_v001.py
+2026-09-20：派生口径升级，改由 source/author_env_rooftop_parapet_damage_v003.py 在 0.80m 三块式 base（source/parapet_v003_work.blend）上重做破损；拼缝判据脚本 source/verify_env_rooftop_parapet_damage_bands.py 同步改为「去重位置集合 + Hausdorff」。</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>Godot原生场景结构Prefab；100F天台四周边界直段的破损变体，由 TowerFloorStage3D 按种子随机替换部分直段槽位的可视件（外观破损、阻挡不变）</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>src/world3d/TowerFloorStage3D.gd</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr">
         <is>
           <t>TowerFloorStage3D</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>BoxShape3D 5×1.80×0.50（与 intact 件同包络），由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）；破损只改外观，不改阻挡高度与缺口宽度</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>GLB / 5×0.50×1.80m / 共享Mesh</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>bottom_center（几何 Y=0..1.80）；朝 +Z</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>100F天台四周边界 / 随机破损档 A（约 1/12 概率）</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr">
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>BoxShape3D 5×0.80×0.50（与 intact 件同包络），由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）；破损只改外观，不改阻挡高度与缺口宽度</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>GLB / 5×0.50×0.80m / 共享Mesh</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>bottom_center（几何 Y=0..0.80）；朝 +Z</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>100F天台四周边界 / 随机破损档 B（每段约 1/4 受损，A/B/C 三档均分）</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
         <is>
           <t>正式美术已接入</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>v001</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr">
+      <c r="O142" s="3" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="P142" s="3" t="inlineStr">
         <is>
           <t>破损口径：through_breach / 贯穿：墙身中段被打穿 2 个带放射裂纹的贯穿洞，可透视到墙外；洞缘粗化。
 实测 GLB 116652 B。
-父项=ENV-ROOFTOP-REF-PARAPET（同包络的派生件，不新增父库）。2026-09-19 新建。用户原话「墙壁帮我再blender里头制作3个变种，带有破损模型破损的，不同三种破损，但是需要能接起来，然后导入变成新的预制体后重新随机排列外墙」。派生做法：author_env_rooftop_parapet_damage_v001.py（headless Blender）把 intact 网格按「积木」拆成 22 块闭合倒角块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），只对与破损区相交的积木做**逐块**布尔剔料再合并。⚠️ 整件一次性布尔会静默吃掉 10 块墙身积木（512→272 顶点、4.52→1.25 m³、31.53 m² 面消失），且换个不接触的刀口也照样发生 —— 必须逐块做，这是本件最大的坑。拼接契约（用户要求的「能接起来」）：两端头带 |x|&gt;=2.05m 与 intact 件逐位相同（GLB 字节层已证：source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true）、包络 5.00×0.50×1.80、原点底面中心均与 intact 件逐值相同 ⇒ 可沿任一边、任意顺序与原件 / 彼此对接，接头无缝、槽位相位不变。色盘：破损新面 UV 已钳回色盘色块（U 0.923..0.977 / V 0.123..0.477），材质仍是02_细腻哑光_青绿大面；.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，探针实测 palette_texture_bound=true。实测：Godot 探针 probe_rooftop_parapet_damage_prefabs 四件（intact + A/B/C）包络逐值相同、端头带点云最近邻最大距离 7.07e-5 m（0.07mm；源文件逐位相同，这点偏差来自 Godot 导入对近重合重复顶点的焊接，不是几何被改）。接线：TowerFloorStage3D.PARAPET_DAMAGE_SCENES + 静态纯函数 split_outer_parapet_damage()，按种子随机分档；种子 ROOFTOP_PARAPET_DAMAGE_SEED=20260919，每段受损概率 0.25（三档均分），可用 set_outer_damage_seed() 在 _ready 前覆盖。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract 新增 _verify_rooftop_parapet_damage：槽位数 61 = 64−门洞补位 3、四批次件数之和 == 槽位数、计划 == 摆放、破损比例 ∈[0.15,0.35]、换种子必换排布、非天台层整批完好）；反向对照已做（破损概率改 0 / 改 1 / 排布忽略种子三种改坏各自变红，脚本 _scratch/task14/reverse_control_parapet_damage.py）。另：本族不像直段那样登记《资产主表》（与 102/104 行口径一致）。</t>
+父项=ENV-ROOFTOP-REF-PARAPET（同包络的派生件，不新增父库）。2026-09-19 新建。用户原话「墙壁帮我再blender里头制作3个变种，带有破损模型破损的，不同三种破损，但是需要能接起来，然后导入变成新的预制体后重新随机排列外墙」。派生做法：author_env_rooftop_parapet_damage_v001.py（headless Blender）把 intact 网格按「积木」拆成 22 块闭合倒角块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），只对与破损区相交的积木做**逐块**布尔剔料再合并。⚠️ 整件一次性布尔会静默吃掉 10 块墙身积木（512→272 顶点、4.52→1.25 m³、31.53 m² 面消失），且换个不接触的刀口也照样发生 —— 必须逐块做，这是本件最大的坑。拼接契约（用户要求的「能接起来」）：两端头带 |x|&gt;=2.05m 与 intact 件逐位相同（GLB 字节层已证：source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true）、包络 5.00×0.50×1.80、原点底面中心均与 intact 件逐值相同 ⇒ 可沿任一边、任意顺序与原件 / 彼此对接，接头无缝、槽位相位不变。色盘：破损新面 UV 已钳回色盘色块（U 0.923..0.977 / V 0.123..0.477），材质仍是02_细腻哑光_青绿大面；.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，探针实测 palette_texture_bound=true。实测：Godot 探针 probe_rooftop_parapet_damage_prefabs 四件（intact + A/B/C）包络逐值相同、端头带点云最近邻最大距离 7.07e-5 m（0.07mm；源文件逐位相同，这点偏差来自 Godot 导入对近重合重复顶点的焊接，不是几何被改）。接线：TowerFloorStage3D.PARAPET_DAMAGE_SCENES + 静态纯函数 split_outer_parapet_damage()，按种子随机分档；种子 ROOFTOP_PARAPET_DAMAGE_SEED=20260919，每段受损概率 0.25（三档均分），可用 set_outer_damage_seed() 在 _ready 前覆盖。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract 新增 _verify_rooftop_parapet_damage：槽位数 61 = 64−门洞补位 3、四批次件数之和 == 槽位数、计划 == 摆放、破损比例 ∈[0.15,0.35]、换种子必换排布、非天台层整批完好）；反向对照已做（破损概率改 0 / 改 1 / 排布忽略种子三种改坏各自变红，脚本 _scratch/task14/reverse_control_parapet_damage.py）。另：本族不像直段那样登记《资产主表》（与 102/104 行口径一致）。
+2026-09-20：随直段降到 0.80m 并改 3 块式 base，破损配方同步重调（through_breach 贯穿：墙身中段打穿 2 个带放射裂纹的贯穿洞，可透视墙外；端头带完整）。asset_version v001→v002；GLB 同路径覆盖重导（37,084 B）。实测：包络 5.0×0.80×0.50、端头带原始顶点 292（去重后 72 —— 多出的 4 个是布尔切割改变了既有端头带顶点的 UV 参数化、glTF 按 (position,normal,uv) 拆点所致，几何未变，Hausdorff 5.22e-5 m）。⚠️ 探针判据已由「原始顶点数相等」改为「去重位置集合相等 + Hausdorff」——原始顶点数是导入管线的记账产物，不是几何；反向对照已做（把端头带起点从 2.05 放宽到 1.0 必变红），确认判据不空转。source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true height_m=0.80。</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>ENV-ROOFTOP-REF-PARAPET-DMG-C</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>女儿墙直段·破损C（塌脚）</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>assets/art/props/dungeon_3d/prp_rooftop_parapet_dmg_c_5m.tscn</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_parapet_dmg_c_top3d.glb</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包（程序化破损派生）；派生脚本 assets/art/environments/tower_zones/rooftop/source/author_env_rooftop_parapet_damage_v001.py</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#女儿墙直段_资产包（程序化破损派生）；派生脚本 assets/art/environments/tower_zones/rooftop/source/author_env_rooftop_parapet_damage_v001.py
+2026-09-20：派生口径升级，改由 source/author_env_rooftop_parapet_damage_v003.py 在 0.80m 三块式 base（source/parapet_v003_work.blend）上重做破损；拼缝判据脚本 source/verify_env_rooftop_parapet_damage_bands.py 同步改为「去重位置集合 + Hausdorff」。</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>Godot原生场景结构Prefab；100F天台四周边界直段的破损变体，由 TowerFloorStage3D 按种子随机替换部分直段槽位的可视件（外观破损、阻挡不变）</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>src/world3d/TowerFloorStage3D.gd</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H143" s="3" t="inlineStr">
         <is>
           <t>开</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I143" s="3" t="inlineStr">
         <is>
           <t>TowerFloorStage3D</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>BoxShape3D 5×1.80×0.50（与 intact 件同包络），由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）；破损只改外观，不改阻挡高度与缺口宽度</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>GLB / 5×0.50×1.80m / 共享Mesh</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>bottom_center（几何 Y=0..1.80）；朝 +Z</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>100F天台四周边界 / 随机破损档 A（约 1/12 概率）</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>BoxShape3D 5×0.80×0.50（与 intact 件同包络），由 OuterBoundaryCollision 按槽位生成（Prefab 不再自带碰撞）；破损只改外观，不改阻挡高度与缺口宽度</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>GLB / 5×0.50×0.80m / 共享Mesh</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>bottom_center（几何 Y=0..0.80）；朝 +Z</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>100F天台四周边界 / 随机破损档 C（每段约 1/4 受损，A/B/C 三档均分）</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
         <is>
           <t>正式美术已接入</t>
         </is>
       </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>v001</t>
-        </is>
-      </c>
-      <c r="P143" t="inlineStr">
+      <c r="O143" s="3" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="P143" s="3" t="inlineStr">
         <is>
           <t>破损口径：base_collapse / 塌脚：墙身中段整体塌到约 0.5m 残根、基座阳角被啃缺口，是最重的一档。
 实测 GLB 86228 B。
-父项=ENV-ROOFTOP-REF-PARAPET（同包络的派生件，不新增父库）。2026-09-19 新建。用户原话「墙壁帮我再blender里头制作3个变种，带有破损模型破损的，不同三种破损，但是需要能接起来，然后导入变成新的预制体后重新随机排列外墙」。派生做法：author_env_rooftop_parapet_damage_v001.py（headless Blender）把 intact 网格按「积木」拆成 22 块闭合倒角块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），只对与破损区相交的积木做**逐块**布尔剔料再合并。⚠️ 整件一次性布尔会静默吃掉 10 块墙身积木（512→272 顶点、4.52→1.25 m³、31.53 m² 面消失），且换个不接触的刀口也照样发生 —— 必须逐块做，这是本件最大的坑。拼接契约（用户要求的「能接起来」）：两端头带 |x|&gt;=2.05m 与 intact 件逐位相同（GLB 字节层已证：source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true）、包络 5.00×0.50×1.80、原点底面中心均与 intact 件逐值相同 ⇒ 可沿任一边、任意顺序与原件 / 彼此对接，接头无缝、槽位相位不变。色盘：破损新面 UV 已钳回色盘色块（U 0.923..0.977 / V 0.123..0.477），材质仍是02_细腻哑光_青绿大面；.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，探针实测 palette_texture_bound=true。实测：Godot 探针 probe_rooftop_parapet_damage_prefabs 四件（intact + A/B/C）包络逐值相同、端头带点云最近邻最大距离 7.07e-5 m（0.07mm；源文件逐位相同，这点偏差来自 Godot 导入对近重合重复顶点的焊接，不是几何被改）。接线：TowerFloorStage3D.PARAPET_DAMAGE_SCENES + 静态纯函数 split_outer_parapet_damage()，按种子随机分档；种子 ROOFTOP_PARAPET_DAMAGE_SEED=20260919，每段受损概率 0.25（三档均分），可用 set_outer_damage_seed() 在 _ready 前覆盖。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract 新增 _verify_rooftop_parapet_damage：槽位数 61 = 64−门洞补位 3、四批次件数之和 == 槽位数、计划 == 摆放、破损比例 ∈[0.15,0.35]、换种子必换排布、非天台层整批完好）；反向对照已做（破损概率改 0 / 改 1 / 排布忽略种子三种改坏各自变红，脚本 _scratch/task14/reverse_control_parapet_damage.py）。另：本族不像直段那样登记《资产主表》（与 102/104 行口径一致）。</t>
+父项=ENV-ROOFTOP-REF-PARAPET（同包络的派生件，不新增父库）。2026-09-19 新建。用户原话「墙壁帮我再blender里头制作3个变种，带有破损模型破损的，不同三种破损，但是需要能接起来，然后导入变成新的预制体后重新随机排列外墙」。派生做法：author_env_rooftop_parapet_damage_v001.py（headless Blender）把 intact 网格按「积木」拆成 22 块闭合倒角块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），只对与破损区相交的积木做**逐块**布尔剔料再合并。⚠️ 整件一次性布尔会静默吃掉 10 块墙身积木（512→272 顶点、4.52→1.25 m³、31.53 m² 面消失），且换个不接触的刀口也照样发生 —— 必须逐块做，这是本件最大的坑。拼接契约（用户要求的「能接起来」）：两端头带 |x|&gt;=2.05m 与 intact 件逐位相同（GLB 字节层已证：source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true）、包络 5.00×0.50×1.80、原点底面中心均与 intact 件逐值相同 ⇒ 可沿任一边、任意顺序与原件 / 彼此对接，接头无缝、槽位相位不变。色盘：破损新面 UV 已钳回色盘色块（U 0.923..0.977 / V 0.123..0.477），材质仍是02_细腻哑光_青绿大面；.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，探针实测 palette_texture_bound=true。实测：Godot 探针 probe_rooftop_parapet_damage_prefabs 四件（intact + A/B/C）包络逐值相同、端头带点云最近邻最大距离 7.07e-5 m（0.07mm；源文件逐位相同，这点偏差来自 Godot 导入对近重合重复顶点的焊接，不是几何被改）。接线：TowerFloorStage3D.PARAPET_DAMAGE_SCENES + 静态纯函数 split_outer_parapet_damage()，按种子随机分档；种子 ROOFTOP_PARAPET_DAMAGE_SEED=20260919，每段受损概率 0.25（三档均分），可用 set_outer_damage_seed() 在 _ready 前覆盖。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract 新增 _verify_rooftop_parapet_damage：槽位数 61 = 64−门洞补位 3、四批次件数之和 == 槽位数、计划 == 摆放、破损比例 ∈[0.15,0.35]、换种子必换排布、非天台层整批完好）；反向对照已做（破损概率改 0 / 改 1 / 排布忽略种子三种改坏各自变红，脚本 _scratch/task14/reverse_control_parapet_damage.py）。另：本族不像直段那样登记《资产主表》（与 102/104 行口径一致）。
+2026-09-20：随直段降到 0.80m 并改 3 块式 base，破损配方同步重调（base_collapse 塌脚：墙身中段整体塌落成约 0.22m 残根、基座带被掏空，最重一档；端头带完整）。asset_version v001→v002；GLB 同路径覆盖重导（29,096 B）。实测：包络 5.0×0.80×0.50、端头带去重位置 72（与 intact 同）、点云双向最近邻 5.22e-5 m；source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_id_identical=true height_m=0.80。</t>
         </is>
       </c>
     </row>
@@ -43401,7 +43438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="50" min="1" max="1"/>
@@ -43539,6 +43576,80 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>v0.1.2</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>资产升版</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>关卡场景</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>天台地板与外立面共三件（ENV-ROOFTOP-REF-FLOOR-FULL 完整地砖 / ENV-ROOFTOP-REF-FACADE-SOLID 标准外墙实墙 / ENV-ROOFTOP-REF-FACADE-WINDOW 标准外墙窗墙）由「仅 Blender 源、未导入 Godot」升为运行时正式资产：从 reference_components/v002 导出 GLB 并建立 prefab assets/art/props/dungeon_3d/prp_rooftop_floor_5m.tscn、prp_rooftop_facade_solid_5m.tscn、prp_rooftop_facade_window_5m.tscn。TowerFloorStage3D 三处接线：①天台地面由 POLISHED_FLOOR_SCENE 改指 ROOFTOP_FLOOR_SCENE（原点契约由几何中心改为 bottom_center，改用 AABB 对齐顶面 Y=0）；②天台外墙不再挖楼梯口门洞，西侧围栏缺口闭合（门洞补位墙 3 件 → 0 件，直段 61 → 64，西侧碰撞由断成两段改为一条连续 Box）；③新增 _build_rooftop_facade_ring：天台同一圈、低一层（y=-12 = 99F 楼面标高）摆 68 槽实/窗外墙（实 1 : 窗 2），并由 FacadeBoundaryCollision_* 提供 12m 高、0.30m 厚碰撞，补上「从天台边缘往下看到的空档」。资产主表未增删行；只升 3D-场景通用 既有三行。</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>AssetID 与版本号不变（v002 = 参考组件库版本），仅补 prefab/GLB 路径、碰撞归属与实测记录。旧地板 POLISHED_FLOOR_SCENE 与旧占位矮墙 prp_tower_wall_parapet_door_5m 保留不动（后者仍被 DungeonRoom3D 引用且在 PREFAB_CONTRACT 清单内）。本次不新增 AssetID，不新增台账行。</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v0.1.3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>资产升版</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>关卡场景</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>天台女儿墙族由 1.80m 改为 0.80m（含压顶总高），并把 v002 的 22 块「密集竖杠」配方重建为方案A 平整墙板（三块式：基座带 + 墙板 + 压顶带）。用户原话「改成0.8米的，变体也要一起改，然后中间的竖杠太密了 不好看，横杆在两边即可」。重导 5 件 GLB 同路径覆盖：ENV-ROOFTOP-REF-PARAPET（v002→v003）、ENV-ROOFTOP-REF-PARAPET-OUTER（v002→v003）、ENV-ROOFTOP-REF-PARAPET-DMG-A/B/C（各 v001→v002）。TowerFloorStage3D.ROOFTOP_PARAPET_HEIGHT 1.80→0.80，碰撞高度与楼梯口矮墙缩放自动跟随；厚度 0.50m 不变，故四边/西侧碰撞位置与槽位相位不动。资产主表未增删行（本族只登记在《3D-场景通用》分页）；总览跨度不变。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AssetID 不变，只升版本；5 件 GLB 均为同路径覆盖重导，不新增文件；旧 v002 配方留档于 source/reference_components/v002（只读）。破损拼缝判据由「原始顶点数相等」改为「去重位置集合 + Hausdorff」，理由见 ENV-ROOFTOP-REF-PARAPET-DMG-B 行备注。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -14320,12 +14320,12 @@
       </c>
       <c r="M108" s="79" t="inlineStr">
         <is>
-          <t>v002</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="N108" s="79" t="inlineStr">
         <is>
-          <t>30×30m围护；本地12—24m墙体；24m封顶；墙视觉11.9m</t>
+          <t>30×30m围护；本地12—24m墙体；24m封顶；墙视觉11.9m；东西南三面=天台v002房间标准墙17块；封顶=天台v002角4+边16+内圈16</t>
         </is>
       </c>
       <c r="O108" s="79" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="T108" s="79" t="inlineStr">
         <is>
-          <t>3c44b2bdd1cf204da495cc7d4196af7fe943b1a0ebd5110b3776f57b0c5e12ae</t>
+          <t>376d1620459eb929233fc62f548ab352c0024222e29a75a94f2a3396f2e31fe4</t>
         </is>
       </c>
       <c r="U108" s="79" t="inlineStr">
@@ -14361,8 +14361,8 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V108" s="79" t="n">
-        <v>46277</v>
+      <c r="V108" s="80" t="n">
+        <v>46285</v>
       </c>
       <c r="W108" s="79" t="inlineStr">
         <is>
@@ -14378,7 +14378,8 @@
         <is>
           <t>北墙两端普通+中间4窗；其余19普通墙，东侧1门墙；18米屋顶挡光；围护与封顶统一投影；不恢复99/100层中间36块。
 2026-08-30 AST-01规范化（原制作状态：正式美术已接入）
-2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base99_floor_player_collision_flow；verify_base_facility_interaction_zones；SHA 127b01c6d9f5→38c3040b8632。</t>
+2026-08-30 AST-02：合法内容更新；文件为Git已跟踪且修改时间不早于原台账日期；验收：verify_base99_floor_player_collision_flow；verify_base_facility_interaction_zones；SHA 127b01c6d9f5→38c3040b8632。
+2026-09-20：东西南三面 17 块 5m 墙与 24m 封顶 36 格换成天台参考组件库 v002 （ENV-ROOFTOP-REF-ROOM-WALL + ROOF-{CORNER,EDGE,FULL}）；北面 4 大窗与东面门洞槽保留 base99。北面窗墙不动的原因是东门槽为 100F 唯一外梯过场门（RoomDoor3D 净尺寸写死 2.2×2.5）。场景 24 墙 = 17 v002 + 2 base99 普通墙 + 4 base99 窗墙 + 1 base99 门墙；封顶 36 格全换。旧 36 格 base99 地砖引用已移除。SHA 随重生成 tscn 刷新。验收 verify_base99_wall_visual_replacement（BASE99_MODULAR_ASSET_INTEGRATION_PASS）+ verify_rooftop_32x32_contract + verify_base_rooftop_transit_door_motion 全绿。</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P143"/>
+  <dimension ref="A1:P145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="50" min="1" max="1"/>
@@ -38587,8 +38588,16 @@
           <t>房间标准墙</t>
         </is>
       </c>
-      <c r="C106" s="69" t="inlineStr"/>
-      <c r="D106" s="69" t="inlineStr"/>
+      <c r="C106" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_room_wall_5x12.tscn</t>
+        </is>
+      </c>
+      <c r="D106" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_room_wall_top3d.glb</t>
+        </is>
+      </c>
       <c r="E106" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#房间标准墙_资产包</t>
@@ -38599,40 +38608,44 @@
           <t>独立资产包；03_房间墙体</t>
         </is>
       </c>
-      <c r="G106" s="69" t="inlineStr"/>
+      <c r="G106" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/Base100UpperShell3D.gd</t>
+        </is>
+      </c>
       <c r="H106" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>开</t>
         </is>
       </c>
       <c r="I106" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>Base100UpperShell3D</t>
         </is>
       </c>
       <c r="J106" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>BoxShape3D；由 Base100UpperShell3D._build_structure_collision() 生成 30×30 连续结构层代理，Prefab 自身不带碰撞节点（内嵌会与结构层重复阻挡）</t>
         </is>
       </c>
       <c r="K106" s="69" t="inlineStr">
         <is>
-          <t>5.000×0.300×11.900 m</t>
+          <t>5.000×11.900×0.300 m（逻辑高 12.000，顶面留 0.10 给 24m 封顶）</t>
         </is>
       </c>
       <c r="L106" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
       <c r="M106" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / room_wall</t>
+          <t>100F 上层围护东西南三面 17 块（南 6 / 西 6 / 东 5，东面 z=-7.5 门洞槽除外）</t>
         </is>
       </c>
       <c r="N106" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O106" s="69" t="inlineStr">
@@ -38642,7 +38655,8 @@
       </c>
       <c r="P106" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_wall/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_wall/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-20：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID。用户要求「把天台参考组件库里的房间墙体与房顶做成正规 prefab，替换 100F 上层围护的东西南三面，北面大窗不动」。导出 GLB 后建立 prefab prp_rooftop_room_wall_5x12.tscn；场景 env_base100_upper_shell_30x30_h12_root_top3d.tscn 用 17 个实例承接，rotation_y = 0（南）/ -90°（西）/ +90°（东）；北面 2 普通墙 + 4 窗墙与东面 1 门墙仍为 base99。碰撞交 Base100UpperShell3D 连续结构层（9 片不变）。验收 verify_base99_wall_visual_replacement（含 base100_rooftop_room_wall_count=17）。</t>
         </is>
       </c>
     </row>
@@ -38657,8 +38671,16 @@
           <t>房间窗墙</t>
         </is>
       </c>
-      <c r="C107" s="69" t="inlineStr"/>
-      <c r="D107" s="69" t="inlineStr"/>
+      <c r="C107" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_room_window_5x12.tscn</t>
+        </is>
+      </c>
+      <c r="D107" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_room_window_top3d.glb</t>
+        </is>
+      </c>
       <c r="E107" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#房间窗墙_资产包</t>
@@ -38669,7 +38691,7 @@
           <t>独立资产包；03_房间墙体</t>
         </is>
       </c>
-      <c r="G107" s="69" t="inlineStr"/>
+      <c r="G107" s="69" t="n"/>
       <c r="H107" s="69" t="inlineStr">
         <is>
           <t>未创建</t>
@@ -38677,32 +38699,32 @@
       </c>
       <c r="I107" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>Base100UpperShell3D</t>
         </is>
       </c>
       <c r="J107" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>Prefab 已声明 collision_owner；尚未在 100F 上层围护场景实例化</t>
         </is>
       </c>
       <c r="K107" s="69" t="inlineStr">
         <is>
-          <t>5.000×0.300×11.900 m</t>
+          <t>5.000×11.900×0.300 m（逻辑高 12.000）</t>
         </is>
       </c>
       <c r="L107" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
       <c r="M107" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / room_window</t>
+          <t>已制作并登记；100F 上层围护**未使用**（北面 4 大窗仍用 base99 窗墙）</t>
         </is>
       </c>
       <c r="N107" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O107" s="69" t="inlineStr">
@@ -38712,7 +38734,8 @@
       </c>
       <c r="P107" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_window/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_window/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-20：随房间墙体套件一并导出 GLB 并建立 prefab；本批场景未摆放 —— 用户口径是「北面大窗不动」，北面 4 块沿用 base99 窗墙。留作后续把北面大窗换成天台 v002 窗墙时直接引用。</t>
         </is>
       </c>
     </row>
@@ -38727,8 +38750,16 @@
           <t>房间门洞墙</t>
         </is>
       </c>
-      <c r="C108" s="69" t="inlineStr"/>
-      <c r="D108" s="69" t="inlineStr"/>
+      <c r="C108" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_room_doorwall_5x12.tscn</t>
+        </is>
+      </c>
+      <c r="D108" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_room_doorwall_top3d.glb</t>
+        </is>
+      </c>
       <c r="E108" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#房间门洞墙_资产包</t>
@@ -38739,7 +38770,7 @@
           <t>独立资产包；03_房间墙体</t>
         </is>
       </c>
-      <c r="G108" s="69" t="inlineStr"/>
+      <c r="G108" s="69" t="n"/>
       <c r="H108" s="69" t="inlineStr">
         <is>
           <t>未创建</t>
@@ -38747,32 +38778,32 @@
       </c>
       <c r="I108" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>Base100UpperShell3D</t>
         </is>
       </c>
       <c r="J108" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>Prefab 已声明 collision_owner；尚未在 100F 上层围护场景实例化</t>
         </is>
       </c>
       <c r="K108" s="69" t="inlineStr">
         <is>
-          <t>5.000×0.300×11.900 m</t>
+          <t>5.000×11.900×0.300 m；门洞净空 3.80×6.80 m（两侧垛各 0.60 m）</t>
         </is>
       </c>
       <c r="L108" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
       <c r="M108" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / room_doorwall</t>
+          <t>已制作并登记；100F 上层围护**未使用**（东面门洞槽仍用 base99 门墙）</t>
         </is>
       </c>
       <c r="N108" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O108" s="69" t="inlineStr">
@@ -38782,7 +38813,8 @@
       </c>
       <c r="P108" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_doorwall/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_doorwall/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-20：随房间墙体套件一并导出 GLB 并建立 prefab；本批场景未摆放。原因：东面 z=-7.5 门洞槽是 100F 唯一的外梯过场门位，由 TowerDescent3D._install_base_rooftop_transit_door() 挂 RoomDoor3D，其净尺寸写死 TOWER_GEOMETRY.DOOR_CLEAR_WIDTH_M/HEIGHT_M = 2.2×2.5；换成本件的 3.80×6.80 洞等于改全游戏所有门的尺寸与碰撞。用户决策「东门不动，新门只入库」。</t>
         </is>
       </c>
     </row>
@@ -38797,8 +38829,16 @@
           <t>房顶完整板</t>
         </is>
       </c>
-      <c r="C109" s="69" t="inlineStr"/>
-      <c r="D109" s="69" t="inlineStr"/>
+      <c r="C109" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_roof_full_5m.tscn</t>
+        </is>
+      </c>
+      <c r="D109" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_roof_full_top3d.glb</t>
+        </is>
+      </c>
       <c r="E109" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#房顶完整板_资产包</t>
@@ -38809,40 +38849,44 @@
           <t>独立资产包；04_房顶模块</t>
         </is>
       </c>
-      <c r="G109" s="69" t="inlineStr"/>
+      <c r="G109" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/Base100UpperShell3D.gd</t>
+        </is>
+      </c>
       <c r="H109" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>开</t>
         </is>
       </c>
       <c r="I109" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>Base100UpperShell3D</t>
         </is>
       </c>
       <c r="J109" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>BoxShape3D；由 Base100UpperShell3D._build_structure_collision() 生成 30×30 连续结构层代理，Prefab 自身不带碰撞节点（内嵌会与结构层重复阻挡）</t>
         </is>
       </c>
       <c r="K109" s="69" t="inlineStr">
         <is>
-          <t>5.000×5.000×0.300 m</t>
+          <t>5.000×5.000×0.300 m（底面原点到顶面 0.30，摆 y=24 占 24.00..24.30）</t>
         </is>
       </c>
       <c r="L109" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
       <c r="M109" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / roof_full</t>
+          <t>100F 24m 封顶 6×6 网格的 16 个内圈格</t>
         </is>
       </c>
       <c r="N109" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O109" s="69" t="inlineStr">
@@ -38852,7 +38896,8 @@
       </c>
       <c r="P109" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/04/roof_full/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/04/roof_full/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-20：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID。用户要求「36 格 base99 地砖换成新房顶模块」。prefab prp_rooftop_roof_full_5m.tscn 只铺 6×6 的 16 个内圈格（rotation_y=0）。</t>
         </is>
       </c>
     </row>
@@ -38867,8 +38912,16 @@
           <t>房顶边缘板</t>
         </is>
       </c>
-      <c r="C110" s="69" t="inlineStr"/>
-      <c r="D110" s="69" t="inlineStr"/>
+      <c r="C110" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_roof_edge_5m.tscn</t>
+        </is>
+      </c>
+      <c r="D110" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_roof_edge_top3d.glb</t>
+        </is>
+      </c>
       <c r="E110" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#房顶边缘板_资产包</t>
@@ -38879,40 +38932,44 @@
           <t>独立资产包；04_房顶模块</t>
         </is>
       </c>
-      <c r="G110" s="69" t="inlineStr"/>
+      <c r="G110" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/Base100UpperShell3D.gd</t>
+        </is>
+      </c>
       <c r="H110" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>开</t>
         </is>
       </c>
       <c r="I110" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>Base100UpperShell3D</t>
         </is>
       </c>
       <c r="J110" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>BoxShape3D；由 Base100UpperShell3D._build_structure_collision() 生成 30×30 连续结构层代理，Prefab 自身不带碰撞节点（内嵌会与结构层重复阻挡）</t>
         </is>
       </c>
       <c r="K110" s="69" t="inlineStr">
         <is>
-          <t>5.000×5.000×0.300 m</t>
+          <t>5.000×5.000×0.300 m（收口线脚在板厚之内，不外扩包络）</t>
         </is>
       </c>
       <c r="L110" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
       <c r="M110" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / roof_edge</t>
+          <t>100F 24m 封顶 6×6 网格的 16 个外圈非角格</t>
         </is>
       </c>
       <c r="N110" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O110" s="69" t="inlineStr">
@@ -38922,7 +38979,8 @@
       </c>
       <c r="P110" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/04/roof_edge/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/04/roof_edge/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-20：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID。收口侧 = 局部 +Z 朝外，按边取 rotation：max z→0° / min z→180° / max x→+90° / min x→-90°。</t>
         </is>
       </c>
     </row>
@@ -38937,8 +38995,16 @@
           <t>房顶角板</t>
         </is>
       </c>
-      <c r="C111" s="69" t="inlineStr"/>
-      <c r="D111" s="69" t="inlineStr"/>
+      <c r="C111" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_roof_corner_5m.tscn</t>
+        </is>
+      </c>
+      <c r="D111" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_roof_corner_top3d.glb</t>
+        </is>
+      </c>
       <c r="E111" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#房顶角板_资产包</t>
@@ -38949,40 +39015,44 @@
           <t>独立资产包；04_房顶模块</t>
         </is>
       </c>
-      <c r="G111" s="69" t="inlineStr"/>
+      <c r="G111" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/Base100UpperShell3D.gd</t>
+        </is>
+      </c>
       <c r="H111" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>开</t>
         </is>
       </c>
       <c r="I111" s="69" t="inlineStr">
         <is>
-          <t>独立包运行包装</t>
+          <t>Base100UpperShell3D</t>
         </is>
       </c>
       <c r="J111" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>BoxShape3D；由 Base100UpperShell3D._build_structure_collision() 生成 30×30 连续结构层代理，Prefab 自身不带碰撞节点（内嵌会与结构层重复阻挡）</t>
         </is>
       </c>
       <c r="K111" s="69" t="inlineStr">
         <is>
-          <t>5.000×5.000×0.300 m</t>
+          <t>5.000×5.000×0.300 m；2 个表面（骨架收口线脚 + 青绿大面）</t>
         </is>
       </c>
       <c r="L111" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
       <c r="M111" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / roof_corner</t>
+          <t>100F 24m 封顶 6×6 网格的 4 个角格</t>
         </is>
       </c>
       <c r="N111" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O111" s="69" t="inlineStr">
@@ -38992,7 +39062,8 @@
       </c>
       <c r="P111" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/04/roof_corner/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/04/roof_corner/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-20：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID。⚠️ 本件收口在**局部 +Z 与 -X 两侧**（不是对称角板），由 reference_assembly.json 四个角格的 rotation_z 反解验证：(min x,max z)→0° / (max x,max z)→+90° / (max x,min z)→180° / (min x,min z)→-90°。</t>
         </is>
       </c>
     </row>
@@ -40705,8 +40776,16 @@
           <t>房间实墙挂藤</t>
         </is>
       </c>
-      <c r="C136" s="69" t="inlineStr"/>
-      <c r="D136" s="69" t="inlineStr"/>
+      <c r="C136" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_room_wall_ivy_5x12.tscn</t>
+        </is>
+      </c>
+      <c r="D136" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_room_wall_ivy_top3d.glb</t>
+        </is>
+      </c>
       <c r="E136" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#房间实墙挂藤_资产包</t>
@@ -40717,7 +40796,7 @@
           <t>独立挂藤墙体变体</t>
         </is>
       </c>
-      <c r="G136" s="69" t="inlineStr"/>
+      <c r="G136" s="69" t="n"/>
       <c r="H136" s="69" t="inlineStr">
         <is>
           <t>未创建</t>
@@ -40725,32 +40804,32 @@
       </c>
       <c r="I136" s="69" t="inlineStr">
         <is>
-          <t>未来由Godot包装持有</t>
+          <t>Base100UpperShell3D</t>
         </is>
       </c>
       <c r="J136" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>Prefab 已声明 collision_owner；尚未在 100F 上层围护场景实例化</t>
         </is>
       </c>
       <c r="K136" s="69" t="inlineStr">
         <is>
-          <t>5.141×0.820×12.013 m</t>
+          <t>5.000×11.900×0.300 m（挂藤装饰在包络之内）</t>
         </is>
       </c>
       <c r="L136" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
       <c r="M136" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / room_wall_ivy</t>
+          <t>已制作并登记；100F 上层围护**未使用**（挂藤留给后续装饰批次）</t>
         </is>
       </c>
       <c r="N136" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O136" s="69" t="inlineStr">
@@ -40760,7 +40839,8 @@
       </c>
       <c r="P136" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_wall_ivy/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_wall_ivy/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-20：随房间墙体套件一并导出 GLB 并建立 prefab；本批场景未摆放。外墙植物包络不进入阻挡（沿用 v002 组件库口径）。</t>
         </is>
       </c>
     </row>
@@ -40775,8 +40855,16 @@
           <t>房间窗墙挂藤</t>
         </is>
       </c>
-      <c r="C137" s="69" t="inlineStr"/>
-      <c r="D137" s="69" t="inlineStr"/>
+      <c r="C137" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_room_window_ivy_5x12.tscn</t>
+        </is>
+      </c>
+      <c r="D137" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_room_window_ivy_top3d.glb</t>
+        </is>
+      </c>
       <c r="E137" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#房间窗墙挂藤_资产包</t>
@@ -40787,7 +40875,7 @@
           <t>独立挂藤墙体变体</t>
         </is>
       </c>
-      <c r="G137" s="69" t="inlineStr"/>
+      <c r="G137" s="69" t="n"/>
       <c r="H137" s="69" t="inlineStr">
         <is>
           <t>未创建</t>
@@ -40795,32 +40883,32 @@
       </c>
       <c r="I137" s="69" t="inlineStr">
         <is>
-          <t>未来由Godot包装持有</t>
+          <t>Base100UpperShell3D</t>
         </is>
       </c>
       <c r="J137" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>Prefab 已声明 collision_owner；尚未在 100F 上层围护场景实例化</t>
         </is>
       </c>
       <c r="K137" s="69" t="inlineStr">
         <is>
-          <t>5.000×0.770×12.018 m</t>
+          <t>5.000×11.900×0.300 m（挂藤装饰在包络之内）</t>
         </is>
       </c>
       <c r="L137" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
       <c r="M137" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / room_window_ivy</t>
+          <t>已制作并登记；100F 上层围护**未使用**</t>
         </is>
       </c>
       <c r="N137" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O137" s="69" t="inlineStr">
@@ -40830,7 +40918,8 @@
       </c>
       <c r="P137" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_window_ivy/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_window_ivy/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-20：随房间墙体套件一并导出 GLB 并建立 prefab；本批场景未摆放。</t>
         </is>
       </c>
     </row>
@@ -40845,8 +40934,16 @@
           <t>房间门洞墙挂藤</t>
         </is>
       </c>
-      <c r="C138" s="69" t="inlineStr"/>
-      <c r="D138" s="69" t="inlineStr"/>
+      <c r="C138" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_room_doorwall_ivy_5x12.tscn</t>
+        </is>
+      </c>
+      <c r="D138" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_room_doorwall_ivy_top3d.glb</t>
+        </is>
+      </c>
       <c r="E138" s="69" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#房间门洞墙挂藤_资产包</t>
@@ -40857,7 +40954,7 @@
           <t>独立挂藤墙体变体</t>
         </is>
       </c>
-      <c r="G138" s="69" t="inlineStr"/>
+      <c r="G138" s="69" t="n"/>
       <c r="H138" s="69" t="inlineStr">
         <is>
           <t>未创建</t>
@@ -40865,32 +40962,32 @@
       </c>
       <c r="I138" s="69" t="inlineStr">
         <is>
-          <t>未来由Godot包装持有</t>
+          <t>Base100UpperShell3D</t>
         </is>
       </c>
       <c r="J138" s="69" t="inlineStr">
         <is>
-          <t>未创建</t>
+          <t>Prefab 已声明 collision_owner；尚未在 100F 上层围护场景实例化</t>
         </is>
       </c>
       <c r="K138" s="69" t="inlineStr">
         <is>
-          <t>5.214×0.811×12.012 m</t>
+          <t>5.000×11.900×0.300 m；门洞净空 3.80×6.80 m</t>
         </is>
       </c>
       <c r="L138" s="69" t="inlineStr">
         <is>
-          <t>XY中心/底面0；-Y</t>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
       <c r="M138" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / room_doorwall_ivy</t>
+          <t>已制作并登记；100F 上层围护**未使用**</t>
         </is>
       </c>
       <c r="N138" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O138" s="69" t="inlineStr">
@@ -40900,7 +40997,8 @@
       </c>
       <c r="P138" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_doorwall_ivy/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/03/room_doorwall_ivy/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
+2026-09-20：随房间墙体套件一并导出 GLB 并建立 prefab；本批场景未摆放。</t>
         </is>
       </c>
     </row>
@@ -41299,6 +41397,160 @@
 实测 GLB 86228 B。
 父项=ENV-ROOFTOP-REF-PARAPET（同包络的派生件，不新增父库）。2026-09-19 新建。用户原话「墙壁帮我再blender里头制作3个变种，带有破损模型破损的，不同三种破损，但是需要能接起来，然后导入变成新的预制体后重新随机排列外墙」。派生做法：author_env_rooftop_parapet_damage_v001.py（headless Blender）把 intact 网格按「积木」拆成 22 块闭合倒角块（基座 + 0.036m 分隔带 + 10 块墙身 + 10 块压顶），只对与破损区相交的积木做**逐块**布尔剔料再合并。⚠️ 整件一次性布尔会静默吃掉 10 块墙身积木（512→272 顶点、4.52→1.25 m³、31.53 m² 面消失），且换个不接触的刀口也照样发生 —— 必须逐块做，这是本件最大的坑。拼接契约（用户要求的「能接起来」）：两端头带 |x|&gt;=2.05m 与 intact 件逐位相同（GLB 字节层已证：source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_bit_identical=true）、包络 5.00×0.50×1.80、原点底面中心均与 intact 件逐值相同 ⇒ 可沿任一边、任意顺序与原件 / 彼此对接，接头无缝、槽位相位不变。色盘：破损新面 UV 已钳回色盘色块（U 0.923..0.977 / V 0.123..0.477），材质仍是02_细腻哑光_青绿大面；.import 已绑 tools/asset_pipeline/scene_facility_shared_palette_post_import.gd，探针实测 palette_texture_bound=true。实测：Godot 探针 probe_rooftop_parapet_damage_prefabs 四件（intact + A/B/C）包络逐值相同、端头带点云最近邻最大距离 7.07e-5 m（0.07mm；源文件逐位相同，这点偏差来自 Godot 导入对近重合重复顶点的焊接，不是几何被改）。接线：TowerFloorStage3D.PARAPET_DAMAGE_SCENES + 静态纯函数 split_outer_parapet_damage()，按种子随机分档；种子 ROOFTOP_PARAPET_DAMAGE_SEED=20260919，每段受损概率 0.25（三档均分），可用 set_outer_damage_seed() 在 _ready 前覆盖。门禁：ROOFTOP_WEST_EXPANSION_CONTRACT_PASS（verify_rooftop_32x32_contract 新增 _verify_rooftop_parapet_damage：槽位数 61 = 64−门洞补位 3、四批次件数之和 == 槽位数、计划 == 摆放、破损比例 ∈[0.15,0.35]、换种子必换排布、非天台层整批完好）；反向对照已做（破损概率改 0 / 改 1 / 排布忽略种子三种改坏各自变红，脚本 _scratch/task14/reverse_control_parapet_damage.py）。另：本族不像直段那样登记《资产主表》（与 102/104 行口径一致）。
 2026-09-20：随直段降到 0.80m 并改 3 块式 base，破损配方同步重调（base_collapse 塌脚：墙身中段整体塌落成约 0.22m 残根、基座带被掏空，最重一档；端头带完整）。asset_version v001→v002；GLB 同路径覆盖重导（29,096 B）。实测：包络 5.0×0.80×0.50、端头带去重位置 72（与 intact 同）、点云双向最近邻 5.22e-5 m；source/verify_env_rooftop_parapet_damage_bands.py 输出 DMG_BANDS_OK band_id_identical=true height_m=0.80。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ENV-ROOFTOP-REF-ROOM-DOOR</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>房间门组件（门框+门垛）</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_room_door.tscn</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_room_door_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#门与暖灯_资产包（导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_ref_room_walls_v001.py）</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>厚石门洞的门框与门垛视觉；与 ENV-ROOFTOP-REF-ROOM-DOOR-LEAF 成对使用。门组件 = 门洞墙基准位 + 0.4175×外法线（沿 +Z 外移半个门洞墙厚 + 半板厚）</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>未创建</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Base100UpperShell3D</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Prefab 已声明 collision_owner；尚未在 100F 上层围护场景实例化</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>门洞净空 3.80×6.80 m；门垛各 0.60 m（外廓随基墙 5.000×11.900×0.300）</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>已制作并登记；100F 上层围护**未使用**（东门槽保留 base99 门墙与 RoomDoor3D）</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>2026-09-20 新建行（全新 AssetID）。来源：天台区块参考组件库 v002 的「门与暖灯_主体」（528 顶点焊接网格，含 22 个松散件）按 5 个制作件 AABB 无损二分：130 面 → 门扇、418 面 → 本件（门组件）。与门洞墙同位、无偏移。⚠️ 本房型门是静态关闭态（Base100UpperShell3D 的门洞只是洞，没有挂 RoomDoor3D）；若日后要做开合动画，必须改 RoomDoor3D 的全局常量TOWER_GEOMETRY.DOOR_CLEAR_*，不能只改本件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ENV-ROOFTOP-REF-ROOM-DOOR-LEAF</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>房间门扇（静态关闭态）</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>assets/art/props/dungeon_3d/prp_rooftop_room_door_leaf.tscn</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_room_door_leaf_top3d.glb</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#门与暖灯_资产包（导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_ref_room_walls_v001.py）</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>厚石门洞的单扇门板视觉；与 ENV-ROOFTOP-REF-ROOM-DOOR 成对；静态关闭态</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>未创建</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Base100UpperShell3D</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Prefab 已声明 collision_owner；尚未在 100F 上层围护场景实例化</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>板 3.680×6.800×0.180 m；可视包络厚 0.410 m</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>已制作并登记；100F 上层围护**未使用**</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>2026-09-20 新建行（全新 AssetID）。门扇板局部 z 中心已平移到 0（原点 = 底面中心），与门洞墙同位装配（不沿 +Z 偏移）；门组件才做 +0.4175×外法线偏移。3 个表面，共享色盘由 scene_facility_shared_palette_post_import.gd 绑定。本行不声明 open_mode：本房型门是静态关闭态；要做开合须改 RoomDoor3D 全局常量。</t>
         </is>
       </c>
     </row>
@@ -43614,37 +43866,37 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>v0.1.3</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>资产升版</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>关卡场景</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>天台女儿墙族由 1.80m 改为 0.80m（含压顶总高），并把 v002 的 22 块「密集竖杠」配方重建为方案A 平整墙板（三块式：基座带 + 墙板 + 压顶带）。用户原话「改成0.8米的，变体也要一起改，然后中间的竖杠太密了 不好看，横杆在两边即可」。重导 5 件 GLB 同路径覆盖：ENV-ROOFTOP-REF-PARAPET（v002→v003）、ENV-ROOFTOP-REF-PARAPET-OUTER（v002→v003）、ENV-ROOFTOP-REF-PARAPET-DMG-A/B/C（各 v001→v002）。TowerFloorStage3D.ROOFTOP_PARAPET_HEIGHT 1.80→0.80，碰撞高度与楼梯口矮墙缩放自动跟随；厚度 0.50m 不变，故四边/西侧碰撞位置与槽位相位不动。资产主表未增删行（本族只登记在《3D-场景通用》分页）；总览跨度不变。</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>AssetID 不变，只升版本；5 件 GLB 均为同路径覆盖重导，不新增文件；旧 v002 配方留档于 source/reference_components/v002（只读）。破损拼缝判据由「原始顶点数相等」改为「去重位置集合 + Hausdorff」，理由见 ENV-ROOFTOP-REF-PARAPET-DMG-B 行备注。</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>摩斯拉</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$240</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1163,22 +1163,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="50">
       <c r="A6" s="55">
-        <f>=COUNTA(资产主表!$A$6:$A$239)</f>
+        <f>=COUNTA(资产主表!$A$6:$A$240)</f>
         <v/>
       </c>
       <c r="B6" s="53" t="inlineStr"/>
       <c r="C6" s="55">
-        <f>=COUNTIF(资产主表!$K$6:$K$239,"已完成")+COUNTIF(资产主表!$K$6:$K$239,"原型已接入")+COUNTIF(资产主表!$K$6:$K$239,"正式美术已接入")+COUNTIF(资产主表!$K$6:$K$239,"已优化并正式接入")+COUNTIF(资产主表!$K$6:$K$239,"Blender源已完成")+COUNTIF(资产主表!$K$6:$K$239,"已导入；优化完成")</f>
+        <f>=COUNTIF(资产主表!$K$6:$K$240,"已完成")+COUNTIF(资产主表!$K$6:$K$240,"原型已接入")+COUNTIF(资产主表!$K$6:$K$240,"正式美术已接入")+COUNTIF(资产主表!$K$6:$K$240,"已优化并正式接入")+COUNTIF(资产主表!$K$6:$K$240,"Blender源已完成")+COUNTIF(资产主表!$K$6:$K$240,"已导入；优化完成")</f>
         <v/>
       </c>
       <c r="D6" s="53" t="inlineStr"/>
       <c r="E6" s="55">
-        <f>=COUNTIF(资产主表!$K$6:$K$239,"待制作")+COUNTIF(资产主表!$K$6:$K$239,"程序占位")</f>
+        <f>=COUNTIF(资产主表!$K$6:$K$240,"待制作")+COUNTIF(资产主表!$K$6:$K$240,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="53" t="inlineStr"/>
       <c r="G6" s="55">
-        <f>=COUNTIF(资产主表!$S$6:$S$239,"重复")</f>
+        <f>=COUNTIF(资产主表!$S$6:$S$240,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="53" t="inlineStr"/>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="B10" s="60">
-        <f>=COUNTIF(资产主表!$C$6:$C$239,A10)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$240,A10)</f>
         <v/>
       </c>
       <c r="C10" s="60">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$239=A10)*((资产主表!$K$6:$K$239="已完成")+(资产主表!$K$6:$K$239="原型已接入")+(资产主表!$K$6:$K$239="正式美术已接入")+(资产主表!$K$6:$K$239="已优化并正式接入")+(资产主表!$K$6:$K$239="Blender源已完成")+(资产主表!$K$6:$K$239="已导入；优化完成")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$240=A10)*((资产主表!$K$6:$K$240="已完成")+(资产主表!$K$6:$K$240="原型已接入")+(资产主表!$K$6:$K$240="正式美术已接入")+(资产主表!$K$6:$K$240="已优化并正式接入")+(资产主表!$K$6:$K$240="Blender源已完成")+(资产主表!$K$6:$K$240="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D10" s="60" t="inlineStr"/>
@@ -1269,11 +1269,11 @@
         </is>
       </c>
       <c r="B11" s="60">
-        <f>=COUNTIF(资产主表!$C$6:$C$239,A11)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$240,A11)</f>
         <v/>
       </c>
       <c r="C11" s="60">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$239=A11)*((资产主表!$K$6:$K$239="已完成")+(资产主表!$K$6:$K$239="原型已接入")+(资产主表!$K$6:$K$239="正式美术已接入")+(资产主表!$K$6:$K$239="已优化并正式接入")+(资产主表!$K$6:$K$239="Blender源已完成")+(资产主表!$K$6:$K$239="已导入；优化完成")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$240=A11)*((资产主表!$K$6:$K$240="已完成")+(资产主表!$K$6:$K$240="原型已接入")+(资产主表!$K$6:$K$240="正式美术已接入")+(资产主表!$K$6:$K$240="已优化并正式接入")+(资产主表!$K$6:$K$240="Blender源已完成")+(资产主表!$K$6:$K$240="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D11" s="60" t="inlineStr"/>
@@ -1291,11 +1291,11 @@
         </is>
       </c>
       <c r="B12" s="60">
-        <f>=COUNTIF(资产主表!$C$6:$C$239,A12)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$240,A12)</f>
         <v/>
       </c>
       <c r="C12" s="60">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$239=A12)*((资产主表!$K$6:$K$239="已完成")+(资产主表!$K$6:$K$239="原型已接入")+(资产主表!$K$6:$K$239="正式美术已接入")+(资产主表!$K$6:$K$239="已优化并正式接入")+(资产主表!$K$6:$K$239="Blender源已完成")+(资产主表!$K$6:$K$239="已导入；优化完成")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$240=A12)*((资产主表!$K$6:$K$240="已完成")+(资产主表!$K$6:$K$240="原型已接入")+(资产主表!$K$6:$K$240="正式美术已接入")+(资产主表!$K$6:$K$240="已优化并正式接入")+(资产主表!$K$6:$K$240="Blender源已完成")+(资产主表!$K$6:$K$240="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D12" s="60" t="inlineStr"/>
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y239"/>
+  <dimension ref="A1:Y240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="50" min="1" max="1"/>
@@ -2155,7 +2155,7 @@
         <v/>
       </c>
       <c r="S6" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="73" t="inlineStr"/>
@@ -2262,7 +2262,7 @@
         <v/>
       </c>
       <c r="S7" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="73" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="S8" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="73" t="inlineStr"/>
@@ -2476,7 +2476,7 @@
         <v/>
       </c>
       <c r="S9" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="73" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
         <v/>
       </c>
       <c r="S10" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="73" t="inlineStr"/>
@@ -2690,7 +2690,7 @@
         <v/>
       </c>
       <c r="S11" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="73" t="inlineStr"/>
@@ -2797,7 +2797,7 @@
         <v/>
       </c>
       <c r="S12" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="73" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         <v/>
       </c>
       <c r="S13" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="73" t="inlineStr"/>
@@ -3011,7 +3011,7 @@
         <v/>
       </c>
       <c r="S14" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="73" t="inlineStr"/>
@@ -3118,7 +3118,7 @@
         <v/>
       </c>
       <c r="S15" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="73" t="inlineStr"/>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="S16" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="73" t="inlineStr"/>
@@ -3332,7 +3332,7 @@
         <v/>
       </c>
       <c r="S17" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="73" t="inlineStr"/>
@@ -3439,7 +3439,7 @@
         <v/>
       </c>
       <c r="S18" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="73" t="inlineStr"/>
@@ -3546,7 +3546,7 @@
         <v/>
       </c>
       <c r="S19" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="73" t="inlineStr"/>
@@ -3653,7 +3653,7 @@
         <v/>
       </c>
       <c r="S20" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="73" t="inlineStr"/>
@@ -3760,7 +3760,7 @@
         <v/>
       </c>
       <c r="S21" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="73" t="inlineStr"/>
@@ -3867,7 +3867,7 @@
         <v/>
       </c>
       <c r="S22" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="73" t="inlineStr"/>
@@ -3974,7 +3974,7 @@
         <v/>
       </c>
       <c r="S23" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="73" t="inlineStr"/>
@@ -4081,7 +4081,7 @@
         <v/>
       </c>
       <c r="S24" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="73" t="inlineStr"/>
@@ -4188,7 +4188,7 @@
         <v/>
       </c>
       <c r="S25" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="73" t="inlineStr"/>
@@ -4295,7 +4295,7 @@
         <v/>
       </c>
       <c r="S26" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="73" t="inlineStr"/>
@@ -4402,7 +4402,7 @@
         <v/>
       </c>
       <c r="S27" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="73" t="inlineStr"/>
@@ -4509,7 +4509,7 @@
         <v/>
       </c>
       <c r="S28" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="73" t="inlineStr"/>
@@ -4616,7 +4616,7 @@
         <v/>
       </c>
       <c r="S29" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="73" t="inlineStr"/>
@@ -4723,7 +4723,7 @@
         <v/>
       </c>
       <c r="S30" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="73" t="inlineStr"/>
@@ -4830,7 +4830,7 @@
         <v/>
       </c>
       <c r="S31" s="73">
-        <f>IF(COUNTIF($R$6:$R$239,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="73" t="inlineStr"/>
@@ -4949,7 +4949,7 @@
         <v/>
       </c>
       <c r="S32" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="76" t="inlineStr">
@@ -5072,7 +5072,7 @@
         <v/>
       </c>
       <c r="S33" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="69" t="inlineStr">
@@ -5195,7 +5195,7 @@
         <v/>
       </c>
       <c r="S34" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="69" t="inlineStr">
@@ -5318,7 +5318,7 @@
         <v/>
       </c>
       <c r="S35" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="69" t="inlineStr">
@@ -5441,7 +5441,7 @@
         <v/>
       </c>
       <c r="S36" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="76" t="inlineStr">
@@ -5565,7 +5565,7 @@
         <v/>
       </c>
       <c r="S37" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="69" t="inlineStr">
@@ -5688,7 +5688,7 @@
         <v/>
       </c>
       <c r="S38" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="69" t="inlineStr">
@@ -5807,7 +5807,7 @@
         <v/>
       </c>
       <c r="S39" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="76" t="inlineStr">
@@ -5930,7 +5930,7 @@
         <v/>
       </c>
       <c r="S40" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="69" t="inlineStr">
@@ -6053,7 +6053,7 @@
         <v/>
       </c>
       <c r="S41" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="69" t="inlineStr">
@@ -6176,7 +6176,7 @@
         <v/>
       </c>
       <c r="S42" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="69" t="inlineStr">
@@ -6299,7 +6299,7 @@
         <v/>
       </c>
       <c r="S43" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="69" t="inlineStr">
@@ -6422,7 +6422,7 @@
         <v/>
       </c>
       <c r="S44" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="76" t="inlineStr">
@@ -6546,7 +6546,7 @@
         <v/>
       </c>
       <c r="S45" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="69" t="inlineStr">
@@ -6669,7 +6669,7 @@
         <v/>
       </c>
       <c r="S46" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="69" t="inlineStr">
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="S47" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="69" t="inlineStr">
@@ -6915,7 +6915,7 @@
         <v/>
       </c>
       <c r="S48" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R48)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R48)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T48" s="69" t="inlineStr">
@@ -7035,7 +7035,7 @@
         <v/>
       </c>
       <c r="S49" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R49)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R49)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T49" s="69" t="inlineStr">
@@ -7158,7 +7158,7 @@
         <v/>
       </c>
       <c r="S50" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R50)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R50)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T50" s="69" t="inlineStr">
@@ -7282,7 +7282,7 @@
         <v/>
       </c>
       <c r="S51" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R51)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R51)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T51" s="69" t="inlineStr">
@@ -7405,7 +7405,7 @@
         <v/>
       </c>
       <c r="S52" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R52)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R52)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T52" s="76" t="inlineStr">
@@ -7529,7 +7529,7 @@
         <v/>
       </c>
       <c r="S53" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R53)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R53)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T53" s="76" t="inlineStr">
@@ -7652,7 +7652,7 @@
         <v/>
       </c>
       <c r="S54" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R54)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R54)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T54" s="76" t="inlineStr">
@@ -7778,7 +7778,7 @@
         <v/>
       </c>
       <c r="S55" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R55)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R55)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T55" s="76" t="inlineStr">
@@ -7905,7 +7905,7 @@
         <v/>
       </c>
       <c r="S56" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R56)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R56)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T56" s="76" t="inlineStr">
@@ -8028,7 +8028,7 @@
         <v/>
       </c>
       <c r="S57" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R57)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R57)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T57" s="76" t="inlineStr">
@@ -8153,7 +8153,7 @@
         <v/>
       </c>
       <c r="S58" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R58)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R58)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T58" s="76" t="inlineStr">
@@ -8276,7 +8276,7 @@
         <v/>
       </c>
       <c r="S59" s="76">
-        <f>IF(COUNTIF($R$6:$R$239,R59)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R59)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T59" s="76" t="inlineStr">
@@ -8395,7 +8395,7 @@
         <v/>
       </c>
       <c r="S60" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R60)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R60)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T60" s="69" t="inlineStr">
@@ -8515,7 +8515,7 @@
         <v/>
       </c>
       <c r="S61" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R61)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R61)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T61" s="69" t="inlineStr">
@@ -8635,7 +8635,7 @@
         <v/>
       </c>
       <c r="S62" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R62)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R62)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T62" s="69" t="inlineStr">
@@ -8755,7 +8755,7 @@
         <v/>
       </c>
       <c r="S63" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R63)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R63)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T63" s="69" t="inlineStr"/>
@@ -8875,7 +8875,7 @@
         <v/>
       </c>
       <c r="S64" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R64)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R64)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T64" s="69" t="inlineStr">
@@ -9000,7 +9000,7 @@
         <v/>
       </c>
       <c r="S65" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R65)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R65)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T65" s="69" t="inlineStr">
@@ -9125,7 +9125,7 @@
         <v/>
       </c>
       <c r="S66" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R66)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R66)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T66" s="69" t="inlineStr">
@@ -9250,7 +9250,7 @@
         <v/>
       </c>
       <c r="S67" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R67)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R67)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T67" s="69" t="inlineStr">
@@ -9375,7 +9375,7 @@
         <v/>
       </c>
       <c r="S68" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R68)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R68)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T68" s="69" t="inlineStr">
@@ -9506,7 +9506,7 @@
         <v/>
       </c>
       <c r="S69" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R69)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R69)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T69" s="69" t="inlineStr">
@@ -9632,7 +9632,7 @@
         <v/>
       </c>
       <c r="S70" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R70)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R70)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T70" s="69" t="inlineStr">
@@ -9756,7 +9756,7 @@
         <v/>
       </c>
       <c r="S71" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R71)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R71)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T71" s="69" t="inlineStr">
@@ -9880,7 +9880,7 @@
         <v/>
       </c>
       <c r="S72" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R72)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R72)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T72" s="69" t="inlineStr">
@@ -10004,7 +10004,7 @@
         <v/>
       </c>
       <c r="S73" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R73)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R73)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T73" s="69" t="inlineStr">
@@ -10128,7 +10128,7 @@
         <v/>
       </c>
       <c r="S74" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R74)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R74)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T74" s="69" t="inlineStr">
@@ -10252,7 +10252,7 @@
         <v/>
       </c>
       <c r="S75" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R75)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R75)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T75" s="69" t="inlineStr">
@@ -10376,7 +10376,7 @@
         <v/>
       </c>
       <c r="S76" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R76)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R76)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T76" s="69" t="inlineStr">
@@ -10500,7 +10500,7 @@
         <v/>
       </c>
       <c r="S77" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R77)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R77)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T77" s="69" t="inlineStr">
@@ -10624,7 +10624,7 @@
         <v/>
       </c>
       <c r="S78" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R78)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R78)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T78" s="69" t="inlineStr">
@@ -10748,7 +10748,7 @@
         <v/>
       </c>
       <c r="S79" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R79)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R79)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T79" s="69" t="inlineStr">
@@ -10872,7 +10872,7 @@
         <v/>
       </c>
       <c r="S80" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R80)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R80)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T80" s="69" t="inlineStr">
@@ -10996,7 +10996,7 @@
         <v/>
       </c>
       <c r="S81" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R81)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R81)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T81" s="69" t="inlineStr">
@@ -11120,7 +11120,7 @@
         <v/>
       </c>
       <c r="S82" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R82)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R82)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T82" s="69" t="inlineStr">
@@ -11244,7 +11244,7 @@
         <v/>
       </c>
       <c r="S83" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R83)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R83)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T83" s="69" t="inlineStr">
@@ -11368,7 +11368,7 @@
         <v/>
       </c>
       <c r="S84" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R84)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R84)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T84" s="69" t="inlineStr">
@@ -11492,7 +11492,7 @@
         <v/>
       </c>
       <c r="S85" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R85)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R85)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T85" s="69" t="inlineStr">
@@ -11616,7 +11616,7 @@
         <v/>
       </c>
       <c r="S86" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R86)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R86)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T86" s="69" t="inlineStr">
@@ -11740,7 +11740,7 @@
         <v/>
       </c>
       <c r="S87" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R87)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R87)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T87" s="69" t="inlineStr">
@@ -11864,7 +11864,7 @@
         <v/>
       </c>
       <c r="S88" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R88)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R88)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T88" s="69" t="inlineStr">
@@ -11988,7 +11988,7 @@
         <v/>
       </c>
       <c r="S89" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R89)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R89)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T89" s="69" t="inlineStr">
@@ -12112,7 +12112,7 @@
         <v/>
       </c>
       <c r="S90" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R90)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R90)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T90" s="69" t="inlineStr">
@@ -12236,7 +12236,7 @@
         <v/>
       </c>
       <c r="S91" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R91)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R91)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T91" s="69" t="inlineStr">
@@ -12360,7 +12360,7 @@
         <v/>
       </c>
       <c r="S92" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R92)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R92)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T92" s="69" t="inlineStr">
@@ -12484,7 +12484,7 @@
         <v/>
       </c>
       <c r="S93" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R93)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R93)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T93" s="69" t="inlineStr">
@@ -12608,7 +12608,7 @@
         <v/>
       </c>
       <c r="S94" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R94)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R94)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T94" s="69" t="inlineStr">
@@ -12732,7 +12732,7 @@
         <v/>
       </c>
       <c r="S95" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R95)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R95)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T95" s="69" t="inlineStr">
@@ -12856,7 +12856,7 @@
         <v/>
       </c>
       <c r="S96" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R96)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R96)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T96" s="69" t="inlineStr">
@@ -12980,7 +12980,7 @@
         <v/>
       </c>
       <c r="S97" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R97)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R97)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T97" s="69" t="inlineStr">
@@ -13104,7 +13104,7 @@
         <v/>
       </c>
       <c r="S98" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R98)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R98)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T98" s="69" t="inlineStr">
@@ -13228,7 +13228,7 @@
         <v/>
       </c>
       <c r="S99" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R99)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R99)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T99" s="69" t="inlineStr">
@@ -13352,7 +13352,7 @@
         <v/>
       </c>
       <c r="S100" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R100)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R100)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T100" s="69" t="inlineStr">
@@ -13476,7 +13476,7 @@
         <v/>
       </c>
       <c r="S101" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R101)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R101)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T101" s="69" t="inlineStr">
@@ -13600,7 +13600,7 @@
         <v/>
       </c>
       <c r="S102" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R102)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R102)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T102" s="69" t="inlineStr">
@@ -13723,7 +13723,7 @@
         <v/>
       </c>
       <c r="S103" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R103)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R103)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T103" s="69" t="inlineStr">
@@ -13848,7 +13848,7 @@
         <v/>
       </c>
       <c r="S104" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R104)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R104)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T104" s="69" t="inlineStr">
@@ -13973,7 +13973,7 @@
         <v/>
       </c>
       <c r="S105" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R105)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R105)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T105" s="69" t="inlineStr">
@@ -14098,7 +14098,7 @@
         <v/>
       </c>
       <c r="S106" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R106)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R106)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T106" s="69" t="inlineStr">
@@ -14223,7 +14223,7 @@
         <v/>
       </c>
       <c r="S107" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R107)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R107)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T107" s="69" t="inlineStr">
@@ -14348,7 +14348,7 @@
         <v/>
       </c>
       <c r="S108" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R108)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R108)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T108" s="79" t="inlineStr">
@@ -14474,7 +14474,7 @@
         <v/>
       </c>
       <c r="S109" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R109)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R109)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T109" s="69" t="inlineStr">
@@ -14600,7 +14600,7 @@
         <v/>
       </c>
       <c r="S110" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R110)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R110)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T110" s="69" t="inlineStr">
@@ -14726,7 +14726,7 @@
         <v/>
       </c>
       <c r="S111" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R111)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R111)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T111" s="69" t="inlineStr">
@@ -14852,7 +14852,7 @@
         <v/>
       </c>
       <c r="S112" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R112)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R112)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T112" s="69" t="inlineStr">
@@ -14975,7 +14975,7 @@
         <v/>
       </c>
       <c r="S113" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R113)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R113)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T113" s="69" t="inlineStr">
@@ -15095,7 +15095,7 @@
         <v/>
       </c>
       <c r="S114" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R114)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R114)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T114" s="79" t="inlineStr">
@@ -15214,7 +15214,7 @@
         <v/>
       </c>
       <c r="S115" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R115)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R115)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T115" s="79" t="inlineStr">
@@ -15332,7 +15332,7 @@
         <v/>
       </c>
       <c r="S116" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R116)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R116)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T116" s="79" t="inlineStr">
@@ -15455,7 +15455,7 @@
         <v/>
       </c>
       <c r="S117" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R117)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R117)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T117" s="69" t="inlineStr">
@@ -15581,7 +15581,7 @@
         <v/>
       </c>
       <c r="S118" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R118)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R118)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T118" s="69" t="inlineStr">
@@ -15704,7 +15704,7 @@
         <v/>
       </c>
       <c r="S119" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R119)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R119)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T119" s="69" t="inlineStr">
@@ -15829,7 +15829,7 @@
         <v/>
       </c>
       <c r="S120" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R120)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R120)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T120" s="69" t="inlineStr">
@@ -15952,7 +15952,7 @@
         <v/>
       </c>
       <c r="S121" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R121)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R121)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T121" s="69" t="inlineStr">
@@ -16077,7 +16077,7 @@
         <v/>
       </c>
       <c r="S122" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R122)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R122)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T122" s="69" t="inlineStr">
@@ -16200,7 +16200,7 @@
         <v/>
       </c>
       <c r="S123" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R123)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R123)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T123" s="69" t="inlineStr">
@@ -16323,7 +16323,7 @@
         <v/>
       </c>
       <c r="S124" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R124)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R124)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T124" s="69" t="inlineStr">
@@ -16446,7 +16446,7 @@
         <v/>
       </c>
       <c r="S125" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R125)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R125)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T125" s="69" t="inlineStr">
@@ -16569,7 +16569,7 @@
         <v/>
       </c>
       <c r="S126" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R126)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R126)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T126" s="69" t="inlineStr">
@@ -16692,7 +16692,7 @@
         <v/>
       </c>
       <c r="S127" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R127)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R127)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T127" s="69" t="inlineStr">
@@ -16815,7 +16815,7 @@
         <v/>
       </c>
       <c r="S128" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R128)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R128)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T128" s="69" t="inlineStr">
@@ -16938,7 +16938,7 @@
         <v/>
       </c>
       <c r="S129" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R129)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R129)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T129" s="69" t="inlineStr">
@@ -17061,7 +17061,7 @@
         <v/>
       </c>
       <c r="S130" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R130)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R130)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T130" s="69" t="inlineStr">
@@ -17184,7 +17184,7 @@
         <v/>
       </c>
       <c r="S131" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R131)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R131)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T131" s="69" t="inlineStr">
@@ -17307,7 +17307,7 @@
         <v/>
       </c>
       <c r="S132" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R132)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R132)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T132" s="69" t="inlineStr">
@@ -17431,7 +17431,7 @@
         <v/>
       </c>
       <c r="S133" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R133)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R133)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T133" s="69" t="inlineStr">
@@ -17554,7 +17554,7 @@
         <v/>
       </c>
       <c r="S134" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R134)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R134)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T134" s="69" t="inlineStr">
@@ -17677,7 +17677,7 @@
         <v/>
       </c>
       <c r="S135" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R135)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R135)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T135" s="69" t="inlineStr">
@@ -17803,7 +17803,7 @@
         <v/>
       </c>
       <c r="S136" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R136)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R136)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T136" s="69" t="inlineStr">
@@ -17929,7 +17929,7 @@
         <v/>
       </c>
       <c r="S137" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R137)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R137)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T137" s="69" t="inlineStr">
@@ -18055,7 +18055,7 @@
         <v/>
       </c>
       <c r="S138" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R138)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R138)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T138" s="69" t="inlineStr">
@@ -18181,7 +18181,7 @@
         <v/>
       </c>
       <c r="S139" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R139)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R139)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T139" s="69" t="inlineStr">
@@ -18307,7 +18307,7 @@
         <v/>
       </c>
       <c r="S140" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R140)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R140)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T140" s="69" t="inlineStr">
@@ -18433,7 +18433,7 @@
         <v/>
       </c>
       <c r="S141" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R141)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R141)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T141" s="69" t="inlineStr">
@@ -18559,7 +18559,7 @@
         <v/>
       </c>
       <c r="S142" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R142)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R142)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T142" s="69" t="inlineStr">
@@ -18685,7 +18685,7 @@
         <v/>
       </c>
       <c r="S143" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R143)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R143)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T143" s="69" t="inlineStr">
@@ -18811,7 +18811,7 @@
         <v/>
       </c>
       <c r="S144" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R144)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R144)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T144" s="69" t="inlineStr">
@@ -18937,7 +18937,7 @@
         <v/>
       </c>
       <c r="S145" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R145)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R145)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T145" s="69" t="inlineStr">
@@ -19063,7 +19063,7 @@
         <v/>
       </c>
       <c r="S146" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R146)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R146)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T146" s="69" t="inlineStr">
@@ -19189,7 +19189,7 @@
         <v/>
       </c>
       <c r="S147" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R147)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R147)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T147" s="69" t="inlineStr">
@@ -19315,7 +19315,7 @@
         <v/>
       </c>
       <c r="S148" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R148)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R148)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T148" s="69" t="inlineStr">
@@ -19441,7 +19441,7 @@
         <v/>
       </c>
       <c r="S149" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R149)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R149)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T149" s="69" t="inlineStr">
@@ -19567,7 +19567,7 @@
         <v/>
       </c>
       <c r="S150" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R150)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R150)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T150" s="69" t="inlineStr">
@@ -19693,7 +19693,7 @@
         <v/>
       </c>
       <c r="S151" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R151)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R151)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T151" s="69" t="inlineStr">
@@ -19819,7 +19819,7 @@
         <v/>
       </c>
       <c r="S152" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R152)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R152)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T152" s="69" t="inlineStr">
@@ -19945,7 +19945,7 @@
         <v/>
       </c>
       <c r="S153" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R153)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R153)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T153" s="69" t="inlineStr">
@@ -20071,7 +20071,7 @@
         <v/>
       </c>
       <c r="S154" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R154)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R154)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T154" s="69" t="inlineStr">
@@ -20197,7 +20197,7 @@
         <v/>
       </c>
       <c r="S155" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R155)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R155)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T155" s="69" t="inlineStr">
@@ -20323,7 +20323,7 @@
         <v/>
       </c>
       <c r="S156" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R156)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R156)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T156" s="69" t="inlineStr">
@@ -20449,7 +20449,7 @@
         <v/>
       </c>
       <c r="S157" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R157)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R157)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T157" s="69" t="inlineStr">
@@ -20575,7 +20575,7 @@
         <v/>
       </c>
       <c r="S158" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R158)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R158)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T158" s="69" t="inlineStr">
@@ -20701,7 +20701,7 @@
         <v/>
       </c>
       <c r="S159" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R159)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R159)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T159" s="69" t="inlineStr">
@@ -20827,7 +20827,7 @@
         <v/>
       </c>
       <c r="S160" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R160)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R160)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T160" s="69" t="inlineStr">
@@ -20953,7 +20953,7 @@
         <v/>
       </c>
       <c r="S161" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R161)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R161)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T161" s="69" t="inlineStr">
@@ -21079,7 +21079,7 @@
         <v/>
       </c>
       <c r="S162" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R162)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R162)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T162" s="69" t="inlineStr">
@@ -21205,7 +21205,7 @@
         <v/>
       </c>
       <c r="S163" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R163)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R163)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T163" s="69" t="inlineStr">
@@ -21331,7 +21331,7 @@
         <v/>
       </c>
       <c r="S164" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R164)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R164)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T164" s="69" t="inlineStr">
@@ -21457,7 +21457,7 @@
         <v/>
       </c>
       <c r="S165" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R165)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R165)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T165" s="69" t="inlineStr">
@@ -21583,7 +21583,7 @@
         <v/>
       </c>
       <c r="S166" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R166)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R166)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T166" s="69" t="inlineStr">
@@ -21709,7 +21709,7 @@
         <v/>
       </c>
       <c r="S167" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R167)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R167)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T167" s="69" t="inlineStr">
@@ -21835,7 +21835,7 @@
         <v/>
       </c>
       <c r="S168" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R168)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R168)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T168" s="69" t="inlineStr">
@@ -21961,7 +21961,7 @@
         <v/>
       </c>
       <c r="S169" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R169)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R169)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T169" s="69" t="inlineStr">
@@ -22087,7 +22087,7 @@
         <v/>
       </c>
       <c r="S170" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R170)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R170)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T170" s="69" t="inlineStr">
@@ -22213,7 +22213,7 @@
         <v/>
       </c>
       <c r="S171" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R171)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R171)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T171" s="69" t="inlineStr">
@@ -22336,7 +22336,7 @@
         <v/>
       </c>
       <c r="S172" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R172)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R172)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T172" s="69" t="inlineStr">
@@ -22459,7 +22459,7 @@
         <v/>
       </c>
       <c r="S173" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R173)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R173)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T173" s="69" t="inlineStr">
@@ -22583,7 +22583,7 @@
         <v/>
       </c>
       <c r="S174" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R174)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R174)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T174" s="69" t="inlineStr">
@@ -22707,7 +22707,7 @@
         <v/>
       </c>
       <c r="S175" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R175)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R175)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T175" s="69" t="inlineStr">
@@ -22831,7 +22831,7 @@
         <v/>
       </c>
       <c r="S176" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R176)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R176)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T176" s="69" t="inlineStr">
@@ -22955,7 +22955,7 @@
         <v/>
       </c>
       <c r="S177" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R177)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R177)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T177" s="69" t="inlineStr">
@@ -23079,7 +23079,7 @@
         <v/>
       </c>
       <c r="S178" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R178)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R178)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T178" s="69" t="inlineStr">
@@ -23204,7 +23204,7 @@
         <v/>
       </c>
       <c r="S179" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R179)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R179)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T179" s="69" t="inlineStr">
@@ -23327,7 +23327,7 @@
         <v/>
       </c>
       <c r="S180" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R180)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R180)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T180" s="69" t="inlineStr">
@@ -23451,7 +23451,7 @@
         <v/>
       </c>
       <c r="S181" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R181)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R181)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T181" s="69" t="inlineStr">
@@ -23574,7 +23574,7 @@
         <v/>
       </c>
       <c r="S182" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R182)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R182)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T182" s="69" t="inlineStr">
@@ -23697,7 +23697,7 @@
         <v/>
       </c>
       <c r="S183" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R183)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R183)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T183" s="69" t="inlineStr">
@@ -23821,7 +23821,7 @@
         <v/>
       </c>
       <c r="S184" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R184)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R184)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T184" s="69" t="inlineStr">
@@ -23946,7 +23946,7 @@
         <v/>
       </c>
       <c r="S185" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R185)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R185)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T185" s="69" t="inlineStr">
@@ -24070,7 +24070,7 @@
         <v/>
       </c>
       <c r="S186" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R186)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R186)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T186" s="69" t="inlineStr">
@@ -24194,7 +24194,7 @@
         <v/>
       </c>
       <c r="S187" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R187)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R187)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T187" s="69" t="inlineStr">
@@ -24318,7 +24318,7 @@
         <v/>
       </c>
       <c r="S188" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R188)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R188)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T188" s="69" t="inlineStr">
@@ -24442,7 +24442,7 @@
         <v/>
       </c>
       <c r="S189" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R189)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R189)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T189" s="69" t="inlineStr">
@@ -24566,7 +24566,7 @@
         <v/>
       </c>
       <c r="S190" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R190)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R190)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T190" s="69" t="inlineStr">
@@ -24690,7 +24690,7 @@
         <v/>
       </c>
       <c r="S191" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R191)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R191)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T191" s="69" t="inlineStr">
@@ -24813,7 +24813,7 @@
         <v/>
       </c>
       <c r="S192" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R192)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R192)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T192" s="69" t="inlineStr">
@@ -24937,7 +24937,7 @@
         <v/>
       </c>
       <c r="S193" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R193)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R193)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T193" s="69" t="inlineStr">
@@ -25060,7 +25060,7 @@
         <v/>
       </c>
       <c r="S194" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R194)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R194)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T194" s="69" t="inlineStr">
@@ -25183,7 +25183,7 @@
         <v/>
       </c>
       <c r="S195" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R195)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R195)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T195" s="69" t="inlineStr">
@@ -25307,7 +25307,7 @@
         <v/>
       </c>
       <c r="S196" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R196)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R196)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T196" s="69" t="inlineStr">
@@ -25430,7 +25430,7 @@
         <v/>
       </c>
       <c r="S197" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R197)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R197)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T197" s="69" t="inlineStr">
@@ -25553,7 +25553,7 @@
         <v/>
       </c>
       <c r="S198" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R198)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R198)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T198" s="69" t="inlineStr">
@@ -25676,7 +25676,7 @@
         <v/>
       </c>
       <c r="S199" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R199)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R199)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T199" s="69" t="inlineStr">
@@ -25799,7 +25799,7 @@
         <v/>
       </c>
       <c r="S200" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R200)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R200)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T200" s="69" t="inlineStr">
@@ -25922,7 +25922,7 @@
         <v/>
       </c>
       <c r="S201" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R201)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R201)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T201" s="69" t="inlineStr">
@@ -26045,7 +26045,7 @@
         <v/>
       </c>
       <c r="S202" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R202)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R202)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T202" s="69" t="inlineStr">
@@ -26168,7 +26168,7 @@
         <v/>
       </c>
       <c r="S203" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R203)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R203)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T203" s="69" t="inlineStr">
@@ -26291,7 +26291,7 @@
         <v/>
       </c>
       <c r="S204" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R204)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R204)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T204" s="69" t="inlineStr">
@@ -26415,7 +26415,7 @@
         <v/>
       </c>
       <c r="S205" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R205)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R205)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T205" s="69" t="inlineStr">
@@ -26539,7 +26539,7 @@
         <v/>
       </c>
       <c r="S206" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R206)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R206)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T206" s="69" t="inlineStr">
@@ -26662,7 +26662,7 @@
         <v/>
       </c>
       <c r="S207" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R207)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R207)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T207" s="69" t="inlineStr">
@@ -26785,7 +26785,7 @@
         <v/>
       </c>
       <c r="S208" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R208)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R208)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T208" s="69" t="inlineStr">
@@ -26908,7 +26908,7 @@
         <v/>
       </c>
       <c r="S209" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R209)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R209)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T209" s="69" t="inlineStr">
@@ -27031,7 +27031,7 @@
         <v/>
       </c>
       <c r="S210" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R210)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R210)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T210" s="69" t="inlineStr">
@@ -27154,7 +27154,7 @@
         <v/>
       </c>
       <c r="S211" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R211)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R211)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T211" s="69" t="inlineStr">
@@ -27277,7 +27277,7 @@
         <v/>
       </c>
       <c r="S212" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R212)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R212)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T212" s="69" t="inlineStr">
@@ -27400,7 +27400,7 @@
         <v/>
       </c>
       <c r="S213" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R213)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R213)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T213" s="69" t="inlineStr">
@@ -27523,7 +27523,7 @@
         <v/>
       </c>
       <c r="S214" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R214)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R214)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T214" s="69" t="inlineStr">
@@ -27646,7 +27646,7 @@
         <v/>
       </c>
       <c r="S215" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R215)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R215)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T215" s="69" t="inlineStr">
@@ -27769,7 +27769,7 @@
         <v/>
       </c>
       <c r="S216" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R216)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R216)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T216" s="69" t="inlineStr">
@@ -27892,7 +27892,7 @@
         <v/>
       </c>
       <c r="S217" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R217)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R217)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T217" s="69" t="inlineStr">
@@ -28016,7 +28016,7 @@
         <v/>
       </c>
       <c r="S218" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R218)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R218)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T218" s="69" t="inlineStr">
@@ -28139,7 +28139,7 @@
         <v/>
       </c>
       <c r="S219" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R219)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R219)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T219" s="69" t="inlineStr">
@@ -28262,7 +28262,7 @@
         <v/>
       </c>
       <c r="S220" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R220)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R220)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T220" s="69" t="inlineStr">
@@ -28385,7 +28385,7 @@
         <v/>
       </c>
       <c r="S221" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R221)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R221)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T221" s="69" t="inlineStr">
@@ -28508,7 +28508,7 @@
         <v/>
       </c>
       <c r="S222" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R222)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R222)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T222" s="69" t="inlineStr">
@@ -28631,7 +28631,7 @@
         <v/>
       </c>
       <c r="S223" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R223)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R223)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T223" s="69" t="inlineStr">
@@ -28754,7 +28754,7 @@
         <v/>
       </c>
       <c r="S224" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R224)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R224)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T224" s="69" t="inlineStr">
@@ -28877,7 +28877,7 @@
         <v/>
       </c>
       <c r="S225" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R225)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R225)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T225" s="69" t="inlineStr">
@@ -29000,7 +29000,7 @@
         <v/>
       </c>
       <c r="S226" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R226)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R226)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T226" s="69" t="inlineStr">
@@ -29123,7 +29123,7 @@
         <v/>
       </c>
       <c r="S227" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R227)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R227)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T227" s="69" t="inlineStr">
@@ -29246,7 +29246,7 @@
         <v/>
       </c>
       <c r="S228" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R228)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R228)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T228" s="69" t="inlineStr">
@@ -29369,7 +29369,7 @@
         <v/>
       </c>
       <c r="S229" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R229)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R229)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T229" s="69" t="inlineStr">
@@ -29492,7 +29492,7 @@
         <v/>
       </c>
       <c r="S230" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R230)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R230)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T230" s="69" t="inlineStr">
@@ -29616,7 +29616,7 @@
         <v/>
       </c>
       <c r="S231" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R231)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R231)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T231" s="79" t="inlineStr">
@@ -29739,7 +29739,7 @@
         <v/>
       </c>
       <c r="S232" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R232)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R232)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T232" s="79" t="inlineStr">
@@ -29859,7 +29859,7 @@
         <v/>
       </c>
       <c r="S233" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R233)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R233)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U233" s="79" t="inlineStr">
@@ -29974,7 +29974,7 @@
         <v/>
       </c>
       <c r="S234" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R234)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R234)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U234" s="79" t="inlineStr">
@@ -30089,7 +30089,7 @@
         <v/>
       </c>
       <c r="S235" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R235)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R235)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U235" s="79" t="inlineStr">
@@ -30204,7 +30204,7 @@
         <v/>
       </c>
       <c r="S236" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R236)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R236)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U236" s="79" t="inlineStr">
@@ -30319,7 +30319,7 @@
         <v/>
       </c>
       <c r="S237" s="79">
-        <f>IF(COUNTIF($R$6:$R$239,R237)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R237)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U237" s="79" t="inlineStr">
@@ -30392,7 +30392,7 @@
       </c>
       <c r="J238" s="69" t="inlineStr">
         <is>
-          <t>100F独立组件制作；未接入运行场景</t>
+          <t>100F独立组件制作；装饰件已按布局接入运行场景</t>
         </is>
       </c>
       <c r="K238" s="69" t="inlineStr">
@@ -30412,7 +30412,7 @@
       </c>
       <c r="N238" s="69" t="inlineStr">
         <is>
-          <t>44包 / 45输出网格 / 4材质</t>
+          <t>47包 / 4共享材质；女儿墙方案A 0.80m；17件已导出（含12件装饰接入）</t>
         </is>
       </c>
       <c r="O238" s="69" t="inlineStr">
@@ -30427,7 +30427,7 @@
       </c>
       <c r="Q238" s="69" t="inlineStr">
         <is>
-          <t>天台;屋顶;女儿墙;外墙;空调;管道;藤蔓</t>
+          <t>天台;屋顶;女儿墙;外墙;空调;管道;藤蔓;女儿墙挂藤</t>
         </is>
       </c>
       <c r="R238" s="69">
@@ -30435,12 +30435,12 @@
         <v/>
       </c>
       <c r="S238" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R238)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R238)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T238" s="69" t="inlineStr">
         <is>
-          <t>ca091c6dec5ac3dc0c63b4e3b28a84934d78d685656388c882087c1a9b9b966e</t>
+          <t>d9e96fa13e39e4e11abaef6c59b7d6211e9c616717a5ca59488c959dda31cc0a</t>
         </is>
       </c>
       <c r="U238" s="69" t="inlineStr">
@@ -30449,7 +30449,7 @@
         </is>
       </c>
       <c r="V238" s="69" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="W238" s="69" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
       </c>
       <c r="Y238" s="69" t="inlineStr">
         <is>
-          <t>v002新增7个挂藤变体；门口加厚并保持门扇尺寸；其余36包源/输出几何及变换签名一致；未导入Godot。</t>
+          <t>2026-09-20 女儿墙 1.80m→0.80m（方案A平整墙板）写回主库，三件破损变种入 02_女儿墙；2026-09-21 组件库升至 47 包；11 类装饰（空调/通风口/水管/藤蔓/花圃盆栽）导出 GLB 并接入 100F 装饰布局。 2026-09-21 二次修正：装饰接入增至 12 类（新增「女儿墙挂藤」，7×01_女儿墙 包），导出件 16 → 17。</t>
         </is>
       </c>
     </row>
@@ -30558,7 +30558,7 @@
         <v/>
       </c>
       <c r="S239" s="69">
-        <f>IF(COUNTIF($R$6:$R$239,R239)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$240,R239)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T239" s="69" t="inlineStr">
@@ -30590,28 +30590,146 @@
         </is>
       </c>
     </row>
-    <row r="240" ht="255" customHeight="1" s="50"/>
+    <row r="240" ht="255" customHeight="1" s="50">
+      <c r="A240" s="69" t="inlineStr">
+        <is>
+          <t>ENV-ROOFTOP-DECOR-LAYOUT-100F</t>
+        </is>
+      </c>
+      <c r="B240" s="69" t="inlineStr">
+        <is>
+          <t>100F天台装饰布局</t>
+        </is>
+      </c>
+      <c r="C240" s="69" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="D240" s="69" t="inlineStr">
+        <is>
+          <t>environment_layout_3d</t>
+        </is>
+      </c>
+      <c r="E240" s="69" t="inlineStr">
+        <is>
+          <t>rooftop_100f_decorated_layout</t>
+        </is>
+      </c>
+      <c r="F240" s="69" t="inlineStr">
+        <is>
+          <t>root_3d</t>
+        </is>
+      </c>
+      <c r="G240" s="69" t="n"/>
+      <c r="H240" s="69" t="inlineStr">
+        <is>
+          <t>Blender Z-up / -Y</t>
+        </is>
+      </c>
+      <c r="I240" s="69" t="inlineStr">
+        <is>
+          <t>static / per_instance(visual_only+blocking)</t>
+        </is>
+      </c>
+      <c r="J240" s="69" t="inlineStr">
+        <is>
+          <t>100F天台专用；只摆共享组件实例，不拥有几何</t>
+        </is>
+      </c>
+      <c r="K240" s="69" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L240" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M240" s="69" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N240" s="69" t="inlineStr">
+        <is>
+          <t>120装饰实例/6组（房屋围护由Base100UpperShell独占）；外围68件（64直段+4外角）；234块5m地砖；20启用碰撞（绿化：8花箱+6大盆栽+6小盆栽，layer=1 包络代理）</t>
+        </is>
+      </c>
+      <c r="O240" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.blend</t>
+        </is>
+      </c>
+      <c r="P240" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json; src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
+      <c r="Q240" s="69" t="inlineStr">
+        <is>
+          <t>天台;装饰布局;空调;通风口;水管;藤蔓;女儿墙挂藤;花圃盆栽;100F</t>
+        </is>
+      </c>
+      <c r="R240" s="69">
+        <f>LOWER(TRIM(C240)&amp;"|"&amp;TRIM(D240)&amp;"|"&amp;TRIM(E240)&amp;"|"&amp;TRIM(F240)&amp;"|"&amp;TRIM(H240)&amp;"|"&amp;TRIM(I240))</f>
+        <v/>
+      </c>
+      <c r="S240" s="69">
+        <f>IF(COUNTIF($R$6:$R$240,R240)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T240" s="69" t="inlineStr">
+        <is>
+          <t>de1d7ce61f0b6806107e3a5af9b1a043f4272aab900f92411c8e4b6996361838</t>
+        </is>
+      </c>
+      <c r="U240" s="69" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V240" s="69" t="n">
+        <v>46286</v>
+      </c>
+      <c r="W240" s="69" t="inlineStr">
+        <is>
+          <t>用户要求「用组件库现有件装饰天台」；Blender 组件实例布局；2026-09-21 业主实机报「坐标偏移 / 范围也错 / 没和 99 层基地正上方的墙壁一体」，修正坐标契约、装饰外皮与重复层</t>
+        </is>
+      </c>
+      <c r="X240" s="69" t="inlineStr">
+        <is>
+          <t>100F_decorated_v001</t>
+        </is>
+      </c>
+      <c r="Y240" s="69" t="inlineStr">
+        <is>
+          <t>2026-09-21 二次修正（业主实机报「花圃花盆悬空 / 藤蔓要更高更错落 / 挡门 / 加栏杆挂藤」）：①竖向基准 —— 运行时天台承重面 y=0（TowerFloorStage3D 把地砖可视顶面对齐到 Y=0），而布局源把落地装饰写在 h=0.3（= 自持地砖顶面），地砖组又不进重放 ⇒ 实机花草整块砖厚悬空 0.30m、藤蔓 0.35m；现落地件统一 h=0，自持参照地砖改 h=−0.30 使砖顶面落 0。②基地东门净空 —— 门洞净宽 2.2m（世界 gz∈[−3.6,−1.4]），东墙藤蔓 gz −5.0→−8.5、东侧大盆栽 −4.0→−6.2，另把正插在门洞正中的东墙立管 −2.0→+5.5。③藤蔓加高错落 —— 11 基座落地 + 5 件上层叠高（2.0/2.4/2.6/3.2/3.6m；运行时禁非单位缩放，故只能用叠件而非 scale）⇒ 顶高 5.80~7.40m。④新增「女儿墙挂藤」8 件，贴外圈女儿墙中心线（四边各 2，宽度与 5m 直段同宽）。重放实例 99 → 112 / 6 组。运行时重放 99 个装饰实例/5组＝空调与通风口6+绿化20+藤蔓11+水管54+立管支架8；布局源按 Godot 世界平面口径书写、写入 Blender 只做 by=−gz 一步换算，运行时用 (x, h, −by) 还原，并断言换算后必须落在 ROOFTOP_WORLD_RECT 内；装饰贴的是 Base100UpperShell（30×30，中心 (0,5)，东墙门 z=−2.5）的外墙皮；全部实例缩放=1且启用碰撞=0；结构壳体（234地砖/68件女儿墙/楼梯与碰撞）仍由 TowerFloorStage3D 拥有。2026-09-21 修正三处：①缺 by=−gz 换算 ⇒ 整份布局南北镜像、整体偏北 10m；②房屋误做 20×20 且偏北，装饰随之偏；③布局源的 24 墙+36 封顶与 Base100UpperShell 自带件重复，改名 shell_reference（仅 Blender 侧参照、不重放），避免逐面 z-fighting。2026-09-21 三次修正（业主实机报「水管接下来接到地板上面基本看不到 / 空调机在墙上的状态需要 90 度旋转让风扇朝外」）：①立管落地 —— pipe_riser 件高 4.945m、原点在管底、顶端是朝 +X 的鹅颈出水口；旧版放 h=5.8 ⇒ 管底悬空 5.8m。现每处摆两段、两段 h 都是 4.945：下段 rotation_x_deg=180 倒装（包络 0~4.945m，原点即上端）、上段正装（4.945~9.89m），合成一根 0~9.89m 连续落水管，与 10.65m 环管之间残留 0.76m 由环管本体与支架轨遮住；支架补一段低位（1.5m）与原有 7.0m 位，覆盖 1.56~10.64m。②墙挂空调倾倒 —— 新增实例朝向分量 rotation_x_deg（绕自身 X 轴的倾倒）；组件 hvac_small 顶面（Blender 局部 +Z）是出风风扇、前面（局部 −Y）是进风格栅，故 4 台墙挂机统一 rotation_x_deg=90 让风扇朝外（旧版风扇朝天）。⚠️ Blender 默认 XYZ 序、Godot 默认 YXZ 序，只有 rz 分量为 0 时 Rz@Rx 与 Ry@Rx 同序、角度可逐值搬运，本布局遵守该约束（tip 只与 yaw 组合）。③立管/支架按各自墙面给 yaw（旧版立管一律 0 ⇒ 东西墙鹅颈朝墙里）；6 个墙挂件（4 空调 + 2 通风口）后背统一埋进墙外皮内 0.05m。重放实例 112 → 120（pipe_risers 8 → 16）。2026-09-21 四次修正（业主实机报「花盆和花圃没有阻挡」）：绿化 20 件（8 花箱 + 6 大盆栽 + 6 小盆栽）由 visual_only 改 blocking —— 布局源 add() 新增实例级 collision 策略（词表 visual_only / blocking，白名单 flowerbox / plant_large / plant_small），运行时 TowerFloorStage3D 新增 _apply_rooftop_collision_policy()：blocking 件用 TowerGeometry3D.resolve_visual_bounds() 量出**实测可视包络**、挂一个 StaticBody3D(BlockingCollision, layer=1, mask=0, PROCESS_MODE_ALWAYS) + BoxShape3D(BlockingBox) 代理挡玩家（尺寸随美术走、不写死常量），其余 462 件仍 visual_only（组件自带碰撞一律先关）。布局清单 design_intent/validation 记 blocking_collision_count=20 / visual_only_collision_count=462；校验器新增第 5 层断言（策略词表 + 白名单 slug + 计数 + 清单交叉一致）。反向对照：把 20 件翻回 visual_only ⇒ 两份运行时探针 exit 1、QA 报 3 条 FAIL；还原后 .blend 与 .json 逐字节一致。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:X239"/>
+  <autoFilter ref="A5:X240"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
   </mergeCells>
-  <conditionalFormatting sqref="S6:S239">
+  <conditionalFormatting sqref="S6:S240">
     <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" text="重复"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K239">
+  <conditionalFormatting sqref="K6:K240">
     <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" text="已完成"/>
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" text="待制作"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C239" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C240" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K239" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K240" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L239" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L240" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -30628,7 +30746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P145"/>
+  <dimension ref="A1:P146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="50" min="1" max="1"/>
@@ -37853,7 +37971,7 @@
       </c>
       <c r="F96" s="69" t="inlineStr">
         <is>
-          <t>44独立包；新增7个挂藤墙体变体，门口具有真实石材厚度与内凹门扇。</t>
+          <t>47独立包（10类）；女儿墙已改方案A 0.80m 并含3件破损变种；11 类装饰（空调/通风口/水管/藤蔓/花圃盆栽）已导出并接入 100F 装饰布局。</t>
         </is>
       </c>
       <c r="G96" s="69" t="inlineStr"/>
@@ -37899,7 +38017,7 @@
       </c>
       <c r="P96" s="69" t="inlineStr">
         <is>
-          <t>2026-09-17：36包锁区签名保持；门柱1.10m/门楣1.16m；4材质；126322面UV通过；未接入Godot。SHA256=ca091c6dec5ac3dc0c63b4e3b28a84934d78d685656388c882087c1a9b9b966e</t>
+          <t>2026-09-20 方案A 0.80m 写回主库；2026-09-21 库内 47 包，16 件已导出，其中 11 件装饰已接入运行时；其余包仍为 Blender 源状态（未导出 GLB）。</t>
         </is>
       </c>
     </row>
@@ -39148,34 +39266,46 @@
           <t>小型空调机组</t>
         </is>
       </c>
-      <c r="C113" s="69" t="inlineStr"/>
-      <c r="D113" s="69" t="inlineStr"/>
+      <c r="C113" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/hvac_small.tscn</t>
+        </is>
+      </c>
+      <c r="D113" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_hvac_small_top3d.glb</t>
+        </is>
+      </c>
       <c r="E113" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#小型空调机组_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F113" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；05_空调与设备</t>
-        </is>
-      </c>
-      <c r="G113" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台房屋四向外墙墙面（避开门洞）（布局内 4 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G113" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H113" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I113" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J113" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I113" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J113" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K113" s="69" t="inlineStr">
         <is>
           <t>2.500×2.365×1.870 m</t>
@@ -39188,12 +39318,12 @@
       </c>
       <c r="M113" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / hvac_small</t>
+          <t>100F天台装饰布局 / hvac_small</t>
         </is>
       </c>
       <c r="N113" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O113" s="69" t="inlineStr">
@@ -39203,7 +39333,7 @@
       </c>
       <c r="P113" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/05/hvac_small/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(a6c115780b91) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -39288,34 +39418,46 @@
           <t>小通风口</t>
         </is>
       </c>
-      <c r="C115" s="69" t="inlineStr"/>
-      <c r="D115" s="69" t="inlineStr"/>
+      <c r="C115" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/hvac_vent.tscn</t>
+        </is>
+      </c>
+      <c r="D115" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_hvac_vent_top3d.glb</t>
+        </is>
+      </c>
       <c r="E115" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#小通风口_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F115" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；05_空调与设备</t>
-        </is>
-      </c>
-      <c r="G115" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台房屋南北墙高处（布局内 2 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G115" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H115" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I115" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J115" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I115" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J115" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K115" s="69" t="inlineStr">
         <is>
           <t>1.400×1.165×0.850 m</t>
@@ -39328,12 +39470,12 @@
       </c>
       <c r="M115" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / hvac_vent</t>
+          <t>100F天台装饰布局 / hvac_vent</t>
         </is>
       </c>
       <c r="N115" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O115" s="69" t="inlineStr">
@@ -39343,7 +39485,7 @@
       </c>
       <c r="P115" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/05/hvac_vent/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(7bf9c80cf1c2) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -39498,34 +39640,46 @@
           <t>直管段</t>
         </is>
       </c>
-      <c r="C118" s="69" t="inlineStr"/>
-      <c r="D118" s="69" t="inlineStr"/>
+      <c r="C118" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/pipe_straight.tscn</t>
+        </is>
+      </c>
+      <c r="D118" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_pipe_straight_top3d.glb</t>
+        </is>
+      </c>
       <c r="E118" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#直管段_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F118" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；06_管线系统</t>
-        </is>
-      </c>
-      <c r="G118" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台房屋四周闭环水管（布局内 32 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G118" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H118" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I118" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J118" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I118" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J118" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K118" s="69" t="inlineStr">
         <is>
           <t>2.640×0.410×0.410 m</t>
@@ -39538,12 +39692,12 @@
       </c>
       <c r="M118" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / pipe_straight</t>
+          <t>100F天台装饰布局 / pipe_straight</t>
         </is>
       </c>
       <c r="N118" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O118" s="69" t="inlineStr">
@@ -39553,7 +39707,7 @@
       </c>
       <c r="P118" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/06/pipe_straight/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(3138e3414ffb) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -39568,34 +39722,46 @@
           <t>转角弯管</t>
         </is>
       </c>
-      <c r="C119" s="69" t="inlineStr"/>
-      <c r="D119" s="69" t="inlineStr"/>
+      <c r="C119" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/pipe_elbow.tscn</t>
+        </is>
+      </c>
+      <c r="D119" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_pipe_elbow_top3d.glb</t>
+        </is>
+      </c>
       <c r="E119" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#转角弯管_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F119" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；06_管线系统</t>
-        </is>
-      </c>
-      <c r="G119" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台闭环水管四角（布局内 4 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G119" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H119" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I119" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J119" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I119" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J119" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K119" s="69" t="inlineStr">
         <is>
           <t>1.575×0.410×1.275 m</t>
@@ -39608,12 +39774,12 @@
       </c>
       <c r="M119" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / pipe_elbow</t>
+          <t>100F天台装饰布局 / pipe_elbow</t>
         </is>
       </c>
       <c r="N119" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O119" s="69" t="inlineStr">
@@ -39623,7 +39789,7 @@
       </c>
       <c r="P119" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/06/pipe_elbow/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(1f5e1a101fba) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -39638,34 +39804,46 @@
           <t>三通管</t>
         </is>
       </c>
-      <c r="C120" s="69" t="inlineStr"/>
-      <c r="D120" s="69" t="inlineStr"/>
+      <c r="C120" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/pipe_tee.tscn</t>
+        </is>
+      </c>
+      <c r="D120" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_pipe_tee_top3d.glb</t>
+        </is>
+      </c>
       <c r="E120" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#三通管_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F120" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；06_管线系统</t>
-        </is>
-      </c>
-      <c r="G120" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台闭环水管灌溉分支（布局内 2 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G120" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H120" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I120" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J120" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I120" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J120" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K120" s="69" t="inlineStr">
         <is>
           <t>2.640×0.410×1.355 m</t>
@@ -39678,12 +39856,12 @@
       </c>
       <c r="M120" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / pipe_tee</t>
+          <t>100F天台装饰布局 / pipe_tee</t>
         </is>
       </c>
       <c r="N120" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O120" s="69" t="inlineStr">
@@ -39693,7 +39871,7 @@
       </c>
       <c r="P120" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/06/pipe_tee/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(3ea17b1e98a6) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -39708,34 +39886,46 @@
           <t>立管下水管</t>
         </is>
       </c>
-      <c r="C121" s="69" t="inlineStr"/>
-      <c r="D121" s="69" t="inlineStr"/>
+      <c r="C121" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/pipe_riser.tscn</t>
+        </is>
+      </c>
+      <c r="D121" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_pipe_riser_top3d.glb</t>
+        </is>
+      </c>
       <c r="E121" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#立管下水管_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F121" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；06_管线系统</t>
-        </is>
-      </c>
-      <c r="G121" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台闭环水管至地面立管（布局内 4 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G121" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H121" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I121" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J121" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I121" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J121" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K121" s="69" t="inlineStr">
         <is>
           <t>0.795×0.485×4.945 m</t>
@@ -39748,12 +39938,12 @@
       </c>
       <c r="M121" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / pipe_riser</t>
+          <t>100F天台装饰布局 / pipe_riser</t>
         </is>
       </c>
       <c r="N121" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O121" s="69" t="inlineStr">
@@ -39763,7 +39953,7 @@
       </c>
       <c r="P121" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/06/pipe_riser/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(e815f0626f41) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -39778,34 +39968,46 @@
           <t>管道支架</t>
         </is>
       </c>
-      <c r="C122" s="69" t="inlineStr"/>
-      <c r="D122" s="69" t="inlineStr"/>
+      <c r="C122" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/pipe_bracket.tscn</t>
+        </is>
+      </c>
+      <c r="D122" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_pipe_bracket_top3d.glb</t>
+        </is>
+      </c>
       <c r="E122" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#管道支架_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F122" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；06_管线系统</t>
-        </is>
-      </c>
-      <c r="G122" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台立管墙面固定（布局内 4 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G122" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H122" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I122" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J122" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I122" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J122" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K122" s="69" t="inlineStr">
         <is>
           <t>0.480×0.876×3.640 m</t>
@@ -39818,12 +40020,12 @@
       </c>
       <c r="M122" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / pipe_bracket</t>
+          <t>100F天台装饰布局 / pipe_bracket</t>
         </is>
       </c>
       <c r="N122" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O122" s="69" t="inlineStr">
@@ -39833,7 +40035,7 @@
       </c>
       <c r="P122" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/06/pipe_bracket/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(50f208d92e99) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -39988,34 +40190,46 @@
           <t>墙面攀爬藤蔓</t>
         </is>
       </c>
-      <c r="C125" s="69" t="inlineStr"/>
-      <c r="D125" s="69" t="inlineStr"/>
+      <c r="C125" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/ivy.tscn</t>
+        </is>
+      </c>
+      <c r="D125" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_ivy_top3d.glb</t>
+        </is>
+      </c>
       <c r="E125" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#墙面攀爬藤蔓_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F125" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；08_固定绿化</t>
-        </is>
-      </c>
-      <c r="G125" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台房屋墙面分段挂藤（布局内 11 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G125" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H125" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I125" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J125" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I125" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J125" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K125" s="69" t="inlineStr">
         <is>
           <t>4.256×0.819×3.802 m</t>
@@ -40028,12 +40242,12 @@
       </c>
       <c r="M125" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / ivy</t>
+          <t>100F天台装饰布局 / ivy</t>
         </is>
       </c>
       <c r="N125" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O125" s="69" t="inlineStr">
@@ -40043,7 +40257,7 @@
       </c>
       <c r="P125" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/08/ivy/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(8c54feeec0f7) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -40058,34 +40272,46 @@
           <t>长条花箱</t>
         </is>
       </c>
-      <c r="C126" s="69" t="inlineStr"/>
-      <c r="D126" s="69" t="inlineStr"/>
+      <c r="C126" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/flowerbox.tscn</t>
+        </is>
+      </c>
+      <c r="D126" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_flowerbox_top3d.glb</t>
+        </is>
+      </c>
       <c r="E126" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#长条花箱_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F126" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；08_固定绿化</t>
-        </is>
-      </c>
-      <c r="G126" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台房屋四周贴墙长条花箱（布局内 6 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G126" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H126" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I126" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J126" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I126" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J126" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K126" s="69" t="inlineStr">
         <is>
           <t>4.500×1.185×2.134 m</t>
@@ -40098,12 +40324,12 @@
       </c>
       <c r="M126" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / flowerbox</t>
+          <t>100F天台装饰布局 / flowerbox</t>
         </is>
       </c>
       <c r="N126" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O126" s="69" t="inlineStr">
@@ -40113,7 +40339,7 @@
       </c>
       <c r="P126" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/08/flowerbox/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(8e7f91af2221) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -40128,34 +40354,46 @@
           <t>大盆栽</t>
         </is>
       </c>
-      <c r="C127" s="69" t="inlineStr"/>
-      <c r="D127" s="69" t="inlineStr"/>
+      <c r="C127" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/plant_large.tscn</t>
+        </is>
+      </c>
+      <c r="D127" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_plant_large_top3d.glb</t>
+        </is>
+      </c>
       <c r="E127" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#大盆栽_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F127" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；08_固定绿化</t>
-        </is>
-      </c>
-      <c r="G127" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台房屋周边高点盆栽（布局内 6 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G127" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H127" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I127" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J127" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I127" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J127" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K127" s="69" t="inlineStr">
         <is>
           <t>1.547×1.745×2.772 m</t>
@@ -40168,12 +40406,12 @@
       </c>
       <c r="M127" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / plant_large</t>
+          <t>100F天台装饰布局 / plant_large</t>
         </is>
       </c>
       <c r="N127" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O127" s="69" t="inlineStr">
@@ -40183,7 +40421,7 @@
       </c>
       <c r="P127" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/08/plant_large/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(138135d836c3) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -40198,34 +40436,46 @@
           <t>小盆栽</t>
         </is>
       </c>
-      <c r="C128" s="69" t="inlineStr"/>
-      <c r="D128" s="69" t="inlineStr"/>
+      <c r="C128" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/runtime/plant_small.tscn</t>
+        </is>
+      </c>
+      <c r="D128" s="69" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_plant_small_top3d.glb</t>
+        </is>
+      </c>
       <c r="E128" s="69" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#小盆栽_资产包</t>
+          <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend</t>
         </is>
       </c>
       <c r="F128" s="69" t="inlineStr">
         <is>
-          <t>独立资产包；08_固定绿化</t>
-        </is>
-      </c>
-      <c r="G128" s="69" t="inlineStr"/>
+          <t>Godot视觉装饰PackedScene；100F天台房屋周边低点盆栽（布局内 6 个实例），由 TowerFloorStage3D 按装饰布局清单实例化</t>
+        </is>
+      </c>
+      <c r="G128" s="69" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
       <c r="H128" s="69" t="inlineStr">
         <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I128" s="69" t="inlineStr">
+        <is>
+          <t>引擎（visual_only）</t>
+        </is>
+      </c>
+      <c r="J128" s="69" t="inlineStr">
+        <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I128" s="69" t="inlineStr">
-        <is>
-          <t>独立包运行包装</t>
-        </is>
-      </c>
-      <c r="J128" s="69" t="inlineStr">
-        <is>
-          <t>未创建</t>
-        </is>
-      </c>
       <c r="K128" s="69" t="inlineStr">
         <is>
           <t>1.096×1.095×1.482 m</t>
@@ -40238,12 +40488,12 @@
       </c>
       <c r="M128" s="69" t="inlineStr">
         <is>
-          <t>天台参考组件库 / plant_small</t>
+          <t>100F天台装饰布局 / plant_small</t>
         </is>
       </c>
       <c r="N128" s="69" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O128" s="69" t="inlineStr">
@@ -40253,7 +40503,7 @@
       </c>
       <c r="P128" s="69" t="inlineStr">
         <is>
-          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/08/plant_small/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。</t>
+          <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；2026-09-21 从 v002 主库导出 GLB(917d1ee05228) 并生成 runtime PackedScene；接入 100F 装饰布局＝99实例/7组/0启用碰撞；布局源=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json</t>
         </is>
       </c>
     </row>
@@ -41401,156 +41651,230 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>ENV-ROOFTOP-REF-ROOM-DOOR</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="3" t="inlineStr">
         <is>
           <t>房间门组件（门框+门垛）</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>assets/art/props/dungeon_3d/prp_rooftop_room_door.tscn</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_room_door_top3d.glb</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#门与暖灯_资产包（导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_ref_room_walls_v001.py）</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr">
         <is>
           <t>厚石门洞的门框与门垛视觉；与 ENV-ROOFTOP-REF-ROOM-DOOR-LEAF 成对使用。门组件 = 门洞墙基准位 + 0.4175×外法线（沿 +Z 外移半个门洞墙厚 + 半板厚）</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="H144" s="3" t="inlineStr">
         <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="I144" s="3" t="inlineStr">
         <is>
           <t>Base100UpperShell3D</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr">
+      <c r="J144" s="3" t="inlineStr">
         <is>
           <t>Prefab 已声明 collision_owner；尚未在 100F 上层围护场景实例化</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="K144" s="3" t="inlineStr">
         <is>
           <t>门洞净空 3.80×6.80 m；门垛各 0.60 m（外廓随基墙 5.000×11.900×0.300）</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="L144" s="3" t="inlineStr">
         <is>
           <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr">
+      <c r="M144" s="3" t="inlineStr">
         <is>
           <t>已制作并登记；100F 上层围护**未使用**（东门槽保留 base99 门墙与 RoomDoor3D）</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr">
+      <c r="N144" s="3" t="inlineStr">
         <is>
           <t>正式美术已接入</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr">
+      <c r="O144" s="3" t="inlineStr">
         <is>
           <t>v002</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr">
+      <c r="P144" s="3" t="inlineStr">
         <is>
           <t>2026-09-20 新建行（全新 AssetID）。来源：天台区块参考组件库 v002 的「门与暖灯_主体」（528 顶点焊接网格，含 22 个松散件）按 5 个制作件 AABB 无损二分：130 面 → 门扇、418 面 → 本件（门组件）。与门洞墙同位、无偏移。⚠️ 本房型门是静态关闭态（Base100UpperShell3D 的门洞只是洞，没有挂 RoomDoor3D）；若日后要做开合动画，必须改 RoomDoor3D 的全局常量TOWER_GEOMETRY.DOOR_CLEAR_*，不能只改本件。</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>ENV-ROOFTOP-REF-ROOM-DOOR-LEAF</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="3" t="inlineStr">
         <is>
           <t>房间门扇（静态关闭态）</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>assets/art/props/dungeon_3d/prp_rooftop_room_door_leaf.tscn</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/components/env_rooftop_ref_room_door_leaf_top3d.glb</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>assets/art/environments/tower_zones/rooftop/source/reference_components/v002/天台区块_参考组件库_v002.blend#门与暖灯_资产包（导出脚本 assets/art/environments/tower_zones/rooftop/source/export_env_rooftop_ref_room_walls_v001.py）</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>厚石门洞的单扇门板视觉；与 ENV-ROOFTOP-REF-ROOM-DOOR 成对；静态关闭态</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="H145" s="3" t="inlineStr">
         <is>
           <t>未创建</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="I145" s="3" t="inlineStr">
         <is>
           <t>Base100UpperShell3D</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr">
+      <c r="J145" s="3" t="inlineStr">
         <is>
           <t>Prefab 已声明 collision_owner；尚未在 100F 上层围护场景实例化</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="K145" s="3" t="inlineStr">
         <is>
           <t>板 3.680×6.800×0.180 m；可视包络厚 0.410 m</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="L145" s="3" t="inlineStr">
         <is>
           <t>bottom_center（几何 Y=0 起）；+Z 朝外。⚠️ 与 99F 系（ENV-BASE99-*，-Z 朝外）差 180°：同一条边 base99 用 -90°、本套件用 +90°。</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr">
+      <c r="M145" s="3" t="inlineStr">
         <is>
           <t>已制作并登记；100F 上层围护**未使用**</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr">
+      <c r="N145" s="3" t="inlineStr">
         <is>
           <t>正式美术已接入</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr">
+      <c r="O145" s="3" t="inlineStr">
         <is>
           <t>v002</t>
         </is>
       </c>
-      <c r="P145" t="inlineStr">
+      <c r="P145" s="3" t="inlineStr">
         <is>
           <t>2026-09-20 新建行（全新 AssetID）。门扇板局部 z 中心已平移到 0（原点 = 底面中心），与门洞墙同位装配（不沿 +Z 偏移）；门组件才做 +0.4175×外法线偏移。3 个表面，共享色盘由 scene_facility_shared_palette_post_import.gd 绑定。本行不声明 open_mode：本房型门是静态关闭态；要做开合须改 RoomDoor3D 全局常量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>ENV-ROOFTOP-DECOR-LAYOUT-100F</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>100F天台装饰布局</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr"/>
+      <c r="D146" s="3" t="inlineStr"/>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.blend</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>Blender组件实例布局源；只摆放共享组件实例、不拥有几何；运行时重放 120 个装饰实例（空调6+绿化20+藤蔓16+女儿墙挂藤8+水管54+立管16）；房屋围护改列 shell_reference 参照层（24墙+36封顶），由 Base100UpperShell 独占，不重放；2026-09-21 四次修正：绿化 20 件（8 花箱+6 大盆栽+6 小盆栽）改 blocking —— 运行时按实测可视包络生成 StaticBody3D 碰撞代理（layer=1，尺寸随美术自动跟随）挡玩家，其余 462 件仍 visual_only</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>src/world3d/TowerFloorStage3D.gd</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>开</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>引擎（per_instance：默认 visual_only，绿化 blocking）</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>BoxShape3D 代理（按 TowerGeometry3D.resolve_visual_bounds 实测可视包络；仅绿化 20 件，layer=1）</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>90×80m天台；外围68件（64直段+4外角）；234块5m地砖（开口=中庭6×6+西侧楼梯口3×6）</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>世界原点对齐 ROOFTOP_WORLD_RECT；Blender Z-up / -Y；Godot=(Blender X, Blender Z, -Blender Y)</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>100F天台 / TowerFloorStage3D 运行时按布局清单重放</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="O146" s="3" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P146" s="3" t="inlineStr">
+        <is>
+          <t>清单=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json；运行时登记=assets/art/environments/tower_zones/rooftop/runtime/rooftop_100f_decorated_runtime_manifest.json；验收=verify_rooftop_32x32_contract + probe_rooftop_decorated_layout + probe_rooftop_decorated_stage_only；全部实例缩放=1、启用碰撞=0；结构壳体（地砖/女儿墙）仍由 TowerFloorStage3D 负责，布局不重复生成；2026-09-21 坐标契约修正（补 by=−gz，此前整体偏北 10m）＋房屋 20×20→30×30 对齐 Base100UpperShell；2026-09-21 三次修正：立管落地 0~9.89m（h=件高4.945、倒装件原点在顶面）、墙挂空调绕 X 轴 90° 倾倒让风扇朝外（Godot 侧读 basis.y）、布局源只写 rotation_x_deg + rotation_y_deg（rz=0，规避 Blender XYZ 序 / Godot YXZ 序的次序差）；2026-09-21 四次修正：绿化 20 件改 blocking（运行时按 TowerGeometry3D.resolve_visual_bounds 实测可视包络生成 layer=1 BoxShape3D 代理挡玩家），其余 visual_only；collision_policy 词表=visual_only/blocking，清单设计意图记 blocking_collision_count=20 / visual_only_collision_count=462</t>
         </is>
       </c>
     </row>
@@ -43690,7 +44014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="50" min="1" max="1"/>
@@ -43902,6 +44226,189 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>v0.1.4</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>资产升版+新条目</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>关卡场景 / 100F天台</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>天台参考组件库升为 47 包（女儿墙方案A 0.80m + 3件破损变种）；11 类装饰组件（HVAC-SMALL/VENT、PIPE-STRAIGHT/ELBOW/TEE/RISER/BRACKET、IVY、FLOWERBOX、PLANT-LARGE/SMALL）由「Blender源已完成」升级为「正式美术已接入」：填 runtime PackedScene 与 GLB 路径、碰撞归零；新增 ENV-ROOFTOP-DECOR-LAYOUT-100F 登记 100F 天台装饰布局（113 实例 / 7 组）。</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>AssetID 全部沿用既有行，无新增组件 ID；仅「装饰布局」为新条目。装饰件无碰撞、无新玩法语义，原有地砖/女儿墙/楼梯结构与碰撞不变；旧账本留档 ShellStorm2_场景账本_v001.xlsx.bak_rooftop_decor_ledger。</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>v0.1.5</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>条目修正</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>关卡场景 / 100F天台</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>100F 天台装饰布局源原地修正三处：①补上缺失的「Godot 平面 → Blender」换算（by = −gz）：此前整份布局在 Godot 里南北镜像、整体偏北 10m（北侧溢出天台边界、南侧缺 10m），业主实机报「坐标偏移 / 范围也错 / 往北偏」；②「房屋」被做成 20×20 且偏北 —— 它其实是 Base100UpperShell（30×30，中心 (0,5)）所在建筑的外皮，装饰（空调/花圃/藤蔓/水管）随之外扩贴到 30×30 墙皮、水管每边 8 → 12 段（2.5m 间距不变）；③发现 Base100UpperShell 的 prefab（env_base100_upper_shell_30x30_h12）自 2026-09-20 起已自带 24 块墙 + 36 格封顶，布局源里同名 60 件属重复层 ⇒ 改名 shell_reference 仅作 Blender 侧参照、运行时不再重放（否则逐面 z-fighting）。重放实例 113 → 99。同时新增防再犯断言：布局 QA 与运行时重放都要求换算后落在 ROOFTOP_WORLD_RECT 内；布局 QA 另断言不得出现 house_shell / house_roof 组名（防止 60 件又被重放）。</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>AssetID / layout_id / layout_version 均不变（原地修正，不新增条目）；装饰件仍 visual_only、0 启用碰撞；结构壳体（234 地砖 / 68 件女儿墙 / 楼梯与碰撞）与玩法不变；旧布局源留档 _scratch/rooftop_decor_fix/layout_before.{blend,json}。</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>v0.1.6</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>条目修正+新条目</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>关卡场景 / 100F天台</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>100F 天台装饰布局二次修正四件事：①竖向基准错位根因——运行时天台承重面是 y=0，而布局源把落地装饰写在自己的地砖顶面 h=0.3，地砖组又不重放 ⇒ 实机花箱/盆栽/藤蔓整块砖厚悬空；现落地件统一 h=0、自持参照地砖改 h=−0.30（砖顶面落 0）。②基地东门净空——门洞世界 gz∈[−3.6,−1.4]，东墙藤蔓 gz −5.0→−8.5、东侧大盆栽 −4.0→−6.2，并把正插门洞的东墙立管 −2.0→+5.5。③藤蔓高低错落——11 基座落地 + 5 件上层叠高（2.0~3.6m；运行时禁非单位缩放，只能用叠件）⇒ 顶高 5.80~7.40m。④业主提供「女儿墙挂藤」组件，新导入 GLB 与 prefab 并登记为第 12 类装饰，摆 8 件贴外圈女儿墙中心线。重放实例 99 → 112 / 6 组。布局 QA 新增第 3 层断言（落地件底面 y=0、地砖顶面 0、东门旋转包络净空、挂藤贴中心线、藤蔓顶高落差 ≥3m），运行时探针新增落地数断言；两者均做过反向对照。</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>AssetID / layout_id / layout_version 均不变（原地修正；「女儿墙挂藤」为组件库既有包新导出，登记在既有组件库行内，不新增 AssetID）；装饰件仍 visual_only、0 启用碰撞；结构壳体（234 地砖 / 68 件女儿墙 / 楼梯与碰撞）与玩法不变；旧布局源与旧 prefab 留档 _scratch/rooftop_ivy/backup_{components,runtime}。</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>v0.1.7</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>条目修正</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>关卡场景 / 100F天台</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>100F 天台装饰布局三次修正两件事：①立管落地——pipe_riser 件高 4.945m、原点在管底，旧版放 h=5.8 ⇒ 管底悬空 5.8m；现每处两段（下段 rotation_x_deg=180 倒装），合成 0~9.89m 连续落水管并落地 y=0，与 10.65m 环管残留 0.76m 由环管/支架遮住。②墙挂空调倾倒——新增 rotation_x_deg 分量（绕自身 X 轴），4 台墙挂机统一 90° 让顶部风扇朝外（旧版风扇朝天）；Blender XYZ 序与 Godot YXZ 序在 rz=0 时同序、角度逐值搬运。</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>AssetID / layout_id / layout_version 均不变（原地修正，不新增条目）；装饰件仍 visual_only、0 启用碰撞；结构壳体（234 地砖 / 68 件女儿墙 / 楼梯与碰撞）与玩法不变；重放实例 112 → 120。</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>v0.1.8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>条目修正</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>关卡场景 / 100F天台</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>100F 天台装饰布局四次修正（业主实机报「花盆和花圃没有阻挡」）：绿化 20 件（8 花箱 + 6 大盆栽 + 6 小盆栽）由 visual_only 改 blocking —— 布局源 add() 新增实例级 collision 策略（词表 visual_only/blocking，白名单 flowerbox/plant_large/plant_small），运行时 TowerFloorStage3D 新增 _apply_rooftop_collision_policy()：blocking 件按 TowerGeometry3D.resolve_visual_bounds() 实测可视包络挂 StaticBody3D(layer=1)+BoxShape3D 代理挡玩家，尺寸随美术自动跟随；其余 462 件仍 visual_only。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AssetID / layout_id / layout_version 均不变（原地修正，不新增条目、不新增资产）；账本门禁维持 46；.blend SHA-256 09e9a917… → de1d7ce6、清单 .json fcf892d7… 同步；结构壳体与玩法不变。</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -467,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="21" fillId="12" borderId="19"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -747,6 +747,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -29744,7 +29747,7 @@
       </c>
       <c r="T232" s="79" t="inlineStr">
         <is>
-          <t>a5dfe6a7bf658ab2f66eb5bdd8044f68a0ce788ebbca6a654a5ea15a67440ba4</t>
+          <t>d153967cd3c333b46dc8fbf2c89b73ffb095a834be12a7daf774fef0418af1a7</t>
         </is>
       </c>
       <c r="U232" s="79" t="inlineStr">
@@ -29754,7 +29757,7 @@
       </c>
       <c r="V232" s="79" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="W232" s="79" t="inlineStr">
@@ -29769,7 +29772,7 @@
       </c>
       <c r="Y232" s="79" t="inlineStr">
         <is>
-          <t>Godot正式导入完成；45个GLB均公共色盘、无嵌入贴图；基地美术布局已实例化</t>
+          <t>Godot正式导入完成；45个GLB均公共色盘、无嵌入贴图；基地美术布局已实例化 ｜ 2026-09-21 业主在 Godot 编辑器内手工微调本包运行时布局并定版：该 .tscn 的节点变换即布局真源（15 件实际位移 / 4 件 facility 包装包空操作覆盖 / 9 份有意多份实例），坐标已固化为 source/env_base99_remaining_facilities_v021_placement.{json,md}；不写回 Blender，重生成通道会覆盖它。SHA-256 d153967cd3c333b46dc8fbf2c89b73ffb095a834be12a7daf774fef0418af1a7</t>
         </is>
       </c>
     </row>
@@ -44014,7 +44017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="50" min="1" max="1"/>
@@ -44306,8 +44309,10 @@
           <t>v0.1.6</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>46286</v>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -44409,7 +44414,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" s="50">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>v0.1.9</t>
@@ -44441,6 +44446,43 @@
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" s="50">
+      <c r="A16" s="97" t="inlineStr">
+        <is>
+          <t>v0.1.10</t>
+        </is>
+      </c>
+      <c r="B16" s="97" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C16" s="97" t="inlineStr">
+        <is>
+          <t>条目修正</t>
+        </is>
+      </c>
+      <c r="D16" s="97" t="inlineStr">
+        <is>
+          <t>关卡场景 / 99F基地</t>
+        </is>
+      </c>
+      <c r="E16" s="97" t="inlineStr">
+        <is>
+          <t>99F 基地「剩余非门非墙独立设施资产包」的运行时布局由业主在 Godot 编辑器内手工微调。本次不写回 Blender，改为先把坐标固化成机器可读记录、再在台账原地标注（业主原话「不用写回 blender，把坐标记下即可。下次改 blender 的时候按照这个坐标换位置即可。写回台账进行标注」）。量化（定版快照 SHA-256 d153967c…，与 HEAD 逐节点比对）：45 个顶层子节点中 —— ① 15 件有实际位移：普通包（*_root_top3d.tscn）覆盖值即纯位移量，如 72_SUPPLY24H自动补给机 Δ=(−19.3582, 0, −10.5085)、51_重型货架与补给箱 Δ=(0.7618, 0, −2.7644)；facility 包装包（*_facility_top3d.tscn）覆盖值是新的绝对 pivot，实际位移 = 覆盖值 − 原 pivot，如 49_武器工作台与弹药附件 Δ=(0, −0.5562, +1.9589)（即 5.3589 − 3.4）；54_蓄电池组另带绕 Y 偏航 −17.210°。② 4 件 facility 包装包覆盖值恰等于预制体 pivot（42_双屏电脑完整工位 / 36_墨绿三人休闲沙发 / 45_MEDICAL医疗柜 / 47_窄型电池柜），位移为 0、画面不变，但父场景从此硬覆盖该 pivot，以后改包装包预制体的 pivot 不再传导到这些件 —— 属「空操作但有副作用」，已单列。③ 2 件仅序列化差异、24 件无变换。另有 9 份「同一资产在同一顶层节点下被摆了多份」（自嵌套同名子节点 parent="X/X" 形式）：58_空气压缩机 1 份、54_蓄电池组 2 份、80_低矮储物收纳区 1 份、56_工业水箱 5 份；业主 2026-09-21 确认这是**有意摆位**（非误复制），Blender 侧应按同份数、同坐标落地。坐标记录见 assets/art/environments/base_facility_3d/source/env_base99_remaining_facilities_v021_placement.{json,md}：逐件给「相对预制体基准 Δ」「相对 HEAD 的本次修订 Δ」「Godot↔Blender 换算」（gx=bx, gy=bz, gz=−by；Godot 绕 +Y 偏航 ≡ Blender 绕 +Z 同值）以及运行时实测件心 AABB 与偏航；多份实例以「各份件心（实测）」为落位口径（部分包 GLB 顶点直接烘绝对坐标，节点原点可差十几米）。</t>
+        </is>
+      </c>
+      <c r="F16" s="97" t="inlineStr">
+        <is>
+          <t>AssetID / 版本号（v004）不变，不新增条目、不新增资产、门禁行数不变；制品几何、组件 GLB 与 manifest 均未变，仅该运行场景 .tscn 的节点变换与 SHA 变化：a5dfe6a7… → d153967c…。⚠ 该 .tscn 会被所有重生成通道覆盖（import_base_facility_*.py / deversion_batch.py / export_base_facility_latest.py），而反向固化通道 build_base_facility_runtime_layout_v002.py 只吃 8 个交互设施 + 结构件、不含这 45 个包 ⇒ 手改只能靠坐标记录保命，下次改 Blender 母版时按记录换位置。另注：tools/asset_pipeline/sync_base99_current_ledger.py 的 explicit 表仍指向去版本化前的 ..._root_top3d_v004.tscn，直接跑会把本行路径回退，故本次为手工改行，该脚本待修。</t>
+        </is>
+      </c>
+      <c r="G16" s="97" t="inlineStr">
         <is>
           <t>摩斯拉</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -30657,7 +30657,7 @@
       </c>
       <c r="N240" s="69" t="inlineStr">
         <is>
-          <t>120装饰实例/6组（房屋围护由Base100UpperShell独占）；外围68件（64直段+4外角）；234块5m地砖；20启用碰撞（绿化：8花箱+6大盆栽+6小盆栽，layer=1 包络代理）</t>
+          <t>120装饰实例/6组（房屋围护由Base100UpperShell独占）；外围72件（68直段+4外角）；266块5m地砖；20启用碰撞（绿化：8花箱+6大盆栽+6小盆栽，layer=1 包络代理）</t>
         </is>
       </c>
       <c r="O240" s="69" t="inlineStr">
@@ -30685,7 +30685,7 @@
       </c>
       <c r="T240" s="69" t="inlineStr">
         <is>
-          <t>7e8b2c511cbe1c9a6715f1f98829dcf480f9e839faaadc7b41318a4d4b19aa4a</t>
+          <t>e65aa1389076254a856b1941e5c680e6663e4e32d8fe260f3a490208cd21a8c5</t>
         </is>
       </c>
       <c r="U240" s="69" t="inlineStr">
@@ -30694,11 +30694,11 @@
         </is>
       </c>
       <c r="V240" s="69" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="W240" s="69" t="inlineStr">
         <is>
-          <t>用户要求「用组件库现有件装饰天台」；Blender 组件实例布局；2026-09-21 业主实机报「坐标偏移 / 范围也错 / 没和 99 层基地正上方的墙壁一体」，修正坐标契约、装饰外皮与重复层</t>
+          <t>用户要求「用组件库现有件装饰天台」；Blender 组件实例布局；2026-09-21 业主实机报「坐标偏移 / 范围也错 / 没和 99 层基地正上方的墙壁一体」，修正坐标契约、装饰外皮与重复层；2026-09-22 业主口径「所有楼层都和 100 层面积一致」：壳体扩到 100×80（20×16 格），布局源随之重生成</t>
         </is>
       </c>
       <c r="X240" s="69" t="inlineStr">
@@ -30708,7 +30708,7 @@
       </c>
       <c r="Y240" s="69" t="inlineStr">
         <is>
-          <t>2026-09-21 二次修正（业主实机报「花圃花盆悬空 / 藤蔓要更高更错落 / 挡门 / 加栏杆挂藤」）：①竖向基准 —— 运行时天台承重面 y=0（TowerFloorStage3D 把地砖可视顶面对齐到 Y=0），而布局源把落地装饰写在 h=0.3（= 自持地砖顶面），地砖组又不进重放 ⇒ 实机花草整块砖厚悬空 0.30m、藤蔓 0.35m；现落地件统一 h=0，自持参照地砖改 h=−0.30 使砖顶面落 0。②基地东门净空 —— 门洞净宽 2.2m（世界 gz∈[−3.6,−1.4]），东墙藤蔓 gz −5.0→−8.5、东侧大盆栽 −4.0→−6.2，另把正插在门洞正中的东墙立管 −2.0→+5.5。③藤蔓加高错落 —— 11 基座落地 + 5 件上层叠高（2.0/2.4/2.6/3.2/3.6m；运行时禁非单位缩放，故只能用叠件而非 scale）⇒ 顶高 5.80~7.40m。④新增「女儿墙挂藤」8 件，贴外圈女儿墙中心线（四边各 2，宽度与 5m 直段同宽）。重放实例 99 → 112 / 6 组。运行时重放 99 个装饰实例/5组＝空调与通风口6+绿化20+藤蔓11+水管54+立管支架8；布局源按 Godot 世界平面口径书写、写入 Blender 只做 by=−gz 一步换算，运行时用 (x, h, −by) 还原，并断言换算后必须落在 ROOFTOP_WORLD_RECT 内；装饰贴的是 Base100UpperShell（30×30，中心 (0,5)，东墙门 z=−2.5）的外墙皮；全部实例缩放=1且启用碰撞=0；结构壳体（234地砖/68件女儿墙/楼梯与碰撞）仍由 TowerFloorStage3D 拥有。2026-09-21 修正三处：①缺 by=−gz 换算 ⇒ 整份布局南北镜像、整体偏北 10m；②房屋误做 20×20 且偏北，装饰随之偏；③布局源的 24 墙+36 封顶与 Base100UpperShell 自带件重复，改名 shell_reference（仅 Blender 侧参照、不重放），避免逐面 z-fighting。2026-09-21 三次修正（业主实机报「水管接下来接到地板上面基本看不到 / 空调机在墙上的状态需要 90 度旋转让风扇朝外」）：①立管落地 —— pipe_riser 件高 4.945m、原点在管底、顶端是朝 +X 的鹅颈出水口；旧版放 h=5.8 ⇒ 管底悬空 5.8m。现每处摆两段、两段 h 都是 4.945：下段 rotation_x_deg=180 倒装（包络 0~4.945m，原点即上端）、上段正装（4.945~9.89m），合成一根 0~9.89m 连续落水管，与 10.65m 环管之间残留 0.76m 由环管本体与支架轨遮住；支架补一段低位（1.5m）与原有 7.0m 位，覆盖 1.56~10.64m。②墙挂空调倾倒 —— 新增实例朝向分量 rotation_x_deg（绕自身 X 轴的倾倒）；组件 hvac_small 顶面（Blender 局部 +Z）是出风风扇、前面（局部 −Y）是进风格栅，故 4 台墙挂机统一 rotation_x_deg=90 让风扇朝外（旧版风扇朝天）。⚠️ Blender 默认 XYZ 序、Godot 默认 YXZ 序，只有 rz 分量为 0 时 Rz@Rx 与 Ry@Rx 同序、角度可逐值搬运，本布局遵守该约束（tip 只与 yaw 组合）。③立管/支架按各自墙面给 yaw（旧版立管一律 0 ⇒ 东西墙鹅颈朝墙里）；6 个墙挂件（4 空调 + 2 通风口）后背统一埋进墙外皮内 0.05m。重放实例 112 → 120（pipe_risers 8 → 16）。2026-09-21 四次修正（业主实机报「花盆和花圃没有阻挡」）：绿化 20 件（8 花箱 + 6 大盆栽 + 6 小盆栽）由 visual_only 改 blocking —— 布局源 add() 新增实例级 collision 策略（词表 visual_only / blocking，白名单 flowerbox / plant_large / plant_small），运行时 TowerFloorStage3D 新增 _apply_rooftop_collision_policy()：blocking 件用 TowerGeometry3D.resolve_visual_bounds() 量出**实测可视包络**、挂一个 StaticBody3D(BlockingCollision, layer=1, mask=0, PROCESS_MODE_ALWAYS) + BoxShape3D(BlockingBox) 代理挡玩家（尺寸随美术走、不写死常量），其余 462 件仍 visual_only（组件自带碰撞一律先关）。布局清单 design_intent/validation 记 blocking_collision_count=20 / visual_only_collision_count=462；校验器新增第 5 层断言（策略词表 + 白名单 slug + 计数 + 清单交叉一致）。反向对照：把 20 件翻回 visual_only ⇒ 两份运行时探针 exit 1、QA 报 3 条 FAIL；还原后 .blend 与 .json 逐字节一致。2026-09-21 五次修正（业主实机报「花盆和花圃靠墙太远了，要挨着墙放，不然还有个空虚」）：绿化环由「离墙中心线 2.15m 单一环线」改为**逐件按自身半进深背贴建筑外皮** —— 件心离墙中心线 = SHELL_WALL_T/2 − WALL_MOUNT_EMBED(0.05) + half_depth（背面埋进外皮 0.05m，与墙挂空调同口径）；花箱 0.5925 / 大盆栽 0.8727377 / 小盆栽 0.5473868，南/北/东/西四边各成对，背面齐平、正面自然错落（旧版每件背后空 1.14~1.45m 可见地砖带）。朝向补齐：三件 front_direction 均为 −Y ⇒ yaw 0/π/+π/2/−π/2 分别朝南/北/东/西（旧版西侧花圃 +π/2 正面朝墙里、与同墙藤蔓 −π/2 矛盾，一并修正）。布局 QA 新增「3e 绿化背贴外皮」断言（背面埋入量 = 0.05、沿墙法线跨度 = 2×半进深），可反向对照。重放实例仍 120/6 组、构件计数与 blocking 20 不变。</t>
+          <t>2026-09-21 二次修正（业主实机报「花圃花盆悬空 / 藤蔓要更高更错落 / 挡门 / 加栏杆挂藤」）：①竖向基准 —— 运行时天台承重面 y=0（TowerFloorStage3D 把地砖可视顶面对齐到 Y=0），而布局源把落地装饰写在 h=0.3（= 自持地砖顶面），地砖组又不进重放 ⇒ 实机花草整块砖厚悬空 0.30m、藤蔓 0.35m；现落地件统一 h=0，自持参照地砖改 h=−0.30 使砖顶面落 0。②基地东门净空 —— 门洞净宽 2.2m（世界 gz∈[−3.6,−1.4]），东墙藤蔓 gz −5.0→−8.5、东侧大盆栽 −4.0→−6.2，另把正插在门洞正中的东墙立管 −2.0→+5.5。③藤蔓加高错落 —— 11 基座落地 + 5 件上层叠高（2.0/2.4/2.6/3.2/3.6m；运行时禁非单位缩放，故只能用叠件而非 scale）⇒ 顶高 5.80~7.40m。④新增「女儿墙挂藤」8 件，贴外圈女儿墙中心线（四边各 2，宽度与 5m 直段同宽）。重放实例 99 → 112 / 6 组。运行时重放 99 个装饰实例/5组＝空调与通风口6+绿化20+藤蔓11+水管54+立管支架8；布局源按 Godot 世界平面口径书写、写入 Blender 只做 by=−gz 一步换算，运行时用 (x, h, −by) 还原，并断言换算后必须落在 ROOFTOP_WORLD_RECT 内；装饰贴的是 Base100UpperShell（30×30，中心 (0,5)，东墙门 z=−2.5）的外墙皮；全部实例缩放=1且启用碰撞=0；结构壳体（234地砖/68件女儿墙/楼梯与碰撞）仍由 TowerFloorStage3D 拥有。2026-09-21 修正三处：①缺 by=−gz 换算 ⇒ 整份布局南北镜像、整体偏北 10m；②房屋误做 20×20 且偏北，装饰随之偏；③布局源的 24 墙+36 封顶与 Base100UpperShell 自带件重复，改名 shell_reference（仅 Blender 侧参照、不重放），避免逐面 z-fighting。2026-09-21 三次修正（业主实机报「水管接下来接到地板上面基本看不到 / 空调机在墙上的状态需要 90 度旋转让风扇朝外」）：①立管落地 —— pipe_riser 件高 4.945m、原点在管底、顶端是朝 +X 的鹅颈出水口；旧版放 h=5.8 ⇒ 管底悬空 5.8m。现每处摆两段、两段 h 都是 4.945：下段 rotation_x_deg=180 倒装（包络 0~4.945m，原点即上端）、上段正装（4.945~9.89m），合成一根 0~9.89m 连续落水管，与 10.65m 环管之间残留 0.76m 由环管本体与支架轨遮住；支架补一段低位（1.5m）与原有 7.0m 位，覆盖 1.56~10.64m。②墙挂空调倾倒 —— 新增实例朝向分量 rotation_x_deg（绕自身 X 轴的倾倒）；组件 hvac_small 顶面（Blender 局部 +Z）是出风风扇、前面（局部 −Y）是进风格栅，故 4 台墙挂机统一 rotation_x_deg=90 让风扇朝外（旧版风扇朝天）。⚠️ Blender 默认 XYZ 序、Godot 默认 YXZ 序，只有 rz 分量为 0 时 Rz@Rx 与 Ry@Rx 同序、角度可逐值搬运，本布局遵守该约束（tip 只与 yaw 组合）。③立管/支架按各自墙面给 yaw（旧版立管一律 0 ⇒ 东西墙鹅颈朝墙里）；6 个墙挂件（4 空调 + 2 通风口）后背统一埋进墙外皮内 0.05m。重放实例 112 → 120（pipe_risers 8 → 16）。2026-09-21 四次修正（业主实机报「花盆和花圃没有阻挡」）：绿化 20 件（8 花箱 + 6 大盆栽 + 6 小盆栽）由 visual_only 改 blocking —— 布局源 add() 新增实例级 collision 策略（词表 visual_only / blocking，白名单 flowerbox / plant_large / plant_small），运行时 TowerFloorStage3D 新增 _apply_rooftop_collision_policy()：blocking 件用 TowerGeometry3D.resolve_visual_bounds() 量出**实测可视包络**、挂一个 StaticBody3D(BlockingCollision, layer=1, mask=0, PROCESS_MODE_ALWAYS) + BoxShape3D(BlockingBox) 代理挡玩家（尺寸随美术走、不写死常量），其余 462 件仍 visual_only（组件自带碰撞一律先关）。布局清单 design_intent/validation 记 blocking_collision_count=20 / visual_only_collision_count=462；校验器新增第 5 层断言（策略词表 + 白名单 slug + 计数 + 清单交叉一致）。反向对照：把 20 件翻回 visual_only ⇒ 两份运行时探针 exit 1、QA 报 3 条 FAIL；还原后 .blend 与 .json 逐字节一致。2026-09-21 五次修正（业主实机报「花盆和花圃靠墙太远了，要挨着墙放，不然还有个空虚」）：绿化环由「离墙中心线 2.15m 单一环线」改为**逐件按自身半进深背贴建筑外皮** —— 件心离墙中心线 = SHELL_WALL_T/2 − WALL_MOUNT_EMBED(0.05) + half_depth（背面埋进外皮 0.05m，与墙挂空调同口径）；花箱 0.5925 / 大盆栽 0.8727377 / 小盆栽 0.5473868，南/北/东/西四边各成对，背面齐平、正面自然错落（旧版每件背后空 1.14~1.45m 可见地砖带）。朝向补齐：三件 front_direction 均为 −Y ⇒ yaw 0/π/+π/2/−π/2 分别朝南/北/东/西（旧版西侧花圃 +π/2 正面朝墙里、与同墙藤蔓 −π/2 矛盾，一并修正）。布局 QA 新增「3e 绿化背贴外皮」断言（背面埋入量 = 0.05、沿墙法线跨度 = 2×半进深），可反向对照。重放实例仍 120/6 组、构件计数与 blocking 20 不变。2026-09-22 六次修正（业主口径「所有楼层都和 100 层面积一致」）：塔楼壳体平面由 18×16 格（90×80m）向东再扩 2 格到 20×16 格（100×80m），98F/99F/100F 三层共用同一矩形（TOWER_SHELL_WORLD_RECT = (-50,-35,100,80)，中心 (0,5)，8000㎡）；原先「100F 走 90×80、99F 楼板 250×250 / 外墙 160×160、普通层 250×250」三套口径作废。驱动原因：east 楼梯井（99↔98）外廓是固定世界常量 x∈[35,50]，90m 窗口（东界 x=40）装不下它；100m 下两个在用井（west x[-45,-30]、east x[35,50]）全部落在壳体内。本布局随之重生成：自持地砖 234→266 块、外围女儿墙 68→72 件（64→68 直段 + 4 外角）；重放 6 组仍 120 件不变（装饰贴 30×30 房屋与环管，只有东侧贴 x_east 的 parapet_ivy 1 件由 x=39.75 东移到 49.75）。</t>
         </is>
       </c>
     </row>
@@ -38083,7 +38083,7 @@
       </c>
       <c r="M97" s="69" t="inlineStr">
         <is>
-          <t>100F天台地面 / 234块5m地砖满铺（替代 POLISHED_FLOOR）</t>
+          <t>100F天台地面 / 266块5m地砖满铺（替代 POLISHED_FLOOR）</t>
         </is>
       </c>
       <c r="N97" s="69" t="inlineStr">
@@ -38621,7 +38621,7 @@
         <is>
           <t>父库=ENV-ROOFTOP-REFERENCE-COMPONENT-LIBRARY；manifest=assets/art/environments/tower_zones/rooftop/source/reference_components/v002/component_packages_v002/02/parapet_outer/asset_manifest.json；外墙植物包络不进入阻挡；未导入Godot。
 2026-09-19：由「仅 Blender 源」升为运行时正式资产，本行不新增 AssetID（asset_version 仍 v002，与参考组件库同版）。实测 GLB 70,140 B / sha256 2bc924b4…，AABB=(-1.25,-1.25,0)~(1.25,1.25,1.8)（Blender Z-up，即 2.5×2.5×1.80）；顶点按象限统计 -X-Z:540 / -X+Z:888 / +X-Z:0 / +X+Z:540，即两臂落在 −X 与 +Z 边、开口朝 +X/−Z，臂中心线 x=−1.0 / z=+1.0。.import 同样绑共享色盘后处理，palette_texture_bound=true。
-只用「外角」一件：100F 天台轮廓是 90×80m 矩形、四个角全是阳角，无内凹，所以ENV-ROOFTOP-REF-PARAPET-INNER 不在本次范围内（保持未导入）。
+只用「外角」一件：100F 天台轮廓是 100×80m 矩形（2026-09-22 起；此前 90×80m）、四个角全是阳角，无内凹，所以ENV-ROOFTOP-REF-PARAPET-INNER 不在本次范围内（保持未导入）。
 放位：转角件包络 2.5×2.5，摆在该角 2.5m 让位区的中心，按角旋转 90° 整数倍——SW=(−48.75, 0, 43.75) rot 0 / SE=(38.75, 0, 43.75) rot π/2 / NE=(38.75, 0, −33.75) rot π / NW=(−48.75, 0, −33.75) rot 3π/2（俯视逆时针）。这套放位让两条臂的中心线正好落在相邻两边的 boundary 上，包络端点与相邻直段无缝相接。这替掉了原来「两根直段在角上交叉」的旧画法。碰撞仍是四边连续体，本 prefab 只产生视觉节点（visual_only / collision_owner=TowerFloorStage3D.OuterBoundaryCollision）。
 实测：probe_rooftop_parapet_alignment 四个转角件 span 尺寸均 2.500×2.500 且 position 与四个2.5m 让位区角点相等；corner_arm_centerlines / corner_open_facing 等朝向口径已写入 prefab 的metadata，供后续换件时核对。门禁 ROOFTOP_WEST_EXPANSION_CONTRACT_PASS 断言 outer_corner_count=4 与四件的位置/朝向（按 wrapf(actual-expected,-π,π) 比角）。
 2026-09-20：随直段一起改为 0.80m（同一套三块式配方）。asset_version v002→v003；GLB 同路径覆盖重导（21,768 B），AABB=2.5×2.5×0.80、底面中心、两臂中心线 x=−1.0 / z=+1.0 与开口朝向均不变；四角落座位置（SW/SE/NE/NW）不动。实测 probe_rooftop_parapet_alignment：转角件 4 件 span 均 2.500×2.500，四条边 coverage=全长 / gap=0.000 / overlap=0.000。</t>
@@ -41852,7 +41852,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>90×80m天台；外围68件（64直段+4外角）；234块5m地砖（开口=中庭6×6+西侧楼梯口3×6）</t>
+          <t>100×80m天台；外围72件（68直段+4外角）；266块5m地砖（开口=中庭6×6+西侧楼梯口3×6）</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr">
@@ -41877,7 +41877,7 @@
       </c>
       <c r="P146" s="3" t="inlineStr">
         <is>
-          <t>清单=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json；运行时登记=assets/art/environments/tower_zones/rooftop/runtime/rooftop_100f_decorated_runtime_manifest.json；验收=verify_rooftop_32x32_contract + probe_rooftop_decorated_layout + probe_rooftop_decorated_stage_only；全部实例缩放=1、启用碰撞=0；结构壳体（地砖/女儿墙）仍由 TowerFloorStage3D 负责，布局不重复生成；2026-09-21 坐标契约修正（补 by=−gz，此前整体偏北 10m）＋房屋 20×20→30×30 对齐 Base100UpperShell；2026-09-21 三次修正：立管落地 0~9.89m（h=件高4.945、倒装件原点在顶面）、墙挂空调绕 X 轴 90° 倾倒让风扇朝外（Godot 侧读 basis.y）、布局源只写 rotation_x_deg + rotation_y_deg（rz=0，规避 Blender XYZ 序 / Godot YXZ 序的次序差）；2026-09-21 四次修正：绿化 20 件改 blocking（运行时按 TowerGeometry3D.resolve_visual_bounds 实测可视包络生成 layer=1 BoxShape3D 代理挡玩家），其余 visual_only；collision_policy 词表=visual_only/blocking，清单设计意图记 blocking_collision_count=20 / visual_only_collision_count=462</t>
+          <t>清单=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json；运行时登记=assets/art/environments/tower_zones/rooftop/runtime/rooftop_100f_decorated_runtime_manifest.json；验收=verify_rooftop_32x32_contract + probe_rooftop_decorated_layout + probe_rooftop_decorated_stage_only；全部实例缩放=1、启用碰撞=0；结构壳体（地砖/女儿墙）仍由 TowerFloorStage3D 负责，布局不重复生成；2026-09-21 坐标契约修正（补 by=−gz，此前整体偏北 10m）＋房屋 20×20→30×30 对齐 Base100UpperShell；2026-09-21 三次修正：立管落地 0~9.89m（h=件高4.945、倒装件原点在顶面）、墙挂空调绕 X 轴 90° 倾倒让风扇朝外（Godot 侧读 basis.y）、布局源只写 rotation_x_deg + rotation_y_deg（rz=0，规避 Blender XYZ 序 / Godot YXZ 序的次序差）；2026-09-21 四次修正：绿化 20 件改 blocking（运行时按 TowerGeometry3D.resolve_visual_bounds 实测可视包络生成 layer=1 BoxShape3D 代理挡玩家），其余 visual_only；collision_policy 词表=visual_only/blocking，清单设计意图记 blocking_collision_count=20 / visual_only_collision_count=462；2026-09-22 六次修正：壳体几何由 TowerFloorStage3D 的 TOWER_SHELL_*（20×16 格 = 100×80m）统管 98F/99F/100F 三层；本行「外形尺寸」的 90×80m天台 / 外围68件（64直段+4外角）/ 234块5m地砖同步为 100×80m / 72件（68直段+4外角）/ 266块；重放 120 件与碰撞 20 件不变。</t>
         </is>
       </c>
     </row>
@@ -44017,7 +44017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="50" min="1" max="1"/>
@@ -44488,6 +44488,43 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="97" t="inlineStr">
+        <is>
+          <t>v0.1.11</t>
+        </is>
+      </c>
+      <c r="B17" s="97" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C17" s="97" t="inlineStr">
+        <is>
+          <t>条目修正</t>
+        </is>
+      </c>
+      <c r="D17" s="97" t="inlineStr">
+        <is>
+          <t>关卡场景 / 全塔壳体（100F天台 / 99F基地 / 98F主人的办公室）</t>
+        </is>
+      </c>
+      <c r="E17" s="97" t="inlineStr">
+        <is>
+          <t>塔楼三层壳体平面统一为 100×80m。业主口径「所有楼层都和 100 层面积一致」，据此把 TowerFloorStage3D 的壳体矩形由 18×16 格（90×80m）向东再扩 2 格到 20×16 格（100×80m），98F/99F/100F 三层共用；原先 100F 走 90×80、99F 走楼板 250×250 / 外墙 160×160、98F 走 250×250 的三套口径作废。驱动原因是 east 楼梯井（99↔98）外廓固定为 x∈[35,50]，90m 窗口装不下；100m 下 west x[-45,-30] 与 east x[35,50] 两个在用井都落在壳体内。100F 天台装饰布局随之重生成：自持地砖 234→266 块、外围女儿墙 68→72 件（64→68 直段+4外角），重放 6 组仍 120 件（仅东侧贴 x_east 的 parapet_ivy 1 件由 39.75 东移到 49.75）。运行时实测三层 map_size / grid_count / floor_world_rect / outer_world_rect 一致为 100×80，tile 266/266/311；立面无缝、四角就位。</t>
+        </is>
+      </c>
+      <c r="F17" s="97" t="inlineStr">
+        <is>
+          <t>AssetID / layout_id / layout_version 均不变（原地修正，不新增条目、不新增资产）；资产主表备注的 68件/234块 已同步为 72件/266块，blend sha256 同步更新，版本列仍 v001。</t>
+        </is>
+      </c>
+      <c r="G17" s="97" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -7627,22 +7627,22 @@
       </c>
       <c r="M54" s="76" t="inlineStr">
         <is>
-          <t>v002</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="N54" s="76" t="inlineStr">
         <is>
-          <t>5×5×0.3005m；716三角面；2材质；共享MultiMesh；承重面不变</t>
+          <t>5×5×0.304m；740三角面；2材质；共享MultiMesh；行走面锚点+0.1500不变；装饰件反共面阶梯+0.1520/+0.1540（XY重叠可见面高度差≥2mm）</t>
         </is>
       </c>
       <c r="O54" s="76" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_descent_3d/runtime/floor_tile_5m/env_tower_floor_tile_5m_root_top3d_v002.tscn</t>
+          <t>assets/art/environments/tower_descent_3d/runtime/floor_tile_5m/env_tower_floor_tile_5m_root_top3d.tscn</t>
         </is>
       </c>
       <c r="P54" s="76" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_descent_3d/source/floor_tile_5m/env_tower_floor_tile_5m_source_v002.blend；assets/art/environments/tower_descent_3d/components/floor_tile_5m/env_tower_floor_tile_5m_top3d_v002.glb；scripts/blender/build_tower_floor_tile_5m_v002.py；tests/verification/verify_tower_journey_polish.tscn</t>
+          <t>assets/art/environments/tower_descent_3d/source/floor_tile_5m/env_tower_floor_tile_5m_source_v003.blend; assets/art/environments/tower_descent_3d/components/floor_tile_5m/env_tower_floor_tile_5m_top3d.glb; scripts/blender/build_tower_floor_tile_5m_v003.py; assets/art/props/dungeon_3d/prp_tower_floor_tile_5m.tscn; tests/verification/verify_tower_journey_polish.tscn</t>
         </is>
       </c>
       <c r="Q54" s="76" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="T54" s="76" t="inlineStr">
         <is>
-          <t>0678524ecdbca8efc085fa4bb65535c63aacc3397fcda0a85542236b1137d185</t>
+          <t>3eb08fd277af14d56a25f55f3bb7e714c9855e21cd549596969686591b389cf6</t>
         </is>
       </c>
       <c r="U54" s="76" t="inlineStr">
@@ -7668,8 +7668,10 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V54" s="77" t="n">
-        <v>46271</v>
+      <c r="V54" s="77" t="inlineStr">
+        <is>
+          <t>2026-09-22 00:00:00</t>
+        </is>
       </c>
       <c r="W54" s="76" t="inlineStr">
         <is>
@@ -7686,7 +7688,8 @@
           <t>2026-08-02：复用于99层楼梯间—基地房间的15m/20m接驳走廊地面，继续遵守5m网格与不透明材质规范。
 2026-08-03：水平通道按每5m一块动态生成地砖实例；使用MultiMesh批量提交但保留逐格坐标，禁止拉伸单块Mesh代替模块拼接。
 2026-08-18：保留通用塔楼地板稳定ID；基地地板另登记ENV-BASE99-FLOOR-PLAIN-5M / RIVET-5M。本轮地板运行时不切换，允许临时复用。
-2026-09-06：纠正旧台账GLB与实际BoxMesh引用差异。v002工业面板、金属压边、紧固槽与检修盖正式接入100F/98F；单包410面逐面PaletteUV验收通过。</t>
+2026-09-06：纠正旧台账GLB与实际BoxMesh引用差异。v002工业面板、金属压边、紧固槽与检修盖正式接入100F/98F；单包410面逐面PaletteUV验收通过。
+2026-09-22：修复细节级闪面（z-fighting）升 v003。v002 顶面四家族（哑光面板/角部紧固座/紧固槽/检修盖板）同落 +0.1500 且 XY 互叠（跨零件共面 13 对、0.3745㎡，最严重一处为检修盖板整片 0.324㎡），相机贴地观察时逐像素闪烁；另一并存缺陷是检修盖框顶面 +0.1480，比面板低 2mm 被永久埋没不可见。v003 采用反共面阶梯：行走面锚点 +0.1500 不动（TowerFloorStage3D 固定 -FLOOR_THICKNESS*0.5=-0.15 偏移契约不受影响），盖框/紧固座/警示短标抬到 +0.1520，紧固槽/盖板格栅条抬到 +0.1540，并将检修盖缝改为 2mm 真实凹槽（通透负空间）。本件与 prp_tower_floor_tile_5m.tscn 共用同一个已去版本化的 GLB，故 98F 标准砖与远征/98F 抛光砖同时受益；99F 自持地砖不受影响。</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -1166,22 +1166,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="50">
       <c r="A6" s="55">
-        <f>=COUNTA(资产主表!$A$6:$A$240)</f>
+        <f>=COUNTA(资产主表!$A$6:$A$241)</f>
         <v/>
       </c>
       <c r="B6" s="53" t="inlineStr"/>
       <c r="C6" s="55">
-        <f>=COUNTIF(资产主表!$K$6:$K$240,"已完成")+COUNTIF(资产主表!$K$6:$K$240,"原型已接入")+COUNTIF(资产主表!$K$6:$K$240,"正式美术已接入")+COUNTIF(资产主表!$K$6:$K$240,"已优化并正式接入")+COUNTIF(资产主表!$K$6:$K$240,"Blender源已完成")+COUNTIF(资产主表!$K$6:$K$240,"已导入；优化完成")</f>
+        <f>=COUNTIF(资产主表!$K$6:$K$241,"已完成")+COUNTIF(资产主表!$K$6:$K$241,"原型已接入")+COUNTIF(资产主表!$K$6:$K$241,"正式美术已接入")+COUNTIF(资产主表!$K$6:$K$241,"已优化并正式接入")+COUNTIF(资产主表!$K$6:$K$241,"Blender源已完成")+COUNTIF(资产主表!$K$6:$K$241,"已导入；优化完成")</f>
         <v/>
       </c>
       <c r="D6" s="53" t="inlineStr"/>
       <c r="E6" s="55">
-        <f>=COUNTIF(资产主表!$K$6:$K$240,"待制作")+COUNTIF(资产主表!$K$6:$K$240,"程序占位")</f>
+        <f>=COUNTIF(资产主表!$K$6:$K$241,"待制作")+COUNTIF(资产主表!$K$6:$K$241,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="53" t="inlineStr"/>
       <c r="G6" s="55">
-        <f>=COUNTIF(资产主表!$S$6:$S$240,"重复")</f>
+        <f>=COUNTIF(资产主表!$S$6:$S$241,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="53" t="inlineStr"/>
@@ -1250,11 +1250,11 @@
         </is>
       </c>
       <c r="B10" s="60">
-        <f>=COUNTIF(资产主表!$C$6:$C$240,A10)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$241,A10)</f>
         <v/>
       </c>
       <c r="C10" s="60">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$240=A10)*((资产主表!$K$6:$K$240="已完成")+(资产主表!$K$6:$K$240="原型已接入")+(资产主表!$K$6:$K$240="正式美术已接入")+(资产主表!$K$6:$K$240="已优化并正式接入")+(资产主表!$K$6:$K$240="Blender源已完成")+(资产主表!$K$6:$K$240="已导入；优化完成")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$241=A10)*((资产主表!$K$6:$K$241="已完成")+(资产主表!$K$6:$K$241="原型已接入")+(资产主表!$K$6:$K$241="正式美术已接入")+(资产主表!$K$6:$K$241="已优化并正式接入")+(资产主表!$K$6:$K$241="Blender源已完成")+(资产主表!$K$6:$K$241="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D10" s="60" t="inlineStr"/>
@@ -1272,11 +1272,11 @@
         </is>
       </c>
       <c r="B11" s="60">
-        <f>=COUNTIF(资产主表!$C$6:$C$240,A11)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$241,A11)</f>
         <v/>
       </c>
       <c r="C11" s="60">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$240=A11)*((资产主表!$K$6:$K$240="已完成")+(资产主表!$K$6:$K$240="原型已接入")+(资产主表!$K$6:$K$240="正式美术已接入")+(资产主表!$K$6:$K$240="已优化并正式接入")+(资产主表!$K$6:$K$240="Blender源已完成")+(资产主表!$K$6:$K$240="已导入；优化完成")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$241=A11)*((资产主表!$K$6:$K$241="已完成")+(资产主表!$K$6:$K$241="原型已接入")+(资产主表!$K$6:$K$241="正式美术已接入")+(资产主表!$K$6:$K$241="已优化并正式接入")+(资产主表!$K$6:$K$241="Blender源已完成")+(资产主表!$K$6:$K$241="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D11" s="60" t="inlineStr"/>
@@ -1294,11 +1294,11 @@
         </is>
       </c>
       <c r="B12" s="60">
-        <f>=COUNTIF(资产主表!$C$6:$C$240,A12)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$241,A12)</f>
         <v/>
       </c>
       <c r="C12" s="60">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$240=A12)*((资产主表!$K$6:$K$240="已完成")+(资产主表!$K$6:$K$240="原型已接入")+(资产主表!$K$6:$K$240="正式美术已接入")+(资产主表!$K$6:$K$240="已优化并正式接入")+(资产主表!$K$6:$K$240="Blender源已完成")+(资产主表!$K$6:$K$240="已导入；优化完成")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$241=A12)*((资产主表!$K$6:$K$241="已完成")+(资产主表!$K$6:$K$241="原型已接入")+(资产主表!$K$6:$K$241="正式美术已接入")+(资产主表!$K$6:$K$241="已优化并正式接入")+(资产主表!$K$6:$K$241="Blender源已完成")+(资产主表!$K$6:$K$241="已导入；优化完成")))</f>
         <v/>
       </c>
       <c r="D12" s="60" t="inlineStr"/>
@@ -1882,7 +1882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y240"/>
+  <dimension ref="A1:Y241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="50" min="1" max="1"/>
@@ -2158,7 +2158,7 @@
         <v/>
       </c>
       <c r="S6" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="73" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
         <v/>
       </c>
       <c r="S7" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="73" t="inlineStr"/>
@@ -2372,7 +2372,7 @@
         <v/>
       </c>
       <c r="S8" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="73" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
         <v/>
       </c>
       <c r="S9" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="73" t="inlineStr"/>
@@ -2586,7 +2586,7 @@
         <v/>
       </c>
       <c r="S10" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="73" t="inlineStr"/>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="S11" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="73" t="inlineStr"/>
@@ -2800,7 +2800,7 @@
         <v/>
       </c>
       <c r="S12" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="73" t="inlineStr"/>
@@ -2907,7 +2907,7 @@
         <v/>
       </c>
       <c r="S13" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="73" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
         <v/>
       </c>
       <c r="S14" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="73" t="inlineStr"/>
@@ -3121,7 +3121,7 @@
         <v/>
       </c>
       <c r="S15" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="73" t="inlineStr"/>
@@ -3228,7 +3228,7 @@
         <v/>
       </c>
       <c r="S16" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="73" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
         <v/>
       </c>
       <c r="S17" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="73" t="inlineStr"/>
@@ -3442,7 +3442,7 @@
         <v/>
       </c>
       <c r="S18" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="73" t="inlineStr"/>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="S19" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="73" t="inlineStr"/>
@@ -3656,7 +3656,7 @@
         <v/>
       </c>
       <c r="S20" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="73" t="inlineStr"/>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="S21" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="73" t="inlineStr"/>
@@ -3870,7 +3870,7 @@
         <v/>
       </c>
       <c r="S22" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="73" t="inlineStr"/>
@@ -3977,7 +3977,7 @@
         <v/>
       </c>
       <c r="S23" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="73" t="inlineStr"/>
@@ -4084,7 +4084,7 @@
         <v/>
       </c>
       <c r="S24" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="73" t="inlineStr"/>
@@ -4191,7 +4191,7 @@
         <v/>
       </c>
       <c r="S25" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="73" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
         <v/>
       </c>
       <c r="S26" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="73" t="inlineStr"/>
@@ -4405,7 +4405,7 @@
         <v/>
       </c>
       <c r="S27" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="73" t="inlineStr"/>
@@ -4512,7 +4512,7 @@
         <v/>
       </c>
       <c r="S28" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="73" t="inlineStr"/>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="S29" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="73" t="inlineStr"/>
@@ -4726,7 +4726,7 @@
         <v/>
       </c>
       <c r="S30" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="73" t="inlineStr"/>
@@ -4833,7 +4833,7 @@
         <v/>
       </c>
       <c r="S31" s="73">
-        <f>IF(COUNTIF($R$6:$R$240,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="73" t="inlineStr"/>
@@ -4952,7 +4952,7 @@
         <v/>
       </c>
       <c r="S32" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="76" t="inlineStr">
@@ -5075,7 +5075,7 @@
         <v/>
       </c>
       <c r="S33" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="69" t="inlineStr">
@@ -5198,7 +5198,7 @@
         <v/>
       </c>
       <c r="S34" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="69" t="inlineStr">
@@ -5321,7 +5321,7 @@
         <v/>
       </c>
       <c r="S35" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="69" t="inlineStr">
@@ -5444,7 +5444,7 @@
         <v/>
       </c>
       <c r="S36" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="76" t="inlineStr">
@@ -5568,7 +5568,7 @@
         <v/>
       </c>
       <c r="S37" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="69" t="inlineStr">
@@ -5691,7 +5691,7 @@
         <v/>
       </c>
       <c r="S38" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="69" t="inlineStr">
@@ -5810,7 +5810,7 @@
         <v/>
       </c>
       <c r="S39" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="76" t="inlineStr">
@@ -5933,7 +5933,7 @@
         <v/>
       </c>
       <c r="S40" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="69" t="inlineStr">
@@ -6056,7 +6056,7 @@
         <v/>
       </c>
       <c r="S41" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="69" t="inlineStr">
@@ -6179,7 +6179,7 @@
         <v/>
       </c>
       <c r="S42" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="69" t="inlineStr">
@@ -6302,7 +6302,7 @@
         <v/>
       </c>
       <c r="S43" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="69" t="inlineStr">
@@ -6425,7 +6425,7 @@
         <v/>
       </c>
       <c r="S44" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="76" t="inlineStr">
@@ -6549,7 +6549,7 @@
         <v/>
       </c>
       <c r="S45" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="69" t="inlineStr">
@@ -6672,7 +6672,7 @@
         <v/>
       </c>
       <c r="S46" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="69" t="inlineStr">
@@ -6795,7 +6795,7 @@
         <v/>
       </c>
       <c r="S47" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="69" t="inlineStr">
@@ -6918,7 +6918,7 @@
         <v/>
       </c>
       <c r="S48" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R48)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R48)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T48" s="69" t="inlineStr">
@@ -7038,7 +7038,7 @@
         <v/>
       </c>
       <c r="S49" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R49)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R49)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T49" s="69" t="inlineStr">
@@ -7161,7 +7161,7 @@
         <v/>
       </c>
       <c r="S50" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R50)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R50)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T50" s="69" t="inlineStr">
@@ -7285,7 +7285,7 @@
         <v/>
       </c>
       <c r="S51" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R51)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R51)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T51" s="69" t="inlineStr">
@@ -7408,7 +7408,7 @@
         <v/>
       </c>
       <c r="S52" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R52)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R52)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T52" s="76" t="inlineStr">
@@ -7532,7 +7532,7 @@
         <v/>
       </c>
       <c r="S53" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R53)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R53)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T53" s="76" t="inlineStr">
@@ -7655,7 +7655,7 @@
         <v/>
       </c>
       <c r="S54" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R54)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R54)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T54" s="76" t="inlineStr">
@@ -7784,7 +7784,7 @@
         <v/>
       </c>
       <c r="S55" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R55)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R55)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T55" s="76" t="inlineStr">
@@ -7911,7 +7911,7 @@
         <v/>
       </c>
       <c r="S56" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R56)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R56)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T56" s="76" t="inlineStr">
@@ -8034,7 +8034,7 @@
         <v/>
       </c>
       <c r="S57" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R57)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R57)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T57" s="76" t="inlineStr">
@@ -8159,7 +8159,7 @@
         <v/>
       </c>
       <c r="S58" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R58)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R58)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T58" s="76" t="inlineStr">
@@ -8282,7 +8282,7 @@
         <v/>
       </c>
       <c r="S59" s="76">
-        <f>IF(COUNTIF($R$6:$R$240,R59)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R59)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T59" s="76" t="inlineStr">
@@ -8401,7 +8401,7 @@
         <v/>
       </c>
       <c r="S60" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R60)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R60)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T60" s="69" t="inlineStr">
@@ -8521,7 +8521,7 @@
         <v/>
       </c>
       <c r="S61" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R61)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R61)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T61" s="69" t="inlineStr">
@@ -8641,7 +8641,7 @@
         <v/>
       </c>
       <c r="S62" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R62)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R62)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T62" s="69" t="inlineStr">
@@ -8761,7 +8761,7 @@
         <v/>
       </c>
       <c r="S63" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R63)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R63)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T63" s="69" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
         <v/>
       </c>
       <c r="S64" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R64)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R64)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T64" s="69" t="inlineStr">
@@ -9006,7 +9006,7 @@
         <v/>
       </c>
       <c r="S65" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R65)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R65)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T65" s="69" t="inlineStr">
@@ -9131,7 +9131,7 @@
         <v/>
       </c>
       <c r="S66" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R66)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R66)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T66" s="69" t="inlineStr">
@@ -9256,7 +9256,7 @@
         <v/>
       </c>
       <c r="S67" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R67)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R67)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T67" s="69" t="inlineStr">
@@ -9381,7 +9381,7 @@
         <v/>
       </c>
       <c r="S68" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R68)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R68)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T68" s="69" t="inlineStr">
@@ -9512,7 +9512,7 @@
         <v/>
       </c>
       <c r="S69" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R69)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R69)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T69" s="69" t="inlineStr">
@@ -9638,7 +9638,7 @@
         <v/>
       </c>
       <c r="S70" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R70)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R70)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T70" s="69" t="inlineStr">
@@ -9762,7 +9762,7 @@
         <v/>
       </c>
       <c r="S71" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R71)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R71)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T71" s="69" t="inlineStr">
@@ -9886,7 +9886,7 @@
         <v/>
       </c>
       <c r="S72" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R72)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R72)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T72" s="69" t="inlineStr">
@@ -10010,7 +10010,7 @@
         <v/>
       </c>
       <c r="S73" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R73)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R73)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T73" s="69" t="inlineStr">
@@ -10134,7 +10134,7 @@
         <v/>
       </c>
       <c r="S74" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R74)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R74)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T74" s="69" t="inlineStr">
@@ -10258,7 +10258,7 @@
         <v/>
       </c>
       <c r="S75" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R75)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R75)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T75" s="69" t="inlineStr">
@@ -10382,7 +10382,7 @@
         <v/>
       </c>
       <c r="S76" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R76)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R76)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T76" s="69" t="inlineStr">
@@ -10506,7 +10506,7 @@
         <v/>
       </c>
       <c r="S77" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R77)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R77)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T77" s="69" t="inlineStr">
@@ -10630,7 +10630,7 @@
         <v/>
       </c>
       <c r="S78" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R78)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R78)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T78" s="69" t="inlineStr">
@@ -10754,7 +10754,7 @@
         <v/>
       </c>
       <c r="S79" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R79)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R79)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T79" s="69" t="inlineStr">
@@ -10878,7 +10878,7 @@
         <v/>
       </c>
       <c r="S80" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R80)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R80)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T80" s="69" t="inlineStr">
@@ -11002,7 +11002,7 @@
         <v/>
       </c>
       <c r="S81" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R81)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R81)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T81" s="69" t="inlineStr">
@@ -11126,7 +11126,7 @@
         <v/>
       </c>
       <c r="S82" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R82)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R82)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T82" s="69" t="inlineStr">
@@ -11250,7 +11250,7 @@
         <v/>
       </c>
       <c r="S83" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R83)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R83)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T83" s="69" t="inlineStr">
@@ -11374,7 +11374,7 @@
         <v/>
       </c>
       <c r="S84" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R84)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R84)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T84" s="69" t="inlineStr">
@@ -11498,7 +11498,7 @@
         <v/>
       </c>
       <c r="S85" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R85)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R85)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T85" s="69" t="inlineStr">
@@ -11622,7 +11622,7 @@
         <v/>
       </c>
       <c r="S86" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R86)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R86)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T86" s="69" t="inlineStr">
@@ -11746,7 +11746,7 @@
         <v/>
       </c>
       <c r="S87" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R87)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R87)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T87" s="69" t="inlineStr">
@@ -11870,7 +11870,7 @@
         <v/>
       </c>
       <c r="S88" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R88)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R88)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T88" s="69" t="inlineStr">
@@ -11994,7 +11994,7 @@
         <v/>
       </c>
       <c r="S89" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R89)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R89)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T89" s="69" t="inlineStr">
@@ -12118,7 +12118,7 @@
         <v/>
       </c>
       <c r="S90" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R90)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R90)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T90" s="69" t="inlineStr">
@@ -12242,7 +12242,7 @@
         <v/>
       </c>
       <c r="S91" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R91)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R91)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T91" s="69" t="inlineStr">
@@ -12366,7 +12366,7 @@
         <v/>
       </c>
       <c r="S92" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R92)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R92)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T92" s="69" t="inlineStr">
@@ -12490,7 +12490,7 @@
         <v/>
       </c>
       <c r="S93" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R93)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R93)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T93" s="69" t="inlineStr">
@@ -12614,7 +12614,7 @@
         <v/>
       </c>
       <c r="S94" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R94)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R94)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T94" s="69" t="inlineStr">
@@ -12738,7 +12738,7 @@
         <v/>
       </c>
       <c r="S95" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R95)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R95)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T95" s="69" t="inlineStr">
@@ -12862,7 +12862,7 @@
         <v/>
       </c>
       <c r="S96" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R96)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R96)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T96" s="69" t="inlineStr">
@@ -12986,7 +12986,7 @@
         <v/>
       </c>
       <c r="S97" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R97)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R97)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T97" s="69" t="inlineStr">
@@ -13110,7 +13110,7 @@
         <v/>
       </c>
       <c r="S98" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R98)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R98)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T98" s="69" t="inlineStr">
@@ -13234,7 +13234,7 @@
         <v/>
       </c>
       <c r="S99" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R99)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R99)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T99" s="69" t="inlineStr">
@@ -13358,7 +13358,7 @@
         <v/>
       </c>
       <c r="S100" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R100)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R100)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T100" s="69" t="inlineStr">
@@ -13482,7 +13482,7 @@
         <v/>
       </c>
       <c r="S101" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R101)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R101)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T101" s="69" t="inlineStr">
@@ -13606,7 +13606,7 @@
         <v/>
       </c>
       <c r="S102" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R102)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R102)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T102" s="69" t="inlineStr">
@@ -13729,7 +13729,7 @@
         <v/>
       </c>
       <c r="S103" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R103)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R103)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T103" s="69" t="inlineStr">
@@ -13854,7 +13854,7 @@
         <v/>
       </c>
       <c r="S104" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R104)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R104)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T104" s="69" t="inlineStr">
@@ -13979,7 +13979,7 @@
         <v/>
       </c>
       <c r="S105" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R105)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R105)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T105" s="69" t="inlineStr">
@@ -14104,7 +14104,7 @@
         <v/>
       </c>
       <c r="S106" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R106)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R106)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T106" s="69" t="inlineStr">
@@ -14229,7 +14229,7 @@
         <v/>
       </c>
       <c r="S107" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R107)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R107)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T107" s="69" t="inlineStr">
@@ -14354,7 +14354,7 @@
         <v/>
       </c>
       <c r="S108" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R108)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R108)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T108" s="79" t="inlineStr">
@@ -14480,7 +14480,7 @@
         <v/>
       </c>
       <c r="S109" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R109)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R109)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T109" s="69" t="inlineStr">
@@ -14606,7 +14606,7 @@
         <v/>
       </c>
       <c r="S110" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R110)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R110)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T110" s="69" t="inlineStr">
@@ -14732,7 +14732,7 @@
         <v/>
       </c>
       <c r="S111" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R111)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R111)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T111" s="69" t="inlineStr">
@@ -14858,7 +14858,7 @@
         <v/>
       </c>
       <c r="S112" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R112)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R112)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T112" s="69" t="inlineStr">
@@ -14981,7 +14981,7 @@
         <v/>
       </c>
       <c r="S113" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R113)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R113)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T113" s="69" t="inlineStr">
@@ -15101,7 +15101,7 @@
         <v/>
       </c>
       <c r="S114" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R114)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R114)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T114" s="79" t="inlineStr">
@@ -15220,7 +15220,7 @@
         <v/>
       </c>
       <c r="S115" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R115)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R115)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T115" s="79" t="inlineStr">
@@ -15338,7 +15338,7 @@
         <v/>
       </c>
       <c r="S116" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R116)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R116)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T116" s="79" t="inlineStr">
@@ -15461,7 +15461,7 @@
         <v/>
       </c>
       <c r="S117" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R117)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R117)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T117" s="69" t="inlineStr">
@@ -15587,7 +15587,7 @@
         <v/>
       </c>
       <c r="S118" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R118)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R118)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T118" s="69" t="inlineStr">
@@ -15710,7 +15710,7 @@
         <v/>
       </c>
       <c r="S119" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R119)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R119)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T119" s="69" t="inlineStr">
@@ -15835,7 +15835,7 @@
         <v/>
       </c>
       <c r="S120" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R120)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R120)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T120" s="69" t="inlineStr">
@@ -15958,7 +15958,7 @@
         <v/>
       </c>
       <c r="S121" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R121)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R121)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T121" s="69" t="inlineStr">
@@ -16083,7 +16083,7 @@
         <v/>
       </c>
       <c r="S122" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R122)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R122)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T122" s="69" t="inlineStr">
@@ -16206,7 +16206,7 @@
         <v/>
       </c>
       <c r="S123" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R123)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R123)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T123" s="69" t="inlineStr">
@@ -16329,7 +16329,7 @@
         <v/>
       </c>
       <c r="S124" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R124)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R124)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T124" s="69" t="inlineStr">
@@ -16452,7 +16452,7 @@
         <v/>
       </c>
       <c r="S125" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R125)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R125)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T125" s="69" t="inlineStr">
@@ -16575,7 +16575,7 @@
         <v/>
       </c>
       <c r="S126" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R126)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R126)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T126" s="69" t="inlineStr">
@@ -16698,7 +16698,7 @@
         <v/>
       </c>
       <c r="S127" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R127)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R127)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T127" s="69" t="inlineStr">
@@ -16821,7 +16821,7 @@
         <v/>
       </c>
       <c r="S128" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R128)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R128)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T128" s="69" t="inlineStr">
@@ -16944,7 +16944,7 @@
         <v/>
       </c>
       <c r="S129" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R129)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R129)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T129" s="69" t="inlineStr">
@@ -17067,7 +17067,7 @@
         <v/>
       </c>
       <c r="S130" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R130)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R130)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T130" s="69" t="inlineStr">
@@ -17190,7 +17190,7 @@
         <v/>
       </c>
       <c r="S131" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R131)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R131)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T131" s="69" t="inlineStr">
@@ -17313,7 +17313,7 @@
         <v/>
       </c>
       <c r="S132" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R132)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R132)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T132" s="69" t="inlineStr">
@@ -17437,7 +17437,7 @@
         <v/>
       </c>
       <c r="S133" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R133)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R133)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T133" s="69" t="inlineStr">
@@ -17560,7 +17560,7 @@
         <v/>
       </c>
       <c r="S134" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R134)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R134)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T134" s="69" t="inlineStr">
@@ -17683,7 +17683,7 @@
         <v/>
       </c>
       <c r="S135" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R135)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R135)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T135" s="69" t="inlineStr">
@@ -17809,7 +17809,7 @@
         <v/>
       </c>
       <c r="S136" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R136)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R136)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T136" s="69" t="inlineStr">
@@ -17935,7 +17935,7 @@
         <v/>
       </c>
       <c r="S137" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R137)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R137)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T137" s="69" t="inlineStr">
@@ -18061,7 +18061,7 @@
         <v/>
       </c>
       <c r="S138" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R138)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R138)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T138" s="69" t="inlineStr">
@@ -18187,7 +18187,7 @@
         <v/>
       </c>
       <c r="S139" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R139)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R139)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T139" s="69" t="inlineStr">
@@ -18313,7 +18313,7 @@
         <v/>
       </c>
       <c r="S140" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R140)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R140)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T140" s="69" t="inlineStr">
@@ -18439,7 +18439,7 @@
         <v/>
       </c>
       <c r="S141" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R141)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R141)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T141" s="69" t="inlineStr">
@@ -18565,7 +18565,7 @@
         <v/>
       </c>
       <c r="S142" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R142)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R142)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T142" s="69" t="inlineStr">
@@ -18691,7 +18691,7 @@
         <v/>
       </c>
       <c r="S143" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R143)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R143)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T143" s="69" t="inlineStr">
@@ -18817,7 +18817,7 @@
         <v/>
       </c>
       <c r="S144" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R144)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R144)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T144" s="69" t="inlineStr">
@@ -18943,7 +18943,7 @@
         <v/>
       </c>
       <c r="S145" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R145)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R145)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T145" s="69" t="inlineStr">
@@ -19069,7 +19069,7 @@
         <v/>
       </c>
       <c r="S146" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R146)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R146)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T146" s="69" t="inlineStr">
@@ -19195,7 +19195,7 @@
         <v/>
       </c>
       <c r="S147" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R147)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R147)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T147" s="69" t="inlineStr">
@@ -19321,7 +19321,7 @@
         <v/>
       </c>
       <c r="S148" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R148)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R148)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T148" s="69" t="inlineStr">
@@ -19447,7 +19447,7 @@
         <v/>
       </c>
       <c r="S149" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R149)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R149)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T149" s="69" t="inlineStr">
@@ -19573,7 +19573,7 @@
         <v/>
       </c>
       <c r="S150" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R150)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R150)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T150" s="69" t="inlineStr">
@@ -19699,7 +19699,7 @@
         <v/>
       </c>
       <c r="S151" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R151)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R151)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T151" s="69" t="inlineStr">
@@ -19825,7 +19825,7 @@
         <v/>
       </c>
       <c r="S152" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R152)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R152)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T152" s="69" t="inlineStr">
@@ -19951,7 +19951,7 @@
         <v/>
       </c>
       <c r="S153" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R153)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R153)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T153" s="69" t="inlineStr">
@@ -20077,7 +20077,7 @@
         <v/>
       </c>
       <c r="S154" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R154)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R154)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T154" s="69" t="inlineStr">
@@ -20203,7 +20203,7 @@
         <v/>
       </c>
       <c r="S155" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R155)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R155)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T155" s="69" t="inlineStr">
@@ -20329,7 +20329,7 @@
         <v/>
       </c>
       <c r="S156" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R156)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R156)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T156" s="69" t="inlineStr">
@@ -20455,7 +20455,7 @@
         <v/>
       </c>
       <c r="S157" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R157)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R157)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T157" s="69" t="inlineStr">
@@ -20581,7 +20581,7 @@
         <v/>
       </c>
       <c r="S158" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R158)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R158)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T158" s="69" t="inlineStr">
@@ -20707,7 +20707,7 @@
         <v/>
       </c>
       <c r="S159" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R159)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R159)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T159" s="69" t="inlineStr">
@@ -20833,7 +20833,7 @@
         <v/>
       </c>
       <c r="S160" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R160)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R160)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T160" s="69" t="inlineStr">
@@ -20959,7 +20959,7 @@
         <v/>
       </c>
       <c r="S161" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R161)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R161)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T161" s="69" t="inlineStr">
@@ -21085,7 +21085,7 @@
         <v/>
       </c>
       <c r="S162" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R162)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R162)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T162" s="69" t="inlineStr">
@@ -21211,7 +21211,7 @@
         <v/>
       </c>
       <c r="S163" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R163)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R163)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T163" s="69" t="inlineStr">
@@ -21337,7 +21337,7 @@
         <v/>
       </c>
       <c r="S164" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R164)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R164)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T164" s="69" t="inlineStr">
@@ -21463,7 +21463,7 @@
         <v/>
       </c>
       <c r="S165" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R165)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R165)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T165" s="69" t="inlineStr">
@@ -21589,7 +21589,7 @@
         <v/>
       </c>
       <c r="S166" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R166)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R166)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T166" s="69" t="inlineStr">
@@ -21715,7 +21715,7 @@
         <v/>
       </c>
       <c r="S167" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R167)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R167)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T167" s="69" t="inlineStr">
@@ -21841,7 +21841,7 @@
         <v/>
       </c>
       <c r="S168" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R168)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R168)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T168" s="69" t="inlineStr">
@@ -21967,7 +21967,7 @@
         <v/>
       </c>
       <c r="S169" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R169)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R169)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T169" s="69" t="inlineStr">
@@ -22093,7 +22093,7 @@
         <v/>
       </c>
       <c r="S170" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R170)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R170)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T170" s="69" t="inlineStr">
@@ -22219,7 +22219,7 @@
         <v/>
       </c>
       <c r="S171" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R171)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R171)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T171" s="69" t="inlineStr">
@@ -22342,7 +22342,7 @@
         <v/>
       </c>
       <c r="S172" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R172)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R172)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T172" s="69" t="inlineStr">
@@ -22465,7 +22465,7 @@
         <v/>
       </c>
       <c r="S173" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R173)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R173)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T173" s="69" t="inlineStr">
@@ -22589,7 +22589,7 @@
         <v/>
       </c>
       <c r="S174" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R174)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R174)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T174" s="69" t="inlineStr">
@@ -22713,7 +22713,7 @@
         <v/>
       </c>
       <c r="S175" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R175)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R175)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T175" s="69" t="inlineStr">
@@ -22837,7 +22837,7 @@
         <v/>
       </c>
       <c r="S176" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R176)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R176)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T176" s="69" t="inlineStr">
@@ -22961,7 +22961,7 @@
         <v/>
       </c>
       <c r="S177" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R177)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R177)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T177" s="69" t="inlineStr">
@@ -23085,7 +23085,7 @@
         <v/>
       </c>
       <c r="S178" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R178)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R178)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T178" s="69" t="inlineStr">
@@ -23210,7 +23210,7 @@
         <v/>
       </c>
       <c r="S179" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R179)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R179)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T179" s="69" t="inlineStr">
@@ -23333,7 +23333,7 @@
         <v/>
       </c>
       <c r="S180" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R180)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R180)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T180" s="69" t="inlineStr">
@@ -23457,7 +23457,7 @@
         <v/>
       </c>
       <c r="S181" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R181)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R181)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T181" s="69" t="inlineStr">
@@ -23580,7 +23580,7 @@
         <v/>
       </c>
       <c r="S182" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R182)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R182)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T182" s="69" t="inlineStr">
@@ -23703,7 +23703,7 @@
         <v/>
       </c>
       <c r="S183" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R183)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R183)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T183" s="69" t="inlineStr">
@@ -23827,7 +23827,7 @@
         <v/>
       </c>
       <c r="S184" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R184)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R184)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T184" s="69" t="inlineStr">
@@ -23952,7 +23952,7 @@
         <v/>
       </c>
       <c r="S185" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R185)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R185)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T185" s="69" t="inlineStr">
@@ -24076,7 +24076,7 @@
         <v/>
       </c>
       <c r="S186" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R186)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R186)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T186" s="69" t="inlineStr">
@@ -24200,7 +24200,7 @@
         <v/>
       </c>
       <c r="S187" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R187)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R187)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T187" s="69" t="inlineStr">
@@ -24324,7 +24324,7 @@
         <v/>
       </c>
       <c r="S188" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R188)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R188)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T188" s="69" t="inlineStr">
@@ -24448,7 +24448,7 @@
         <v/>
       </c>
       <c r="S189" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R189)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R189)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T189" s="69" t="inlineStr">
@@ -24572,7 +24572,7 @@
         <v/>
       </c>
       <c r="S190" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R190)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R190)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T190" s="69" t="inlineStr">
@@ -24696,7 +24696,7 @@
         <v/>
       </c>
       <c r="S191" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R191)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R191)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T191" s="69" t="inlineStr">
@@ -24819,7 +24819,7 @@
         <v/>
       </c>
       <c r="S192" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R192)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R192)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T192" s="69" t="inlineStr">
@@ -24943,7 +24943,7 @@
         <v/>
       </c>
       <c r="S193" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R193)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R193)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T193" s="69" t="inlineStr">
@@ -25066,7 +25066,7 @@
         <v/>
       </c>
       <c r="S194" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R194)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R194)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T194" s="69" t="inlineStr">
@@ -25189,7 +25189,7 @@
         <v/>
       </c>
       <c r="S195" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R195)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R195)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T195" s="69" t="inlineStr">
@@ -25313,7 +25313,7 @@
         <v/>
       </c>
       <c r="S196" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R196)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R196)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T196" s="69" t="inlineStr">
@@ -25436,7 +25436,7 @@
         <v/>
       </c>
       <c r="S197" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R197)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R197)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T197" s="69" t="inlineStr">
@@ -25559,7 +25559,7 @@
         <v/>
       </c>
       <c r="S198" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R198)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R198)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T198" s="69" t="inlineStr">
@@ -25682,7 +25682,7 @@
         <v/>
       </c>
       <c r="S199" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R199)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R199)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T199" s="69" t="inlineStr">
@@ -25805,7 +25805,7 @@
         <v/>
       </c>
       <c r="S200" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R200)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R200)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T200" s="69" t="inlineStr">
@@ -25928,7 +25928,7 @@
         <v/>
       </c>
       <c r="S201" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R201)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R201)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T201" s="69" t="inlineStr">
@@ -26051,7 +26051,7 @@
         <v/>
       </c>
       <c r="S202" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R202)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R202)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T202" s="69" t="inlineStr">
@@ -26174,7 +26174,7 @@
         <v/>
       </c>
       <c r="S203" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R203)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R203)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T203" s="69" t="inlineStr">
@@ -26297,7 +26297,7 @@
         <v/>
       </c>
       <c r="S204" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R204)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R204)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T204" s="69" t="inlineStr">
@@ -26421,7 +26421,7 @@
         <v/>
       </c>
       <c r="S205" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R205)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R205)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T205" s="69" t="inlineStr">
@@ -26545,7 +26545,7 @@
         <v/>
       </c>
       <c r="S206" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R206)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R206)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T206" s="69" t="inlineStr">
@@ -26668,7 +26668,7 @@
         <v/>
       </c>
       <c r="S207" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R207)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R207)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T207" s="69" t="inlineStr">
@@ -26791,7 +26791,7 @@
         <v/>
       </c>
       <c r="S208" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R208)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R208)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T208" s="69" t="inlineStr">
@@ -26914,7 +26914,7 @@
         <v/>
       </c>
       <c r="S209" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R209)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R209)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T209" s="69" t="inlineStr">
@@ -27037,7 +27037,7 @@
         <v/>
       </c>
       <c r="S210" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R210)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R210)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T210" s="69" t="inlineStr">
@@ -27160,7 +27160,7 @@
         <v/>
       </c>
       <c r="S211" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R211)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R211)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T211" s="69" t="inlineStr">
@@ -27283,7 +27283,7 @@
         <v/>
       </c>
       <c r="S212" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R212)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R212)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T212" s="69" t="inlineStr">
@@ -27406,7 +27406,7 @@
         <v/>
       </c>
       <c r="S213" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R213)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R213)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T213" s="69" t="inlineStr">
@@ -27529,7 +27529,7 @@
         <v/>
       </c>
       <c r="S214" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R214)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R214)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T214" s="69" t="inlineStr">
@@ -27652,7 +27652,7 @@
         <v/>
       </c>
       <c r="S215" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R215)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R215)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T215" s="69" t="inlineStr">
@@ -27775,7 +27775,7 @@
         <v/>
       </c>
       <c r="S216" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R216)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R216)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T216" s="69" t="inlineStr">
@@ -27898,7 +27898,7 @@
         <v/>
       </c>
       <c r="S217" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R217)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R217)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T217" s="69" t="inlineStr">
@@ -28022,7 +28022,7 @@
         <v/>
       </c>
       <c r="S218" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R218)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R218)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T218" s="69" t="inlineStr">
@@ -28145,7 +28145,7 @@
         <v/>
       </c>
       <c r="S219" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R219)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R219)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T219" s="69" t="inlineStr">
@@ -28268,7 +28268,7 @@
         <v/>
       </c>
       <c r="S220" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R220)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R220)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T220" s="69" t="inlineStr">
@@ -28391,7 +28391,7 @@
         <v/>
       </c>
       <c r="S221" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R221)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R221)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T221" s="69" t="inlineStr">
@@ -28514,7 +28514,7 @@
         <v/>
       </c>
       <c r="S222" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R222)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R222)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T222" s="69" t="inlineStr">
@@ -28637,7 +28637,7 @@
         <v/>
       </c>
       <c r="S223" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R223)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R223)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T223" s="69" t="inlineStr">
@@ -28760,7 +28760,7 @@
         <v/>
       </c>
       <c r="S224" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R224)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R224)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T224" s="69" t="inlineStr">
@@ -28883,7 +28883,7 @@
         <v/>
       </c>
       <c r="S225" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R225)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R225)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T225" s="69" t="inlineStr">
@@ -29006,7 +29006,7 @@
         <v/>
       </c>
       <c r="S226" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R226)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R226)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T226" s="69" t="inlineStr">
@@ -29129,7 +29129,7 @@
         <v/>
       </c>
       <c r="S227" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R227)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R227)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T227" s="69" t="inlineStr">
@@ -29252,7 +29252,7 @@
         <v/>
       </c>
       <c r="S228" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R228)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R228)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T228" s="69" t="inlineStr">
@@ -29375,7 +29375,7 @@
         <v/>
       </c>
       <c r="S229" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R229)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R229)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T229" s="69" t="inlineStr">
@@ -29498,7 +29498,7 @@
         <v/>
       </c>
       <c r="S230" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R230)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R230)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T230" s="69" t="inlineStr">
@@ -29622,7 +29622,7 @@
         <v/>
       </c>
       <c r="S231" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R231)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R231)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T231" s="79" t="inlineStr">
@@ -29745,7 +29745,7 @@
         <v/>
       </c>
       <c r="S232" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R232)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R232)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T232" s="79" t="inlineStr">
@@ -29865,7 +29865,7 @@
         <v/>
       </c>
       <c r="S233" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R233)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R233)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U233" s="79" t="inlineStr">
@@ -29980,7 +29980,7 @@
         <v/>
       </c>
       <c r="S234" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R234)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R234)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U234" s="79" t="inlineStr">
@@ -30095,7 +30095,7 @@
         <v/>
       </c>
       <c r="S235" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R235)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R235)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U235" s="79" t="inlineStr">
@@ -30210,7 +30210,7 @@
         <v/>
       </c>
       <c r="S236" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R236)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R236)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U236" s="79" t="inlineStr">
@@ -30325,7 +30325,7 @@
         <v/>
       </c>
       <c r="S237" s="79">
-        <f>IF(COUNTIF($R$6:$R$240,R237)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R237)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U237" s="79" t="inlineStr">
@@ -30441,7 +30441,7 @@
         <v/>
       </c>
       <c r="S238" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R238)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R238)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T238" s="69" t="inlineStr">
@@ -30564,7 +30564,7 @@
         <v/>
       </c>
       <c r="S239" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R239)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R239)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T239" s="69" t="inlineStr">
@@ -30683,7 +30683,7 @@
         <v/>
       </c>
       <c r="S240" s="69">
-        <f>IF(COUNTIF($R$6:$R$240,R240)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$241,R240)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T240" s="69" t="inlineStr">
@@ -30712,6 +30712,123 @@
       <c r="Y240" s="69" t="inlineStr">
         <is>
           <t>2026-09-21 二次修正（业主实机报「花圃花盆悬空 / 藤蔓要更高更错落 / 挡门 / 加栏杆挂藤」）：①竖向基准 —— 运行时天台承重面 y=0（TowerFloorStage3D 把地砖可视顶面对齐到 Y=0），而布局源把落地装饰写在 h=0.3（= 自持地砖顶面），地砖组又不进重放 ⇒ 实机花草整块砖厚悬空 0.30m、藤蔓 0.35m；现落地件统一 h=0，自持参照地砖改 h=−0.30 使砖顶面落 0。②基地东门净空 —— 门洞净宽 2.2m（世界 gz∈[−3.6,−1.4]），东墙藤蔓 gz −5.0→−8.5、东侧大盆栽 −4.0→−6.2，另把正插在门洞正中的东墙立管 −2.0→+5.5。③藤蔓加高错落 —— 11 基座落地 + 5 件上层叠高（2.0/2.4/2.6/3.2/3.6m；运行时禁非单位缩放，故只能用叠件而非 scale）⇒ 顶高 5.80~7.40m。④新增「女儿墙挂藤」8 件，贴外圈女儿墙中心线（四边各 2，宽度与 5m 直段同宽）。重放实例 99 → 112 / 6 组。运行时重放 99 个装饰实例/5组＝空调与通风口6+绿化20+藤蔓11+水管54+立管支架8；布局源按 Godot 世界平面口径书写、写入 Blender 只做 by=−gz 一步换算，运行时用 (x, h, −by) 还原，并断言换算后必须落在 ROOFTOP_WORLD_RECT 内；装饰贴的是 Base100UpperShell（30×30，中心 (0,5)，东墙门 z=−2.5）的外墙皮；全部实例缩放=1且启用碰撞=0；结构壳体（234地砖/68件女儿墙/楼梯与碰撞）仍由 TowerFloorStage3D 拥有。2026-09-21 修正三处：①缺 by=−gz 换算 ⇒ 整份布局南北镜像、整体偏北 10m；②房屋误做 20×20 且偏北，装饰随之偏；③布局源的 24 墙+36 封顶与 Base100UpperShell 自带件重复，改名 shell_reference（仅 Blender 侧参照、不重放），避免逐面 z-fighting。2026-09-21 三次修正（业主实机报「水管接下来接到地板上面基本看不到 / 空调机在墙上的状态需要 90 度旋转让风扇朝外」）：①立管落地 —— pipe_riser 件高 4.945m、原点在管底、顶端是朝 +X 的鹅颈出水口；旧版放 h=5.8 ⇒ 管底悬空 5.8m。现每处摆两段、两段 h 都是 4.945：下段 rotation_x_deg=180 倒装（包络 0~4.945m，原点即上端）、上段正装（4.945~9.89m），合成一根 0~9.89m 连续落水管，与 10.65m 环管之间残留 0.76m 由环管本体与支架轨遮住；支架补一段低位（1.5m）与原有 7.0m 位，覆盖 1.56~10.64m。②墙挂空调倾倒 —— 新增实例朝向分量 rotation_x_deg（绕自身 X 轴的倾倒）；组件 hvac_small 顶面（Blender 局部 +Z）是出风风扇、前面（局部 −Y）是进风格栅，故 4 台墙挂机统一 rotation_x_deg=90 让风扇朝外（旧版风扇朝天）。⚠️ Blender 默认 XYZ 序、Godot 默认 YXZ 序，只有 rz 分量为 0 时 Rz@Rx 与 Ry@Rx 同序、角度可逐值搬运，本布局遵守该约束（tip 只与 yaw 组合）。③立管/支架按各自墙面给 yaw（旧版立管一律 0 ⇒ 东西墙鹅颈朝墙里）；6 个墙挂件（4 空调 + 2 通风口）后背统一埋进墙外皮内 0.05m。重放实例 112 → 120（pipe_risers 8 → 16）。2026-09-21 四次修正（业主实机报「花盆和花圃没有阻挡」）：绿化 20 件（8 花箱 + 6 大盆栽 + 6 小盆栽）由 visual_only 改 blocking —— 布局源 add() 新增实例级 collision 策略（词表 visual_only / blocking，白名单 flowerbox / plant_large / plant_small），运行时 TowerFloorStage3D 新增 _apply_rooftop_collision_policy()：blocking 件用 TowerGeometry3D.resolve_visual_bounds() 量出**实测可视包络**、挂一个 StaticBody3D(BlockingCollision, layer=1, mask=0, PROCESS_MODE_ALWAYS) + BoxShape3D(BlockingBox) 代理挡玩家（尺寸随美术走、不写死常量），其余 462 件仍 visual_only（组件自带碰撞一律先关）。布局清单 design_intent/validation 记 blocking_collision_count=20 / visual_only_collision_count=462；校验器新增第 5 层断言（策略词表 + 白名单 slug + 计数 + 清单交叉一致）。反向对照：把 20 件翻回 visual_only ⇒ 两份运行时探针 exit 1、QA 报 3 条 FAIL；还原后 .blend 与 .json 逐字节一致。2026-09-21 五次修正（业主实机报「花盆和花圃靠墙太远了，要挨着墙放，不然还有个空虚」）：绿化环由「离墙中心线 2.15m 单一环线」改为**逐件按自身半进深背贴建筑外皮** —— 件心离墙中心线 = SHELL_WALL_T/2 − WALL_MOUNT_EMBED(0.05) + half_depth（背面埋进外皮 0.05m，与墙挂空调同口径）；花箱 0.5925 / 大盆栽 0.8727377 / 小盆栽 0.5473868，南/北/东/西四边各成对，背面齐平、正面自然错落（旧版每件背后空 1.14~1.45m 可见地砖带）。朝向补齐：三件 front_direction 均为 −Y ⇒ yaw 0/π/+π/2/−π/2 分别朝南/北/东/西（旧版西侧花圃 +π/2 正面朝墙里、与同墙藤蔓 −π/2 矛盾，一并修正）。布局 QA 新增「3e 绿化背贴外皮」断言（背面埋入量 = 0.05、沿墙法线跨度 = 2×半进深），可反向对照。重放实例仍 120/6 组、构件计数与 blocking 20 不变。2026-09-22 六次修正（业主口径「所有楼层都和 100 层面积一致」）：塔楼壳体平面由 18×16 格（90×80m）向东再扩 2 格到 20×16 格（100×80m），98F/99F/100F 三层共用同一矩形（TOWER_SHELL_WORLD_RECT = (-50,-35,100,80)，中心 (0,5)，8000㎡）；原先「100F 走 90×80、99F 楼板 250×250 / 外墙 160×160、普通层 250×250」三套口径作废。驱动原因：east 楼梯井（99↔98）外廓是固定世界常量 x∈[35,50]，90m 窗口（东界 x=40）装不下它；100m 下两个在用井（west x[-45,-30]、east x[35,50]）全部落在壳体内。本布局随之重生成：自持地砖 234→266 块、外围女儿墙 68→72 件（64→68 直段 + 4 外角）；重放 6 组仍 120 件不变（装饰贴 30×30 房屋与环管，只有东侧贴 x_east 的 parapet_ivy 1 件由 x=39.75 东移到 49.75）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="255" customHeight="1" s="50">
+      <c r="A241" s="69" t="inlineStr">
+        <is>
+          <t>ENV-EXPEDITION-L01-BOSS-ARENA</t>
+        </is>
+      </c>
+      <c r="B241" s="69" t="inlineStr">
+        <is>
+          <t>远征关卡01 Boss竞技场 50×40m 白模</t>
+        </is>
+      </c>
+      <c r="C241" s="69" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="D241" s="69" t="inlineStr">
+        <is>
+          <t>boss_arena</t>
+        </is>
+      </c>
+      <c r="E241" s="69" t="inlineStr">
+        <is>
+          <t>expedition_01_boss_arena</t>
+        </is>
+      </c>
+      <c r="F241" s="69" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="G241" s="69" t="n"/>
+      <c r="H241" s="69" t="inlineStr">
+        <is>
+          <t>Top3D / Blender Z-up</t>
+        </is>
+      </c>
+      <c r="I241" s="69" t="inlineStr">
+        <is>
+          <t>whitebox / default</t>
+        </is>
+      </c>
+      <c r="J241" s="69" t="inlineStr">
+        <is>
+          <t>远征关卡01 专用</t>
+        </is>
+      </c>
+      <c r="K241" s="69" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L241" s="69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M241" s="69" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N241" s="69" t="inlineStr">
+        <is>
+          <t>50×40×11.9m；10×8 个 5m 槽</t>
+        </is>
+      </c>
+      <c r="O241" s="69" t="inlineStr">
+        <is>
+          <t>source/art/whitebox/tower_zones/expedition_01/v001/blender/远征关卡01_白模_Boss竞技场_50x40m_v001.blend</t>
+        </is>
+      </c>
+      <c r="P241" s="69" t="inlineStr">
+        <is>
+          <t>source/art/whitebox/tower_zones/battle_level01/v003/blender/局内关卡01_白模_Boss竞技场_190x90m_v003.blend</t>
+        </is>
+      </c>
+      <c r="Q241" s="69" t="inlineStr">
+        <is>
+          <t>远征关卡01;Boss竞技场;白模;50×40m;竞技场</t>
+        </is>
+      </c>
+      <c r="R241" s="69">
+        <f>LOWER(TRIM(C241)&amp;"|"&amp;TRIM(D241)&amp;"|"&amp;TRIM(E241)&amp;"|"&amp;TRIM(F241)&amp;"|"&amp;TRIM(H241)&amp;"|"&amp;TRIM(I241))</f>
+        <v/>
+      </c>
+      <c r="S241" s="69">
+        <f>IF(COUNTIF($R$6:$R$241,R241)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T241" s="69" t="n"/>
+      <c r="U241" s="69" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V241" s="69" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="W241" s="69" t="inlineStr">
+        <is>
+          <t>用户设计（由局内关卡01竞技场白模派生）</t>
+        </is>
+      </c>
+      <c r="X241" s="69" t="inlineStr">
+        <is>
+          <t>远征关卡01 Boss竞技场 50×40m 白模_资产管理</t>
+        </is>
+      </c>
+      <c r="Y241" s="69" t="inlineStr">
+        <is>
+          <t>由局内关卡01 Boss竞技场190×90m白模v003按5m网格重建（非缩放；1/3线性缩放落在63.33×30m、X轴非5m整数倍，业主裁决取50×40m）。墙按固定5m槽位拼装，门墙完整占用5m槽并保留左右柱与门楣；两轴均为5m整数倍，无FIXED_TRIM收边。门：南→boss_prep(+2.5)、西→boss_exit(-2.5)。未导GLB、未接Godot。</t>
         </is>
       </c>
     </row>
@@ -30752,7 +30869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P146"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="50" min="1" max="1"/>
@@ -41881,6 +41998,88 @@
       <c r="P146" s="3" t="inlineStr">
         <is>
           <t>清单=assets/art/environments/tower_zones/rooftop/source/layouts/100f_decorated_v001/rooftop_100f_decorated_layout_v001.json；运行时登记=assets/art/environments/tower_zones/rooftop/runtime/rooftop_100f_decorated_runtime_manifest.json；验收=verify_rooftop_32x32_contract + probe_rooftop_decorated_layout + probe_rooftop_decorated_stage_only；全部实例缩放=1、启用碰撞=0；结构壳体（地砖/女儿墙）仍由 TowerFloorStage3D 负责，布局不重复生成；2026-09-21 坐标契约修正（补 by=−gz，此前整体偏北 10m）＋房屋 20×20→30×30 对齐 Base100UpperShell；2026-09-21 三次修正：立管落地 0~9.89m（h=件高4.945、倒装件原点在顶面）、墙挂空调绕 X 轴 90° 倾倒让风扇朝外（Godot 侧读 basis.y）、布局源只写 rotation_x_deg + rotation_y_deg（rz=0，规避 Blender XYZ 序 / Godot YXZ 序的次序差）；2026-09-21 四次修正：绿化 20 件改 blocking（运行时按 TowerGeometry3D.resolve_visual_bounds 实测可视包络生成 layer=1 BoxShape3D 代理挡玩家），其余 visual_only；collision_policy 词表=visual_only/blocking，清单设计意图记 blocking_collision_count=20 / visual_only_collision_count=462；2026-09-22 六次修正：壳体几何由 TowerFloorStage3D 的 TOWER_SHELL_*（20×16 格 = 100×80m）统管 98F/99F/100F 三层；本行「外形尺寸」的 90×80m天台 / 外围68件（64直段+4外角）/ 234块5m地砖同步为 100×80m / 72件（68直段+4外角）/ 266块；重放 120 件与碰撞 20 件不变。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>ENV-EXPEDITION-L01-BOSS-ARENA</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>远征关卡01 Boss竞技场 50×40m 白模</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>未制作</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>未制作</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>source/art/whitebox/tower_zones/expedition_01/v001/blender/远征关卡01_白模_Boss竞技场_50x40m_v001.blend</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>远征关卡01 Boss竞技场白盒；50×40m / 10×8个5m槽；墙按固定5m槽位拼装，门墙完整占用5m槽并保留左右柱与门楣；两轴均为5m整数倍，无FIXED_TRIM收边。</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>50×40×11.9m</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>房间局部坐标：X/Y居中；底面Z=0；Godot -Z</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>远征关卡01 / Expedition</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
+          <t>白模源已完成；QA PASS</t>
+        </is>
+      </c>
+      <c r="O147" s="3" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>由局内关卡01 Boss竞技场190×90m白模v003按5m网格重建（非缩放）；1/3=63.33×30m不合5m模数，业主裁决取50×40m；南门boss_prep(+2.5)、西门boss_exit(-2.5)；未导GLB。</t>
         </is>
       </c>
     </row>
@@ -44020,7 +44219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="50" min="1" max="1"/>
@@ -44528,6 +44727,43 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="97" t="inlineStr">
+        <is>
+          <t>v0.1.12</t>
+        </is>
+      </c>
+      <c r="B18" s="97" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C18" s="97" t="inlineStr">
+        <is>
+          <t>新增条目</t>
+        </is>
+      </c>
+      <c r="D18" s="97" t="inlineStr">
+        <is>
+          <t>关卡场景 / 远征关卡01</t>
+        </is>
+      </c>
+      <c r="E18" s="97" t="inlineStr">
+        <is>
+          <t>新增 ENV-EXPEDITION-L01-BOSS-ARENA（远征关卡01 Boss竞技场 50×40m 白模）：由局内关卡01 Boss竞技场190×90m白模按5m网格重建（非缩放）；1/3线性缩放落在63.33×30m、X轴非5m整数倍，经业主裁决取50×40m（10×8槽）。墙按固定5m槽位拼装，门墙完整占用5m槽，两轴无FIXED_TRIM收边；南门boss_prep(+2.5)、西门boss_exit(-2.5)。同批登记《资产主表》第241行与《3D-场景通用》第147行。未导GLB、未接Godot。</t>
+        </is>
+      </c>
+      <c r="F18" s="97" t="inlineStr">
+        <is>
+          <t>新增条目，不改动既有 AssetID / 路径 / 哈希；账本门禁历史问题数不变（仍为6项：1项主账本索引漂移 + 5项「白盒组件」非法状态）。</t>
+        </is>
+      </c>
+      <c r="G18" s="97" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -1476,22 +1476,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="60">
       <c r="A6" s="65">
-        <f>COUNTA('资产主表'!$A$6:$A$241)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$242)</f>
         <v/>
       </c>
       <c r="B6" s="63" t="n"/>
       <c r="C6" s="65">
-        <f>COUNTIF('资产主表'!$K$6:$K$241,"已完成")+COUNTIF('资产主表'!$K$6:$K$241,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$241,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$241,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$241,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$241,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$241,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$242,"已完成")+COUNTIF('资产主表'!$K$6:$K$242,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$242,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$242,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$242,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$242,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$242,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="63" t="n"/>
       <c r="E6" s="65">
-        <f>COUNTIF('资产主表'!$K$6:$K$241,"待制作")+COUNTIF('资产主表'!$K$6:$K$241,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$242,"待制作")+COUNTIF('资产主表'!$K$6:$K$242,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="63" t="n"/>
       <c r="G6" s="65">
-        <f>COUNTIF('资产主表'!$S$6:$S$241,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$242,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="63" t="n"/>
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="B10" s="70">
-        <f>COUNTIF('资产主表'!$C$6:$C$241,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$242,A10)</f>
         <v/>
       </c>
       <c r="C10" s="70">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$241=A10)*(('资产主表'!$K$6:$K$241="已完成")+('资产主表'!$K$6:$K$241="原型已接入")+('资产主表'!$K$6:$K$241="正式美术已接入")+('资产主表'!$K$6:$K$241="已优化并正式接入")+('资产主表'!$K$6:$K$241="Blender源已完成")+('资产主表'!$K$6:$K$241="已导入；优化完成")+('资产主表'!$K$6:$K$241="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$242=A10)*(('资产主表'!$K$6:$K$242="已完成")+('资产主表'!$K$6:$K$242="原型已接入")+('资产主表'!$K$6:$K$242="正式美术已接入")+('资产主表'!$K$6:$K$242="已优化并正式接入")+('资产主表'!$K$6:$K$242="Blender源已完成")+('资产主表'!$K$6:$K$242="已导入；优化完成")+('资产主表'!$K$6:$K$242="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="70" t="n"/>
@@ -1582,11 +1582,11 @@
         </is>
       </c>
       <c r="B11" s="70">
-        <f>COUNTIF('资产主表'!$C$6:$C$241,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$242,A11)</f>
         <v/>
       </c>
       <c r="C11" s="70">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$241=A11)*(('资产主表'!$K$6:$K$241="已完成")+('资产主表'!$K$6:$K$241="原型已接入")+('资产主表'!$K$6:$K$241="正式美术已接入")+('资产主表'!$K$6:$K$241="已优化并正式接入")+('资产主表'!$K$6:$K$241="Blender源已完成")+('资产主表'!$K$6:$K$241="已导入；优化完成")+('资产主表'!$K$6:$K$241="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$242=A11)*(('资产主表'!$K$6:$K$242="已完成")+('资产主表'!$K$6:$K$242="原型已接入")+('资产主表'!$K$6:$K$242="正式美术已接入")+('资产主表'!$K$6:$K$242="已优化并正式接入")+('资产主表'!$K$6:$K$242="Blender源已完成")+('资产主表'!$K$6:$K$242="已导入；优化完成")+('资产主表'!$K$6:$K$242="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="70" t="n"/>
@@ -1604,11 +1604,11 @@
         </is>
       </c>
       <c r="B12" s="70">
-        <f>COUNTIF('资产主表'!$C$6:$C$241,A12)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$242,A12)</f>
         <v/>
       </c>
       <c r="C12" s="70">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$241=A12)*(('资产主表'!$K$6:$K$241="已完成")+('资产主表'!$K$6:$K$241="原型已接入")+('资产主表'!$K$6:$K$241="正式美术已接入")+('资产主表'!$K$6:$K$241="已优化并正式接入")+('资产主表'!$K$6:$K$241="Blender源已完成")+('资产主表'!$K$6:$K$241="已导入；优化完成")+('资产主表'!$K$6:$K$241="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$242=A12)*(('资产主表'!$K$6:$K$242="已完成")+('资产主表'!$K$6:$K$242="原型已接入")+('资产主表'!$K$6:$K$242="正式美术已接入")+('资产主表'!$K$6:$K$242="已优化并正式接入")+('资产主表'!$K$6:$K$242="Blender源已完成")+('资产主表'!$K$6:$K$242="已导入；优化完成")+('资产主表'!$K$6:$K$242="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D12" s="70" t="n"/>
@@ -1626,11 +1626,11 @@
         </is>
       </c>
       <c r="B13" s="66">
-        <f>COUNTIF('资产主表'!$C$6:$C$241,A13)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$242,A13)</f>
         <v/>
       </c>
       <c r="C13" s="66">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$241=A13)*(('资产主表'!$K$6:$K$241="已完成")+('资产主表'!$K$6:$K$241="原型已接入")+('资产主表'!$K$6:$K$241="正式美术已接入")+('资产主表'!$K$6:$K$241="已优化并正式接入")+('资产主表'!$K$6:$K$241="Blender源已完成")+('资产主表'!$K$6:$K$241="已导入；优化完成")+('资产主表'!$K$6:$K$241="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$242=A13)*(('资产主表'!$K$6:$K$242="已完成")+('资产主表'!$K$6:$K$242="原型已接入")+('资产主表'!$K$6:$K$242="正式美术已接入")+('资产主表'!$K$6:$K$242="已优化并正式接入")+('资产主表'!$K$6:$K$242="Blender源已完成")+('资产主表'!$K$6:$K$242="已导入；优化完成")+('资产主表'!$K$6:$K$242="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D13" s="66" t="n"/>
@@ -2194,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y241"/>
+  <dimension ref="A1:Y242"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.80859375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="25" customWidth="1" style="59" min="1" max="1"/>
@@ -2470,7 +2470,7 @@
         <v/>
       </c>
       <c r="S6" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="71" t="n"/>
@@ -2577,7 +2577,7 @@
         <v/>
       </c>
       <c r="S7" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="71" t="n"/>
@@ -2684,7 +2684,7 @@
         <v/>
       </c>
       <c r="S8" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="71" t="n"/>
@@ -2791,7 +2791,7 @@
         <v/>
       </c>
       <c r="S9" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="71" t="n"/>
@@ -2898,7 +2898,7 @@
         <v/>
       </c>
       <c r="S10" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="71" t="n"/>
@@ -3005,7 +3005,7 @@
         <v/>
       </c>
       <c r="S11" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="71" t="n"/>
@@ -3112,7 +3112,7 @@
         <v/>
       </c>
       <c r="S12" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="71" t="n"/>
@@ -3219,7 +3219,7 @@
         <v/>
       </c>
       <c r="S13" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="71" t="n"/>
@@ -3326,7 +3326,7 @@
         <v/>
       </c>
       <c r="S14" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="71" t="n"/>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="S15" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="71" t="n"/>
@@ -3540,7 +3540,7 @@
         <v/>
       </c>
       <c r="S16" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="71" t="n"/>
@@ -3647,7 +3647,7 @@
         <v/>
       </c>
       <c r="S17" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="71" t="n"/>
@@ -3754,7 +3754,7 @@
         <v/>
       </c>
       <c r="S18" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="71" t="n"/>
@@ -3861,7 +3861,7 @@
         <v/>
       </c>
       <c r="S19" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="71" t="n"/>
@@ -3968,7 +3968,7 @@
         <v/>
       </c>
       <c r="S20" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="71" t="n"/>
@@ -4075,7 +4075,7 @@
         <v/>
       </c>
       <c r="S21" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="71" t="n"/>
@@ -4182,7 +4182,7 @@
         <v/>
       </c>
       <c r="S22" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="71" t="n"/>
@@ -4289,7 +4289,7 @@
         <v/>
       </c>
       <c r="S23" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="71" t="n"/>
@@ -4396,7 +4396,7 @@
         <v/>
       </c>
       <c r="S24" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="71" t="n"/>
@@ -4503,7 +4503,7 @@
         <v/>
       </c>
       <c r="S25" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="71" t="n"/>
@@ -4610,7 +4610,7 @@
         <v/>
       </c>
       <c r="S26" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="71" t="n"/>
@@ -4717,7 +4717,7 @@
         <v/>
       </c>
       <c r="S27" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="71" t="n"/>
@@ -4824,7 +4824,7 @@
         <v/>
       </c>
       <c r="S28" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="71" t="n"/>
@@ -4931,7 +4931,7 @@
         <v/>
       </c>
       <c r="S29" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="71" t="n"/>
@@ -5038,7 +5038,7 @@
         <v/>
       </c>
       <c r="S30" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="71" t="n"/>
@@ -5145,7 +5145,7 @@
         <v/>
       </c>
       <c r="S31" s="71">
-        <f>IF(COUNTIF($R$6:$R$241,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="71" t="n"/>
@@ -5264,7 +5264,7 @@
         <v/>
       </c>
       <c r="S32" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="87" t="inlineStr">
@@ -5387,7 +5387,7 @@
         <v/>
       </c>
       <c r="S33" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="90" t="inlineStr">
@@ -5510,7 +5510,7 @@
         <v/>
       </c>
       <c r="S34" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="90" t="inlineStr">
@@ -5633,7 +5633,7 @@
         <v/>
       </c>
       <c r="S35" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="90" t="inlineStr">
@@ -5756,7 +5756,7 @@
         <v/>
       </c>
       <c r="S36" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="87" t="inlineStr">
@@ -5880,7 +5880,7 @@
         <v/>
       </c>
       <c r="S37" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="90" t="inlineStr">
@@ -6003,7 +6003,7 @@
         <v/>
       </c>
       <c r="S38" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="90" t="inlineStr">
@@ -6122,7 +6122,7 @@
         <v/>
       </c>
       <c r="S39" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="87" t="inlineStr">
@@ -6245,7 +6245,7 @@
         <v/>
       </c>
       <c r="S40" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="90" t="inlineStr">
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="S41" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="90" t="inlineStr">
@@ -6491,7 +6491,7 @@
         <v/>
       </c>
       <c r="S42" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="90" t="inlineStr">
@@ -6614,7 +6614,7 @@
         <v/>
       </c>
       <c r="S43" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="90" t="inlineStr">
@@ -6737,7 +6737,7 @@
         <v/>
       </c>
       <c r="S44" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="87" t="inlineStr">
@@ -6861,7 +6861,7 @@
         <v/>
       </c>
       <c r="S45" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="90" t="inlineStr">
@@ -6984,7 +6984,7 @@
         <v/>
       </c>
       <c r="S46" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="90" t="inlineStr">
@@ -7107,7 +7107,7 @@
         <v/>
       </c>
       <c r="S47" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="90" t="inlineStr">
@@ -7230,7 +7230,7 @@
         <v/>
       </c>
       <c r="S48" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R48)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R48)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T48" s="90" t="inlineStr">
@@ -7350,7 +7350,7 @@
         <v/>
       </c>
       <c r="S49" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R49)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R49)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T49" s="90" t="inlineStr">
@@ -7473,7 +7473,7 @@
         <v/>
       </c>
       <c r="S50" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R50)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R50)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T50" s="90" t="inlineStr">
@@ -7597,7 +7597,7 @@
         <v/>
       </c>
       <c r="S51" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R51)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R51)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T51" s="90" t="inlineStr">
@@ -7720,7 +7720,7 @@
         <v/>
       </c>
       <c r="S52" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R52)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R52)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T52" s="87" t="inlineStr">
@@ -7844,7 +7844,7 @@
         <v/>
       </c>
       <c r="S53" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R53)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R53)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T53" s="87" t="inlineStr">
@@ -7967,7 +7967,7 @@
         <v/>
       </c>
       <c r="S54" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R54)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R54)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T54" s="87" t="inlineStr">
@@ -8096,7 +8096,7 @@
         <v/>
       </c>
       <c r="S55" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R55)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R55)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T55" s="87" t="inlineStr">
@@ -8223,7 +8223,7 @@
         <v/>
       </c>
       <c r="S56" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R56)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R56)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T56" s="87" t="inlineStr">
@@ -8346,7 +8346,7 @@
         <v/>
       </c>
       <c r="S57" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R57)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R57)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T57" s="87" t="inlineStr">
@@ -8471,7 +8471,7 @@
         <v/>
       </c>
       <c r="S58" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R58)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R58)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T58" s="87" t="inlineStr">
@@ -8594,7 +8594,7 @@
         <v/>
       </c>
       <c r="S59" s="88">
-        <f>IF(COUNTIF($R$6:$R$241,R59)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R59)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T59" s="87" t="inlineStr">
@@ -8713,7 +8713,7 @@
         <v/>
       </c>
       <c r="S60" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R60)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R60)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T60" s="90" t="inlineStr">
@@ -8833,7 +8833,7 @@
         <v/>
       </c>
       <c r="S61" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R61)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R61)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T61" s="90" t="inlineStr">
@@ -8953,7 +8953,7 @@
         <v/>
       </c>
       <c r="S62" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R62)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R62)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T62" s="90" t="inlineStr">
@@ -9073,7 +9073,7 @@
         <v/>
       </c>
       <c r="S63" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R63)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R63)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T63" s="90" t="n"/>
@@ -9193,7 +9193,7 @@
         <v/>
       </c>
       <c r="S64" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R64)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R64)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T64" s="90" t="inlineStr">
@@ -9318,7 +9318,7 @@
         <v/>
       </c>
       <c r="S65" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R65)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R65)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T65" s="90" t="inlineStr">
@@ -9443,7 +9443,7 @@
         <v/>
       </c>
       <c r="S66" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R66)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R66)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T66" s="90" t="inlineStr">
@@ -9568,7 +9568,7 @@
         <v/>
       </c>
       <c r="S67" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R67)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R67)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T67" s="90" t="inlineStr">
@@ -9693,7 +9693,7 @@
         <v/>
       </c>
       <c r="S68" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R68)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R68)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T68" s="90" t="inlineStr">
@@ -9824,7 +9824,7 @@
         <v/>
       </c>
       <c r="S69" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R69)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R69)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T69" s="90" t="inlineStr">
@@ -9950,7 +9950,7 @@
         <v/>
       </c>
       <c r="S70" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R70)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R70)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T70" s="90" t="inlineStr">
@@ -10074,7 +10074,7 @@
         <v/>
       </c>
       <c r="S71" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R71)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R71)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T71" s="90" t="inlineStr">
@@ -10198,7 +10198,7 @@
         <v/>
       </c>
       <c r="S72" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R72)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R72)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T72" s="90" t="inlineStr">
@@ -10322,7 +10322,7 @@
         <v/>
       </c>
       <c r="S73" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R73)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R73)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T73" s="90" t="inlineStr">
@@ -10446,7 +10446,7 @@
         <v/>
       </c>
       <c r="S74" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R74)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R74)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T74" s="90" t="inlineStr">
@@ -10570,7 +10570,7 @@
         <v/>
       </c>
       <c r="S75" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R75)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R75)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T75" s="90" t="inlineStr">
@@ -10694,7 +10694,7 @@
         <v/>
       </c>
       <c r="S76" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R76)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R76)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T76" s="90" t="inlineStr">
@@ -10818,7 +10818,7 @@
         <v/>
       </c>
       <c r="S77" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R77)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R77)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T77" s="90" t="inlineStr">
@@ -10942,7 +10942,7 @@
         <v/>
       </c>
       <c r="S78" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R78)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R78)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T78" s="90" t="inlineStr">
@@ -11066,7 +11066,7 @@
         <v/>
       </c>
       <c r="S79" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R79)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R79)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T79" s="90" t="inlineStr">
@@ -11190,7 +11190,7 @@
         <v/>
       </c>
       <c r="S80" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R80)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R80)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T80" s="90" t="inlineStr">
@@ -11314,7 +11314,7 @@
         <v/>
       </c>
       <c r="S81" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R81)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R81)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T81" s="90" t="inlineStr">
@@ -11438,7 +11438,7 @@
         <v/>
       </c>
       <c r="S82" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R82)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R82)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T82" s="90" t="inlineStr">
@@ -11562,7 +11562,7 @@
         <v/>
       </c>
       <c r="S83" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R83)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R83)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T83" s="90" t="inlineStr">
@@ -11686,7 +11686,7 @@
         <v/>
       </c>
       <c r="S84" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R84)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R84)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T84" s="90" t="inlineStr">
@@ -11810,7 +11810,7 @@
         <v/>
       </c>
       <c r="S85" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R85)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R85)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T85" s="90" t="inlineStr">
@@ -11934,7 +11934,7 @@
         <v/>
       </c>
       <c r="S86" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R86)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R86)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T86" s="90" t="inlineStr">
@@ -12058,7 +12058,7 @@
         <v/>
       </c>
       <c r="S87" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R87)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R87)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T87" s="90" t="inlineStr">
@@ -12182,7 +12182,7 @@
         <v/>
       </c>
       <c r="S88" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R88)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R88)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T88" s="90" t="inlineStr">
@@ -12306,7 +12306,7 @@
         <v/>
       </c>
       <c r="S89" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R89)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R89)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T89" s="90" t="inlineStr">
@@ -12430,7 +12430,7 @@
         <v/>
       </c>
       <c r="S90" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R90)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R90)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T90" s="90" t="inlineStr">
@@ -12554,7 +12554,7 @@
         <v/>
       </c>
       <c r="S91" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R91)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R91)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T91" s="90" t="inlineStr">
@@ -12678,7 +12678,7 @@
         <v/>
       </c>
       <c r="S92" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R92)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R92)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T92" s="90" t="inlineStr">
@@ -12802,7 +12802,7 @@
         <v/>
       </c>
       <c r="S93" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R93)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R93)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T93" s="90" t="inlineStr">
@@ -12926,7 +12926,7 @@
         <v/>
       </c>
       <c r="S94" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R94)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R94)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T94" s="90" t="inlineStr">
@@ -13050,7 +13050,7 @@
         <v/>
       </c>
       <c r="S95" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R95)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R95)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T95" s="90" t="inlineStr">
@@ -13174,7 +13174,7 @@
         <v/>
       </c>
       <c r="S96" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R96)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R96)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T96" s="90" t="inlineStr">
@@ -13298,7 +13298,7 @@
         <v/>
       </c>
       <c r="S97" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R97)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R97)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T97" s="90" t="inlineStr">
@@ -13422,7 +13422,7 @@
         <v/>
       </c>
       <c r="S98" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R98)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R98)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T98" s="90" t="inlineStr">
@@ -13546,7 +13546,7 @@
         <v/>
       </c>
       <c r="S99" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R99)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R99)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T99" s="90" t="inlineStr">
@@ -13670,7 +13670,7 @@
         <v/>
       </c>
       <c r="S100" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R100)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R100)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T100" s="90" t="inlineStr">
@@ -13794,7 +13794,7 @@
         <v/>
       </c>
       <c r="S101" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R101)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R101)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T101" s="90" t="inlineStr">
@@ -13918,7 +13918,7 @@
         <v/>
       </c>
       <c r="S102" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R102)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R102)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T102" s="90" t="inlineStr">
@@ -14041,7 +14041,7 @@
         <v/>
       </c>
       <c r="S103" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R103)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R103)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T103" s="90" t="inlineStr">
@@ -14166,7 +14166,7 @@
         <v/>
       </c>
       <c r="S104" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R104)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R104)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T104" s="90" t="inlineStr">
@@ -14291,7 +14291,7 @@
         <v/>
       </c>
       <c r="S105" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R105)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R105)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T105" s="90" t="inlineStr">
@@ -14416,7 +14416,7 @@
         <v/>
       </c>
       <c r="S106" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R106)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R106)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T106" s="90" t="inlineStr">
@@ -14541,7 +14541,7 @@
         <v/>
       </c>
       <c r="S107" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R107)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R107)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T107" s="90" t="inlineStr">
@@ -14666,7 +14666,7 @@
         <v/>
       </c>
       <c r="S108" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R108)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R108)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T108" s="93" t="inlineStr">
@@ -14792,7 +14792,7 @@
         <v/>
       </c>
       <c r="S109" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R109)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R109)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T109" s="90" t="inlineStr">
@@ -14918,7 +14918,7 @@
         <v/>
       </c>
       <c r="S110" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R110)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R110)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T110" s="90" t="inlineStr">
@@ -15044,7 +15044,7 @@
         <v/>
       </c>
       <c r="S111" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R111)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R111)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T111" s="90" t="inlineStr">
@@ -15170,7 +15170,7 @@
         <v/>
       </c>
       <c r="S112" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R112)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R112)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T112" s="90" t="inlineStr">
@@ -15293,7 +15293,7 @@
         <v/>
       </c>
       <c r="S113" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R113)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R113)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T113" s="90" t="inlineStr">
@@ -15413,7 +15413,7 @@
         <v/>
       </c>
       <c r="S114" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R114)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R114)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T114" s="93" t="inlineStr">
@@ -15532,7 +15532,7 @@
         <v/>
       </c>
       <c r="S115" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R115)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R115)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T115" s="93" t="inlineStr">
@@ -15650,7 +15650,7 @@
         <v/>
       </c>
       <c r="S116" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R116)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R116)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T116" s="93" t="inlineStr">
@@ -15773,7 +15773,7 @@
         <v/>
       </c>
       <c r="S117" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R117)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R117)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T117" s="90" t="inlineStr">
@@ -15899,7 +15899,7 @@
         <v/>
       </c>
       <c r="S118" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R118)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R118)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T118" s="90" t="inlineStr">
@@ -16022,7 +16022,7 @@
         <v/>
       </c>
       <c r="S119" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R119)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R119)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T119" s="90" t="inlineStr">
@@ -16147,7 +16147,7 @@
         <v/>
       </c>
       <c r="S120" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R120)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R120)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T120" s="90" t="inlineStr">
@@ -16270,7 +16270,7 @@
         <v/>
       </c>
       <c r="S121" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R121)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R121)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T121" s="90" t="inlineStr">
@@ -16395,7 +16395,7 @@
         <v/>
       </c>
       <c r="S122" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R122)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R122)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T122" s="90" t="inlineStr">
@@ -16518,7 +16518,7 @@
         <v/>
       </c>
       <c r="S123" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R123)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R123)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T123" s="90" t="inlineStr">
@@ -16641,7 +16641,7 @@
         <v/>
       </c>
       <c r="S124" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R124)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R124)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T124" s="90" t="inlineStr">
@@ -16764,7 +16764,7 @@
         <v/>
       </c>
       <c r="S125" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R125)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R125)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T125" s="90" t="inlineStr">
@@ -16887,7 +16887,7 @@
         <v/>
       </c>
       <c r="S126" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R126)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R126)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T126" s="90" t="inlineStr">
@@ -17010,7 +17010,7 @@
         <v/>
       </c>
       <c r="S127" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R127)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R127)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T127" s="90" t="inlineStr">
@@ -17133,7 +17133,7 @@
         <v/>
       </c>
       <c r="S128" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R128)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R128)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T128" s="90" t="inlineStr">
@@ -17256,7 +17256,7 @@
         <v/>
       </c>
       <c r="S129" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R129)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R129)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T129" s="90" t="inlineStr">
@@ -17379,7 +17379,7 @@
         <v/>
       </c>
       <c r="S130" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R130)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R130)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T130" s="90" t="inlineStr">
@@ -17502,7 +17502,7 @@
         <v/>
       </c>
       <c r="S131" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R131)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R131)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T131" s="90" t="inlineStr">
@@ -17625,7 +17625,7 @@
         <v/>
       </c>
       <c r="S132" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R132)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R132)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T132" s="90" t="inlineStr">
@@ -17749,7 +17749,7 @@
         <v/>
       </c>
       <c r="S133" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R133)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R133)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T133" s="90" t="inlineStr">
@@ -17872,7 +17872,7 @@
         <v/>
       </c>
       <c r="S134" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R134)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R134)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T134" s="90" t="inlineStr">
@@ -17995,7 +17995,7 @@
         <v/>
       </c>
       <c r="S135" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R135)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R135)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T135" s="90" t="inlineStr">
@@ -18121,7 +18121,7 @@
         <v/>
       </c>
       <c r="S136" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R136)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R136)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T136" s="90" t="inlineStr">
@@ -18247,7 +18247,7 @@
         <v/>
       </c>
       <c r="S137" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R137)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R137)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T137" s="90" t="inlineStr">
@@ -18373,7 +18373,7 @@
         <v/>
       </c>
       <c r="S138" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R138)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R138)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T138" s="90" t="inlineStr">
@@ -18499,7 +18499,7 @@
         <v/>
       </c>
       <c r="S139" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R139)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R139)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T139" s="90" t="inlineStr">
@@ -18625,7 +18625,7 @@
         <v/>
       </c>
       <c r="S140" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R140)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R140)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T140" s="90" t="inlineStr">
@@ -18751,7 +18751,7 @@
         <v/>
       </c>
       <c r="S141" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R141)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R141)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T141" s="90" t="inlineStr">
@@ -18877,7 +18877,7 @@
         <v/>
       </c>
       <c r="S142" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R142)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R142)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T142" s="90" t="inlineStr">
@@ -19003,7 +19003,7 @@
         <v/>
       </c>
       <c r="S143" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R143)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R143)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T143" s="90" t="inlineStr">
@@ -19129,7 +19129,7 @@
         <v/>
       </c>
       <c r="S144" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R144)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R144)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T144" s="90" t="inlineStr">
@@ -19255,7 +19255,7 @@
         <v/>
       </c>
       <c r="S145" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R145)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R145)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T145" s="90" t="inlineStr">
@@ -19381,7 +19381,7 @@
         <v/>
       </c>
       <c r="S146" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R146)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R146)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T146" s="90" t="inlineStr">
@@ -19507,7 +19507,7 @@
         <v/>
       </c>
       <c r="S147" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R147)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R147)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T147" s="90" t="inlineStr">
@@ -19633,7 +19633,7 @@
         <v/>
       </c>
       <c r="S148" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R148)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R148)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T148" s="90" t="inlineStr">
@@ -19759,7 +19759,7 @@
         <v/>
       </c>
       <c r="S149" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R149)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R149)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T149" s="90" t="inlineStr">
@@ -19885,7 +19885,7 @@
         <v/>
       </c>
       <c r="S150" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R150)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R150)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T150" s="90" t="inlineStr">
@@ -20011,7 +20011,7 @@
         <v/>
       </c>
       <c r="S151" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R151)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R151)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T151" s="90" t="inlineStr">
@@ -20137,7 +20137,7 @@
         <v/>
       </c>
       <c r="S152" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R152)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R152)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T152" s="90" t="inlineStr">
@@ -20263,7 +20263,7 @@
         <v/>
       </c>
       <c r="S153" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R153)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R153)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T153" s="90" t="inlineStr">
@@ -20389,7 +20389,7 @@
         <v/>
       </c>
       <c r="S154" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R154)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R154)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T154" s="90" t="inlineStr">
@@ -20515,7 +20515,7 @@
         <v/>
       </c>
       <c r="S155" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R155)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R155)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T155" s="90" t="inlineStr">
@@ -20641,7 +20641,7 @@
         <v/>
       </c>
       <c r="S156" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R156)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R156)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T156" s="90" t="inlineStr">
@@ -20767,7 +20767,7 @@
         <v/>
       </c>
       <c r="S157" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R157)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R157)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T157" s="90" t="inlineStr">
@@ -20893,7 +20893,7 @@
         <v/>
       </c>
       <c r="S158" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R158)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R158)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T158" s="90" t="inlineStr">
@@ -21019,7 +21019,7 @@
         <v/>
       </c>
       <c r="S159" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R159)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R159)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T159" s="90" t="inlineStr">
@@ -21145,7 +21145,7 @@
         <v/>
       </c>
       <c r="S160" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R160)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R160)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T160" s="90" t="inlineStr">
@@ -21271,7 +21271,7 @@
         <v/>
       </c>
       <c r="S161" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R161)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R161)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T161" s="90" t="inlineStr">
@@ -21397,7 +21397,7 @@
         <v/>
       </c>
       <c r="S162" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R162)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R162)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T162" s="90" t="inlineStr">
@@ -21523,7 +21523,7 @@
         <v/>
       </c>
       <c r="S163" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R163)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R163)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T163" s="90" t="inlineStr">
@@ -21649,7 +21649,7 @@
         <v/>
       </c>
       <c r="S164" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R164)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R164)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T164" s="90" t="inlineStr">
@@ -21775,7 +21775,7 @@
         <v/>
       </c>
       <c r="S165" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R165)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R165)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T165" s="90" t="inlineStr">
@@ -21901,7 +21901,7 @@
         <v/>
       </c>
       <c r="S166" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R166)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R166)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T166" s="90" t="inlineStr">
@@ -22027,7 +22027,7 @@
         <v/>
       </c>
       <c r="S167" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R167)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R167)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T167" s="90" t="inlineStr">
@@ -22153,7 +22153,7 @@
         <v/>
       </c>
       <c r="S168" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R168)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R168)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T168" s="90" t="inlineStr">
@@ -22279,7 +22279,7 @@
         <v/>
       </c>
       <c r="S169" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R169)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R169)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T169" s="90" t="inlineStr">
@@ -22405,7 +22405,7 @@
         <v/>
       </c>
       <c r="S170" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R170)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R170)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T170" s="90" t="inlineStr">
@@ -22531,7 +22531,7 @@
         <v/>
       </c>
       <c r="S171" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R171)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R171)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T171" s="90" t="inlineStr">
@@ -22654,7 +22654,7 @@
         <v/>
       </c>
       <c r="S172" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R172)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R172)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T172" s="90" t="inlineStr">
@@ -22777,7 +22777,7 @@
         <v/>
       </c>
       <c r="S173" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R173)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R173)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T173" s="90" t="inlineStr">
@@ -22901,7 +22901,7 @@
         <v/>
       </c>
       <c r="S174" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R174)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R174)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T174" s="90" t="inlineStr">
@@ -23025,7 +23025,7 @@
         <v/>
       </c>
       <c r="S175" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R175)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R175)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T175" s="90" t="inlineStr">
@@ -23149,7 +23149,7 @@
         <v/>
       </c>
       <c r="S176" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R176)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R176)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T176" s="90" t="inlineStr">
@@ -23273,7 +23273,7 @@
         <v/>
       </c>
       <c r="S177" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R177)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R177)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T177" s="90" t="inlineStr">
@@ -23397,7 +23397,7 @@
         <v/>
       </c>
       <c r="S178" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R178)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R178)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T178" s="90" t="inlineStr">
@@ -23522,7 +23522,7 @@
         <v/>
       </c>
       <c r="S179" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R179)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R179)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T179" s="90" t="inlineStr">
@@ -23645,7 +23645,7 @@
         <v/>
       </c>
       <c r="S180" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R180)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R180)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T180" s="90" t="inlineStr">
@@ -23769,7 +23769,7 @@
         <v/>
       </c>
       <c r="S181" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R181)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R181)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T181" s="90" t="inlineStr">
@@ -23892,7 +23892,7 @@
         <v/>
       </c>
       <c r="S182" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R182)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R182)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T182" s="90" t="inlineStr">
@@ -24015,7 +24015,7 @@
         <v/>
       </c>
       <c r="S183" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R183)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R183)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T183" s="90" t="inlineStr">
@@ -24139,7 +24139,7 @@
         <v/>
       </c>
       <c r="S184" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R184)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R184)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T184" s="90" t="inlineStr">
@@ -24264,7 +24264,7 @@
         <v/>
       </c>
       <c r="S185" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R185)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R185)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T185" s="90" t="inlineStr">
@@ -24388,7 +24388,7 @@
         <v/>
       </c>
       <c r="S186" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R186)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R186)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T186" s="90" t="inlineStr">
@@ -24512,7 +24512,7 @@
         <v/>
       </c>
       <c r="S187" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R187)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R187)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T187" s="90" t="inlineStr">
@@ -24636,7 +24636,7 @@
         <v/>
       </c>
       <c r="S188" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R188)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R188)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T188" s="90" t="inlineStr">
@@ -24760,7 +24760,7 @@
         <v/>
       </c>
       <c r="S189" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R189)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R189)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T189" s="90" t="inlineStr">
@@ -24884,7 +24884,7 @@
         <v/>
       </c>
       <c r="S190" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R190)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R190)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T190" s="90" t="inlineStr">
@@ -25008,7 +25008,7 @@
         <v/>
       </c>
       <c r="S191" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R191)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R191)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T191" s="90" t="inlineStr">
@@ -25131,7 +25131,7 @@
         <v/>
       </c>
       <c r="S192" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R192)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R192)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T192" s="90" t="inlineStr">
@@ -25255,7 +25255,7 @@
         <v/>
       </c>
       <c r="S193" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R193)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R193)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T193" s="90" t="inlineStr">
@@ -25378,7 +25378,7 @@
         <v/>
       </c>
       <c r="S194" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R194)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R194)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T194" s="90" t="inlineStr">
@@ -25501,7 +25501,7 @@
         <v/>
       </c>
       <c r="S195" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R195)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R195)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T195" s="90" t="inlineStr">
@@ -25625,7 +25625,7 @@
         <v/>
       </c>
       <c r="S196" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R196)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R196)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T196" s="90" t="inlineStr">
@@ -25748,7 +25748,7 @@
         <v/>
       </c>
       <c r="S197" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R197)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R197)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T197" s="90" t="inlineStr">
@@ -25871,7 +25871,7 @@
         <v/>
       </c>
       <c r="S198" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R198)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R198)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T198" s="90" t="inlineStr">
@@ -25994,7 +25994,7 @@
         <v/>
       </c>
       <c r="S199" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R199)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R199)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T199" s="90" t="inlineStr">
@@ -26117,7 +26117,7 @@
         <v/>
       </c>
       <c r="S200" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R200)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R200)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T200" s="90" t="inlineStr">
@@ -26240,7 +26240,7 @@
         <v/>
       </c>
       <c r="S201" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R201)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R201)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T201" s="90" t="inlineStr">
@@ -26363,7 +26363,7 @@
         <v/>
       </c>
       <c r="S202" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R202)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R202)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T202" s="90" t="inlineStr">
@@ -26486,7 +26486,7 @@
         <v/>
       </c>
       <c r="S203" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R203)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R203)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T203" s="90" t="inlineStr">
@@ -26609,7 +26609,7 @@
         <v/>
       </c>
       <c r="S204" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R204)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R204)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T204" s="90" t="inlineStr">
@@ -26733,7 +26733,7 @@
         <v/>
       </c>
       <c r="S205" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R205)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R205)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T205" s="90" t="inlineStr">
@@ -26857,7 +26857,7 @@
         <v/>
       </c>
       <c r="S206" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R206)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R206)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T206" s="90" t="inlineStr">
@@ -26980,7 +26980,7 @@
         <v/>
       </c>
       <c r="S207" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R207)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R207)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T207" s="90" t="inlineStr">
@@ -27103,7 +27103,7 @@
         <v/>
       </c>
       <c r="S208" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R208)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R208)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T208" s="90" t="inlineStr">
@@ -27226,7 +27226,7 @@
         <v/>
       </c>
       <c r="S209" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R209)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R209)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T209" s="90" t="inlineStr">
@@ -27349,7 +27349,7 @@
         <v/>
       </c>
       <c r="S210" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R210)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R210)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T210" s="90" t="inlineStr">
@@ -27472,7 +27472,7 @@
         <v/>
       </c>
       <c r="S211" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R211)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R211)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T211" s="90" t="inlineStr">
@@ -27595,7 +27595,7 @@
         <v/>
       </c>
       <c r="S212" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R212)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R212)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T212" s="90" t="inlineStr">
@@ -27718,7 +27718,7 @@
         <v/>
       </c>
       <c r="S213" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R213)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R213)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T213" s="90" t="inlineStr">
@@ -27841,7 +27841,7 @@
         <v/>
       </c>
       <c r="S214" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R214)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R214)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T214" s="90" t="inlineStr">
@@ -27964,7 +27964,7 @@
         <v/>
       </c>
       <c r="S215" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R215)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R215)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T215" s="90" t="inlineStr">
@@ -28087,7 +28087,7 @@
         <v/>
       </c>
       <c r="S216" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R216)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R216)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T216" s="90" t="inlineStr">
@@ -28210,7 +28210,7 @@
         <v/>
       </c>
       <c r="S217" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R217)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R217)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T217" s="90" t="inlineStr">
@@ -28334,7 +28334,7 @@
         <v/>
       </c>
       <c r="S218" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R218)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R218)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T218" s="90" t="inlineStr">
@@ -28457,7 +28457,7 @@
         <v/>
       </c>
       <c r="S219" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R219)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R219)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T219" s="90" t="inlineStr">
@@ -28580,7 +28580,7 @@
         <v/>
       </c>
       <c r="S220" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R220)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R220)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T220" s="90" t="inlineStr">
@@ -28703,7 +28703,7 @@
         <v/>
       </c>
       <c r="S221" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R221)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R221)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T221" s="90" t="inlineStr">
@@ -28826,7 +28826,7 @@
         <v/>
       </c>
       <c r="S222" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R222)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R222)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T222" s="90" t="inlineStr">
@@ -28949,7 +28949,7 @@
         <v/>
       </c>
       <c r="S223" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R223)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R223)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T223" s="90" t="inlineStr">
@@ -29072,7 +29072,7 @@
         <v/>
       </c>
       <c r="S224" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R224)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R224)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T224" s="90" t="inlineStr">
@@ -29195,7 +29195,7 @@
         <v/>
       </c>
       <c r="S225" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R225)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R225)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T225" s="90" t="inlineStr">
@@ -29318,7 +29318,7 @@
         <v/>
       </c>
       <c r="S226" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R226)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R226)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T226" s="90" t="inlineStr">
@@ -29441,7 +29441,7 @@
         <v/>
       </c>
       <c r="S227" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R227)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R227)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T227" s="90" t="inlineStr">
@@ -29564,7 +29564,7 @@
         <v/>
       </c>
       <c r="S228" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R228)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R228)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T228" s="90" t="inlineStr">
@@ -29687,7 +29687,7 @@
         <v/>
       </c>
       <c r="S229" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R229)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R229)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T229" s="90" t="inlineStr">
@@ -29810,7 +29810,7 @@
         <v/>
       </c>
       <c r="S230" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R230)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R230)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T230" s="90" t="inlineStr">
@@ -29934,7 +29934,7 @@
         <v/>
       </c>
       <c r="S231" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R231)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R231)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T231" s="93" t="inlineStr">
@@ -30057,7 +30057,7 @@
         <v/>
       </c>
       <c r="S232" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R232)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R232)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T232" s="93" t="inlineStr">
@@ -30177,7 +30177,7 @@
         <v/>
       </c>
       <c r="S233" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R233)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R233)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U233" s="93" t="inlineStr">
@@ -30293,7 +30293,7 @@
         <v/>
       </c>
       <c r="S234" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R234)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R234)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U234" s="93" t="inlineStr">
@@ -30409,7 +30409,7 @@
         <v/>
       </c>
       <c r="S235" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R235)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R235)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U235" s="93" t="inlineStr">
@@ -30525,7 +30525,7 @@
         <v/>
       </c>
       <c r="S236" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R236)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R236)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U236" s="93" t="inlineStr">
@@ -30641,7 +30641,7 @@
         <v/>
       </c>
       <c r="S237" s="94">
-        <f>IF(COUNTIF($R$6:$R$241,R237)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R237)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U237" s="93" t="inlineStr">
@@ -30758,7 +30758,7 @@
         <v/>
       </c>
       <c r="S238" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R238)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R238)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T238" s="90" t="inlineStr">
@@ -30881,7 +30881,7 @@
         <v/>
       </c>
       <c r="S239" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R239)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R239)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T239" s="90" t="inlineStr">
@@ -31000,7 +31000,7 @@
         <v/>
       </c>
       <c r="S240" s="63">
-        <f>IF(COUNTIF($R$6:$R$241,R240)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R240)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T240" s="90" t="inlineStr">
@@ -31119,7 +31119,7 @@
         <v/>
       </c>
       <c r="S241" s="90">
-        <f>IF(COUNTIF($R$6:$R$241,R241)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$242,R241)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T241" s="90" t="inlineStr">
@@ -31150,6 +31150,127 @@
       <c r="Y241" s="63" t="inlineStr">
         <is>
           <t>由局内关卡01 Boss竞技场190×90m白模v003按5m网格重建（非缩放；1/3线性缩放落在63.33×30m、X轴非5m整数倍，业主裁决取50×40m）。墙按固定5m槽位拼装，门墙完整占用5m槽并保留左右柱与门楣；两轴均为5m整数倍，无FIXED_TRIM收边。门：南→boss_prep(+2.5)、西→boss_exit(-2.5)。未导GLB、未接Godot。</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="255" customHeight="1" s="60">
+      <c r="A242" s="90" t="inlineStr">
+        <is>
+          <t>ENV-EXPEDITION-L01-L-CORRIDOR</t>
+        </is>
+      </c>
+      <c r="B242" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 L型走廊 数据连廊 45×40m 房间种类源</t>
+        </is>
+      </c>
+      <c r="C242" s="63" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="D242" s="90" t="inlineStr">
+        <is>
+          <t>l_corridor</t>
+        </is>
+      </c>
+      <c r="E242" s="90" t="inlineStr">
+        <is>
+          <t>expedition_01_l_corridor</t>
+        </is>
+      </c>
+      <c r="F242" s="90" t="inlineStr">
+        <is>
+          <t>room_type</t>
+        </is>
+      </c>
+      <c r="G242" s="90" t="n"/>
+      <c r="H242" s="90" t="inlineStr">
+        <is>
+          <t>Top3D / Blender Z-up</t>
+        </is>
+      </c>
+      <c r="I242" s="90" t="inlineStr">
+        <is>
+          <t>scene_art / reference_derived</t>
+        </is>
+      </c>
+      <c r="J242" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 专用；连接房间之间的 L 型通廊房间种类源</t>
+        </is>
+      </c>
+      <c r="K242" s="90" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L242" s="90" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M242" s="90" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="N242" s="90" t="inlineStr">
+        <is>
+          <t>45×40×11.9m；横臂 9×3 + 竖臂 3×5 个 5m 槽；走廊净宽 15m（三砖）；42 块地砖 / 121 个独立组件包 / 4 个门位</t>
+        </is>
+      </c>
+      <c r="O242" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/l_corridor/v003/L型走廊种类_数据连廊_45x40m_v003.blend</t>
+        </is>
+      </c>
+      <c r="P242" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/l_corridor/v003/widen_l_corridor_v003.py</t>
+        </is>
+      </c>
+      <c r="Q242" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01;L型走廊;数据连廊;房间种类;45×40m;走廊;服务器机柜;运维通道</t>
+        </is>
+      </c>
+      <c r="R242" s="90">
+        <f>LOWER(TRIM(C242)&amp;"|"&amp;TRIM(D242)&amp;"|"&amp;TRIM(E242)&amp;"|"&amp;TRIM(F242)&amp;"|"&amp;TRIM(H242)&amp;"|"&amp;TRIM(I242))</f>
+        <v/>
+      </c>
+      <c r="S242" s="90">
+        <f>IF(COUNTIF($R$6:$R$242,R242)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T242" s="90" t="inlineStr">
+        <is>
+          <t>9c323876f7165f656e016049135652a96c83ed0adb45f4f28c49fc50cfb5adae</t>
+        </is>
+      </c>
+      <c r="U242" s="63" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V242" s="90" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="W242" s="63" t="inlineStr">
+        <is>
+          <t>用户设计（参考图推定尺寸；业主 2026-09-24 裁决归属远征关卡01）</t>
+        </is>
+      </c>
+      <c r="X242" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y242" s="63" t="inlineStr">
+        <is>
+          <t>由 battle 区块房间种类源迁入（原 ENV-BATTLE-L-CORRIDOR-TYPE，原路径 tower_zones/battle/source/room_types/l_corridor/；业主 2026-09-24 裁决归属远征关卡01，battle 侧不留副本）。远征01 版图与白盒目录均无走廊白模，尺寸与门位按参考图推定。v001/v002 为 10m 宽走廊（外包络 45×35m / 28 块地砖 / 88、111 个组件包），v003 拓宽为 15m（45×40m / 42 块地砖 / 121 个组件包 / 4 个门位：西1 北2 南1）。随迁统一内部结构：component_packages_vNNN→component_packages、facility→facilities、散放渲染图入 renders/。共享件引用由 ENV-BATTLE-COMMON-* 更正为 shared 库现有 ENV-SHARED-GENERIC-*。未导 GLB、未接 Godot。</t>
         </is>
       </c>
     </row>
@@ -31173,15 +31294,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C240" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C6:C242" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K240" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K6:K242" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L240" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="L6:L242" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"P0,P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -31201,7 +31322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P147"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.80859375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="59" min="1" max="1"/>
@@ -42411,6 +42532,88 @@
       <c r="P147" s="119" t="inlineStr">
         <is>
           <t>由局内关卡01 Boss竞技场190×90m白模v003按5m网格重建（非缩放）；1/3=63.33×30m不合5m模数，业主裁决取50×40m；南门boss_prep(+2.5)、西门boss_exit(-2.5)；未导GLB。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="118" t="inlineStr">
+        <is>
+          <t>ENV-EXPEDITION-L01-L-CORRIDOR</t>
+        </is>
+      </c>
+      <c r="B148" s="119" t="inlineStr">
+        <is>
+          <t>远征关卡01 L型走廊 数据连廊 45×40m 房间种类源</t>
+        </is>
+      </c>
+      <c r="C148" s="119" t="inlineStr">
+        <is>
+          <t>未制作</t>
+        </is>
+      </c>
+      <c r="D148" s="119" t="inlineStr">
+        <is>
+          <t>未制作</t>
+        </is>
+      </c>
+      <c r="E148" s="118" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/l_corridor/v003/L型走廊种类_数据连廊_45x40m_v003.blend</t>
+        </is>
+      </c>
+      <c r="F148" s="119" t="inlineStr">
+        <is>
+          <t>远征关卡01 L型走廊房间种类源；45×40m（横臂 9×3 + 竖臂 3×5 个 5m 槽）；走廊净宽 15m 即三块 5m 地砖并列；42 块地砖 / 121 个独立组件包；门位 4 个（西1、北2、南1），门墙槽留空由通用门墙组件补位。</t>
+        </is>
+      </c>
+      <c r="G148" s="119" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H148" s="119" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I148" s="119" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J148" s="119" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K148" s="118" t="inlineStr">
+        <is>
+          <t>45×40×11.9m</t>
+        </is>
+      </c>
+      <c r="L148" s="119" t="inlineStr">
+        <is>
+          <t>房间局部坐标：X/Y 居中；底面 Z=0；Godot -Z</t>
+        </is>
+      </c>
+      <c r="M148" s="119" t="inlineStr">
+        <is>
+          <t>远征关卡01 / Expedition</t>
+        </is>
+      </c>
+      <c r="N148" s="119" t="inlineStr">
+        <is>
+          <t>房间种类源已完成；QA PASS</t>
+        </is>
+      </c>
+      <c r="O148" s="118" t="inlineStr">
+        <is>
+          <t>v003</t>
+        </is>
+      </c>
+      <c r="P148" s="119" t="inlineStr">
+        <is>
+          <t>由 battle 区块迁入（原 l_corridor_room_type_v003.blend）；无白模，尺寸按参考图推定；v001/v002（10m 宽）保留在同目录历史版本；未导 GLB、未接 Godot。</t>
         </is>
       </c>
     </row>
@@ -44450,7 +44653,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="60">
       <c r="A4" s="99" t="inlineStr">
         <is>
@@ -44564,7 +44766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.80859375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="59" min="1" max="1"/>
@@ -45109,6 +45311,43 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="118" t="inlineStr">
+        <is>
+          <t>v0.1.13</t>
+        </is>
+      </c>
+      <c r="B19" s="118" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C19" s="119" t="inlineStr">
+        <is>
+          <t>归属迁移</t>
+        </is>
+      </c>
+      <c r="D19" s="119" t="inlineStr">
+        <is>
+          <t>关卡场景 / 远征关卡01</t>
+        </is>
+      </c>
+      <c r="E19" s="119" t="inlineStr">
+        <is>
+          <t>新增 ENV-EXPEDITION-L01-L-CORRIDOR（远征关卡01 L型走廊 数据连廊 45×40m 房间种类源）：原为 battle 区块房间种类源（ENV-BATTLE-L-CORRIDOR-TYPE），业主 2026-09-24 裁决归属远征关卡01，整目录迁至 tower_zones/expedition/source/room_types/l_corridor/，battle 侧不留副本。随迁统一：component_packages_vNNN→component_packages、facility→facilities、渲染图入 renders/、源改名 L型走廊种类_数据连廊_&lt;尺寸&gt;m_vNNN.blend；共享件引用由 ENV-BATTLE-COMMON-* 更正为 shared 库现有 ENV-SHARED-GENERIC-*。同批登记《资产主表》第242行与《3D-场景通用》第148行。v001/v002 为 10m 宽（45×35m / 88、111 包），v003 为 15m 宽（45×40m / 121 包）。未导 GLB、未接 Godot。</t>
+        </is>
+      </c>
+      <c r="F19" s="119" t="inlineStr">
+        <is>
+          <t>新增条目，不改动既有 AssetID / 路径 / 哈希；battle 区块的 room_types 目录随迁后为空。远征01 版图与白盒目录仍无走廊白模，接入前需远征白盒补走廊席位。《资产主表》DV 此前落后一行（C6:C240 未覆盖第241行），本次一并扩到 C6:C242。</t>
+        </is>
+      </c>
+      <c r="G19" s="119" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-场景通用" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3D-设施" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3D-其他" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="域变更日志" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$240</definedName>
@@ -1476,22 +1476,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="60">
       <c r="A6" s="65">
-        <f>COUNTA('资产主表'!$A$6:$A$242)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$246)</f>
         <v/>
       </c>
       <c r="B6" s="63" t="n"/>
       <c r="C6" s="65">
-        <f>COUNTIF('资产主表'!$K$6:$K$242,"已完成")+COUNTIF('资产主表'!$K$6:$K$242,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$242,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$242,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$242,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$242,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$242,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$246,"已完成")+COUNTIF('资产主表'!$K$6:$K$246,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$246,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$246,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$246,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$246,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$246,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="63" t="n"/>
       <c r="E6" s="65">
-        <f>COUNTIF('资产主表'!$K$6:$K$242,"待制作")+COUNTIF('资产主表'!$K$6:$K$242,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$246,"待制作")+COUNTIF('资产主表'!$K$6:$K$246,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="63" t="n"/>
       <c r="G6" s="65">
-        <f>COUNTIF('资产主表'!$S$6:$S$242,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$246,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="63" t="n"/>
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="B10" s="70">
-        <f>COUNTIF('资产主表'!$C$6:$C$242,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$246,A10)</f>
         <v/>
       </c>
       <c r="C10" s="70">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$242=A10)*(('资产主表'!$K$6:$K$242="已完成")+('资产主表'!$K$6:$K$242="原型已接入")+('资产主表'!$K$6:$K$242="正式美术已接入")+('资产主表'!$K$6:$K$242="已优化并正式接入")+('资产主表'!$K$6:$K$242="Blender源已完成")+('资产主表'!$K$6:$K$242="已导入；优化完成")+('资产主表'!$K$6:$K$242="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$246=A10)*(('资产主表'!$K$6:$K$246="已完成")+('资产主表'!$K$6:$K$246="原型已接入")+('资产主表'!$K$6:$K$246="正式美术已接入")+('资产主表'!$K$6:$K$246="已优化并正式接入")+('资产主表'!$K$6:$K$246="Blender源已完成")+('资产主表'!$K$6:$K$246="已导入；优化完成")+('资产主表'!$K$6:$K$246="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="70" t="n"/>
@@ -1582,11 +1582,11 @@
         </is>
       </c>
       <c r="B11" s="70">
-        <f>COUNTIF('资产主表'!$C$6:$C$242,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$246,A11)</f>
         <v/>
       </c>
       <c r="C11" s="70">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$242=A11)*(('资产主表'!$K$6:$K$242="已完成")+('资产主表'!$K$6:$K$242="原型已接入")+('资产主表'!$K$6:$K$242="正式美术已接入")+('资产主表'!$K$6:$K$242="已优化并正式接入")+('资产主表'!$K$6:$K$242="Blender源已完成")+('资产主表'!$K$6:$K$242="已导入；优化完成")+('资产主表'!$K$6:$K$242="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$246=A11)*(('资产主表'!$K$6:$K$246="已完成")+('资产主表'!$K$6:$K$246="原型已接入")+('资产主表'!$K$6:$K$246="正式美术已接入")+('资产主表'!$K$6:$K$246="已优化并正式接入")+('资产主表'!$K$6:$K$246="Blender源已完成")+('资产主表'!$K$6:$K$246="已导入；优化完成")+('资产主表'!$K$6:$K$246="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="70" t="n"/>
@@ -1604,11 +1604,11 @@
         </is>
       </c>
       <c r="B12" s="70">
-        <f>COUNTIF('资产主表'!$C$6:$C$242,A12)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$246,A12)</f>
         <v/>
       </c>
       <c r="C12" s="70">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$242=A12)*(('资产主表'!$K$6:$K$242="已完成")+('资产主表'!$K$6:$K$242="原型已接入")+('资产主表'!$K$6:$K$242="正式美术已接入")+('资产主表'!$K$6:$K$242="已优化并正式接入")+('资产主表'!$K$6:$K$242="Blender源已完成")+('资产主表'!$K$6:$K$242="已导入；优化完成")+('资产主表'!$K$6:$K$242="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$246=A12)*(('资产主表'!$K$6:$K$246="已完成")+('资产主表'!$K$6:$K$246="原型已接入")+('资产主表'!$K$6:$K$246="正式美术已接入")+('资产主表'!$K$6:$K$246="已优化并正式接入")+('资产主表'!$K$6:$K$246="Blender源已完成")+('资产主表'!$K$6:$K$246="已导入；优化完成")+('资产主表'!$K$6:$K$246="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D12" s="70" t="n"/>
@@ -1626,11 +1626,11 @@
         </is>
       </c>
       <c r="B13" s="66">
-        <f>COUNTIF('资产主表'!$C$6:$C$242,A13)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$246,A13)</f>
         <v/>
       </c>
       <c r="C13" s="66">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$242=A13)*(('资产主表'!$K$6:$K$242="已完成")+('资产主表'!$K$6:$K$242="原型已接入")+('资产主表'!$K$6:$K$242="正式美术已接入")+('资产主表'!$K$6:$K$242="已优化并正式接入")+('资产主表'!$K$6:$K$242="Blender源已完成")+('资产主表'!$K$6:$K$242="已导入；优化完成")+('资产主表'!$K$6:$K$242="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$246=A13)*(('资产主表'!$K$6:$K$246="已完成")+('资产主表'!$K$6:$K$246="原型已接入")+('资产主表'!$K$6:$K$246="正式美术已接入")+('资产主表'!$K$6:$K$246="已优化并正式接入")+('资产主表'!$K$6:$K$246="Blender源已完成")+('资产主表'!$K$6:$K$246="已导入；优化完成")+('资产主表'!$K$6:$K$246="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D13" s="66" t="n"/>
@@ -2194,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y242"/>
+  <dimension ref="A1:Y246"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.80859375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="25" customWidth="1" style="59" min="1" max="1"/>
@@ -2470,7 +2470,7 @@
         <v/>
       </c>
       <c r="S6" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="71" t="n"/>
@@ -2577,7 +2577,7 @@
         <v/>
       </c>
       <c r="S7" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="71" t="n"/>
@@ -2684,7 +2684,7 @@
         <v/>
       </c>
       <c r="S8" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="71" t="n"/>
@@ -2791,7 +2791,7 @@
         <v/>
       </c>
       <c r="S9" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="71" t="n"/>
@@ -2898,7 +2898,7 @@
         <v/>
       </c>
       <c r="S10" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="71" t="n"/>
@@ -3005,7 +3005,7 @@
         <v/>
       </c>
       <c r="S11" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="71" t="n"/>
@@ -3112,7 +3112,7 @@
         <v/>
       </c>
       <c r="S12" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="71" t="n"/>
@@ -3219,7 +3219,7 @@
         <v/>
       </c>
       <c r="S13" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="71" t="n"/>
@@ -3326,7 +3326,7 @@
         <v/>
       </c>
       <c r="S14" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="71" t="n"/>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="S15" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="71" t="n"/>
@@ -3540,7 +3540,7 @@
         <v/>
       </c>
       <c r="S16" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="71" t="n"/>
@@ -3647,7 +3647,7 @@
         <v/>
       </c>
       <c r="S17" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="71" t="n"/>
@@ -3754,7 +3754,7 @@
         <v/>
       </c>
       <c r="S18" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="71" t="n"/>
@@ -3861,7 +3861,7 @@
         <v/>
       </c>
       <c r="S19" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="71" t="n"/>
@@ -3968,7 +3968,7 @@
         <v/>
       </c>
       <c r="S20" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="71" t="n"/>
@@ -4075,7 +4075,7 @@
         <v/>
       </c>
       <c r="S21" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="71" t="n"/>
@@ -4182,7 +4182,7 @@
         <v/>
       </c>
       <c r="S22" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="71" t="n"/>
@@ -4289,7 +4289,7 @@
         <v/>
       </c>
       <c r="S23" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="71" t="n"/>
@@ -4396,7 +4396,7 @@
         <v/>
       </c>
       <c r="S24" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="71" t="n"/>
@@ -4503,7 +4503,7 @@
         <v/>
       </c>
       <c r="S25" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="71" t="n"/>
@@ -4610,7 +4610,7 @@
         <v/>
       </c>
       <c r="S26" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="71" t="n"/>
@@ -4717,7 +4717,7 @@
         <v/>
       </c>
       <c r="S27" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="71" t="n"/>
@@ -4824,7 +4824,7 @@
         <v/>
       </c>
       <c r="S28" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="71" t="n"/>
@@ -4931,7 +4931,7 @@
         <v/>
       </c>
       <c r="S29" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="71" t="n"/>
@@ -5038,7 +5038,7 @@
         <v/>
       </c>
       <c r="S30" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="71" t="n"/>
@@ -5145,7 +5145,7 @@
         <v/>
       </c>
       <c r="S31" s="71">
-        <f>IF(COUNTIF($R$6:$R$242,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="71" t="n"/>
@@ -5264,7 +5264,7 @@
         <v/>
       </c>
       <c r="S32" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="87" t="inlineStr">
@@ -5387,7 +5387,7 @@
         <v/>
       </c>
       <c r="S33" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="90" t="inlineStr">
@@ -5510,7 +5510,7 @@
         <v/>
       </c>
       <c r="S34" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="90" t="inlineStr">
@@ -5633,7 +5633,7 @@
         <v/>
       </c>
       <c r="S35" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="90" t="inlineStr">
@@ -5756,7 +5756,7 @@
         <v/>
       </c>
       <c r="S36" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="87" t="inlineStr">
@@ -5880,7 +5880,7 @@
         <v/>
       </c>
       <c r="S37" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="90" t="inlineStr">
@@ -6003,7 +6003,7 @@
         <v/>
       </c>
       <c r="S38" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="90" t="inlineStr">
@@ -6122,7 +6122,7 @@
         <v/>
       </c>
       <c r="S39" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="87" t="inlineStr">
@@ -6245,7 +6245,7 @@
         <v/>
       </c>
       <c r="S40" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="90" t="inlineStr">
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="S41" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="90" t="inlineStr">
@@ -6491,7 +6491,7 @@
         <v/>
       </c>
       <c r="S42" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="90" t="inlineStr">
@@ -6614,7 +6614,7 @@
         <v/>
       </c>
       <c r="S43" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="90" t="inlineStr">
@@ -6737,7 +6737,7 @@
         <v/>
       </c>
       <c r="S44" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="87" t="inlineStr">
@@ -6861,7 +6861,7 @@
         <v/>
       </c>
       <c r="S45" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="90" t="inlineStr">
@@ -6984,7 +6984,7 @@
         <v/>
       </c>
       <c r="S46" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="90" t="inlineStr">
@@ -7107,7 +7107,7 @@
         <v/>
       </c>
       <c r="S47" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="90" t="inlineStr">
@@ -7230,7 +7230,7 @@
         <v/>
       </c>
       <c r="S48" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R48)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R48)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T48" s="90" t="inlineStr">
@@ -7350,7 +7350,7 @@
         <v/>
       </c>
       <c r="S49" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R49)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R49)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T49" s="90" t="inlineStr">
@@ -7473,7 +7473,7 @@
         <v/>
       </c>
       <c r="S50" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R50)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R50)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T50" s="90" t="inlineStr">
@@ -7597,7 +7597,7 @@
         <v/>
       </c>
       <c r="S51" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R51)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R51)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T51" s="90" t="inlineStr">
@@ -7720,7 +7720,7 @@
         <v/>
       </c>
       <c r="S52" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R52)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R52)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T52" s="87" t="inlineStr">
@@ -7844,7 +7844,7 @@
         <v/>
       </c>
       <c r="S53" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R53)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R53)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T53" s="87" t="inlineStr">
@@ -7967,7 +7967,7 @@
         <v/>
       </c>
       <c r="S54" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R54)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R54)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T54" s="87" t="inlineStr">
@@ -8096,7 +8096,7 @@
         <v/>
       </c>
       <c r="S55" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R55)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R55)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T55" s="87" t="inlineStr">
@@ -8223,7 +8223,7 @@
         <v/>
       </c>
       <c r="S56" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R56)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R56)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T56" s="87" t="inlineStr">
@@ -8346,7 +8346,7 @@
         <v/>
       </c>
       <c r="S57" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R57)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R57)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T57" s="87" t="inlineStr">
@@ -8471,7 +8471,7 @@
         <v/>
       </c>
       <c r="S58" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R58)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R58)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T58" s="87" t="inlineStr">
@@ -8594,7 +8594,7 @@
         <v/>
       </c>
       <c r="S59" s="88">
-        <f>IF(COUNTIF($R$6:$R$242,R59)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R59)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T59" s="87" t="inlineStr">
@@ -8713,7 +8713,7 @@
         <v/>
       </c>
       <c r="S60" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R60)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R60)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T60" s="90" t="inlineStr">
@@ -8833,7 +8833,7 @@
         <v/>
       </c>
       <c r="S61" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R61)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R61)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T61" s="90" t="inlineStr">
@@ -8953,7 +8953,7 @@
         <v/>
       </c>
       <c r="S62" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R62)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R62)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T62" s="90" t="inlineStr">
@@ -9073,7 +9073,7 @@
         <v/>
       </c>
       <c r="S63" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R63)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R63)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T63" s="90" t="n"/>
@@ -9193,7 +9193,7 @@
         <v/>
       </c>
       <c r="S64" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R64)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R64)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T64" s="90" t="inlineStr">
@@ -9318,7 +9318,7 @@
         <v/>
       </c>
       <c r="S65" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R65)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R65)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T65" s="90" t="inlineStr">
@@ -9443,7 +9443,7 @@
         <v/>
       </c>
       <c r="S66" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R66)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R66)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T66" s="90" t="inlineStr">
@@ -9568,7 +9568,7 @@
         <v/>
       </c>
       <c r="S67" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R67)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R67)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T67" s="90" t="inlineStr">
@@ -9693,7 +9693,7 @@
         <v/>
       </c>
       <c r="S68" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R68)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R68)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T68" s="90" t="inlineStr">
@@ -9824,7 +9824,7 @@
         <v/>
       </c>
       <c r="S69" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R69)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R69)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T69" s="90" t="inlineStr">
@@ -9950,7 +9950,7 @@
         <v/>
       </c>
       <c r="S70" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R70)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R70)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T70" s="90" t="inlineStr">
@@ -10074,7 +10074,7 @@
         <v/>
       </c>
       <c r="S71" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R71)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R71)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T71" s="90" t="inlineStr">
@@ -10198,7 +10198,7 @@
         <v/>
       </c>
       <c r="S72" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R72)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R72)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T72" s="90" t="inlineStr">
@@ -10322,7 +10322,7 @@
         <v/>
       </c>
       <c r="S73" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R73)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R73)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T73" s="90" t="inlineStr">
@@ -10446,7 +10446,7 @@
         <v/>
       </c>
       <c r="S74" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R74)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R74)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T74" s="90" t="inlineStr">
@@ -10570,7 +10570,7 @@
         <v/>
       </c>
       <c r="S75" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R75)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R75)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T75" s="90" t="inlineStr">
@@ -10694,7 +10694,7 @@
         <v/>
       </c>
       <c r="S76" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R76)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R76)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T76" s="90" t="inlineStr">
@@ -10818,7 +10818,7 @@
         <v/>
       </c>
       <c r="S77" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R77)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R77)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T77" s="90" t="inlineStr">
@@ -10942,7 +10942,7 @@
         <v/>
       </c>
       <c r="S78" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R78)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R78)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T78" s="90" t="inlineStr">
@@ -11066,7 +11066,7 @@
         <v/>
       </c>
       <c r="S79" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R79)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R79)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T79" s="90" t="inlineStr">
@@ -11190,7 +11190,7 @@
         <v/>
       </c>
       <c r="S80" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R80)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R80)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T80" s="90" t="inlineStr">
@@ -11314,7 +11314,7 @@
         <v/>
       </c>
       <c r="S81" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R81)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R81)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T81" s="90" t="inlineStr">
@@ -11438,7 +11438,7 @@
         <v/>
       </c>
       <c r="S82" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R82)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R82)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T82" s="90" t="inlineStr">
@@ -11562,7 +11562,7 @@
         <v/>
       </c>
       <c r="S83" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R83)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R83)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T83" s="90" t="inlineStr">
@@ -11686,7 +11686,7 @@
         <v/>
       </c>
       <c r="S84" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R84)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R84)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T84" s="90" t="inlineStr">
@@ -11810,7 +11810,7 @@
         <v/>
       </c>
       <c r="S85" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R85)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R85)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T85" s="90" t="inlineStr">
@@ -11934,7 +11934,7 @@
         <v/>
       </c>
       <c r="S86" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R86)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R86)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T86" s="90" t="inlineStr">
@@ -12058,7 +12058,7 @@
         <v/>
       </c>
       <c r="S87" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R87)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R87)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T87" s="90" t="inlineStr">
@@ -12182,7 +12182,7 @@
         <v/>
       </c>
       <c r="S88" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R88)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R88)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T88" s="90" t="inlineStr">
@@ -12306,7 +12306,7 @@
         <v/>
       </c>
       <c r="S89" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R89)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R89)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T89" s="90" t="inlineStr">
@@ -12430,7 +12430,7 @@
         <v/>
       </c>
       <c r="S90" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R90)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R90)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T90" s="90" t="inlineStr">
@@ -12554,7 +12554,7 @@
         <v/>
       </c>
       <c r="S91" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R91)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R91)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T91" s="90" t="inlineStr">
@@ -12678,7 +12678,7 @@
         <v/>
       </c>
       <c r="S92" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R92)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R92)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T92" s="90" t="inlineStr">
@@ -12802,7 +12802,7 @@
         <v/>
       </c>
       <c r="S93" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R93)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R93)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T93" s="90" t="inlineStr">
@@ -12926,7 +12926,7 @@
         <v/>
       </c>
       <c r="S94" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R94)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R94)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T94" s="90" t="inlineStr">
@@ -13050,7 +13050,7 @@
         <v/>
       </c>
       <c r="S95" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R95)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R95)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T95" s="90" t="inlineStr">
@@ -13174,7 +13174,7 @@
         <v/>
       </c>
       <c r="S96" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R96)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R96)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T96" s="90" t="inlineStr">
@@ -13298,7 +13298,7 @@
         <v/>
       </c>
       <c r="S97" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R97)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R97)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T97" s="90" t="inlineStr">
@@ -13422,7 +13422,7 @@
         <v/>
       </c>
       <c r="S98" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R98)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R98)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T98" s="90" t="inlineStr">
@@ -13546,7 +13546,7 @@
         <v/>
       </c>
       <c r="S99" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R99)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R99)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T99" s="90" t="inlineStr">
@@ -13670,7 +13670,7 @@
         <v/>
       </c>
       <c r="S100" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R100)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R100)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T100" s="90" t="inlineStr">
@@ -13794,7 +13794,7 @@
         <v/>
       </c>
       <c r="S101" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R101)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R101)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T101" s="90" t="inlineStr">
@@ -13918,7 +13918,7 @@
         <v/>
       </c>
       <c r="S102" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R102)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R102)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T102" s="90" t="inlineStr">
@@ -14041,7 +14041,7 @@
         <v/>
       </c>
       <c r="S103" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R103)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R103)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T103" s="90" t="inlineStr">
@@ -14166,7 +14166,7 @@
         <v/>
       </c>
       <c r="S104" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R104)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R104)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T104" s="90" t="inlineStr">
@@ -14291,7 +14291,7 @@
         <v/>
       </c>
       <c r="S105" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R105)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R105)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T105" s="90" t="inlineStr">
@@ -14416,7 +14416,7 @@
         <v/>
       </c>
       <c r="S106" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R106)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R106)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T106" s="90" t="inlineStr">
@@ -14541,7 +14541,7 @@
         <v/>
       </c>
       <c r="S107" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R107)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R107)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T107" s="90" t="inlineStr">
@@ -14666,7 +14666,7 @@
         <v/>
       </c>
       <c r="S108" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R108)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R108)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T108" s="93" t="inlineStr">
@@ -14792,7 +14792,7 @@
         <v/>
       </c>
       <c r="S109" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R109)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R109)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T109" s="90" t="inlineStr">
@@ -14918,7 +14918,7 @@
         <v/>
       </c>
       <c r="S110" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R110)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R110)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T110" s="90" t="inlineStr">
@@ -15044,7 +15044,7 @@
         <v/>
       </c>
       <c r="S111" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R111)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R111)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T111" s="90" t="inlineStr">
@@ -15170,7 +15170,7 @@
         <v/>
       </c>
       <c r="S112" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R112)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R112)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T112" s="90" t="inlineStr">
@@ -15293,7 +15293,7 @@
         <v/>
       </c>
       <c r="S113" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R113)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R113)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T113" s="90" t="inlineStr">
@@ -15413,7 +15413,7 @@
         <v/>
       </c>
       <c r="S114" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R114)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R114)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T114" s="93" t="inlineStr">
@@ -15532,7 +15532,7 @@
         <v/>
       </c>
       <c r="S115" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R115)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R115)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T115" s="93" t="inlineStr">
@@ -15650,7 +15650,7 @@
         <v/>
       </c>
       <c r="S116" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R116)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R116)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T116" s="93" t="inlineStr">
@@ -15773,7 +15773,7 @@
         <v/>
       </c>
       <c r="S117" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R117)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R117)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T117" s="90" t="inlineStr">
@@ -15899,7 +15899,7 @@
         <v/>
       </c>
       <c r="S118" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R118)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R118)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T118" s="90" t="inlineStr">
@@ -16022,7 +16022,7 @@
         <v/>
       </c>
       <c r="S119" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R119)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R119)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T119" s="90" t="inlineStr">
@@ -16147,7 +16147,7 @@
         <v/>
       </c>
       <c r="S120" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R120)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R120)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T120" s="90" t="inlineStr">
@@ -16270,7 +16270,7 @@
         <v/>
       </c>
       <c r="S121" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R121)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R121)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T121" s="90" t="inlineStr">
@@ -16395,7 +16395,7 @@
         <v/>
       </c>
       <c r="S122" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R122)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R122)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T122" s="90" t="inlineStr">
@@ -16518,7 +16518,7 @@
         <v/>
       </c>
       <c r="S123" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R123)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R123)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T123" s="90" t="inlineStr">
@@ -16641,7 +16641,7 @@
         <v/>
       </c>
       <c r="S124" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R124)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R124)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T124" s="90" t="inlineStr">
@@ -16764,7 +16764,7 @@
         <v/>
       </c>
       <c r="S125" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R125)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R125)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T125" s="90" t="inlineStr">
@@ -16887,7 +16887,7 @@
         <v/>
       </c>
       <c r="S126" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R126)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R126)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T126" s="90" t="inlineStr">
@@ -17010,7 +17010,7 @@
         <v/>
       </c>
       <c r="S127" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R127)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R127)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T127" s="90" t="inlineStr">
@@ -17133,7 +17133,7 @@
         <v/>
       </c>
       <c r="S128" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R128)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R128)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T128" s="90" t="inlineStr">
@@ -17256,7 +17256,7 @@
         <v/>
       </c>
       <c r="S129" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R129)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R129)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T129" s="90" t="inlineStr">
@@ -17379,7 +17379,7 @@
         <v/>
       </c>
       <c r="S130" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R130)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R130)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T130" s="90" t="inlineStr">
@@ -17502,7 +17502,7 @@
         <v/>
       </c>
       <c r="S131" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R131)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R131)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T131" s="90" t="inlineStr">
@@ -17625,7 +17625,7 @@
         <v/>
       </c>
       <c r="S132" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R132)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R132)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T132" s="90" t="inlineStr">
@@ -17749,7 +17749,7 @@
         <v/>
       </c>
       <c r="S133" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R133)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R133)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T133" s="90" t="inlineStr">
@@ -17872,7 +17872,7 @@
         <v/>
       </c>
       <c r="S134" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R134)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R134)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T134" s="90" t="inlineStr">
@@ -17995,7 +17995,7 @@
         <v/>
       </c>
       <c r="S135" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R135)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R135)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T135" s="90" t="inlineStr">
@@ -18121,7 +18121,7 @@
         <v/>
       </c>
       <c r="S136" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R136)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R136)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T136" s="90" t="inlineStr">
@@ -18247,7 +18247,7 @@
         <v/>
       </c>
       <c r="S137" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R137)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R137)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T137" s="90" t="inlineStr">
@@ -18373,7 +18373,7 @@
         <v/>
       </c>
       <c r="S138" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R138)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R138)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T138" s="90" t="inlineStr">
@@ -18499,7 +18499,7 @@
         <v/>
       </c>
       <c r="S139" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R139)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R139)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T139" s="90" t="inlineStr">
@@ -18625,7 +18625,7 @@
         <v/>
       </c>
       <c r="S140" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R140)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R140)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T140" s="90" t="inlineStr">
@@ -18751,7 +18751,7 @@
         <v/>
       </c>
       <c r="S141" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R141)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R141)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T141" s="90" t="inlineStr">
@@ -18877,7 +18877,7 @@
         <v/>
       </c>
       <c r="S142" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R142)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R142)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T142" s="90" t="inlineStr">
@@ -19003,7 +19003,7 @@
         <v/>
       </c>
       <c r="S143" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R143)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R143)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T143" s="90" t="inlineStr">
@@ -19129,7 +19129,7 @@
         <v/>
       </c>
       <c r="S144" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R144)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R144)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T144" s="90" t="inlineStr">
@@ -19255,7 +19255,7 @@
         <v/>
       </c>
       <c r="S145" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R145)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R145)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T145" s="90" t="inlineStr">
@@ -19381,7 +19381,7 @@
         <v/>
       </c>
       <c r="S146" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R146)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R146)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T146" s="90" t="inlineStr">
@@ -19507,7 +19507,7 @@
         <v/>
       </c>
       <c r="S147" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R147)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R147)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T147" s="90" t="inlineStr">
@@ -19633,7 +19633,7 @@
         <v/>
       </c>
       <c r="S148" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R148)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R148)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T148" s="90" t="inlineStr">
@@ -19759,7 +19759,7 @@
         <v/>
       </c>
       <c r="S149" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R149)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R149)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T149" s="90" t="inlineStr">
@@ -19885,7 +19885,7 @@
         <v/>
       </c>
       <c r="S150" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R150)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R150)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T150" s="90" t="inlineStr">
@@ -20011,7 +20011,7 @@
         <v/>
       </c>
       <c r="S151" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R151)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R151)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T151" s="90" t="inlineStr">
@@ -20137,7 +20137,7 @@
         <v/>
       </c>
       <c r="S152" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R152)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R152)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T152" s="90" t="inlineStr">
@@ -20263,7 +20263,7 @@
         <v/>
       </c>
       <c r="S153" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R153)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R153)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T153" s="90" t="inlineStr">
@@ -20389,7 +20389,7 @@
         <v/>
       </c>
       <c r="S154" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R154)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R154)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T154" s="90" t="inlineStr">
@@ -20515,7 +20515,7 @@
         <v/>
       </c>
       <c r="S155" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R155)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R155)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T155" s="90" t="inlineStr">
@@ -20641,7 +20641,7 @@
         <v/>
       </c>
       <c r="S156" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R156)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R156)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T156" s="90" t="inlineStr">
@@ -20767,7 +20767,7 @@
         <v/>
       </c>
       <c r="S157" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R157)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R157)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T157" s="90" t="inlineStr">
@@ -20893,7 +20893,7 @@
         <v/>
       </c>
       <c r="S158" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R158)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R158)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T158" s="90" t="inlineStr">
@@ -21019,7 +21019,7 @@
         <v/>
       </c>
       <c r="S159" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R159)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R159)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T159" s="90" t="inlineStr">
@@ -21145,7 +21145,7 @@
         <v/>
       </c>
       <c r="S160" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R160)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R160)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T160" s="90" t="inlineStr">
@@ -21271,7 +21271,7 @@
         <v/>
       </c>
       <c r="S161" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R161)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R161)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T161" s="90" t="inlineStr">
@@ -21397,7 +21397,7 @@
         <v/>
       </c>
       <c r="S162" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R162)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R162)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T162" s="90" t="inlineStr">
@@ -21523,7 +21523,7 @@
         <v/>
       </c>
       <c r="S163" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R163)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R163)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T163" s="90" t="inlineStr">
@@ -21649,7 +21649,7 @@
         <v/>
       </c>
       <c r="S164" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R164)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R164)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T164" s="90" t="inlineStr">
@@ -21775,7 +21775,7 @@
         <v/>
       </c>
       <c r="S165" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R165)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R165)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T165" s="90" t="inlineStr">
@@ -21901,7 +21901,7 @@
         <v/>
       </c>
       <c r="S166" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R166)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R166)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T166" s="90" t="inlineStr">
@@ -22027,7 +22027,7 @@
         <v/>
       </c>
       <c r="S167" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R167)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R167)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T167" s="90" t="inlineStr">
@@ -22153,7 +22153,7 @@
         <v/>
       </c>
       <c r="S168" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R168)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R168)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T168" s="90" t="inlineStr">
@@ -22279,7 +22279,7 @@
         <v/>
       </c>
       <c r="S169" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R169)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R169)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T169" s="90" t="inlineStr">
@@ -22405,7 +22405,7 @@
         <v/>
       </c>
       <c r="S170" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R170)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R170)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T170" s="90" t="inlineStr">
@@ -22531,7 +22531,7 @@
         <v/>
       </c>
       <c r="S171" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R171)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R171)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T171" s="90" t="inlineStr">
@@ -22654,7 +22654,7 @@
         <v/>
       </c>
       <c r="S172" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R172)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R172)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T172" s="90" t="inlineStr">
@@ -22777,7 +22777,7 @@
         <v/>
       </c>
       <c r="S173" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R173)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R173)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T173" s="90" t="inlineStr">
@@ -22901,7 +22901,7 @@
         <v/>
       </c>
       <c r="S174" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R174)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R174)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T174" s="90" t="inlineStr">
@@ -23025,7 +23025,7 @@
         <v/>
       </c>
       <c r="S175" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R175)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R175)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T175" s="90" t="inlineStr">
@@ -23149,7 +23149,7 @@
         <v/>
       </c>
       <c r="S176" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R176)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R176)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T176" s="90" t="inlineStr">
@@ -23273,7 +23273,7 @@
         <v/>
       </c>
       <c r="S177" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R177)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R177)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T177" s="90" t="inlineStr">
@@ -23397,7 +23397,7 @@
         <v/>
       </c>
       <c r="S178" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R178)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R178)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T178" s="90" t="inlineStr">
@@ -23522,7 +23522,7 @@
         <v/>
       </c>
       <c r="S179" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R179)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R179)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T179" s="90" t="inlineStr">
@@ -23645,7 +23645,7 @@
         <v/>
       </c>
       <c r="S180" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R180)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R180)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T180" s="90" t="inlineStr">
@@ -23769,7 +23769,7 @@
         <v/>
       </c>
       <c r="S181" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R181)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R181)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T181" s="90" t="inlineStr">
@@ -23892,7 +23892,7 @@
         <v/>
       </c>
       <c r="S182" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R182)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R182)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T182" s="90" t="inlineStr">
@@ -24015,7 +24015,7 @@
         <v/>
       </c>
       <c r="S183" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R183)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R183)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T183" s="90" t="inlineStr">
@@ -24139,7 +24139,7 @@
         <v/>
       </c>
       <c r="S184" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R184)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R184)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T184" s="90" t="inlineStr">
@@ -24264,7 +24264,7 @@
         <v/>
       </c>
       <c r="S185" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R185)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R185)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T185" s="90" t="inlineStr">
@@ -24388,7 +24388,7 @@
         <v/>
       </c>
       <c r="S186" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R186)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R186)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T186" s="90" t="inlineStr">
@@ -24512,7 +24512,7 @@
         <v/>
       </c>
       <c r="S187" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R187)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R187)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T187" s="90" t="inlineStr">
@@ -24636,7 +24636,7 @@
         <v/>
       </c>
       <c r="S188" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R188)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R188)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T188" s="90" t="inlineStr">
@@ -24760,7 +24760,7 @@
         <v/>
       </c>
       <c r="S189" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R189)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R189)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T189" s="90" t="inlineStr">
@@ -24884,7 +24884,7 @@
         <v/>
       </c>
       <c r="S190" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R190)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R190)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T190" s="90" t="inlineStr">
@@ -25008,7 +25008,7 @@
         <v/>
       </c>
       <c r="S191" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R191)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R191)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T191" s="90" t="inlineStr">
@@ -25131,7 +25131,7 @@
         <v/>
       </c>
       <c r="S192" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R192)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R192)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T192" s="90" t="inlineStr">
@@ -25255,7 +25255,7 @@
         <v/>
       </c>
       <c r="S193" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R193)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R193)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T193" s="90" t="inlineStr">
@@ -25378,7 +25378,7 @@
         <v/>
       </c>
       <c r="S194" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R194)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R194)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T194" s="90" t="inlineStr">
@@ -25501,7 +25501,7 @@
         <v/>
       </c>
       <c r="S195" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R195)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R195)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T195" s="90" t="inlineStr">
@@ -25625,7 +25625,7 @@
         <v/>
       </c>
       <c r="S196" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R196)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R196)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T196" s="90" t="inlineStr">
@@ -25748,7 +25748,7 @@
         <v/>
       </c>
       <c r="S197" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R197)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R197)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T197" s="90" t="inlineStr">
@@ -25871,7 +25871,7 @@
         <v/>
       </c>
       <c r="S198" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R198)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R198)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T198" s="90" t="inlineStr">
@@ -25994,7 +25994,7 @@
         <v/>
       </c>
       <c r="S199" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R199)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R199)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T199" s="90" t="inlineStr">
@@ -26117,7 +26117,7 @@
         <v/>
       </c>
       <c r="S200" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R200)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R200)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T200" s="90" t="inlineStr">
@@ -26240,7 +26240,7 @@
         <v/>
       </c>
       <c r="S201" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R201)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R201)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T201" s="90" t="inlineStr">
@@ -26363,7 +26363,7 @@
         <v/>
       </c>
       <c r="S202" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R202)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R202)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T202" s="90" t="inlineStr">
@@ -26486,7 +26486,7 @@
         <v/>
       </c>
       <c r="S203" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R203)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R203)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T203" s="90" t="inlineStr">
@@ -26609,7 +26609,7 @@
         <v/>
       </c>
       <c r="S204" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R204)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R204)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T204" s="90" t="inlineStr">
@@ -26733,7 +26733,7 @@
         <v/>
       </c>
       <c r="S205" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R205)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R205)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T205" s="90" t="inlineStr">
@@ -26857,7 +26857,7 @@
         <v/>
       </c>
       <c r="S206" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R206)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R206)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T206" s="90" t="inlineStr">
@@ -26980,7 +26980,7 @@
         <v/>
       </c>
       <c r="S207" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R207)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R207)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T207" s="90" t="inlineStr">
@@ -27103,7 +27103,7 @@
         <v/>
       </c>
       <c r="S208" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R208)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R208)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T208" s="90" t="inlineStr">
@@ -27226,7 +27226,7 @@
         <v/>
       </c>
       <c r="S209" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R209)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R209)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T209" s="90" t="inlineStr">
@@ -27349,7 +27349,7 @@
         <v/>
       </c>
       <c r="S210" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R210)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R210)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T210" s="90" t="inlineStr">
@@ -27472,7 +27472,7 @@
         <v/>
       </c>
       <c r="S211" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R211)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R211)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T211" s="90" t="inlineStr">
@@ -27595,7 +27595,7 @@
         <v/>
       </c>
       <c r="S212" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R212)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R212)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T212" s="90" t="inlineStr">
@@ -27718,7 +27718,7 @@
         <v/>
       </c>
       <c r="S213" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R213)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R213)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T213" s="90" t="inlineStr">
@@ -27841,7 +27841,7 @@
         <v/>
       </c>
       <c r="S214" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R214)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R214)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T214" s="90" t="inlineStr">
@@ -27964,7 +27964,7 @@
         <v/>
       </c>
       <c r="S215" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R215)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R215)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T215" s="90" t="inlineStr">
@@ -28087,7 +28087,7 @@
         <v/>
       </c>
       <c r="S216" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R216)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R216)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T216" s="90" t="inlineStr">
@@ -28210,7 +28210,7 @@
         <v/>
       </c>
       <c r="S217" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R217)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R217)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T217" s="90" t="inlineStr">
@@ -28334,7 +28334,7 @@
         <v/>
       </c>
       <c r="S218" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R218)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R218)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T218" s="90" t="inlineStr">
@@ -28457,7 +28457,7 @@
         <v/>
       </c>
       <c r="S219" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R219)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R219)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T219" s="90" t="inlineStr">
@@ -28580,7 +28580,7 @@
         <v/>
       </c>
       <c r="S220" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R220)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R220)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T220" s="90" t="inlineStr">
@@ -28703,7 +28703,7 @@
         <v/>
       </c>
       <c r="S221" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R221)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R221)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T221" s="90" t="inlineStr">
@@ -28826,7 +28826,7 @@
         <v/>
       </c>
       <c r="S222" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R222)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R222)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T222" s="90" t="inlineStr">
@@ -28949,7 +28949,7 @@
         <v/>
       </c>
       <c r="S223" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R223)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R223)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T223" s="90" t="inlineStr">
@@ -29072,7 +29072,7 @@
         <v/>
       </c>
       <c r="S224" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R224)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R224)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T224" s="90" t="inlineStr">
@@ -29195,7 +29195,7 @@
         <v/>
       </c>
       <c r="S225" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R225)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R225)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T225" s="90" t="inlineStr">
@@ -29318,7 +29318,7 @@
         <v/>
       </c>
       <c r="S226" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R226)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R226)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T226" s="90" t="inlineStr">
@@ -29441,7 +29441,7 @@
         <v/>
       </c>
       <c r="S227" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R227)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R227)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T227" s="90" t="inlineStr">
@@ -29564,7 +29564,7 @@
         <v/>
       </c>
       <c r="S228" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R228)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R228)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T228" s="90" t="inlineStr">
@@ -29687,7 +29687,7 @@
         <v/>
       </c>
       <c r="S229" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R229)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R229)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T229" s="90" t="inlineStr">
@@ -29810,7 +29810,7 @@
         <v/>
       </c>
       <c r="S230" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R230)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R230)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T230" s="90" t="inlineStr">
@@ -29934,7 +29934,7 @@
         <v/>
       </c>
       <c r="S231" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R231)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R231)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T231" s="93" t="inlineStr">
@@ -30057,7 +30057,7 @@
         <v/>
       </c>
       <c r="S232" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R232)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R232)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T232" s="93" t="inlineStr">
@@ -30177,7 +30177,7 @@
         <v/>
       </c>
       <c r="S233" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R233)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R233)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U233" s="93" t="inlineStr">
@@ -30293,7 +30293,7 @@
         <v/>
       </c>
       <c r="S234" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R234)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R234)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U234" s="93" t="inlineStr">
@@ -30409,7 +30409,7 @@
         <v/>
       </c>
       <c r="S235" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R235)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R235)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U235" s="93" t="inlineStr">
@@ -30525,7 +30525,7 @@
         <v/>
       </c>
       <c r="S236" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R236)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R236)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U236" s="93" t="inlineStr">
@@ -30641,7 +30641,7 @@
         <v/>
       </c>
       <c r="S237" s="94">
-        <f>IF(COUNTIF($R$6:$R$242,R237)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R237)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U237" s="93" t="inlineStr">
@@ -30758,7 +30758,7 @@
         <v/>
       </c>
       <c r="S238" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R238)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R238)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T238" s="90" t="inlineStr">
@@ -30881,7 +30881,7 @@
         <v/>
       </c>
       <c r="S239" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R239)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R239)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T239" s="90" t="inlineStr">
@@ -31000,7 +31000,7 @@
         <v/>
       </c>
       <c r="S240" s="63">
-        <f>IF(COUNTIF($R$6:$R$242,R240)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R240)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T240" s="90" t="inlineStr">
@@ -31119,7 +31119,7 @@
         <v/>
       </c>
       <c r="S241" s="90">
-        <f>IF(COUNTIF($R$6:$R$242,R241)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R241)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T241" s="90" t="inlineStr">
@@ -31240,7 +31240,7 @@
         <v/>
       </c>
       <c r="S242" s="90">
-        <f>IF(COUNTIF($R$6:$R$242,R242)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$246,R242)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T242" s="90" t="inlineStr">
@@ -31271,6 +31271,490 @@
       <c r="Y242" s="63" t="inlineStr">
         <is>
           <t>由 battle 区块房间种类源迁入（原 ENV-BATTLE-L-CORRIDOR-TYPE，原路径 tower_zones/battle/source/room_types/l_corridor/；业主 2026-09-24 裁决归属远征关卡01，battle 侧不留副本）。远征01 版图与白盒目录均无走廊白模，尺寸与门位按参考图推定。v001/v002 为 10m 宽走廊（外包络 45×35m / 28 块地砖 / 88、111 个组件包），v003 拓宽为 15m（45×40m / 42 块地砖 / 121 个组件包 / 4 个门位：西1 北2 南1）。随迁统一内部结构：component_packages_vNNN→component_packages、facility→facilities、散放渲染图入 renders/。共享件引用由 ENV-BATTLE-COMMON-* 更正为 shared 库现有 ENV-SHARED-GENERIC-*。未导 GLB、未接 Godot。</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="255" customHeight="1" s="60">
+      <c r="A243" s="90" t="inlineStr">
+        <is>
+          <t>ENV-EXPEDITION-L01-OFFICE-ROOM</t>
+        </is>
+      </c>
+      <c r="B243" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 办公室 开放办公 30×40m 房间种类源</t>
+        </is>
+      </c>
+      <c r="C243" s="63" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="D243" s="90" t="inlineStr">
+        <is>
+          <t>office_room</t>
+        </is>
+      </c>
+      <c r="E243" s="90" t="inlineStr">
+        <is>
+          <t>expedition_01_office_room</t>
+        </is>
+      </c>
+      <c r="F243" s="90" t="inlineStr">
+        <is>
+          <t>room_type</t>
+        </is>
+      </c>
+      <c r="G243" s="90" t="n"/>
+      <c r="H243" s="90" t="inlineStr">
+        <is>
+          <t>Top3D / Blender Z-up</t>
+        </is>
+      </c>
+      <c r="I243" s="90" t="inlineStr">
+        <is>
+          <t>scene_art / reference_derived</t>
+        </is>
+      </c>
+      <c r="J243" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 专用；room_03 与 room_09 两处实例共用同一房型源（同 office_60x70 模板）</t>
+        </is>
+      </c>
+      <c r="K243" s="90" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L243" s="90" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M243" s="90" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N243" s="90" t="inlineStr">
+        <is>
+          <t>30×40×11.9m（6×8 个 5m 槽 / 28 个墙位）；106 个独立组件包 / 193 输出网格 / 211708 面；无内墙；4 组工位；门洞 2.2×2.5m（净空底 0.30m、门楣 2.80m）；QA PASS（22 项断言）</t>
+        </is>
+      </c>
+      <c r="O243" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/office_room/v001/办公室房间种类_开放办公_30x40m_v001.blend</t>
+        </is>
+      </c>
+      <c r="P243" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/office_room/v001/build_office_room_v001.py；白盒 source/art/whitebox/tower_zones/expedition_01/v001/data/room_templates/office_60x70.json</t>
+        </is>
+      </c>
+      <c r="Q243" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01;办公室;开放办公;房间种类;30×40m;工位;文件柜;白板;图腾;绿植</t>
+        </is>
+      </c>
+      <c r="R243" s="90">
+        <f>LOWER(TRIM(C243)&amp;"|"&amp;TRIM(D243)&amp;"|"&amp;TRIM(E243)&amp;"|"&amp;TRIM(F243)&amp;"|"&amp;TRIM(H243)&amp;"|"&amp;TRIM(I243))</f>
+        <v/>
+      </c>
+      <c r="S243" s="90">
+        <f>IF(COUNTIF($R$6:$R$246,R243)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T243" s="90" t="inlineStr">
+        <is>
+          <t>4cf7138d0010405202d9cb9dd2aef0af9a676984ceeb90501b5a8d92304ed95f</t>
+        </is>
+      </c>
+      <c r="U243" s="63" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V243" s="90" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W243" s="63" t="inlineStr">
+        <is>
+          <t>用户设计（参考图 docs/v0.1/design/refs/expedition01/办公室01.jpg）</t>
+        </is>
+      </c>
+      <c r="X243" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y243" s="63" t="inlineStr">
+        <is>
+          <t>服务远征关卡01 的 room_03（COMBAT，中心 -45/50）与 room_09（EVENT，中心 15/-45）；两房实测同为 office_60x70（30×40m）模板 ⇒ 共用一份房型源。白盒尺寸/门洞/墙高锁定，只做场景美术。未导 GLB、未接 Godot。</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="255" customHeight="1" s="60">
+      <c r="A244" s="90" t="inlineStr">
+        <is>
+          <t>ENV-EXPEDITION-L01-BRIDGE-ROOM</t>
+        </is>
+      </c>
+      <c r="B244" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 通道桥 工字型 30×60m 房间种类源</t>
+        </is>
+      </c>
+      <c r="C244" s="63" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="D244" s="90" t="inlineStr">
+        <is>
+          <t>bridge_room</t>
+        </is>
+      </c>
+      <c r="E244" s="90" t="inlineStr">
+        <is>
+          <t>expedition_01_bridge_room</t>
+        </is>
+      </c>
+      <c r="F244" s="90" t="inlineStr">
+        <is>
+          <t>room_type</t>
+        </is>
+      </c>
+      <c r="G244" s="90" t="n"/>
+      <c r="H244" s="90" t="inlineStr">
+        <is>
+          <t>Top3D / Blender Z-up</t>
+        </is>
+      </c>
+      <c r="I244" s="90" t="inlineStr">
+        <is>
+          <t>scene_art / reference_derived</t>
+        </is>
+      </c>
+      <c r="J244" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 专用；room_05 通道桥房间（工字型）</t>
+        </is>
+      </c>
+      <c r="K244" s="90" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L244" s="90" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M244" s="90" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="N244" s="90" t="inlineStr">
+        <is>
+          <t>30×60×11.9m（工字型）；上层平台 30×60（Z∈[-0.32,0]）；中央跨桥 10×30m；下沉坑 30×30m、坑底 Z=-12.0；4 个下层服务标高；242 个独立组件包 / 314 输出网格 / 312370 面；门洞 2.2×2.5m；QA PASS（17 项断言）</t>
+        </is>
+      </c>
+      <c r="O244" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/bridge_room/v002/通道桥房间种类_工字型_30x60m_v002.blend</t>
+        </is>
+      </c>
+      <c r="P244" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/bridge_room/v002/build_bridge_room_v002.py；白盒 source/art/whitebox/tower_zones/expedition_01/v001/data/room_templates/bridge_60x50.json</t>
+        </is>
+      </c>
+      <c r="Q244" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01;通道桥;工字型;房间种类;30×60m;跨桥;下沉区;多层几何</t>
+        </is>
+      </c>
+      <c r="R244" s="90">
+        <f>LOWER(TRIM(C244)&amp;"|"&amp;TRIM(D244)&amp;"|"&amp;TRIM(E244)&amp;"|"&amp;TRIM(F244)&amp;"|"&amp;TRIM(H244)&amp;"|"&amp;TRIM(I244))</f>
+        <v/>
+      </c>
+      <c r="S244" s="90">
+        <f>IF(COUNTIF($R$6:$R$246,R244)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T244" s="90" t="inlineStr">
+        <is>
+          <t>7ba287e92a7a16fb7ee5234d027be6a969bdbccb4f12de5b741aaecfc7b2b59e</t>
+        </is>
+      </c>
+      <c r="U244" s="63" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V244" s="90" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="W244" s="63" t="inlineStr">
+        <is>
+          <t>用户设计（参考图见 room_type_manifest.json 的 reference_image）</t>
+        </is>
+      </c>
+      <c r="X244" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y244" s="63" t="inlineStr">
+        <is>
+          <t>服务远征关卡01 的 room_05（通道桥房间 30×60 · 工字型；转置姿态用 template_rotation_deg:90）。本批唯一需多层几何与碰撞的房型。v001 保留在同目录历史版本。未导 GLB、未接 Godot。</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="255" customHeight="1" s="60">
+      <c r="A245" s="90" t="inlineStr">
+        <is>
+          <t>ENV-EXPEDITION-L01-ROOM-STD-25X25</t>
+        </is>
+      </c>
+      <c r="B245" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 标准房间 四墙平房 25×25m 房间种类源</t>
+        </is>
+      </c>
+      <c r="C245" s="63" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="D245" s="90" t="inlineStr">
+        <is>
+          <t>std_25x25</t>
+        </is>
+      </c>
+      <c r="E245" s="90" t="inlineStr">
+        <is>
+          <t>expedition_01_std_room</t>
+        </is>
+      </c>
+      <c r="F245" s="90" t="inlineStr">
+        <is>
+          <t>room_type</t>
+        </is>
+      </c>
+      <c r="G245" s="90" t="n"/>
+      <c r="H245" s="90" t="inlineStr">
+        <is>
+          <t>Top3D / Blender Z-up</t>
+        </is>
+      </c>
+      <c r="I245" s="90" t="inlineStr">
+        <is>
+          <t>scene_art / composed_from_linked_components</t>
+        </is>
+      </c>
+      <c r="J245" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 专用；room_07 标准房间（25×25m）。本房型不自持几何：25 地砖 + 18 实墙 + 2 门墙 + 37 陈设共 82 个集合实例，全部 Library Link 自 office_room/v001 与 bridge_room/v002 两批已验收资产包</t>
+        </is>
+      </c>
+      <c r="K245" s="90" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L245" s="90" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M245" s="90" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N245" s="90" t="inlineStr">
+        <is>
+          <t>25×25×11.9m（5×5 个 5m 槽；四墙各 5 槽，墙槽心 ±10/±5/0）；82 个集合实例 / 引用 81 个已验收资产包 / 本文件自持网格 0；西·东墙 lane 0 对穿门洞 2.2×2.5m（净空底 0.30m、门楣 2.80m）；QA PASS（9 组断言）</t>
+        </is>
+      </c>
+      <c r="O245" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/std_25x25/v001/标准房间种类_四墙平房_25x25m_v001.blend</t>
+        </is>
+      </c>
+      <c r="P245" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/std_25x25/v001/build_std25_room_v001.py；摆位真源 同目录 std_25x25_v001.layout.json（由 _scratch/std25_layout/plan_std25_layout.py 算出）；白盒 source/art/whitebox/tower_zones/expedition_01/v001/data/room_templates/std_25x25.json</t>
+        </is>
+      </c>
+      <c r="Q245" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01;标准房间;四墙平房;房间种类;25×25m;组件拼装;LibraryLink;西东对穿;office_room;bridge_room</t>
+        </is>
+      </c>
+      <c r="R245" s="90">
+        <f>LOWER(TRIM(C245)&amp;"|"&amp;TRIM(D245)&amp;"|"&amp;TRIM(E245)&amp;"|"&amp;TRIM(F245)&amp;"|"&amp;TRIM(H245)&amp;"|"&amp;TRIM(I245))</f>
+        <v/>
+      </c>
+      <c r="S245" s="90">
+        <f>IF(COUNTIF($R$6:$R$246,R245)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T245" s="90" t="inlineStr">
+        <is>
+          <t>e5b69bef2804a6a46d44bef72b3b2e58f89bfe7440b4fa4a1551aa7ac7cf5974</t>
+        </is>
+      </c>
+      <c r="U245" s="63" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V245" s="90" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="W245" s="63" t="inlineStr">
+        <is>
+          <t>用户设计（组件拼装；组件来源 office_room/v001 与 bridge_room/v002 两批已验收房型源）</t>
+        </is>
+      </c>
+      <c r="X245" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y245" s="63" t="inlineStr">
+        <is>
+          <t>服务远征关卡01 的 room_07（标准房间，中心 −17.5/−87.5）。与 office/bridge 两行的语义差异：那两行是房型**自持几何**的组件源，本行是 skill 03 意义上的**实例布局源** ⇒ 自持几何 0、组件几何/材质/根原点一律不改、不缩放进位、不 Append 复制网格。与本房型摆位真源 std_25x25_v001.layout.json 配套的清单为同目录 component_inventory.json（记**被引用的**81 个外部资产包及本房用法）与 room_type_manifest.json。门位冻结为西/东墙 lane 0 对穿（依据设计页 §4.2.1 与参考图 08-标准房间.svg）。未导 GLB、未接 Godot。</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="255" customHeight="1" s="60">
+      <c r="A246" s="90" t="inlineStr">
+        <is>
+          <t>ENV-EXPEDITION-L01-ROOM-DB-70X50</t>
+        </is>
+      </c>
+      <c r="B246" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 数据库房间 数据机房 40×30m 房间种类源</t>
+        </is>
+      </c>
+      <c r="C246" s="63" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="D246" s="90" t="inlineStr">
+        <is>
+          <t>db_room</t>
+        </is>
+      </c>
+      <c r="E246" s="90" t="inlineStr">
+        <is>
+          <t>expedition_01_db_room</t>
+        </is>
+      </c>
+      <c r="F246" s="90" t="inlineStr">
+        <is>
+          <t>room_type</t>
+        </is>
+      </c>
+      <c r="G246" s="90" t="n"/>
+      <c r="H246" s="90" t="inlineStr">
+        <is>
+          <t>Top3D / Blender Z-up</t>
+        </is>
+      </c>
+      <c r="I246" s="90" t="inlineStr">
+        <is>
+          <t>scene_art / reference_derived_with_linked_shell</t>
+        </is>
+      </c>
+      <c r="J246" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 专用；room_02 / room_06 / room_10 三处实例共用同一房型源（同 db_70x50 模板）。本轮按参考图做 db_01 布局（主体 40×25 + 南侧中段外凸 10×5）；墙体与地砖 Library Link 复用 office_room/v001，其余 37 个组件包为数据库机房专属新制</t>
+        </is>
+      </c>
+      <c r="K246" s="90" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L246" s="90" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M246" s="90" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N246" s="90" t="inlineStr">
+        <is>
+          <t>40×30m 包围盒（8×6 个 5m 槽）；db_01 轮廓 = 主体 40×25 + 南侧中段外凸 10×5，占用 1050 m²（包围盒 1200 m²）；28 樘墙件 + 42 格地砖共 70 个集合实例，全部 Library Link 自 office_room/v001（本文件自持墙/砖网格 0）；37 个数据库机房专属组件包 / 49 输出网格 / 127164 面；门洞 2.2×2.5m（净空底 0.30m、门楣 2.80m）；16 个可开槽；QA PASS（26 项断言）</t>
+        </is>
+      </c>
+      <c r="O246" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/db_room/v001/数据库房间种类_数据机房_40x30m_v001.blend</t>
+        </is>
+      </c>
+      <c r="P246" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/db_room/v001/build_db_room_v001.py；白盒 source/art/whitebox/tower_zones/expedition_01/v001/data/room_templates/db_70x50.json；参考图 docs/v0.1/design/refs/expedition01/数据库房间01.jpg</t>
+        </is>
+      </c>
+      <c r="Q246" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01;数据库房间;数据机房;房间种类;40×30m;db_01;db_02;机柜;工作台;壁挂大屏;工具车;电缆盘;警示边带;LibraryLink;office_room</t>
+        </is>
+      </c>
+      <c r="R246" s="90">
+        <f>LOWER(TRIM(C246)&amp;"|"&amp;TRIM(D246)&amp;"|"&amp;TRIM(E246)&amp;"|"&amp;TRIM(F246)&amp;"|"&amp;TRIM(H246)&amp;"|"&amp;TRIM(I246))</f>
+        <v/>
+      </c>
+      <c r="S246" s="90">
+        <f>IF(COUNTIF($R$6:$R$246,R246)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T246" s="90" t="inlineStr">
+        <is>
+          <t>153eaa883b21b4489a3b5bb0b2d67a38419186ee0e7d1ff603bd3ad8f3c291a3</t>
+        </is>
+      </c>
+      <c r="U246" s="63" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V246" s="90" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="W246" s="63" t="inlineStr">
+        <is>
+          <t>用户设计（参考图 docs/v0.1/design/refs/expedition01/数据库房间01.jpg；墙件与地砖复用 office_room/v001 已验收组件）</t>
+        </is>
+      </c>
+      <c r="X246" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y246" s="63" t="inlineStr">
+        <is>
+          <t>服务远征关卡01 的 room_02 / room_06 / room_10（三处实例共用同一房型源）。本轮按参考图做 **db_01** 布局（主体 40×25 + 南侧中段外凸 10×5，面积 1050 m²）；同模板的另一内部布局 db_02（双缺角 15×10 / 15×5，面积 975 m²）按 room_type_manifest.json 显式标注为待另轮制作。与 office / bridge 两行的差别：墙件（28 樘）与地砖（42 格）**不重新制作**，改为 Library Link 引用 office_room/v001 的已验收组件包（本文件自持墙/砖网格 0、不 Append、不改组件几何/材质/根原点）；其余 37 个组件包（地面标识 / 格栅 / 设备坑抬升平台 / 西侧机柜列 7 台 / 中部机柜组 / 东墙 L 形工作台 / 西墙检修台 / 壁挂大屏组 / 红黄工具车 / 中央作业台 / 货箱堆场 / 重型货架 / 零件柜 / 电缆盘与线圈 / 花箱绿植 / 设备机架 / 墙面灯柱 / 顶部桥架管道风管灯具等）为数据库机房专属新制。未导 GLB、未接 Godot。</t>
         </is>
       </c>
     </row>
@@ -31294,17 +31778,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C242" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C6:C246" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K6:K242" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K6:K246" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L6:L242" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="L6:L246" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -44766,7 +45247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.80859375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="59" min="1" max="1"/>
@@ -44793,6 +45274,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="60">
       <c r="A5" s="66" t="inlineStr">
         <is>
@@ -45343,6 +45825,117 @@
         </is>
       </c>
       <c r="G19" s="119" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" s="60">
+      <c r="A20" s="118" t="inlineStr">
+        <is>
+          <t>v0.1.14</t>
+        </is>
+      </c>
+      <c r="B20" s="118" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C20" s="119" t="inlineStr">
+        <is>
+          <t>新增条目</t>
+        </is>
+      </c>
+      <c r="D20" s="119" t="inlineStr">
+        <is>
+          <t>关卡场景 / 远征关卡01</t>
+        </is>
+      </c>
+      <c r="E20" s="119" t="inlineStr">
+        <is>
+          <t>新增 ENV-EXPEDITION-L01-OFFICE-ROOM（远征关卡01 办公室 开放办公 30×40m 房间种类源，v001，服务 room_03 / room_09）与 ENV-EXPEDITION-L01-BRIDGE-ROOM（远征关卡01 通道桥 工字型 30×60m 房间种类源，v002，服务 room_05）。两者均由房型美术源制作完成（QA 分别 22 / 17 项断言全通过），白盒尺寸与门洞契约锁定，只做场景美术。</t>
+        </is>
+      </c>
+      <c r="F20" s="119" t="inlineStr">
+        <is>
+          <t>新增条目，不改动既有 AssetID / 路径 / 哈希；两行只落《资产主表》，《3D-场景通用》分页与专属摘要按「摘要锁死表须单独开事务」的规定留待导出 GLB / 接入 Godot 时一并处理。《总览》资产主表区间由 $…$242 扩到 $…$244，S 列查重结果逐行重算，DV 扩到第 244 行。</t>
+        </is>
+      </c>
+      <c r="G20" s="119" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" s="60">
+      <c r="A21" s="118" t="inlineStr">
+        <is>
+          <t>v0.1.15</t>
+        </is>
+      </c>
+      <c r="B21" s="118" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C21" s="119" t="inlineStr">
+        <is>
+          <t>新增条目</t>
+        </is>
+      </c>
+      <c r="D21" s="119" t="inlineStr">
+        <is>
+          <t>关卡场景 / 远征关卡01</t>
+        </is>
+      </c>
+      <c r="E21" s="119" t="inlineStr">
+        <is>
+          <t>新增 ENV-EXPEDITION-L01-ROOM-STD-25X25（远征关卡01 标准房间 四墙平房 25×25m 房间种类源，v001，服务 room_07）。本行是「实例布局源」而非「自持几何的组件源」：25 地砖 + 18 实墙 + 2 门墙 + 37 陈设共 82 个集合实例，全部 Library Link 自 office_room/v001（54 包）与 bridge_room/v002（27 包）两批已验收资产包，本文件自持网格 0、不 Append、不改组件几何/材质/根原点、无缩放。门位冻结为西/东墙 lane 0 对穿门洞（依据设计页 §4.2.1 与参考图 08-标准房间.svg）。结构契约校验 9 组断言全通过，渲染 6 机位验收。</t>
+        </is>
+      </c>
+      <c r="F21" s="119" t="inlineStr">
+        <is>
+          <t>新增条目，不改动既有 AssetID / 路径 / 哈希；本行只落《资产主表》，《3D-场景通用》分页（已声明「一行 = 一个实际存在的 Godot PackedScene」）按摘要锁死表规矩留待导出 GLB / 接入 Godot 时一并处理。《总览》资产主表区间由 $…$244 扩到 $…$245，S 列查重结果逐行重算，DV 扩到第 245 行；无损基线同步补录。</t>
+        </is>
+      </c>
+      <c r="G21" s="119" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" s="60">
+      <c r="A22" s="118" t="inlineStr">
+        <is>
+          <t>v0.1.16</t>
+        </is>
+      </c>
+      <c r="B22" s="118" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C22" s="119" t="inlineStr">
+        <is>
+          <t>新增条目</t>
+        </is>
+      </c>
+      <c r="D22" s="119" t="inlineStr">
+        <is>
+          <t>关卡场景 / 远征关卡01</t>
+        </is>
+      </c>
+      <c r="E22" s="119" t="inlineStr">
+        <is>
+          <t>新增 ENV-EXPEDITION-L01-ROOM-DB-70X50（远征关卡01 数据库房间 数据机房 40×30m 房间种类源，v001，服务 room_02 / room_06 / room_10）。本轮按参考图做 db_01 布局（主体 40×25 + 南侧中段外凸 10×5，占用 1050 m²）；**墙件 28 樘与地砖 42 格不自制**，改为 Library Link 引用 office_room/v001 的已验收组件包（本文件自持墙/砖网格 0）；其余 37 个组件包为数据库机房专属新制。结构契约校验 26 项断言全通过，渲染 6 机位验收。</t>
+        </is>
+      </c>
+      <c r="F22" s="119" t="inlineStr">
+        <is>
+          <t>新增条目，不改动既有 AssetID / 路径 / 哈希；本行只落《资产主表》，《3D-场景通用》分页（已声明「一行 = 一个实际存在的 Godot PackedScene」）按摘要锁死表规矩留待导出 GLB / 接入 Godot 时一并处理。《总览》资产主表区间由 $…$245 扩到 $…$246，S 列查重结果逐行重算，DV 扩到第 246 行；无损基线同步补录。</t>
+        </is>
+      </c>
+      <c r="G22" s="119" t="inlineStr">
         <is>
           <t>摩斯拉</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -1476,22 +1476,22 @@
     </row>
     <row r="6" ht="42" customHeight="1" s="60">
       <c r="A6" s="65">
-        <f>COUNTA('资产主表'!$A$6:$A$246)</f>
+        <f>COUNTA('资产主表'!$A$6:$A$247)</f>
         <v/>
       </c>
       <c r="B6" s="63" t="n"/>
       <c r="C6" s="65">
-        <f>COUNTIF('资产主表'!$K$6:$K$246,"已完成")+COUNTIF('资产主表'!$K$6:$K$246,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$246,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$246,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$246,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$246,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$246,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$247,"已完成")+COUNTIF('资产主表'!$K$6:$K$247,"原型已接入")+COUNTIF('资产主表'!$K$6:$K$247,"正式美术已接入")+COUNTIF('资产主表'!$K$6:$K$247,"已优化并正式接入")+COUNTIF('资产主表'!$K$6:$K$247,"Blender源已完成")+COUNTIF('资产主表'!$K$6:$K$247,"已导入；优化完成")+COUNTIF('资产主表'!$K$6:$K$247,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="63" t="n"/>
       <c r="E6" s="65">
-        <f>COUNTIF('资产主表'!$K$6:$K$246,"待制作")+COUNTIF('资产主表'!$K$6:$K$246,"程序占位")</f>
+        <f>COUNTIF('资产主表'!$K$6:$K$247,"待制作")+COUNTIF('资产主表'!$K$6:$K$247,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="63" t="n"/>
       <c r="G6" s="65">
-        <f>COUNTIF('资产主表'!$S$6:$S$246,"重复")</f>
+        <f>COUNTIF('资产主表'!$S$6:$S$247,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="63" t="n"/>
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="B10" s="70">
-        <f>COUNTIF('资产主表'!$C$6:$C$246,A10)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$247,A10)</f>
         <v/>
       </c>
       <c r="C10" s="70">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$246=A10)*(('资产主表'!$K$6:$K$246="已完成")+('资产主表'!$K$6:$K$246="原型已接入")+('资产主表'!$K$6:$K$246="正式美术已接入")+('资产主表'!$K$6:$K$246="已优化并正式接入")+('资产主表'!$K$6:$K$246="Blender源已完成")+('资产主表'!$K$6:$K$246="已导入；优化完成")+('资产主表'!$K$6:$K$246="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$247=A10)*(('资产主表'!$K$6:$K$247="已完成")+('资产主表'!$K$6:$K$247="原型已接入")+('资产主表'!$K$6:$K$247="正式美术已接入")+('资产主表'!$K$6:$K$247="已优化并正式接入")+('资产主表'!$K$6:$K$247="Blender源已完成")+('资产主表'!$K$6:$K$247="已导入；优化完成")+('资产主表'!$K$6:$K$247="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="70" t="n"/>
@@ -1582,11 +1582,11 @@
         </is>
       </c>
       <c r="B11" s="70">
-        <f>COUNTIF('资产主表'!$C$6:$C$246,A11)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$247,A11)</f>
         <v/>
       </c>
       <c r="C11" s="70">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$246=A11)*(('资产主表'!$K$6:$K$246="已完成")+('资产主表'!$K$6:$K$246="原型已接入")+('资产主表'!$K$6:$K$246="正式美术已接入")+('资产主表'!$K$6:$K$246="已优化并正式接入")+('资产主表'!$K$6:$K$246="Blender源已完成")+('资产主表'!$K$6:$K$246="已导入；优化完成")+('资产主表'!$K$6:$K$246="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$247=A11)*(('资产主表'!$K$6:$K$247="已完成")+('资产主表'!$K$6:$K$247="原型已接入")+('资产主表'!$K$6:$K$247="正式美术已接入")+('资产主表'!$K$6:$K$247="已优化并正式接入")+('资产主表'!$K$6:$K$247="Blender源已完成")+('资产主表'!$K$6:$K$247="已导入；优化完成")+('资产主表'!$K$6:$K$247="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="70" t="n"/>
@@ -1604,11 +1604,11 @@
         </is>
       </c>
       <c r="B12" s="70">
-        <f>COUNTIF('资产主表'!$C$6:$C$246,A12)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$247,A12)</f>
         <v/>
       </c>
       <c r="C12" s="70">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$246=A12)*(('资产主表'!$K$6:$K$246="已完成")+('资产主表'!$K$6:$K$246="原型已接入")+('资产主表'!$K$6:$K$246="正式美术已接入")+('资产主表'!$K$6:$K$246="已优化并正式接入")+('资产主表'!$K$6:$K$246="Blender源已完成")+('资产主表'!$K$6:$K$246="已导入；优化完成")+('资产主表'!$K$6:$K$246="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$247=A12)*(('资产主表'!$K$6:$K$247="已完成")+('资产主表'!$K$6:$K$247="原型已接入")+('资产主表'!$K$6:$K$247="正式美术已接入")+('资产主表'!$K$6:$K$247="已优化并正式接入")+('资产主表'!$K$6:$K$247="Blender源已完成")+('资产主表'!$K$6:$K$247="已导入；优化完成")+('资产主表'!$K$6:$K$247="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D12" s="70" t="n"/>
@@ -1626,11 +1626,11 @@
         </is>
       </c>
       <c r="B13" s="66">
-        <f>COUNTIF('资产主表'!$C$6:$C$246,A13)</f>
+        <f>COUNTIF('资产主表'!$C$6:$C$247,A13)</f>
         <v/>
       </c>
       <c r="C13" s="66">
-        <f>SUMPRODUCT(('资产主表'!$C$6:$C$246=A13)*(('资产主表'!$K$6:$K$246="已完成")+('资产主表'!$K$6:$K$246="原型已接入")+('资产主表'!$K$6:$K$246="正式美术已接入")+('资产主表'!$K$6:$K$246="已优化并正式接入")+('资产主表'!$K$6:$K$246="Blender源已完成")+('资产主表'!$K$6:$K$246="已导入；优化完成")+('资产主表'!$K$6:$K$246="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT(('资产主表'!$C$6:$C$247=A13)*(('资产主表'!$K$6:$K$247="已完成")+('资产主表'!$K$6:$K$247="原型已接入")+('资产主表'!$K$6:$K$247="正式美术已接入")+('资产主表'!$K$6:$K$247="已优化并正式接入")+('资产主表'!$K$6:$K$247="Blender源已完成")+('资产主表'!$K$6:$K$247="已导入；优化完成")+('资产主表'!$K$6:$K$247="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D13" s="66" t="n"/>
@@ -2194,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y246"/>
+  <dimension ref="A1:Y247"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.80859375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="25" customWidth="1" style="59" min="1" max="1"/>
@@ -2470,7 +2470,7 @@
         <v/>
       </c>
       <c r="S6" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="71" t="n"/>
@@ -2577,7 +2577,7 @@
         <v/>
       </c>
       <c r="S7" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="71" t="n"/>
@@ -2684,7 +2684,7 @@
         <v/>
       </c>
       <c r="S8" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="71" t="n"/>
@@ -2791,7 +2791,7 @@
         <v/>
       </c>
       <c r="S9" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="71" t="n"/>
@@ -2898,7 +2898,7 @@
         <v/>
       </c>
       <c r="S10" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="71" t="n"/>
@@ -3005,7 +3005,7 @@
         <v/>
       </c>
       <c r="S11" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="71" t="n"/>
@@ -3112,7 +3112,7 @@
         <v/>
       </c>
       <c r="S12" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="71" t="n"/>
@@ -3219,7 +3219,7 @@
         <v/>
       </c>
       <c r="S13" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="71" t="n"/>
@@ -3326,7 +3326,7 @@
         <v/>
       </c>
       <c r="S14" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="71" t="n"/>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="S15" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="71" t="n"/>
@@ -3540,7 +3540,7 @@
         <v/>
       </c>
       <c r="S16" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="71" t="n"/>
@@ -3647,7 +3647,7 @@
         <v/>
       </c>
       <c r="S17" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="71" t="n"/>
@@ -3754,7 +3754,7 @@
         <v/>
       </c>
       <c r="S18" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="71" t="n"/>
@@ -3861,7 +3861,7 @@
         <v/>
       </c>
       <c r="S19" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="71" t="n"/>
@@ -3968,7 +3968,7 @@
         <v/>
       </c>
       <c r="S20" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="71" t="n"/>
@@ -4075,7 +4075,7 @@
         <v/>
       </c>
       <c r="S21" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="71" t="n"/>
@@ -4182,7 +4182,7 @@
         <v/>
       </c>
       <c r="S22" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="71" t="n"/>
@@ -4289,7 +4289,7 @@
         <v/>
       </c>
       <c r="S23" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="71" t="n"/>
@@ -4396,7 +4396,7 @@
         <v/>
       </c>
       <c r="S24" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="71" t="n"/>
@@ -4503,7 +4503,7 @@
         <v/>
       </c>
       <c r="S25" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="71" t="n"/>
@@ -4610,7 +4610,7 @@
         <v/>
       </c>
       <c r="S26" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="71" t="n"/>
@@ -4717,7 +4717,7 @@
         <v/>
       </c>
       <c r="S27" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="71" t="n"/>
@@ -4824,7 +4824,7 @@
         <v/>
       </c>
       <c r="S28" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="71" t="n"/>
@@ -4931,7 +4931,7 @@
         <v/>
       </c>
       <c r="S29" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="71" t="n"/>
@@ -5038,7 +5038,7 @@
         <v/>
       </c>
       <c r="S30" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="71" t="n"/>
@@ -5145,7 +5145,7 @@
         <v/>
       </c>
       <c r="S31" s="71">
-        <f>IF(COUNTIF($R$6:$R$246,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="71" t="n"/>
@@ -5264,7 +5264,7 @@
         <v/>
       </c>
       <c r="S32" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="87" t="inlineStr">
@@ -5387,7 +5387,7 @@
         <v/>
       </c>
       <c r="S33" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="90" t="inlineStr">
@@ -5510,7 +5510,7 @@
         <v/>
       </c>
       <c r="S34" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="90" t="inlineStr">
@@ -5633,7 +5633,7 @@
         <v/>
       </c>
       <c r="S35" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="90" t="inlineStr">
@@ -5756,7 +5756,7 @@
         <v/>
       </c>
       <c r="S36" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="87" t="inlineStr">
@@ -5880,7 +5880,7 @@
         <v/>
       </c>
       <c r="S37" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="90" t="inlineStr">
@@ -6003,7 +6003,7 @@
         <v/>
       </c>
       <c r="S38" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="90" t="inlineStr">
@@ -6122,7 +6122,7 @@
         <v/>
       </c>
       <c r="S39" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="87" t="inlineStr">
@@ -6245,7 +6245,7 @@
         <v/>
       </c>
       <c r="S40" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="90" t="inlineStr">
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="S41" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="90" t="inlineStr">
@@ -6491,7 +6491,7 @@
         <v/>
       </c>
       <c r="S42" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="90" t="inlineStr">
@@ -6614,7 +6614,7 @@
         <v/>
       </c>
       <c r="S43" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="90" t="inlineStr">
@@ -6737,7 +6737,7 @@
         <v/>
       </c>
       <c r="S44" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="87" t="inlineStr">
@@ -6861,7 +6861,7 @@
         <v/>
       </c>
       <c r="S45" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="90" t="inlineStr">
@@ -6984,7 +6984,7 @@
         <v/>
       </c>
       <c r="S46" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="90" t="inlineStr">
@@ -7107,7 +7107,7 @@
         <v/>
       </c>
       <c r="S47" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="90" t="inlineStr">
@@ -7230,7 +7230,7 @@
         <v/>
       </c>
       <c r="S48" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R48)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R48)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T48" s="90" t="inlineStr">
@@ -7350,7 +7350,7 @@
         <v/>
       </c>
       <c r="S49" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R49)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R49)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T49" s="90" t="inlineStr">
@@ -7473,7 +7473,7 @@
         <v/>
       </c>
       <c r="S50" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R50)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R50)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T50" s="90" t="inlineStr">
@@ -7597,7 +7597,7 @@
         <v/>
       </c>
       <c r="S51" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R51)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R51)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T51" s="90" t="inlineStr">
@@ -7720,7 +7720,7 @@
         <v/>
       </c>
       <c r="S52" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R52)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R52)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T52" s="87" t="inlineStr">
@@ -7844,7 +7844,7 @@
         <v/>
       </c>
       <c r="S53" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R53)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R53)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T53" s="87" t="inlineStr">
@@ -7967,7 +7967,7 @@
         <v/>
       </c>
       <c r="S54" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R54)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R54)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T54" s="87" t="inlineStr">
@@ -8096,7 +8096,7 @@
         <v/>
       </c>
       <c r="S55" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R55)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R55)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T55" s="87" t="inlineStr">
@@ -8223,7 +8223,7 @@
         <v/>
       </c>
       <c r="S56" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R56)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R56)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T56" s="87" t="inlineStr">
@@ -8346,7 +8346,7 @@
         <v/>
       </c>
       <c r="S57" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R57)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R57)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T57" s="87" t="inlineStr">
@@ -8471,7 +8471,7 @@
         <v/>
       </c>
       <c r="S58" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R58)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R58)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T58" s="87" t="inlineStr">
@@ -8594,7 +8594,7 @@
         <v/>
       </c>
       <c r="S59" s="88">
-        <f>IF(COUNTIF($R$6:$R$246,R59)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R59)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T59" s="87" t="inlineStr">
@@ -8713,7 +8713,7 @@
         <v/>
       </c>
       <c r="S60" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R60)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R60)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T60" s="90" t="inlineStr">
@@ -8833,7 +8833,7 @@
         <v/>
       </c>
       <c r="S61" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R61)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R61)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T61" s="90" t="inlineStr">
@@ -8953,7 +8953,7 @@
         <v/>
       </c>
       <c r="S62" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R62)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R62)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T62" s="90" t="inlineStr">
@@ -9073,7 +9073,7 @@
         <v/>
       </c>
       <c r="S63" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R63)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R63)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T63" s="90" t="n"/>
@@ -9193,7 +9193,7 @@
         <v/>
       </c>
       <c r="S64" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R64)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R64)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T64" s="90" t="inlineStr">
@@ -9318,7 +9318,7 @@
         <v/>
       </c>
       <c r="S65" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R65)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R65)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T65" s="90" t="inlineStr">
@@ -9443,7 +9443,7 @@
         <v/>
       </c>
       <c r="S66" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R66)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R66)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T66" s="90" t="inlineStr">
@@ -9568,7 +9568,7 @@
         <v/>
       </c>
       <c r="S67" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R67)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R67)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T67" s="90" t="inlineStr">
@@ -9693,7 +9693,7 @@
         <v/>
       </c>
       <c r="S68" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R68)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R68)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T68" s="90" t="inlineStr">
@@ -9824,7 +9824,7 @@
         <v/>
       </c>
       <c r="S69" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R69)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R69)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T69" s="90" t="inlineStr">
@@ -9950,7 +9950,7 @@
         <v/>
       </c>
       <c r="S70" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R70)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R70)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T70" s="90" t="inlineStr">
@@ -10074,7 +10074,7 @@
         <v/>
       </c>
       <c r="S71" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R71)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R71)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T71" s="90" t="inlineStr">
@@ -10198,7 +10198,7 @@
         <v/>
       </c>
       <c r="S72" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R72)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R72)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T72" s="90" t="inlineStr">
@@ -10322,7 +10322,7 @@
         <v/>
       </c>
       <c r="S73" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R73)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R73)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T73" s="90" t="inlineStr">
@@ -10446,7 +10446,7 @@
         <v/>
       </c>
       <c r="S74" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R74)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R74)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T74" s="90" t="inlineStr">
@@ -10570,7 +10570,7 @@
         <v/>
       </c>
       <c r="S75" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R75)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R75)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T75" s="90" t="inlineStr">
@@ -10694,7 +10694,7 @@
         <v/>
       </c>
       <c r="S76" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R76)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R76)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T76" s="90" t="inlineStr">
@@ -10818,7 +10818,7 @@
         <v/>
       </c>
       <c r="S77" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R77)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R77)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T77" s="90" t="inlineStr">
@@ -10942,7 +10942,7 @@
         <v/>
       </c>
       <c r="S78" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R78)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R78)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T78" s="90" t="inlineStr">
@@ -11066,7 +11066,7 @@
         <v/>
       </c>
       <c r="S79" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R79)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R79)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T79" s="90" t="inlineStr">
@@ -11190,7 +11190,7 @@
         <v/>
       </c>
       <c r="S80" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R80)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R80)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T80" s="90" t="inlineStr">
@@ -11314,7 +11314,7 @@
         <v/>
       </c>
       <c r="S81" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R81)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R81)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T81" s="90" t="inlineStr">
@@ -11438,7 +11438,7 @@
         <v/>
       </c>
       <c r="S82" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R82)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R82)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T82" s="90" t="inlineStr">
@@ -11562,7 +11562,7 @@
         <v/>
       </c>
       <c r="S83" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R83)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R83)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T83" s="90" t="inlineStr">
@@ -11686,7 +11686,7 @@
         <v/>
       </c>
       <c r="S84" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R84)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R84)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T84" s="90" t="inlineStr">
@@ -11810,7 +11810,7 @@
         <v/>
       </c>
       <c r="S85" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R85)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R85)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T85" s="90" t="inlineStr">
@@ -11934,7 +11934,7 @@
         <v/>
       </c>
       <c r="S86" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R86)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R86)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T86" s="90" t="inlineStr">
@@ -12058,7 +12058,7 @@
         <v/>
       </c>
       <c r="S87" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R87)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R87)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T87" s="90" t="inlineStr">
@@ -12182,7 +12182,7 @@
         <v/>
       </c>
       <c r="S88" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R88)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R88)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T88" s="90" t="inlineStr">
@@ -12306,7 +12306,7 @@
         <v/>
       </c>
       <c r="S89" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R89)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R89)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T89" s="90" t="inlineStr">
@@ -12430,7 +12430,7 @@
         <v/>
       </c>
       <c r="S90" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R90)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R90)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T90" s="90" t="inlineStr">
@@ -12554,7 +12554,7 @@
         <v/>
       </c>
       <c r="S91" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R91)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R91)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T91" s="90" t="inlineStr">
@@ -12678,7 +12678,7 @@
         <v/>
       </c>
       <c r="S92" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R92)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R92)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T92" s="90" t="inlineStr">
@@ -12802,7 +12802,7 @@
         <v/>
       </c>
       <c r="S93" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R93)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R93)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T93" s="90" t="inlineStr">
@@ -12926,7 +12926,7 @@
         <v/>
       </c>
       <c r="S94" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R94)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R94)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T94" s="90" t="inlineStr">
@@ -13050,7 +13050,7 @@
         <v/>
       </c>
       <c r="S95" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R95)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R95)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T95" s="90" t="inlineStr">
@@ -13174,7 +13174,7 @@
         <v/>
       </c>
       <c r="S96" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R96)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R96)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T96" s="90" t="inlineStr">
@@ -13298,7 +13298,7 @@
         <v/>
       </c>
       <c r="S97" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R97)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R97)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T97" s="90" t="inlineStr">
@@ -13422,7 +13422,7 @@
         <v/>
       </c>
       <c r="S98" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R98)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R98)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T98" s="90" t="inlineStr">
@@ -13546,7 +13546,7 @@
         <v/>
       </c>
       <c r="S99" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R99)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R99)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T99" s="90" t="inlineStr">
@@ -13670,7 +13670,7 @@
         <v/>
       </c>
       <c r="S100" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R100)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R100)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T100" s="90" t="inlineStr">
@@ -13794,7 +13794,7 @@
         <v/>
       </c>
       <c r="S101" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R101)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R101)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T101" s="90" t="inlineStr">
@@ -13918,7 +13918,7 @@
         <v/>
       </c>
       <c r="S102" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R102)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R102)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T102" s="90" t="inlineStr">
@@ -14041,7 +14041,7 @@
         <v/>
       </c>
       <c r="S103" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R103)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R103)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T103" s="90" t="inlineStr">
@@ -14166,7 +14166,7 @@
         <v/>
       </c>
       <c r="S104" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R104)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R104)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T104" s="90" t="inlineStr">
@@ -14291,7 +14291,7 @@
         <v/>
       </c>
       <c r="S105" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R105)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R105)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T105" s="90" t="inlineStr">
@@ -14416,7 +14416,7 @@
         <v/>
       </c>
       <c r="S106" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R106)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R106)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T106" s="90" t="inlineStr">
@@ -14541,7 +14541,7 @@
         <v/>
       </c>
       <c r="S107" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R107)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R107)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T107" s="90" t="inlineStr">
@@ -14666,7 +14666,7 @@
         <v/>
       </c>
       <c r="S108" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R108)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R108)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T108" s="93" t="inlineStr">
@@ -14792,7 +14792,7 @@
         <v/>
       </c>
       <c r="S109" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R109)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R109)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T109" s="90" t="inlineStr">
@@ -14918,7 +14918,7 @@
         <v/>
       </c>
       <c r="S110" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R110)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R110)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T110" s="90" t="inlineStr">
@@ -15044,7 +15044,7 @@
         <v/>
       </c>
       <c r="S111" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R111)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R111)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T111" s="90" t="inlineStr">
@@ -15170,7 +15170,7 @@
         <v/>
       </c>
       <c r="S112" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R112)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R112)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T112" s="90" t="inlineStr">
@@ -15293,7 +15293,7 @@
         <v/>
       </c>
       <c r="S113" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R113)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R113)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T113" s="90" t="inlineStr">
@@ -15413,7 +15413,7 @@
         <v/>
       </c>
       <c r="S114" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R114)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R114)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T114" s="93" t="inlineStr">
@@ -15532,7 +15532,7 @@
         <v/>
       </c>
       <c r="S115" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R115)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R115)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T115" s="93" t="inlineStr">
@@ -15650,7 +15650,7 @@
         <v/>
       </c>
       <c r="S116" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R116)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R116)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T116" s="93" t="inlineStr">
@@ -15773,7 +15773,7 @@
         <v/>
       </c>
       <c r="S117" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R117)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R117)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T117" s="90" t="inlineStr">
@@ -15899,7 +15899,7 @@
         <v/>
       </c>
       <c r="S118" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R118)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R118)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T118" s="90" t="inlineStr">
@@ -16022,7 +16022,7 @@
         <v/>
       </c>
       <c r="S119" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R119)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R119)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T119" s="90" t="inlineStr">
@@ -16147,7 +16147,7 @@
         <v/>
       </c>
       <c r="S120" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R120)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R120)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T120" s="90" t="inlineStr">
@@ -16270,7 +16270,7 @@
         <v/>
       </c>
       <c r="S121" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R121)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R121)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T121" s="90" t="inlineStr">
@@ -16395,7 +16395,7 @@
         <v/>
       </c>
       <c r="S122" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R122)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R122)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T122" s="90" t="inlineStr">
@@ -16518,7 +16518,7 @@
         <v/>
       </c>
       <c r="S123" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R123)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R123)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T123" s="90" t="inlineStr">
@@ -16641,7 +16641,7 @@
         <v/>
       </c>
       <c r="S124" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R124)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R124)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T124" s="90" t="inlineStr">
@@ -16764,7 +16764,7 @@
         <v/>
       </c>
       <c r="S125" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R125)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R125)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T125" s="90" t="inlineStr">
@@ -16887,7 +16887,7 @@
         <v/>
       </c>
       <c r="S126" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R126)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R126)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T126" s="90" t="inlineStr">
@@ -17010,7 +17010,7 @@
         <v/>
       </c>
       <c r="S127" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R127)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R127)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T127" s="90" t="inlineStr">
@@ -17133,7 +17133,7 @@
         <v/>
       </c>
       <c r="S128" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R128)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R128)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T128" s="90" t="inlineStr">
@@ -17256,7 +17256,7 @@
         <v/>
       </c>
       <c r="S129" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R129)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R129)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T129" s="90" t="inlineStr">
@@ -17379,7 +17379,7 @@
         <v/>
       </c>
       <c r="S130" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R130)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R130)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T130" s="90" t="inlineStr">
@@ -17502,7 +17502,7 @@
         <v/>
       </c>
       <c r="S131" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R131)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R131)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T131" s="90" t="inlineStr">
@@ -17625,7 +17625,7 @@
         <v/>
       </c>
       <c r="S132" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R132)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R132)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T132" s="90" t="inlineStr">
@@ -17749,7 +17749,7 @@
         <v/>
       </c>
       <c r="S133" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R133)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R133)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T133" s="90" t="inlineStr">
@@ -17872,7 +17872,7 @@
         <v/>
       </c>
       <c r="S134" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R134)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R134)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T134" s="90" t="inlineStr">
@@ -17995,7 +17995,7 @@
         <v/>
       </c>
       <c r="S135" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R135)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R135)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T135" s="90" t="inlineStr">
@@ -18121,7 +18121,7 @@
         <v/>
       </c>
       <c r="S136" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R136)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R136)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T136" s="90" t="inlineStr">
@@ -18247,7 +18247,7 @@
         <v/>
       </c>
       <c r="S137" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R137)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R137)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T137" s="90" t="inlineStr">
@@ -18373,7 +18373,7 @@
         <v/>
       </c>
       <c r="S138" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R138)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R138)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T138" s="90" t="inlineStr">
@@ -18499,7 +18499,7 @@
         <v/>
       </c>
       <c r="S139" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R139)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R139)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T139" s="90" t="inlineStr">
@@ -18625,7 +18625,7 @@
         <v/>
       </c>
       <c r="S140" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R140)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R140)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T140" s="90" t="inlineStr">
@@ -18751,7 +18751,7 @@
         <v/>
       </c>
       <c r="S141" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R141)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R141)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T141" s="90" t="inlineStr">
@@ -18877,7 +18877,7 @@
         <v/>
       </c>
       <c r="S142" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R142)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R142)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T142" s="90" t="inlineStr">
@@ -19003,7 +19003,7 @@
         <v/>
       </c>
       <c r="S143" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R143)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R143)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T143" s="90" t="inlineStr">
@@ -19129,7 +19129,7 @@
         <v/>
       </c>
       <c r="S144" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R144)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R144)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T144" s="90" t="inlineStr">
@@ -19255,7 +19255,7 @@
         <v/>
       </c>
       <c r="S145" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R145)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R145)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T145" s="90" t="inlineStr">
@@ -19381,7 +19381,7 @@
         <v/>
       </c>
       <c r="S146" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R146)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R146)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T146" s="90" t="inlineStr">
@@ -19507,7 +19507,7 @@
         <v/>
       </c>
       <c r="S147" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R147)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R147)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T147" s="90" t="inlineStr">
@@ -19633,7 +19633,7 @@
         <v/>
       </c>
       <c r="S148" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R148)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R148)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T148" s="90" t="inlineStr">
@@ -19759,7 +19759,7 @@
         <v/>
       </c>
       <c r="S149" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R149)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R149)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T149" s="90" t="inlineStr">
@@ -19885,7 +19885,7 @@
         <v/>
       </c>
       <c r="S150" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R150)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R150)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T150" s="90" t="inlineStr">
@@ -20011,7 +20011,7 @@
         <v/>
       </c>
       <c r="S151" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R151)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R151)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T151" s="90" t="inlineStr">
@@ -20137,7 +20137,7 @@
         <v/>
       </c>
       <c r="S152" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R152)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R152)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T152" s="90" t="inlineStr">
@@ -20263,7 +20263,7 @@
         <v/>
       </c>
       <c r="S153" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R153)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R153)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T153" s="90" t="inlineStr">
@@ -20389,7 +20389,7 @@
         <v/>
       </c>
       <c r="S154" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R154)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R154)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T154" s="90" t="inlineStr">
@@ -20515,7 +20515,7 @@
         <v/>
       </c>
       <c r="S155" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R155)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R155)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T155" s="90" t="inlineStr">
@@ -20641,7 +20641,7 @@
         <v/>
       </c>
       <c r="S156" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R156)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R156)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T156" s="90" t="inlineStr">
@@ -20767,7 +20767,7 @@
         <v/>
       </c>
       <c r="S157" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R157)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R157)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T157" s="90" t="inlineStr">
@@ -20893,7 +20893,7 @@
         <v/>
       </c>
       <c r="S158" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R158)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R158)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T158" s="90" t="inlineStr">
@@ -21019,7 +21019,7 @@
         <v/>
       </c>
       <c r="S159" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R159)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R159)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T159" s="90" t="inlineStr">
@@ -21145,7 +21145,7 @@
         <v/>
       </c>
       <c r="S160" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R160)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R160)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T160" s="90" t="inlineStr">
@@ -21271,7 +21271,7 @@
         <v/>
       </c>
       <c r="S161" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R161)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R161)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T161" s="90" t="inlineStr">
@@ -21397,7 +21397,7 @@
         <v/>
       </c>
       <c r="S162" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R162)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R162)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T162" s="90" t="inlineStr">
@@ -21523,7 +21523,7 @@
         <v/>
       </c>
       <c r="S163" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R163)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R163)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T163" s="90" t="inlineStr">
@@ -21649,7 +21649,7 @@
         <v/>
       </c>
       <c r="S164" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R164)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R164)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T164" s="90" t="inlineStr">
@@ -21775,7 +21775,7 @@
         <v/>
       </c>
       <c r="S165" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R165)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R165)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T165" s="90" t="inlineStr">
@@ -21901,7 +21901,7 @@
         <v/>
       </c>
       <c r="S166" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R166)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R166)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T166" s="90" t="inlineStr">
@@ -22027,7 +22027,7 @@
         <v/>
       </c>
       <c r="S167" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R167)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R167)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T167" s="90" t="inlineStr">
@@ -22153,7 +22153,7 @@
         <v/>
       </c>
       <c r="S168" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R168)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R168)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T168" s="90" t="inlineStr">
@@ -22279,7 +22279,7 @@
         <v/>
       </c>
       <c r="S169" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R169)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R169)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T169" s="90" t="inlineStr">
@@ -22405,7 +22405,7 @@
         <v/>
       </c>
       <c r="S170" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R170)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R170)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T170" s="90" t="inlineStr">
@@ -22531,7 +22531,7 @@
         <v/>
       </c>
       <c r="S171" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R171)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R171)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T171" s="90" t="inlineStr">
@@ -22654,7 +22654,7 @@
         <v/>
       </c>
       <c r="S172" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R172)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R172)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T172" s="90" t="inlineStr">
@@ -22777,7 +22777,7 @@
         <v/>
       </c>
       <c r="S173" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R173)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R173)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T173" s="90" t="inlineStr">
@@ -22901,7 +22901,7 @@
         <v/>
       </c>
       <c r="S174" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R174)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R174)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T174" s="90" t="inlineStr">
@@ -23025,7 +23025,7 @@
         <v/>
       </c>
       <c r="S175" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R175)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R175)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T175" s="90" t="inlineStr">
@@ -23149,7 +23149,7 @@
         <v/>
       </c>
       <c r="S176" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R176)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R176)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T176" s="90" t="inlineStr">
@@ -23273,7 +23273,7 @@
         <v/>
       </c>
       <c r="S177" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R177)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R177)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T177" s="90" t="inlineStr">
@@ -23397,7 +23397,7 @@
         <v/>
       </c>
       <c r="S178" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R178)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R178)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T178" s="90" t="inlineStr">
@@ -23522,7 +23522,7 @@
         <v/>
       </c>
       <c r="S179" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R179)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R179)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T179" s="90" t="inlineStr">
@@ -23645,7 +23645,7 @@
         <v/>
       </c>
       <c r="S180" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R180)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R180)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T180" s="90" t="inlineStr">
@@ -23769,7 +23769,7 @@
         <v/>
       </c>
       <c r="S181" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R181)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R181)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T181" s="90" t="inlineStr">
@@ -23892,7 +23892,7 @@
         <v/>
       </c>
       <c r="S182" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R182)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R182)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T182" s="90" t="inlineStr">
@@ -24015,7 +24015,7 @@
         <v/>
       </c>
       <c r="S183" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R183)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R183)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T183" s="90" t="inlineStr">
@@ -24139,7 +24139,7 @@
         <v/>
       </c>
       <c r="S184" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R184)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R184)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T184" s="90" t="inlineStr">
@@ -24264,7 +24264,7 @@
         <v/>
       </c>
       <c r="S185" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R185)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R185)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T185" s="90" t="inlineStr">
@@ -24388,7 +24388,7 @@
         <v/>
       </c>
       <c r="S186" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R186)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R186)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T186" s="90" t="inlineStr">
@@ -24512,7 +24512,7 @@
         <v/>
       </c>
       <c r="S187" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R187)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R187)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T187" s="90" t="inlineStr">
@@ -24636,7 +24636,7 @@
         <v/>
       </c>
       <c r="S188" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R188)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R188)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T188" s="90" t="inlineStr">
@@ -24760,7 +24760,7 @@
         <v/>
       </c>
       <c r="S189" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R189)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R189)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T189" s="90" t="inlineStr">
@@ -24884,7 +24884,7 @@
         <v/>
       </c>
       <c r="S190" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R190)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R190)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T190" s="90" t="inlineStr">
@@ -25008,7 +25008,7 @@
         <v/>
       </c>
       <c r="S191" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R191)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R191)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T191" s="90" t="inlineStr">
@@ -25131,7 +25131,7 @@
         <v/>
       </c>
       <c r="S192" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R192)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R192)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T192" s="90" t="inlineStr">
@@ -25255,7 +25255,7 @@
         <v/>
       </c>
       <c r="S193" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R193)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R193)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T193" s="90" t="inlineStr">
@@ -25378,7 +25378,7 @@
         <v/>
       </c>
       <c r="S194" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R194)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R194)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T194" s="90" t="inlineStr">
@@ -25501,7 +25501,7 @@
         <v/>
       </c>
       <c r="S195" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R195)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R195)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T195" s="90" t="inlineStr">
@@ -25625,7 +25625,7 @@
         <v/>
       </c>
       <c r="S196" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R196)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R196)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T196" s="90" t="inlineStr">
@@ -25748,7 +25748,7 @@
         <v/>
       </c>
       <c r="S197" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R197)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R197)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T197" s="90" t="inlineStr">
@@ -25871,7 +25871,7 @@
         <v/>
       </c>
       <c r="S198" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R198)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R198)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T198" s="90" t="inlineStr">
@@ -25994,7 +25994,7 @@
         <v/>
       </c>
       <c r="S199" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R199)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R199)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T199" s="90" t="inlineStr">
@@ -26117,7 +26117,7 @@
         <v/>
       </c>
       <c r="S200" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R200)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R200)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T200" s="90" t="inlineStr">
@@ -26240,7 +26240,7 @@
         <v/>
       </c>
       <c r="S201" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R201)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R201)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T201" s="90" t="inlineStr">
@@ -26363,7 +26363,7 @@
         <v/>
       </c>
       <c r="S202" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R202)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R202)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T202" s="90" t="inlineStr">
@@ -26486,7 +26486,7 @@
         <v/>
       </c>
       <c r="S203" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R203)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R203)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T203" s="90" t="inlineStr">
@@ -26609,7 +26609,7 @@
         <v/>
       </c>
       <c r="S204" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R204)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R204)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T204" s="90" t="inlineStr">
@@ -26733,7 +26733,7 @@
         <v/>
       </c>
       <c r="S205" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R205)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R205)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T205" s="90" t="inlineStr">
@@ -26857,7 +26857,7 @@
         <v/>
       </c>
       <c r="S206" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R206)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R206)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T206" s="90" t="inlineStr">
@@ -26980,7 +26980,7 @@
         <v/>
       </c>
       <c r="S207" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R207)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R207)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T207" s="90" t="inlineStr">
@@ -27103,7 +27103,7 @@
         <v/>
       </c>
       <c r="S208" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R208)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R208)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T208" s="90" t="inlineStr">
@@ -27226,7 +27226,7 @@
         <v/>
       </c>
       <c r="S209" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R209)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R209)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T209" s="90" t="inlineStr">
@@ -27349,7 +27349,7 @@
         <v/>
       </c>
       <c r="S210" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R210)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R210)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T210" s="90" t="inlineStr">
@@ -27472,7 +27472,7 @@
         <v/>
       </c>
       <c r="S211" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R211)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R211)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T211" s="90" t="inlineStr">
@@ -27595,7 +27595,7 @@
         <v/>
       </c>
       <c r="S212" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R212)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R212)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T212" s="90" t="inlineStr">
@@ -27718,7 +27718,7 @@
         <v/>
       </c>
       <c r="S213" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R213)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R213)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T213" s="90" t="inlineStr">
@@ -27841,7 +27841,7 @@
         <v/>
       </c>
       <c r="S214" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R214)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R214)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T214" s="90" t="inlineStr">
@@ -27964,7 +27964,7 @@
         <v/>
       </c>
       <c r="S215" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R215)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R215)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T215" s="90" t="inlineStr">
@@ -28087,7 +28087,7 @@
         <v/>
       </c>
       <c r="S216" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R216)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R216)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T216" s="90" t="inlineStr">
@@ -28210,7 +28210,7 @@
         <v/>
       </c>
       <c r="S217" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R217)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R217)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T217" s="90" t="inlineStr">
@@ -28334,7 +28334,7 @@
         <v/>
       </c>
       <c r="S218" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R218)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R218)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T218" s="90" t="inlineStr">
@@ -28457,7 +28457,7 @@
         <v/>
       </c>
       <c r="S219" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R219)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R219)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T219" s="90" t="inlineStr">
@@ -28580,7 +28580,7 @@
         <v/>
       </c>
       <c r="S220" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R220)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R220)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T220" s="90" t="inlineStr">
@@ -28703,7 +28703,7 @@
         <v/>
       </c>
       <c r="S221" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R221)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R221)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T221" s="90" t="inlineStr">
@@ -28826,7 +28826,7 @@
         <v/>
       </c>
       <c r="S222" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R222)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R222)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T222" s="90" t="inlineStr">
@@ -28949,7 +28949,7 @@
         <v/>
       </c>
       <c r="S223" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R223)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R223)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T223" s="90" t="inlineStr">
@@ -29072,7 +29072,7 @@
         <v/>
       </c>
       <c r="S224" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R224)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R224)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T224" s="90" t="inlineStr">
@@ -29195,7 +29195,7 @@
         <v/>
       </c>
       <c r="S225" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R225)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R225)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T225" s="90" t="inlineStr">
@@ -29318,7 +29318,7 @@
         <v/>
       </c>
       <c r="S226" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R226)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R226)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T226" s="90" t="inlineStr">
@@ -29441,7 +29441,7 @@
         <v/>
       </c>
       <c r="S227" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R227)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R227)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T227" s="90" t="inlineStr">
@@ -29564,7 +29564,7 @@
         <v/>
       </c>
       <c r="S228" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R228)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R228)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T228" s="90" t="inlineStr">
@@ -29687,7 +29687,7 @@
         <v/>
       </c>
       <c r="S229" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R229)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R229)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T229" s="90" t="inlineStr">
@@ -29810,7 +29810,7 @@
         <v/>
       </c>
       <c r="S230" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R230)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R230)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T230" s="90" t="inlineStr">
@@ -29934,7 +29934,7 @@
         <v/>
       </c>
       <c r="S231" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R231)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R231)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T231" s="93" t="inlineStr">
@@ -30057,7 +30057,7 @@
         <v/>
       </c>
       <c r="S232" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R232)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R232)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T232" s="93" t="inlineStr">
@@ -30177,7 +30177,7 @@
         <v/>
       </c>
       <c r="S233" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R233)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R233)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U233" s="93" t="inlineStr">
@@ -30293,7 +30293,7 @@
         <v/>
       </c>
       <c r="S234" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R234)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R234)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U234" s="93" t="inlineStr">
@@ -30409,7 +30409,7 @@
         <v/>
       </c>
       <c r="S235" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R235)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R235)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U235" s="93" t="inlineStr">
@@ -30525,7 +30525,7 @@
         <v/>
       </c>
       <c r="S236" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R236)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R236)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U236" s="93" t="inlineStr">
@@ -30641,7 +30641,7 @@
         <v/>
       </c>
       <c r="S237" s="94">
-        <f>IF(COUNTIF($R$6:$R$246,R237)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R237)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U237" s="93" t="inlineStr">
@@ -30758,7 +30758,7 @@
         <v/>
       </c>
       <c r="S238" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R238)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R238)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T238" s="90" t="inlineStr">
@@ -30881,7 +30881,7 @@
         <v/>
       </c>
       <c r="S239" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R239)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R239)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T239" s="90" t="inlineStr">
@@ -31000,7 +31000,7 @@
         <v/>
       </c>
       <c r="S240" s="63">
-        <f>IF(COUNTIF($R$6:$R$246,R240)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R240)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T240" s="90" t="inlineStr">
@@ -31119,7 +31119,7 @@
         <v/>
       </c>
       <c r="S241" s="90">
-        <f>IF(COUNTIF($R$6:$R$246,R241)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R241)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T241" s="90" t="inlineStr">
@@ -31240,7 +31240,7 @@
         <v/>
       </c>
       <c r="S242" s="90">
-        <f>IF(COUNTIF($R$6:$R$246,R242)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R242)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T242" s="90" t="inlineStr">
@@ -31323,7 +31323,7 @@
       </c>
       <c r="K243" s="90" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="L243" s="90" t="inlineStr">
@@ -31338,7 +31338,7 @@
       </c>
       <c r="N243" s="90" t="inlineStr">
         <is>
-          <t>30×40×11.9m（6×8 个 5m 槽 / 28 个墙位）；106 个独立组件包 / 193 输出网格 / 211708 面；无内墙；4 组工位；门洞 2.2×2.5m（净空底 0.30m、门楣 2.80m）；QA PASS（22 项断言）</t>
+          <t>30×40×11.9m（6×8 个 5m 槽 / 28 个墙位）；106 个独立组件包 / 193 输出网格 / 211708 面；无内墙；4 组工位；门洞 2.2×2.5m（净空底 0.30m、门楣 2.80m）；QA PASS（22 项断言）；组件库 v006：25 个唯一组件 / 106 个实例，运行时按 component_instances.json 逐组件重放</t>
         </is>
       </c>
       <c r="O243" s="90" t="inlineStr">
@@ -31361,7 +31361,7 @@
         <v/>
       </c>
       <c r="S243" s="90">
-        <f>IF(COUNTIF($R$6:$R$246,R243)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R243)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T243" s="90" t="inlineStr">
@@ -31376,7 +31376,7 @@
       </c>
       <c r="V243" s="90" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="W243" s="63" t="inlineStr">
@@ -31391,7 +31391,7 @@
       </c>
       <c r="Y243" s="63" t="inlineStr">
         <is>
-          <t>服务远征关卡01 的 room_03（COMBAT，中心 -45/50）与 room_09（EVENT，中心 15/-45）；两房实测同为 office_60x70（30×40m）模板 ⇒ 共用一份房型源。白盒尺寸/门洞/墙高锁定，只做场景美术。未导 GLB、未接 Godot。</t>
+          <t>服务远征关卡01 的 room_03（COMBAT，中心 -45/50）与 room_09（EVENT，中心 15/-45）；两房实测同为 office_60x70（30×40m）模板 ⇒ 共用一份房型源。白盒尺寸/门洞/墙高锁定，只做场景美术。2026-09-27：房型组件库 v006 已逐件导出 25 个稳定 GLB/PackedScene 并接入运行时（room_03 / room_09 各 106 实例、unresolved=0、门 2 扇）；主层地砖运行时换通用 C01/C02 棋盘砖。</t>
         </is>
       </c>
     </row>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="K244" s="90" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="L244" s="90" t="inlineStr">
@@ -31459,7 +31459,7 @@
       </c>
       <c r="N244" s="90" t="inlineStr">
         <is>
-          <t>30×60×11.9m（工字型）；上层平台 30×60（Z∈[-0.32,0]）；中央跨桥 10×30m；下沉坑 30×30m、坑底 Z=-12.0；4 个下层服务标高；242 个独立组件包 / 314 输出网格 / 312370 面；门洞 2.2×2.5m；QA PASS（17 项断言）</t>
+          <t>30×60×11.9m（工字型）；上层平台 30×60（Z∈[-0.32,0]）；中央跨桥 10×30m；下沉坑 30×30m、坑底 Z=-12.0；4 个下层服务标高；242 个独立组件包 / 314 输出网格 / 312370 面；门洞 2.2×2.5m；QA PASS（17 项断言）；组件库 v007：35 个唯一组件 / 242 个实例，运行时按 component_instances.json 逐组件重放</t>
         </is>
       </c>
       <c r="O244" s="90" t="inlineStr">
@@ -31482,7 +31482,7 @@
         <v/>
       </c>
       <c r="S244" s="90">
-        <f>IF(COUNTIF($R$6:$R$246,R244)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R244)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T244" s="90" t="inlineStr">
@@ -31497,7 +31497,7 @@
       </c>
       <c r="V244" s="90" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="W244" s="63" t="inlineStr">
@@ -31512,7 +31512,7 @@
       </c>
       <c r="Y244" s="63" t="inlineStr">
         <is>
-          <t>服务远征关卡01 的 room_05（通道桥房间 30×60 · 工字型；转置姿态用 template_rotation_deg:90）。本批唯一需多层几何与碰撞的房型。v001 保留在同目录历史版本。未导 GLB、未接 Godot。</t>
+          <t>服务远征关卡01 的 room_05（通道桥房间 30×60 · 工字型；转置姿态用 template_rotation_deg:90）。本批唯一需多层几何与碰撞的房型。v001 保留在同目录历史版本。2026-09-27：房型组件库 v007 已逐件导出 35 个稳定 GLB/PackedScene 并接入运行时（room_05 242 实例、unresolved=0、门 2 扇）；主层地砖换通用 C01/C02 棋盘砖，坑底 36 块砖保持原样。</t>
         </is>
       </c>
     </row>
@@ -31603,7 +31603,7 @@
         <v/>
       </c>
       <c r="S245" s="90">
-        <f>IF(COUNTIF($R$6:$R$246,R245)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R245)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T245" s="90" t="inlineStr">
@@ -31724,7 +31724,7 @@
         <v/>
       </c>
       <c r="S246" s="90">
-        <f>IF(COUNTIF($R$6:$R$246,R246)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$247,R246)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T246" s="90" t="inlineStr">
@@ -31755,6 +31755,127 @@
       <c r="Y246" s="63" t="inlineStr">
         <is>
           <t>服务远征关卡01 的 room_02 / room_06 / room_10（三处实例共用同一房型源）。本轮按参考图做 **db_01** 布局（主体 40×25 + 南侧中段外凸 10×5，面积 1050 m²）；同模板的另一内部布局 db_02（双缺角 15×10 / 15×5，面积 975 m²）按 room_type_manifest.json 显式标注为待另轮制作。与 office / bridge 两行的差别：墙件（28 樘）与地砖（42 格）**不重新制作**，改为 Library Link 引用 office_room/v001 的已验收组件包（本文件自持墙/砖网格 0、不 Append、不改组件几何/材质/根原点）；其余 37 个组件包（地面标识 / 格栅 / 设备坑抬升平台 / 西侧机柜列 7 台 / 中部机柜组 / 东墙 L 形工作台 / 西墙检修台 / 壁挂大屏组 / 红黄工具车 / 中央作业台 / 货箱堆场 / 重型货架 / 零件柜 / 电缆盘与线圈 / 花箱绿植 / 设备机架 / 墙面灯柱 / 顶部桥架管道风管灯具等）为数据库机房专属新制。未导 GLB、未接 Godot。</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="255" customHeight="1" s="60">
+      <c r="A247" s="90" t="inlineStr">
+        <is>
+          <t>ENV-EXPEDITION-L01-BOSS-ROOM</t>
+        </is>
+      </c>
+      <c r="B247" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 Boss竞技场 故障数据库 50×40m 房间种类源</t>
+        </is>
+      </c>
+      <c r="C247" s="63" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="D247" s="90" t="inlineStr">
+        <is>
+          <t>boss_room</t>
+        </is>
+      </c>
+      <c r="E247" s="90" t="inlineStr">
+        <is>
+          <t>expedition_01_boss_room</t>
+        </is>
+      </c>
+      <c r="F247" s="90" t="inlineStr">
+        <is>
+          <t>room_type</t>
+        </is>
+      </c>
+      <c r="G247" s="90" t="n"/>
+      <c r="H247" s="90" t="inlineStr">
+        <is>
+          <t>Top3D / Blender Z-up</t>
+        </is>
+      </c>
+      <c r="I247" s="90" t="inlineStr">
+        <is>
+          <t>scene_art / reference_derived</t>
+        </is>
+      </c>
+      <c r="J247" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01 专用；boss 房（boss_50x40，50×40m）。房型套件为独立一库（common_components/v008，与 office / bridge 两批不混用）</t>
+        </is>
+      </c>
+      <c r="K247" s="90" t="inlineStr">
+        <is>
+          <t>正式美术已接入</t>
+        </is>
+      </c>
+      <c r="L247" s="90" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M247" s="90" t="inlineStr">
+        <is>
+          <t>v002</t>
+        </is>
+      </c>
+      <c r="N247" s="90" t="inlineStr">
+        <is>
+          <t>50×40×11.9m（10×8 个 5m 槽 / 72 个墙位）；组件库 v008：38 个唯一组件 / 210 个实例（17 族）；主层地砖 80 格运行时换通用 C01/C02 棋盘砖；门位 2（西 / 东 lane −2.5）；QA PASS（专项探针 2051 项断言）</t>
+        </is>
+      </c>
+      <c r="O247" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/boss_room/v002/Boss房种类_故障数据库_50x40m_v002.blend</t>
+        </is>
+      </c>
+      <c r="P247" s="90" t="inlineStr">
+        <is>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/boss_room/v002/room_type_manifest.json；assets/art/environments/tower_zones/expedition/source/common_components/v008/component_plan.json；component_slug_map.json；归并工具 scripts/blender/regroup_room_type_components.py</t>
+        </is>
+      </c>
+      <c r="Q247" s="63" t="inlineStr">
+        <is>
+          <t>远征关卡01;Boss竞技场;故障数据库;房间种类;50×40m;服务器机柜;主屏;桥架;组件库;v008</t>
+        </is>
+      </c>
+      <c r="R247" s="90">
+        <f>LOWER(TRIM(C247)&amp;"|"&amp;TRIM(D247)&amp;"|"&amp;TRIM(E247)&amp;"|"&amp;TRIM(F247)&amp;"|"&amp;TRIM(H247)&amp;"|"&amp;TRIM(I247))</f>
+        <v/>
+      </c>
+      <c r="S247" s="90">
+        <f>IF(COUNTIF($R$6:$R$247,R247)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T247" s="90" t="inlineStr">
+        <is>
+          <t>e61a8ca0dcd5b133a09bc13d6567bbcba513838709ea77fbac951670b9ad0b29</t>
+        </is>
+      </c>
+      <c r="U247" s="63" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="V247" s="90" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="W247" s="63" t="inlineStr">
+        <is>
+          <t>用户设计（参考图见 room_type_manifest.json 的 reference_image）</t>
+        </is>
+      </c>
+      <c r="X247" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y247" s="63" t="inlineStr">
+        <is>
+          <t>服务远征关卡01 的 boss 房（BOSS，中心 -20/0/-85）。房型套件独立一库（common_components/v008，38 组件 / 210 实例），运行时按 component_instances.json 重放；主层地砖统一换通用 C01/C02 棋盘砖，墙 / 家具 / 标识 / 碎屑保留自有美术。</t>
         </is>
       </c>
     </row>
@@ -31778,13 +31899,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C246" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C247" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K246" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K247" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L246" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L247" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -45247,7 +45368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.80859375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="59" min="1" max="1"/>
@@ -45274,7 +45395,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="60">
       <c r="A5" s="66" t="inlineStr">
         <is>
@@ -45936,6 +46056,43 @@
         </is>
       </c>
       <c r="G22" s="119" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="118" t="inlineStr">
+        <is>
+          <t>v0.1.17</t>
+        </is>
+      </c>
+      <c r="B23" s="118" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C23" s="119" t="inlineStr">
+        <is>
+          <t>状态转正 + 新增条目</t>
+        </is>
+      </c>
+      <c r="D23" s="119" t="inlineStr">
+        <is>
+          <t>关卡场景 / 远征关卡01</t>
+        </is>
+      </c>
+      <c r="E23" s="119" t="inlineStr">
+        <is>
+          <t>① ENV-EXPEDITION-L01-OFFICE-ROOM（组件库 v006）与 ENV-EXPEDITION-L01-BRIDGE-ROOM（组件库 v007）制作状态「Blender源已完成」→「正式美术已接入」：两套房型源按组件优先规则归并为唯一组件库，逐件导出稳定 GLB / PackedScene 并接入运行时（room_03 / room_09 各 106 实例、room_05 242 实例，unresolved 全 0，主层地砖统一换通用 C01/C02 棋盘砖）。② 新增 ENV-EXPEDITION-L01-BOSS-ROOM（远征关卡01 Boss竞技场 故障数据库 50×40m 房间种类源，v002，服务 boss 房）：房型套件为独立一库，组件库 v008 = 38 个唯一组件 / 210 个实例。</t>
+        </is>
+      </c>
+      <c r="F23" s="119" t="inlineStr">
+        <is>
+          <t>① 两行只改「制作状态 / 规格 / 备注 / 更新时间」，AssetID、路径、SHA-256 逐格未动（--scope full 既有 40 条 sha_mismatch 逐项不变，可反向对照）。② 新增一行 ⇒ S 列派生公式区间与《总览》12 格区间随之扩到 $247（属预期，门禁 stale_overview_formula 盯着）。③ 《3D-场景通用》等摘要锁死表未动。④ 无损基线按既有「从当前分账本重建」口径做最小补录（加新行指纹、更新两行既有指纹，其余 413 条逐位不变，列摘要与分类计数重算），补录前基线备份见 _scratch/ledger_roomtype/ledger_split_baseline.json.bak_before。</t>
+        </is>
+      </c>
+      <c r="G23" s="119" t="inlineStr">
         <is>
           <t>摩斯拉</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -31255,7 +31255,7 @@
       </c>
       <c r="V242" s="90" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="W242" s="63" t="inlineStr">
@@ -31270,7 +31270,7 @@
       </c>
       <c r="Y242" s="63" t="inlineStr">
         <is>
-          <t>由 battle 区块房间种类源迁入（原 ENV-BATTLE-L-CORRIDOR-TYPE，原路径 tower_zones/battle/source/room_types/l_corridor/；业主 2026-09-24 裁决归属远征关卡01，battle 侧不留副本）。远征01 版图与白盒目录均无走廊白模，尺寸与门位按参考图推定。v001/v002 为 10m 宽走廊（外包络 45×35m / 28 块地砖 / 88、111 个组件包），v003 拓宽为 15m（45×40m / 42 块地砖 / 121 个组件包 / 4 个门位：西1 北2 南1）。随迁统一内部结构：component_packages_vNNN→component_packages、facility→facilities、散放渲染图入 renders/。共享件引用由 ENV-BATTLE-COMMON-* 更正为 shared 库现有 ENV-SHARED-GENERIC-*。未导 GLB、未接 Godot。</t>
+          <t>由 battle 区块房间种类源迁入（原 ENV-BATTLE-L-CORRIDOR-TYPE，原路径 tower_zones/battle/source/room_types/l_corridor/；业主 2026-09-24 裁决归属远征关卡01，battle 侧不留副本）。远征01 版图与白盒目录均无走廊白模，尺寸与门位按参考图推定。v001/v002 为 10m 宽走廊（外包络 45×35m / 28 块地砖 / 88、111 个组件包），v003 拓宽为 15m（45×40m / 42 块地砖 / 121 个组件包 / 4 个门位：西1 北2 南1）。随迁统一内部结构：component_packages_vNNN→component_packages、facility→facilities、散放渲染图入 renders/。共享件引用由 ENV-BATTLE-COMMON-* 更正为 shared 库现有 ENV-SHARED-GENERIC-*。未导 GLB、未接 Godot。2026-09-27（业主裁定，本轮同批）：① 组件库 v002（122 个 blend）UV 配色保色相提亮 3 个挡位，深色面（HSV 明度 &lt;40%）占比 13.9% → 4.8%（母版 96774 面中移动 90498 面）。② 材质主面判据：改 268 槽 / 2696 面，金属面积占比 12.0% → 9.7%；保留金属小件为 `前墙` / `侧墙`。③ ⚠️ 本库尚未进入导出链（`export_expedition_room_type_components.py` 的 LIBRARIES 只含 office/bridge/boss）⇒ 未导 GLB、未接 Godot，制作状态保持「Blender源已完成」。房型概念源 blend 未动，SHA-256 不变。</t>
         </is>
       </c>
     </row>
@@ -31338,7 +31338,7 @@
       </c>
       <c r="N243" s="90" t="inlineStr">
         <is>
-          <t>30×40×11.9m（6×8 个 5m 槽 / 28 个墙位）；106 个独立组件包 / 193 输出网格 / 211708 面；无内墙；4 组工位；门洞 2.2×2.5m（净空底 0.30m、门楣 2.80m）；QA PASS（22 项断言）；组件库 v006：25 个唯一组件 / 106 个实例，运行时按 component_instances.json 逐组件重放</t>
+          <t>30×40×11.9m（6×8 个 5m 槽 / 28 个墙位）；106 个独立组件包 / 193 输出网格 / 211708 面；无内墙；4 组工位；门洞 2.2×2.5m（净空底 0.30m、门楣 2.80m）；QA PASS（22 项断言）；组件库 v009：25 个唯一组件 / 106 个实例，运行时按 component_instances.json 逐组件重放</t>
         </is>
       </c>
       <c r="O243" s="90" t="inlineStr">
@@ -31391,7 +31391,7 @@
       </c>
       <c r="Y243" s="63" t="inlineStr">
         <is>
-          <t>服务远征关卡01 的 room_03（COMBAT，中心 -45/50）与 room_09（EVENT，中心 15/-45）；两房实测同为 office_60x70（30×40m）模板 ⇒ 共用一份房型源。白盒尺寸/门洞/墙高锁定，只做场景美术。2026-09-27：房型组件库 v006 已逐件导出 25 个稳定 GLB/PackedScene 并接入运行时（room_03 / room_09 各 106 实例、unresolved=0、门 2 扇）；主层地砖运行时换通用 C01/C02 棋盘砖。</t>
+          <t>服务远征关卡01 的 room_03（COMBAT，中心 -45/50）与 room_09（EVENT，中心 15/-45）；两房实测同为 office_60x70（30×40m）模板 ⇒ 共用一份房型源。白盒尺寸/门洞/墙高锁定，只做场景美术。2026-09-27：房型组件库 v009 已逐件导出 25 个稳定 GLB/PackedScene 并接入运行时（room_03 / room_09 各 106 实例、unresolved=0、门 2 扇）；主层地砖运行时换通用 C01/C02 棋盘砖。2026-09-27（同轮，业主裁定）：① UV 配色「保色相提亮 3 个挡位」——组件库 v009 的 20 个在用例按图面行 +3 重导向（第 10 列冷调灰阶栏行 +3、彩色族同族列 +3、封顶列 8；浅端溢出与近黑 `0_0` #05050c 原样保留），深色面（HSV 明度 &lt;40%）占比 65.7% → 30.0%（母版 118206 面中移动 75934 面）。② 材质按「主面判据」（按槽面积不按面数）改亚光——本库全部为哑光/反光/自发光，无金属槽 ⇒ 实际改动 0 处，金属面积占比 0.0% 不变。③ 随后按新源重导出 98 个稳定 GLB（本库 25 件）并重建 PackedScene 与 `shell_component_catalog.json`（110 条），Godot 重导后房型重放验收 2051 项断言全通过（room_03 / room_09 各 106 实例、unresolved=0）。房型概念源 blend 未动，SHA-256 不变。④ 2026-09-27（同轮收尾）：按 `04-battle-room-runtime-assembler`「房间输出」要求补齐**逐房间运行时装配清单** —— `room_03` / `room_09` 各产出 `runtime/room_instances/f00_room_0{3,9}/room_runtime_manifest.json` + `acceptance/`，`assembly_route = room_type_layout_replay`（分支 A0，具体房间白模与房型默认尺寸/门槽/必需设施一致、无 instance_overrides）。清单记 106 实例（door_wall 1 / solid_wall 28 / room_type_component 29 / floor_tile 48）、组件库源哈希 83c1e268…、逐组件 PackedScene 与碰撞责任、门洞契约与门位（门位不冻结、按种子现算；RUN_SEED=77001199 实测 `room_03` 北接 room_02 / 南接 room_04，`room_09` 南接 room_08 / 北接 room_10；以 `acceptance/runtime_doors.txt` 为准）。⑤ 2026-09-27（同轮收尾·组件库升版）：按 `02-battle-room-component-decomposer` 第 184 行「生成组件源版本，不覆盖房间种类源，也不覆盖历史组件源」，把**组件库由原地改写改为正式升版 v006 → v009**（目录 `common_components/v006` → `v009`，母版改名 `…_v009.blend`）：v009 = 提亮 + 亚光后的当前源；原 v006 目录内容由 `git checkout HEAD --` 恢复为**提亮前的历史源**（只读留档）。同步改写全部引用：① `component_catalog.json` 的 `version` / `component_library` / 25 个包的 `component_library_blend`；② `component_instances.json` 的 `library`（**改** ＝ 本库自身版本；`source_library` = v004 与 `source_blend_sha256` 指向**整屋／房间种类源** v004 母版，**未动**）；③ 组件库级 `runtime_manifest.json` 与 `room_03` / `room_09` 的 `room_runtime_manifest.json`；④ 98 个 PackedScene 的 `metadata/asset_version` 与 `source_blend`；⑤ `FloorPlanGenerator.ROOM_TYPE_LAYOUT_SOURCES`、两个导出脚本的 `LIBRARIES`、`build_room_runtime_manifests.py` 的 `ROOM_TYPE_BINDING`、重放验收探针 `expected_version`。**运行时路径一律不带版本号**（`04-battle-room-runtime-assembler` 第 155 行：替换即覆盖同路径同名文件），版本只写在 `source/`、`asset_manifest.json`、PackedScene metadata、布局快照与本账本。组件库母版 SHA-256：v006 `f5e666ee…`（提亮前）→ v009 `926a881d…`。升版后重导出 98 个稳定 GLB、重建 98 个 PackedScene 与 `shell_component_catalog.json`（110 条），Godot 重导后房型重放验收 2051 项断言全通过。</t>
         </is>
       </c>
     </row>
@@ -31459,7 +31459,7 @@
       </c>
       <c r="N244" s="90" t="inlineStr">
         <is>
-          <t>30×60×11.9m（工字型）；上层平台 30×60（Z∈[-0.32,0]）；中央跨桥 10×30m；下沉坑 30×30m、坑底 Z=-12.0；4 个下层服务标高；242 个独立组件包 / 314 输出网格 / 312370 面；门洞 2.2×2.5m；QA PASS（17 项断言）；组件库 v007：35 个唯一组件 / 242 个实例，运行时按 component_instances.json 逐组件重放</t>
+          <t>30×60×11.9m（工字型）；上层平台 30×60（Z∈[-0.32,0]）；中央跨桥 10×30m；下沉坑 30×30m、坑底 Z=-12.0；4 个下层服务标高；242 个独立组件包 / 314 输出网格 / 312370 面；门洞 2.2×2.5m；QA PASS（17 项断言）；组件库 v010：35 个唯一组件 / 242 个实例，运行时按 component_instances.json 逐组件重放</t>
         </is>
       </c>
       <c r="O244" s="90" t="inlineStr">
@@ -31512,7 +31512,7 @@
       </c>
       <c r="Y244" s="63" t="inlineStr">
         <is>
-          <t>服务远征关卡01 的 room_05（通道桥房间 30×60 · 工字型；转置姿态用 template_rotation_deg:90）。本批唯一需多层几何与碰撞的房型。v001 保留在同目录历史版本。2026-09-27：房型组件库 v007 已逐件导出 35 个稳定 GLB/PackedScene 并接入运行时（room_05 242 实例、unresolved=0、门 2 扇）；主层地砖换通用 C01/C02 棋盘砖，坑底 36 块砖保持原样。</t>
+          <t>服务远征关卡01 的 room_05（通道桥房间 30×60 · 工字型；转置姿态用 template_rotation_deg:90）。本批唯一需多层几何与碰撞的房型。v001 保留在同目录历史版本。2026-09-27：房型组件库 v010 已逐件导出 35 个稳定 GLB/PackedScene 并接入运行时（room_05 242 实例、unresolved=0、门 2 扇）；主层地砖换通用 C01/C02 棋盘砖，坑底 36 块砖保持原样。2026-09-27（同轮，业主裁定）：① 组件库 v010（36 个 blend）UV 配色保色相提亮 3 个挡位，深色面（HSV 明度 &lt;40%）占比 59.2% → 17.2%（母版 135984 面中移动 113068 面）。② 材质主面判据：本库无金属槽 ⇒ 改动 0 处，金属面积占比 0.0% 不变。③ 按新源重导出 98 个稳定 GLB（本库 35 件）并重建 PackedScene / 组件目录（110 条），Godot 重导后房型重放验收全通过（room_05 242 实例、unresolved=0）。房型概念源 blend 未动，SHA-256 不变。④ 2026-09-27（同轮收尾）：补齐**逐房间运行时装配清单** —— `room_05` 产出 `runtime/room_instances/f00_room_05/room_runtime_manifest.json` + `acceptance/`，`assembly_route = room_type_layout_replay`。清单记 242 实例（room_type_component 158 / solid_wall 36 / floor_tile 48，另有 36 块坑底 tile_lower 保留下沉标高不入主层刷怪格）、组件库源哈希 89e46e4e…、门位不冻结、按种子现算（RUN_SEED=77001199 实测东接 room_04 / 西接 room_06；探针日志 `acceptance/runtime_doors.txt`）、下沉坑底砖不计入换砖数。⑤ 2026-09-27（同轮收尾·组件库升版）：按 `02-battle-room-component-decomposer` 第 184 行「生成组件源版本，不覆盖房间种类源，也不覆盖历史组件源」，把**组件库由原地改写改为正式升版 v007 → v010**（目录 `common_components/v007` → `v010`，母版改名 `…_v010.blend`）：v010 = 提亮 + 亚光后的当前源；原 v007 目录由 `git checkout HEAD --` 恢复为**提亮前的历史源**（只读留档）。同步改写全部引用：① `component_catalog.json` 的 `version` / `component_library` / 35 个包的 `component_library_blend`；② `component_instances.json` 的 `library`（`source_library` = v005 与 `source_blend_sha256` 指向**整屋／房间种类源** v005 母版，**未动**）；③ 组件库级 `runtime_manifest.json` 与 `room_05` 的 `room_runtime_manifest.json`；④ 98 个 PackedScene 的 `metadata/asset_version` 与 `source_blend`；⑤ `FloorPlanGenerator.ROOM_TYPE_LAYOUT_SOURCES`、两个导出脚本的 `LIBRARIES`、`build_room_runtime_manifests.py` 的 `ROOM_TYPE_BINDING`、重放验收探针 `expected_version`。运行时路径不带版本号，版本只写在 source / manifest / PackedScene metadata / 布局快照 / 本账本。组件库母版 SHA-256：v007 `9f6a23ab…`（提亮前）→ v010 `f219156e…`。升版后重导出 98 个稳定 GLB 并重建 PackedScene 与组件目录，Godot 重导后房型重放验收 2051 项断言全通过（room_05 242 实例、unresolved=0）。</t>
         </is>
       </c>
     </row>
@@ -31739,7 +31739,7 @@
       </c>
       <c r="V246" s="90" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="W246" s="63" t="inlineStr">
@@ -31754,7 +31754,7 @@
       </c>
       <c r="Y246" s="63" t="inlineStr">
         <is>
-          <t>服务远征关卡01 的 room_02 / room_06 / room_10（三处实例共用同一房型源）。本轮按参考图做 **db_01** 布局（主体 40×25 + 南侧中段外凸 10×5，面积 1050 m²）；同模板的另一内部布局 db_02（双缺角 15×10 / 15×5，面积 975 m²）按 room_type_manifest.json 显式标注为待另轮制作。与 office / bridge 两行的差别：墙件（28 樘）与地砖（42 格）**不重新制作**，改为 Library Link 引用 office_room/v001 的已验收组件包（本文件自持墙/砖网格 0、不 Append、不改组件几何/材质/根原点）；其余 37 个组件包（地面标识 / 格栅 / 设备坑抬升平台 / 西侧机柜列 7 台 / 中部机柜组 / 东墙 L 形工作台 / 西墙检修台 / 壁挂大屏组 / 红黄工具车 / 中央作业台 / 货箱堆场 / 重型货架 / 零件柜 / 电缆盘与线圈 / 花箱绿植 / 设备机架 / 墙面灯柱 / 顶部桥架管道风管灯具等）为数据库机房专属新制。未导 GLB、未接 Godot。</t>
+          <t>服务远征关卡01 的 room_02 / room_06 / room_10（三处实例共用同一房型源）。本轮按参考图做 **db_01** 布局（主体 40×25 + 南侧中段外凸 10×5，面积 1050 m²）；同模板的另一内部布局 db_02（双缺角 15×10 / 15×5，面积 975 m²）按 room_type_manifest.json 显式标注为待另轮制作。与 office / bridge 两行的差别：墙件（28 樘）与地砖（42 格）**不重新制作**，改为 Library Link 引用 office_room/v001 的已验收组件包（本文件自持墙/砖网格 0、不 Append、不改组件几何/材质/根原点）；其余 37 个组件包（地面标识 / 格栅 / 设备坑抬升平台 / 西侧机柜列 7 台 / 中部机柜组 / 东墙 L 形工作台 / 西墙检修台 / 壁挂大屏组 / 红黄工具车 / 中央作业台 / 货箱堆场 / 重型货架 / 零件柜 / 电缆盘与线圈 / 花箱绿植 / 设备机架 / 墙面灯柱 / 顶部桥架管道风管灯具等）为数据库机房专属新制。未导 GLB、未接 Godot。2026-09-27（业主裁定，本轮同批）：① 组件库 v003（38 个 blend）UV 配色保色相提亮 3 个挡位，深色面（HSV 明度 &lt;40%）占比 56.1% → 30.6%（母版 254328 面中移动 123356 面）。② 材质主面判据：改 148 槽 / 409512 面，金属面积占比 100.0% → 0.0%（本库原为全金属）。③ ⚠️ 本库尚未进入导出链 ⇒ 未导 GLB、未接 Godot，制作状态保持「Blender源已完成」。房型概念源 blend 未动，SHA-256 不变。</t>
         </is>
       </c>
     </row>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="J247" s="63" t="inlineStr">
         <is>
-          <t>远征关卡01 专用；boss 房（boss_50x40，50×40m）。房型套件为独立一库（common_components/v008，与 office / bridge 两批不混用）</t>
+          <t>远征关卡01 专用；boss 房（boss_50x40，50×40m）。房型套件为独立一库（common_components/v011，与 office / bridge 两批不混用）</t>
         </is>
       </c>
       <c r="K247" s="90" t="inlineStr">
@@ -31822,7 +31822,7 @@
       </c>
       <c r="N247" s="90" t="inlineStr">
         <is>
-          <t>50×40×11.9m（10×8 个 5m 槽 / 72 个墙位）；组件库 v008：38 个唯一组件 / 210 个实例（17 族）；主层地砖 80 格运行时换通用 C01/C02 棋盘砖；门位 2（西 / 东 lane −2.5）；QA PASS（专项探针 2051 项断言）</t>
+          <t>50×40×11.9m（10×8 个 5m 槽 / 72 个墙位）；组件库 v011：38 个唯一组件 / 210 个实例（17 族）；主层地砖 80 格运行时换通用 C01/C02 棋盘砖；门位 2（西 / 东 lane −2.5）；QA PASS（专项探针 2051 项断言）</t>
         </is>
       </c>
       <c r="O247" s="90" t="inlineStr">
@@ -31832,12 +31832,12 @@
       </c>
       <c r="P247" s="90" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/expedition/source/room_types/boss_room/v002/room_type_manifest.json；assets/art/environments/tower_zones/expedition/source/common_components/v008/component_plan.json；component_slug_map.json；归并工具 scripts/blender/regroup_room_type_components.py</t>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/boss_room/v002/room_type_manifest.json；assets/art/environments/tower_zones/expedition/source/common_components/v011/component_plan.json；component_slug_map.json；归并工具 scripts/blender/regroup_room_type_components.py</t>
         </is>
       </c>
       <c r="Q247" s="63" t="inlineStr">
         <is>
-          <t>远征关卡01;Boss竞技场;故障数据库;房间种类;50×40m;服务器机柜;主屏;桥架;组件库;v008</t>
+          <t>远征关卡01;Boss竞技场;故障数据库;房间种类;50×40m;服务器机柜;主屏;桥架;组件库;v011</t>
         </is>
       </c>
       <c r="R247" s="90">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="Y247" s="63" t="inlineStr">
         <is>
-          <t>服务远征关卡01 的 boss 房（BOSS，中心 -20/0/-85）。房型套件独立一库（common_components/v008，38 组件 / 210 实例），运行时按 component_instances.json 重放；主层地砖统一换通用 C01/C02 棋盘砖，墙 / 家具 / 标识 / 碎屑保留自有美术。</t>
+          <t>服务远征关卡01 的 boss 房（BOSS，中心 -20/0/-85）。房型套件独立一库（common_components/v011，38 组件 / 210 实例），运行时按 component_instances.json 重放；主层地砖统一换通用 C01/C02 棋盘砖，墙 / 家具 / 标识 / 碎屑保留自有美术。2026-09-27（同轮，业主裁定）：① 组件库 v011（39 个 blend）UV 配色保色相提亮 3 个挡位，深色面（HSV 明度 &lt;40%）占比 72.6% → 24.5%（母版 39930 面中移动 39444 面）。② 材质主面判据：把面积占多数的 `01_精工金属` 槽改指 `02_细腻哑光`（只改槽指向，不动 PBR 参数 / 几何 / UV / 色盘格），改 60 槽 / 17896 面，金属面积占比 37.4% → 2.9%；按判据保留金属的小件为 `workstation_a/b/c`、`chair`、`archive_shelf`、`debris_*`。③ 按新源重导出 98 个稳定 GLB（本库 38 件）并重建 PackedScene / 组件目录，Godot 重导后房型重放验收全通过（boss 210 实例、unresolved=0）。房型概念源 blend 未动，SHA-256 不变。④ 2026-09-27（同轮收尾）：补齐**逐房间运行时装配清单** —— `boss` 产出 `runtime/room_instances/f00_boss/room_runtime_manifest.json` + `acceptance/`，`assembly_route = room_type_layout_replay`。清单记 210 实例（room_type_component 58 / solid_wall 72 / floor_tile 80）、组件库源哈希 5047d566…、门位不冻结、按种子现算（RUN_SEED=77001199 实测西接 room_10 / 东接撤离屋 —— 与静态兜底样例推导的「南接撤离屋」不一致，落地以探针为准）、运行时门扇节点数 2。⑤ 2026-09-27（同轮收尾·组件库升版）：按 `02-battle-room-component-decomposer` 第 184 行「生成组件源版本，不覆盖房间种类源，也不覆盖历史组件源」，把**独立组件库由原地改写改为正式升版 v008 → v011**（目录 `common_components/v008` → `v011`，母版改名 `…_v011.blend`，`component_slug_map.json` 与 `component_catalog.json` 的 `regroup_analysis` 随迁）：v011 = 提亮 + 亚光校正后的当前源；原 v008 目录由 `git checkout HEAD --` 恢复为**提亮前的历史源**（只读留档）。同步改写全部引用：① `component_catalog.json` 的 `version` / `component_library` / 38 个包的 `component_library_blend`；② `component_instances.json` 的 `library`（`source_library` = v001 与 `source_blend_sha256` 指向**整屋／房间种类源** v001 母版，**未动**）；③ 组件库级 `runtime_manifest.json` 与 `boss` 的 `room_runtime_manifest.json`；④ 98 个 PackedScene 的 `metadata/asset_version` 与 `source_blend`；⑤ `FloorPlanGenerator.ROOM_TYPE_LAYOUT_SOURCES`、两个导出脚本的 `LIBRARIES`、`build_room_runtime_manifests.py` 的 `ROOM_TYPE_BINDING`、重放验收探针 `expected_version`；⑥ 本行 J / N / P / Q 列的版本串。组件库母版 SHA-256：v008 `9ffd58e5…`（提亮前）→ v011 `b05b0151…`。升版后重导出 98 个稳定 GLB 并重建 PackedScene 与组件目录，Godot 重导后房型重放验收 2051 项断言全通过（boss 210 实例、unresolved=0、门位净空 0 覆盖）。</t>
         </is>
       </c>
     </row>
@@ -45368,7 +45368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.80859375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="59" min="1" max="1"/>
@@ -46061,7 +46061,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" s="60">
       <c r="A23" s="118" t="inlineStr">
         <is>
           <t>v0.1.17</t>
@@ -46093,6 +46093,154 @@
         </is>
       </c>
       <c r="G23" s="119" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" s="60">
+      <c r="A24" s="118" t="inlineStr">
+        <is>
+          <t>v0.1.18</t>
+        </is>
+      </c>
+      <c r="B24" s="118" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C24" s="119" t="inlineStr">
+        <is>
+          <t>条目修正</t>
+        </is>
+      </c>
+      <c r="D24" s="119" t="inlineStr">
+        <is>
+          <t>关卡场景 / 远征关卡01</t>
+        </is>
+      </c>
+      <c r="E24" s="119" t="inlineStr">
+        <is>
+          <t>远征关卡01 五套房型组件库（office_room/v006、bridge_room/v007、boss_room/v008、l_corridor/v002、db_room/v003，合计 261 个 blend）按业主裁定做两项全量校正，随后把已完成的三套重导出并接入运行时：① **UV 配色保色相提亮 3 个挡位** —— 第 10 列冷调灰阶栏按图面行 +3、彩色族同族列 +3、封顶列 8，浅端溢出与近黑 `0_0`（#05050c，斜角描边面与 db 黄黑警示边带黑条）原样保留；行 0 饱和原色行与 行 9 近黑阴影行不是渐变、不动。跨格 0、越界 0。深色面（HSV 明度 &lt;40%）占比：office 65.7% → 30.0%、bridge 59.2% → 17.2%、boss 72.6% → 24.5%、corridor 13.9% → 4.8%、db 56.1% → 30.6%。② **材质按「主面判据」亚光化** —— 判据 `金属面积 &gt;= 哑光+反光面积` 即按槽面积从大到小改指 `02_细腻哑光`，直到 `金属 &lt; 哑光+反光`；只改槽指向，不动 PBR 参数 / 几何 / UV / 色盘格，不新增材质种类。金属面积占比（256 个输出包、输出侧口径）：office 0.0% → 0.0%（无金属槽，0 处改动）、bridge 0.0% → 0.0%（0 处）、boss 37.4% → 2.9%（60 槽）、corridor 12.0% → 9.7%（268 槽）、db 100.0% → 0.0%（148 槽），合计 32.6% → 3.8%。平衡单元 = 组件 × 镜像集合（`_制作源` 与 `_输出包` 各自独立判定，集合名先剥 Blender 重名去重后缀 .001/.002/.003）。③ **导入拼装** —— office / bridge / boss 三库按新源重导出 98 个稳定 GLB（`export_image_format=NONE`、外链共享色盘不 Pack）、重建 98 个 PackedScene 与 `shell_component_catalog.json`（110 条）、Godot 默认 APPDATA 重导（98/98 `.scn` 重建）后房型重放验收 2051 项断言全通过（room_03/room_09 各 106、room_05 242、boss 210 实例，unresolved 全 0，门位净空 0 覆盖）。运行时探针实测 9 个取样组件的表面金属度 0.000~0.860（仅 `workstation_a` 保留 1 个高金属面）且 `albedo_texture` 全部指向共享色盘。</t>
+        </is>
+      </c>
+      <c r="F24" s="119" t="inlineStr">
+        <is>
+          <t>① 只改 5 行的「备注 / 更新时间」，AssetID、路径、版本、SHA-256、制作状态、规格、大类逐格未动 —— 房型**概念源** blend 全程未改写，7 个房型源 SHA-256 与账本登记逐位一致（已实测）。② 共享色盘 PNG（`ART-PALETTE-FACILITY-LOWLIGHT-DOPAMINE`）未改写，SHA-256 逐位一致 —— 本次提亮只改UV 色盘格的**导向**，不动色盘本体。③ 不动派生列与《总览》公式（未增删行，区间仍 $247）。④ 《3D-场景通用》等摘要锁死表未动。⑤ 无损基线按既有「从当前分账本重建」口径做最小补录（只更新这 5 行的行指纹 + 重算列摘要与分类计数，其余 411 条逐位不变），补录前基线备份见 `assets/registry/ledger_split_baseline.json.bak_palette_lighten_matte`。⑥ 🔴 遗留待裁定：组件库为**原地改写**、未升版本号（v006/v007/v008/v002/v003 路径不变而内容已变）；若需按版本追溯须另开事务把五库升版并同步 catalog / `FloorPlanGenerator` / 运行时路径。⑦ ⚠️ corridor / db 两库已校正但**未进导出链**，制作状态仍为「Blender源已完成」。</t>
+        </is>
+      </c>
+      <c r="G24" s="119" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" s="60">
+      <c r="A25" s="118" t="inlineStr">
+        <is>
+          <t>v0.1.19</t>
+        </is>
+      </c>
+      <c r="B25" s="118" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C25" s="119" t="inlineStr">
+        <is>
+          <t>条目修正</t>
+        </is>
+      </c>
+      <c r="D25" s="119" t="inlineStr">
+        <is>
+          <t>关卡场景 / 远征关卡01</t>
+        </is>
+      </c>
+      <c r="E25" s="119" t="inlineStr">
+        <is>
+          <t>远征关卡01 三套已接入房型组件库补登**逐房间运行时装配清单**（`04-battle-room-runtime-assembler`「房间输出」要求）—— 四处实例 `room_03` / `room_05` / `room_09` / `boss` 各产出 `assets/art/environments/tower_zones/expedition/runtime/room_instances/f00_&lt;room&gt;/room_runtime_manifest.json` 与 `acceptance/`（房型重放验收日志 + 运行时材质探针日志）。① **`assembly_route` 全为 `room_type_layout_replay`**（分支 A0）：具体房间白模与房型默认尺寸、门槽与必需设施一致，且无 `instance_overrides` ⇒ 直接重放房型 `component_instances.json`，Godot 侧不做第二套手工摆位。② 清单逐房登记：房间编号/种类/白模源/组件源、逐组件稳定 PackedScene 与碰撞责任、实例总数与角色分解（106 / 242 / 106 / 210）、房间局部包络（Godot 局部 XZ/垂直 Y 契约）、门洞契约（2.2×2.5、门槛底 0.3、门楣底 2.8）与门位、组件库 `source_blend` SHA-256、验收日志与关卡调用登记。③ **门位口径**：清单记的是**设计源兜底样例**的相邻面（跨语言南北红线 `+y` → 南、`−y` → 北），实跑门位由 `FloorPlanGenerator` 按种子现算，运行时门扇节点数以验收日志 runtime 行为准（四房均 2）。④ 组件库级 `runtime_manifest.json` 由 `scripts/generate_expedition_room_type_prefabs.py` 加两字段 `room_runtime_manifests` / `assembly_route_scope=per_room_instance` 指向逐房间清单（生成器已实测幂等：`shell_component_catalog.json` 逐字节不变、`records` 98 条不变）。⑤ 运行时取证：九个取样件逐表面读运行时材质并渲染成对照图 `outputs/room_type_runtime_probe_after_import.png` —— 除按判据保留金属的 `workstation_a`（1 个 `metallic=0.860` 面）外全部可判面 `metallic ≤ 0.180`，`albedo` 全部绑定共享色盘。</t>
+        </is>
+      </c>
+      <c r="F25" s="119" t="inlineStr">
+        <is>
+          <t>① 只改 3 行的「备注 / 更新时间」，AssetID、路径、版本、SHA-256、制作状态、规格、大类逐格未动。② 未增删资产行 ⇒ 派生列与《总览》公式区间不变（仍 `$247`）；《3D-场景通用》等摘要锁死表未动。③ 本事务只新增**运行时清单 JSON 与验收证据**（`runtime/room_instances/**`），不含新资产、不含新 AssetID ⇒ 无损基线**无需补录**（行内容未变则行指纹不变）。④ ⚠️ 清单记的门位是设计源兜底样例的相邻面；实跑门位按种子现算（设计页 §4.4：Boss 房哪两面墙取决于种子）。⑤ 🔴 遗留待裁定（承 v0.1.18）：组件库为原地改写、未升版本号；corridor / db 两库已校正但未进导出链，制作状态仍为「Blender源已完成」。</t>
+        </is>
+      </c>
+      <c r="G25" s="119" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" s="60">
+      <c r="A26" s="118" t="inlineStr">
+        <is>
+          <t>v0.1.20</t>
+        </is>
+      </c>
+      <c r="B26" s="118" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C26" s="119" t="inlineStr">
+        <is>
+          <t>条目修正</t>
+        </is>
+      </c>
+      <c r="D26" s="119" t="inlineStr">
+        <is>
+          <t>关卡场景 / 远征关卡01</t>
+        </is>
+      </c>
+      <c r="E26" s="119" t="inlineStr">
+        <is>
+          <t>**门位口径修正**：远征关卡01 三行房型资产（办公室 / 通道桥 / Boss竞技场）「备注」里的门位描述，由**静态兜底样例推导**改为**运行时探针实测**。缘由：房型源按规范不冻结门位，实跑版图由 `FloorPlanGenerator` 按种子**整张重算**（设计页 §4.4）——同一房型在兜底样例 `floor_00.json` 与实跑版图里**中心坐标与相邻面都不同**（如 Boss 房兜底 `(95,−45)`、实跑 `(−20,−85)`），故静态推导的相邻面必然失效。本次以探针 `_scratch/palette_shift/probe_runtime_doors.gd`（`RUN_SEED=77001199`）实测为准：`room_03` 北接 room_02 / 南接 room_04；`room_05` 东接 room_04 / 西接 room_06；`room_09` 南接 room_08 / 北接 room_10；`boss` 西接 room_10 / 东接撤离屋。① 四处实例的 `room_runtime_manifest.json` 的 `assembly.door_apertures` 同步改为实测值（含 `aperture_center_local_m` / `aperture_center_world_m` / `door_probe.run_seed`），静态推导保留在 `door_apertures_static_reference` 只作对照。② 每房 `acceptance/` 增加探针日志 `runtime_doors.txt`。③ 方向口径不变：跨语言红线 `+y` → 南、`−y` → 北。</t>
+        </is>
+      </c>
+      <c r="F26" s="119" t="inlineStr">
+        <is>
+          <t>① 只改 3 行的「备注 / 更新时间」，AssetID、路径、版本、SHA-256、制作状态、规格、大类逐格未动。② 未增删资产行 ⇒ 派生列与《总览》公式区间不变；摘要锁死表未动。③ 本事务只修正**备注文本 + 运行时清单 JSON 的门位字段**，不含新资产、不含新 AssetID，但**行内容已变** ⇒ 无损基线（`ledger_split_baseline.json`）须补录 3 行新指纹。④ 遗留（承 v0.1.19）：组件库为原地改写、未升版本号；corridor / db 两库已校正但未进导出链。</t>
+        </is>
+      </c>
+      <c r="G26" s="119" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" s="60">
+      <c r="A27" s="118" t="inlineStr">
+        <is>
+          <t>v0.1.21</t>
+        </is>
+      </c>
+      <c r="B27" s="118" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C27" s="119" t="inlineStr">
+        <is>
+          <t>资产升版</t>
+        </is>
+      </c>
+      <c r="D27" s="119" t="inlineStr">
+        <is>
+          <t>关卡场景 / 远征关卡01</t>
+        </is>
+      </c>
+      <c r="E27" s="119" t="inlineStr">
+        <is>
+          <t>**三套房型组件库按版本规范正式升版**：远征关卡01 已接入的三套组件库由「原地改写、版本号不变」改为**另立新版本** —— office `v006` → `v009`、bridge `v007` → `v010`、boss `v008` → `v011`（依据 `02-battle-room-component-decomposer` 第 184 行「生成组件源版本，不覆盖房间种类源，也不覆盖历史组件源」）。做法：新目录承载提亮 + 亚光后的**当前源**（目录改名 + 母版改名 `&lt;库&gt;_v0NN.blend`），旧目录用 `git checkout HEAD --` 恢复为**提亮前的历史源**（只读留档）。新旧母版 SHA-256 互不相同即证两版内容确有差异：office `f5e666ee…` → `926a881d…`、bridge `9f6a23ab…` → `f219156e…`、boss `9ffd58e5…` → `b05b0151…`。同步改写全部引用：① 各库 `component_catalog.json` 的 `version` / `component_library` / 每包 `component_library_blend`；② `component_instances.json` 的 `library`（**改** ＝ 本库自身版本；`source_library` = v004 / v005 / v001 与 `source_blend_sha256` 指向**整屋／房间种类源**母版，**未动**）；③ 组件库级 `runtime_manifest.json` 与四处实例的 `room_runtime_manifest.json`；④ 98 个 PackedScene 根节点 `metadata/asset_version` 与 `source_blend`；⑤ `FloorPlanGenerator.ROOM_TYPE_LAYOUT_SOURCES`、`export_expedition_room_type_components.py` / `generate_expedition_room_type_prefabs.py` 的 `LIBRARIES`、`build_room_runtime_manifests.py` 的 `ROOM_TYPE_BINDING`、重放验收探针的 `expected_version`。**运行时路径一律不带版本号**（`04-battle-room-runtime-assembler` 第 155 行：替换即覆盖同路径同名文件），版本只写在 `source/`、`asset_manifest.json`、PackedScene metadata、布局快照与本账本。升版后重导出 98 个稳定 GLB、重建 98 个 PackedScene 与 `shell_component_catalog.json`（110 条，全 v009/v010/v011），Godot 重导（98/98 `.scn` 与 GLB 字节同步）后房型重放验收 2051 项断言全通过（`room_03` / `room_09` 各 106、`room_05` 242、`boss` 210 实例，unresolved 全 0，门位净空 0 覆盖）；材质探针按 `AGENTS.md` 第 10 行以**真实渲染器**（非 headless）复跑九件取样，结构面 `metallic=0.030`、`albedo_texture` 全部指向共享色盘。</t>
+        </is>
+      </c>
+      <c r="F27" s="119" t="inlineStr">
+        <is>
+          <t>① 只改 3 行房型资产的「规格 / 复用范围 / 源码依据 / 关键词 / 备注 / 更新时间」，AssetID、文件路径、**版本列（M，仍 v001 / v002）**、SHA-256、制作状态、大类逐格未动 —— 房型**概念源** blend全程未改写，7 个房型源 SHA-256 与登记逐位一致。② 未增删资产行 ⇒ 派生列与《总览》公式区间不变（仍 `$247`）；《3D-场景通用》等摘要锁死表未动（该页 `v006` 命中均为 battle 塔楼库 `tower_zones/battle/components/common_components/v006`，与本事务无关）。③ 旧版本目录 v006 / v007 / v008 **不删除**，由 Git 恢复为提亮前历史源，路径与内容保留可追溯。④ 无损基线（`ledger_split_baseline.json`）按既有「从当前分账本重建」口径做最小补录：更新这 3 行行指纹 + 重算列摘要与分类计数，其余行逐位不变；补录前基线备份见 `assets/registry/ledger_split_baseline.json.bak_library_bump`。⑤ 本事务**结清 v0.1.18 / v0.1.19 / v0.1.20 连续三轮遗留的「组件库原地改写、未升版本号」**。⑥ 仍遗留：`l_corridor`（v002）/ `db_room`（v003）两套组件库已做提亮 + 亚光校正但**未进导出链**，制作状态仍「Blender源已完成」，其规范化归并与升版随请求线 A 一并进行。</t>
+        </is>
+      </c>
+      <c r="G27" s="119" t="inlineStr">
         <is>
           <t>摩斯拉</t>
         </is>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3D-场景通用" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3D-设施" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3D-其他" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="域变更日志" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$240</definedName>
@@ -31686,7 +31686,7 @@
       </c>
       <c r="K246" s="90" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="L246" s="90" t="inlineStr">
@@ -31696,22 +31696,22 @@
       </c>
       <c r="M246" s="90" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v014</t>
         </is>
       </c>
       <c r="N246" s="90" t="inlineStr">
         <is>
-          <t>40×30m 包围盒（8×6 个 5m 槽）；db_01 轮廓 = 主体 40×25 + 南侧中段外凸 10×5，占用 1050 m²（包围盒 1200 m²）；28 樘墙件 + 42 格地砖共 70 个集合实例，全部 Library Link 自 office_room/v001（本文件自持墙/砖网格 0）；37 个数据库机房专属组件包 / 49 输出网格 / 127164 面；门洞 2.2×2.5m（净空底 0.30m、门楣 2.80m）；16 个可开槽；QA PASS（26 项断言）</t>
+          <t>40×30m；房型组件库 v014：35 个唯一组件 / 86 个实例；运行时 3 间房均按 component_instances.json 重放，42 块主层地砖换通用 C01/C02，44 个普通房型组件，unresolved=0，门 2 扇；db_02 仍待另行制作</t>
         </is>
       </c>
       <c r="O246" s="90" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/expedition/source/room_types/db_room/v001/数据库房间种类_数据机房_40x30m_v001.blend</t>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/db_room/v002/</t>
         </is>
       </c>
       <c r="P246" s="90" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/expedition/source/room_types/db_room/v001/build_db_room_v001.py；白盒 source/art/whitebox/tower_zones/expedition_01/v001/data/room_templates/db_70x50.json；参考图 docs/v0.1/design/refs/expedition01/数据库房间01.jpg</t>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/db_room/v002/；assets/art/environments/tower_zones/expedition/source/common_components/v014/component_catalog.json；component_instances.json；运行时 PackedScene 注册表 shell_component_catalog.json</t>
         </is>
       </c>
       <c r="Q246" s="63" t="inlineStr">
@@ -31729,7 +31729,7 @@
       </c>
       <c r="T246" s="90" t="inlineStr">
         <is>
-          <t>153eaa883b21b4489a3b5bb0b2d67a38419186ee0e7d1ff603bd3ad8f3c291a3</t>
+          <t>ba0d29bcd4e89d901fa3102f66fa449ea6028bcb860c5be170bdc50fd31303c6</t>
         </is>
       </c>
       <c r="U246" s="63" t="inlineStr">
@@ -31754,7 +31754,7 @@
       </c>
       <c r="Y246" s="63" t="inlineStr">
         <is>
-          <t>服务远征关卡01 的 room_02 / room_06 / room_10（三处实例共用同一房型源）。本轮按参考图做 **db_01** 布局（主体 40×25 + 南侧中段外凸 10×5，面积 1050 m²）；同模板的另一内部布局 db_02（双缺角 15×10 / 15×5，面积 975 m²）按 room_type_manifest.json 显式标注为待另轮制作。与 office / bridge 两行的差别：墙件（28 樘）与地砖（42 格）**不重新制作**，改为 Library Link 引用 office_room/v001 的已验收组件包（本文件自持墙/砖网格 0、不 Append、不改组件几何/材质/根原点）；其余 37 个组件包（地面标识 / 格栅 / 设备坑抬升平台 / 西侧机柜列 7 台 / 中部机柜组 / 东墙 L 形工作台 / 西墙检修台 / 壁挂大屏组 / 红黄工具车 / 中央作业台 / 货箱堆场 / 重型货架 / 零件柜 / 电缆盘与线圈 / 花箱绿植 / 设备机架 / 墙面灯柱 / 顶部桥架管道风管灯具等）为数据库机房专属新制。未导 GLB、未接 Godot。2026-09-27（业主裁定，本轮同批）：① 组件库 v003（38 个 blend）UV 配色保色相提亮 3 个挡位，深色面（HSV 明度 &lt;40%）占比 56.1% → 30.6%（母版 254328 面中移动 123356 面）。② 材质主面判据：改 148 槽 / 409512 面，金属面积占比 100.0% → 0.0%（本库原为全金属）。③ ⚠️ 本库尚未进入导出链 ⇒ 未导 GLB、未接 Godot，制作状态保持「Blender源已完成」。房型概念源 blend 未动，SHA-256 不变。</t>
+          <t>2026-09-27：数据库房 v014 已完成 35 个独立 GLB/PackedScene 导出并接入 Godot。room_02 / room_06 / room_10 均通过组件重放验收（86 实例、42 通用棋盘砖、44 普通组件、unresolved=0、2 扇门）；room_06 当前暂重放 db_01 默认布局，db_02 变体仍待另行制作。</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -31202,7 +31202,7 @@
       </c>
       <c r="K242" s="90" t="inlineStr">
         <is>
-          <t>Blender源已完成</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="L242" s="90" t="inlineStr">
@@ -31212,22 +31212,22 @@
       </c>
       <c r="M242" s="90" t="inlineStr">
         <is>
-          <t>v003</t>
+          <t>v012</t>
         </is>
       </c>
       <c r="N242" s="90" t="inlineStr">
         <is>
-          <t>45×40×11.9m；横臂 9×3 + 竖臂 3×5 个 5m 槽；走廊净宽 15m（三砖）；42 块地砖 / 121 个独立组件包 / 4 个门位</t>
+          <t>45×40m；组件库 v012：27 个唯一组件 / 121 个 l_turn 实例；room_01 / room_08 正式重放，42 块通用 C01/C02 地砖、49 个普通组件、30 个结构墙、unresolved=0、2 扇门；u_turn 差异布局待制作</t>
         </is>
       </c>
       <c r="O242" s="90" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/expedition/source/room_types/l_corridor/v003/L型走廊种类_数据连廊_45x40m_v003.blend</t>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/l_corridor/v003/</t>
         </is>
       </c>
       <c r="P242" s="90" t="inlineStr">
         <is>
-          <t>assets/art/environments/tower_zones/expedition/source/room_types/l_corridor/v003/widen_l_corridor_v003.py</t>
+          <t>assets/art/environments/tower_zones/expedition/source/room_types/l_corridor/v003/；assets/art/environments/tower_zones/expedition/source/common_components/v012/component_catalog.json；component_instances.json；运行时 PackedScene 注册表 shell_component_catalog.json</t>
         </is>
       </c>
       <c r="Q242" s="63" t="inlineStr">
@@ -31245,7 +31245,7 @@
       </c>
       <c r="T242" s="90" t="inlineStr">
         <is>
-          <t>9c323876f7165f656e016049135652a96c83ed0adb45f4f28c49fc50cfb5adae</t>
+          <t>1ec561cf6c9668c580e662a41ad947df8e94e017ce451b8e2c70857ae6912b33</t>
         </is>
       </c>
       <c r="U242" s="63" t="inlineStr">
@@ -31270,7 +31270,7 @@
       </c>
       <c r="Y242" s="63" t="inlineStr">
         <is>
-          <t>由 battle 区块房间种类源迁入（原 ENV-BATTLE-L-CORRIDOR-TYPE，原路径 tower_zones/battle/source/room_types/l_corridor/；业主 2026-09-24 裁决归属远征关卡01，battle 侧不留副本）。远征01 版图与白盒目录均无走廊白模，尺寸与门位按参考图推定。v001/v002 为 10m 宽走廊（外包络 45×35m / 28 块地砖 / 88、111 个组件包），v003 拓宽为 15m（45×40m / 42 块地砖 / 121 个组件包 / 4 个门位：西1 北2 南1）。随迁统一内部结构：component_packages_vNNN→component_packages、facility→facilities、散放渲染图入 renders/。共享件引用由 ENV-BATTLE-COMMON-* 更正为 shared 库现有 ENV-SHARED-GENERIC-*。未导 GLB、未接 Godot。2026-09-27（业主裁定，本轮同批）：① 组件库 v002（122 个 blend）UV 配色保色相提亮 3 个挡位，深色面（HSV 明度 &lt;40%）占比 13.9% → 4.8%（母版 96774 面中移动 90498 面）。② 材质主面判据：改 268 槽 / 2696 面，金属面积占比 12.0% → 9.7%；保留金属小件为 `前墙` / `侧墙`。③ ⚠️ 本库尚未进入导出链（`export_expedition_room_type_components.py` 的 LIBRARIES 只含 office/bridge/boss）⇒ 未导 GLB、未接 Godot，制作状态保持「Blender源已完成」。房型概念源 blend 未动，SHA-256 不变。</t>
+          <t>2026-09-27：走廊 v012 已完成 27 个独立 GLB/PackedScene 导出并接入 Godot。room_01 / room_08 通过组件重放验收（121 实例、42 通用棋盘砖、49 普通组件、30 结构墙、unresolved=0、2 扇门）；room_04 的 u_turn 只复用组件库，差异实例布局仍待制作。</t>
         </is>
       </c>
     </row>
@@ -43150,12 +43150,12 @@
       </c>
       <c r="C148" s="119" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="D148" s="119" t="inlineStr">
         <is>
-          <t>未制作</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E148" s="118" t="inlineStr">
@@ -43205,17 +43205,17 @@
       </c>
       <c r="N148" s="119" t="inlineStr">
         <is>
-          <t>房间种类源已完成；QA PASS</t>
+          <t>正式美术已接入</t>
         </is>
       </c>
       <c r="O148" s="118" t="inlineStr">
         <is>
-          <t>v003</t>
+          <t>v012</t>
         </is>
       </c>
       <c r="P148" s="119" t="inlineStr">
         <is>
-          <t>由 battle 区块迁入（原 l_corridor_room_type_v003.blend）；无白模，尺寸按参考图推定；v001/v002（10m 宽）保留在同目录历史版本；未导 GLB、未接 Godot。</t>
+          <t>27 个唯一组件 / 121 条 l_turn 实例；room_01、room_08 已接入；u_turn 差异布局待制作</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3D-场景通用" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3D-设施" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3D-其他" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="域变更日志" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账本说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资产主表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-场景通用" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-设施" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D-其他" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$240</definedName>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="K118" s="103" t="inlineStr">
         <is>
-          <t>已优化并正式接入</t>
+          <t>弃用</t>
         </is>
       </c>
       <c r="L118" s="102" t="inlineStr">
@@ -15903,7 +15903,7 @@
         </is>
       </c>
       <c r="V118" s="100" t="n">
-        <v>46277</v>
+        <v>46294</v>
       </c>
       <c r="W118" s="72" t="inlineStr">
         <is>
@@ -15917,7 +15917,8 @@
       </c>
       <c r="Y118" s="99" t="inlineStr">
         <is>
-          <t>2026-09-13：随标准层高升级，保留5米平台起点与东门平面坐标，重制为20级、0.35米级高并以连续坡面碰撞接至12米门槛。T列为v002运行包装SHA-256。</t>
+          <t>2026-09-13：随标准层高升级，保留5米平台起点与东门平面坐标，重制为20级、0.35米级高并以连续坡面碰撞接至12米门槛。T列为v002运行包装SHA-256。
+2026-09-29：99F东侧旧斜梯从运行时布局移除；历史源与Prefab保留；由PRP-BASE99-TELESCOPIC-LADDER-3D替换。</t>
         </is>
       </c>
     </row>
@@ -45367,7 +45368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.808590000000001" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="68" min="1" max="1"/>
@@ -45394,7 +45395,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customFormat="1" customHeight="1" s="69">
       <c r="A5" s="75" t="inlineStr">
         <is>
@@ -46280,6 +46280,43 @@
       <c r="G28" s="62" t="inlineStr">
         <is>
           <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="61" t="inlineStr">
+        <is>
+          <t>v0.1.23</t>
+        </is>
+      </c>
+      <c r="B29" s="61" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C29" s="62" t="inlineStr">
+        <is>
+          <t>东侧旧斜梯退役</t>
+        </is>
+      </c>
+      <c r="D29" s="62" t="inlineStr">
+        <is>
+          <t>场景 / 基地结构</t>
+        </is>
+      </c>
+      <c r="E29" s="62" t="inlineStr">
+        <is>
+          <t>BPK-BASE99-EAST-UPPER-TRANSITION-STAIR从运行时移除并标记弃用，保留历史源。</t>
+        </is>
+      </c>
+      <c r="F29" s="62" t="inlineStr">
+        <is>
+          <t>更新资产主表与运行时事实源；既有历史资源保留。</t>
+        </is>
+      </c>
+      <c r="G29" s="62" t="inlineStr">
+        <is>
+          <t>Codex</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域变更日志" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$X$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资产主表'!$A$5:$Y$248</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1466,22 +1466,22 @@
     </row>
     <row r="6" ht="42" customFormat="1" customHeight="1" s="69">
       <c r="A6" s="74">
-        <f>=COUNTA(资产主表!$A$6:$A$247)</f>
+        <f>=COUNTA(资产主表!$A$6:$A$248)</f>
         <v/>
       </c>
       <c r="B6" s="72" t="inlineStr"/>
       <c r="C6" s="74">
-        <f>=COUNTIF(资产主表!$K$6:$K$247,"已完成")+COUNTIF(资产主表!$K$6:$K$247,"原型已接入")+COUNTIF(资产主表!$K$6:$K$247,"正式美术已接入")+COUNTIF(资产主表!$K$6:$K$247,"已优化并正式接入")+COUNTIF(资产主表!$K$6:$K$247,"Blender源已完成")+COUNTIF(资产主表!$K$6:$K$247,"已导入；优化完成")+COUNTIF(资产主表!$K$6:$K$247,"白模源已完成；QA PASS")</f>
+        <f>=COUNTIF(资产主表!$K$6:$K$248,"已完成")+COUNTIF(资产主表!$K$6:$K$248,"原型已接入")+COUNTIF(资产主表!$K$6:$K$248,"正式美术已接入")+COUNTIF(资产主表!$K$6:$K$248,"已优化并正式接入")+COUNTIF(资产主表!$K$6:$K$248,"Blender源已完成")+COUNTIF(资产主表!$K$6:$K$248,"已导入；优化完成")+COUNTIF(资产主表!$K$6:$K$248,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="72" t="inlineStr"/>
       <c r="E6" s="74">
-        <f>=COUNTIF(资产主表!$K$6:$K$247,"待制作")+COUNTIF(资产主表!$K$6:$K$247,"程序占位")</f>
+        <f>=COUNTIF(资产主表!$K$6:$K$248,"待制作")+COUNTIF(资产主表!$K$6:$K$248,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="72" t="inlineStr"/>
       <c r="G6" s="74">
-        <f>=COUNTIF(资产主表!$S$6:$S$247,"重复")</f>
+        <f>=COUNTIF(资产主表!$S$6:$S$248,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="72" t="inlineStr"/>
@@ -1550,11 +1550,11 @@
         </is>
       </c>
       <c r="B10" s="79">
-        <f>=COUNTIF(资产主表!$C$6:$C$247,A10)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$248,A10)</f>
         <v/>
       </c>
       <c r="C10" s="79">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$247=A10)*((资产主表!$K$6:$K$247="已完成")+(资产主表!$K$6:$K$247="原型已接入")+(资产主表!$K$6:$K$247="正式美术已接入")+(资产主表!$K$6:$K$247="已优化并正式接入")+(资产主表!$K$6:$K$247="Blender源已完成")+(资产主表!$K$6:$K$247="已导入；优化完成")+(资产主表!$K$6:$K$247="白模源已完成；QA PASS")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$248=A10)*((资产主表!$K$6:$K$248="已完成")+(资产主表!$K$6:$K$248="原型已接入")+(资产主表!$K$6:$K$248="正式美术已接入")+(资产主表!$K$6:$K$248="已优化并正式接入")+(资产主表!$K$6:$K$248="Blender源已完成")+(资产主表!$K$6:$K$248="已导入；优化完成")+(资产主表!$K$6:$K$248="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="79" t="inlineStr"/>
@@ -1572,11 +1572,11 @@
         </is>
       </c>
       <c r="B11" s="79">
-        <f>=COUNTIF(资产主表!$C$6:$C$247,A11)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$248,A11)</f>
         <v/>
       </c>
       <c r="C11" s="79">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$247=A11)*((资产主表!$K$6:$K$247="已完成")+(资产主表!$K$6:$K$247="原型已接入")+(资产主表!$K$6:$K$247="正式美术已接入")+(资产主表!$K$6:$K$247="已优化并正式接入")+(资产主表!$K$6:$K$247="Blender源已完成")+(资产主表!$K$6:$K$247="已导入；优化完成")+(资产主表!$K$6:$K$247="白模源已完成；QA PASS")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$248=A11)*((资产主表!$K$6:$K$248="已完成")+(资产主表!$K$6:$K$248="原型已接入")+(资产主表!$K$6:$K$248="正式美术已接入")+(资产主表!$K$6:$K$248="已优化并正式接入")+(资产主表!$K$6:$K$248="Blender源已完成")+(资产主表!$K$6:$K$248="已导入；优化完成")+(资产主表!$K$6:$K$248="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="79" t="inlineStr"/>
@@ -1594,11 +1594,11 @@
         </is>
       </c>
       <c r="B12" s="79">
-        <f>=COUNTIF(资产主表!$C$6:$C$247,A12)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$248,A12)</f>
         <v/>
       </c>
       <c r="C12" s="79">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$247=A12)*((资产主表!$K$6:$K$247="已完成")+(资产主表!$K$6:$K$247="原型已接入")+(资产主表!$K$6:$K$247="正式美术已接入")+(资产主表!$K$6:$K$247="已优化并正式接入")+(资产主表!$K$6:$K$247="Blender源已完成")+(资产主表!$K$6:$K$247="已导入；优化完成")+(资产主表!$K$6:$K$247="白模源已完成；QA PASS")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$248=A12)*((资产主表!$K$6:$K$248="已完成")+(资产主表!$K$6:$K$248="原型已接入")+(资产主表!$K$6:$K$248="正式美术已接入")+(资产主表!$K$6:$K$248="已优化并正式接入")+(资产主表!$K$6:$K$248="Blender源已完成")+(资产主表!$K$6:$K$248="已导入；优化完成")+(资产主表!$K$6:$K$248="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D12" s="79" t="inlineStr"/>
@@ -1616,11 +1616,11 @@
         </is>
       </c>
       <c r="B13" s="75">
-        <f>=COUNTIF(资产主表!$C$6:$C$247,A13)</f>
+        <f>=COUNTIF(资产主表!$C$6:$C$248,A13)</f>
         <v/>
       </c>
       <c r="C13" s="75">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$247=A13)*((资产主表!$K$6:$K$247="已完成")+(资产主表!$K$6:$K$247="原型已接入")+(资产主表!$K$6:$K$247="正式美术已接入")+(资产主表!$K$6:$K$247="已优化并正式接入")+(资产主表!$K$6:$K$247="Blender源已完成")+(资产主表!$K$6:$K$247="已导入；优化完成")+(资产主表!$K$6:$K$247="白模源已完成；QA PASS")))</f>
+        <f>=SUMPRODUCT((资产主表!$C$6:$C$248=A13)*((资产主表!$K$6:$K$248="已完成")+(资产主表!$K$6:$K$248="原型已接入")+(资产主表!$K$6:$K$248="正式美术已接入")+(资产主表!$K$6:$K$248="已优化并正式接入")+(资产主表!$K$6:$K$248="Blender源已完成")+(资产主表!$K$6:$K$248="已导入；优化完成")+(资产主表!$K$6:$K$248="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D13" s="75" t="inlineStr"/>
@@ -2184,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y247"/>
+  <dimension ref="A1:Y248"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.808590000000001" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="25" customWidth="1" style="68" min="1" max="1"/>
@@ -2460,7 +2460,7 @@
         <v/>
       </c>
       <c r="S6" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="80" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
         <v/>
       </c>
       <c r="S7" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="80" t="inlineStr"/>
@@ -2674,7 +2674,7 @@
         <v/>
       </c>
       <c r="S8" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="80" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
         <v/>
       </c>
       <c r="S9" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="80" t="inlineStr"/>
@@ -2888,7 +2888,7 @@
         <v/>
       </c>
       <c r="S10" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="80" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
         <v/>
       </c>
       <c r="S11" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="80" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
         <v/>
       </c>
       <c r="S12" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="80" t="inlineStr"/>
@@ -3209,7 +3209,7 @@
         <v/>
       </c>
       <c r="S13" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="80" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
         <v/>
       </c>
       <c r="S14" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="80" t="inlineStr"/>
@@ -3423,7 +3423,7 @@
         <v/>
       </c>
       <c r="S15" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="80" t="inlineStr"/>
@@ -3530,7 +3530,7 @@
         <v/>
       </c>
       <c r="S16" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="80" t="inlineStr"/>
@@ -3637,7 +3637,7 @@
         <v/>
       </c>
       <c r="S17" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="80" t="inlineStr"/>
@@ -3744,7 +3744,7 @@
         <v/>
       </c>
       <c r="S18" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="80" t="inlineStr"/>
@@ -3851,7 +3851,7 @@
         <v/>
       </c>
       <c r="S19" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="80" t="inlineStr"/>
@@ -3958,7 +3958,7 @@
         <v/>
       </c>
       <c r="S20" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="80" t="inlineStr"/>
@@ -4065,7 +4065,7 @@
         <v/>
       </c>
       <c r="S21" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="80" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
         <v/>
       </c>
       <c r="S22" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="80" t="inlineStr"/>
@@ -4279,7 +4279,7 @@
         <v/>
       </c>
       <c r="S23" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="80" t="inlineStr"/>
@@ -4386,7 +4386,7 @@
         <v/>
       </c>
       <c r="S24" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="80" t="inlineStr"/>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="S25" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="80" t="inlineStr"/>
@@ -4600,7 +4600,7 @@
         <v/>
       </c>
       <c r="S26" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="80" t="inlineStr"/>
@@ -4707,7 +4707,7 @@
         <v/>
       </c>
       <c r="S27" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="80" t="inlineStr"/>
@@ -4814,7 +4814,7 @@
         <v/>
       </c>
       <c r="S28" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="80" t="inlineStr"/>
@@ -4921,7 +4921,7 @@
         <v/>
       </c>
       <c r="S29" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="80" t="inlineStr"/>
@@ -5028,7 +5028,7 @@
         <v/>
       </c>
       <c r="S30" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="80" t="inlineStr"/>
@@ -5135,7 +5135,7 @@
         <v/>
       </c>
       <c r="S31" s="80">
-        <f>IF(COUNTIF($R$6:$R$247,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="80" t="inlineStr"/>
@@ -5254,7 +5254,7 @@
         <v/>
       </c>
       <c r="S32" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="96" t="inlineStr">
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="S33" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="99" t="inlineStr">
@@ -5500,7 +5500,7 @@
         <v/>
       </c>
       <c r="S34" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="99" t="inlineStr">
@@ -5623,7 +5623,7 @@
         <v/>
       </c>
       <c r="S35" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="99" t="inlineStr">
@@ -5746,7 +5746,7 @@
         <v/>
       </c>
       <c r="S36" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="96" t="inlineStr">
@@ -5870,7 +5870,7 @@
         <v/>
       </c>
       <c r="S37" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="99" t="inlineStr">
@@ -5993,7 +5993,7 @@
         <v/>
       </c>
       <c r="S38" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="99" t="inlineStr">
@@ -6112,7 +6112,7 @@
         <v/>
       </c>
       <c r="S39" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="96" t="inlineStr">
@@ -6235,7 +6235,7 @@
         <v/>
       </c>
       <c r="S40" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="99" t="inlineStr">
@@ -6358,7 +6358,7 @@
         <v/>
       </c>
       <c r="S41" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="99" t="inlineStr">
@@ -6481,7 +6481,7 @@
         <v/>
       </c>
       <c r="S42" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="99" t="inlineStr">
@@ -6604,7 +6604,7 @@
         <v/>
       </c>
       <c r="S43" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="99" t="inlineStr">
@@ -6727,7 +6727,7 @@
         <v/>
       </c>
       <c r="S44" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="96" t="inlineStr">
@@ -6851,7 +6851,7 @@
         <v/>
       </c>
       <c r="S45" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="99" t="inlineStr">
@@ -6974,7 +6974,7 @@
         <v/>
       </c>
       <c r="S46" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="99" t="inlineStr">
@@ -7097,7 +7097,7 @@
         <v/>
       </c>
       <c r="S47" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="99" t="inlineStr">
@@ -7220,7 +7220,7 @@
         <v/>
       </c>
       <c r="S48" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R48)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R48)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T48" s="99" t="inlineStr">
@@ -7340,7 +7340,7 @@
         <v/>
       </c>
       <c r="S49" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R49)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R49)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T49" s="99" t="inlineStr">
@@ -7463,7 +7463,7 @@
         <v/>
       </c>
       <c r="S50" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R50)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R50)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T50" s="99" t="inlineStr">
@@ -7587,7 +7587,7 @@
         <v/>
       </c>
       <c r="S51" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R51)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R51)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T51" s="99" t="inlineStr">
@@ -7710,7 +7710,7 @@
         <v/>
       </c>
       <c r="S52" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R52)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R52)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T52" s="96" t="inlineStr">
@@ -7834,7 +7834,7 @@
         <v/>
       </c>
       <c r="S53" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R53)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R53)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T53" s="96" t="inlineStr">
@@ -7957,7 +7957,7 @@
         <v/>
       </c>
       <c r="S54" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R54)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R54)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T54" s="96" t="inlineStr">
@@ -8086,7 +8086,7 @@
         <v/>
       </c>
       <c r="S55" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R55)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R55)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T55" s="96" t="inlineStr">
@@ -8213,7 +8213,7 @@
         <v/>
       </c>
       <c r="S56" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R56)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R56)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T56" s="96" t="inlineStr">
@@ -8336,7 +8336,7 @@
         <v/>
       </c>
       <c r="S57" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R57)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R57)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T57" s="96" t="inlineStr">
@@ -8461,7 +8461,7 @@
         <v/>
       </c>
       <c r="S58" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R58)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R58)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T58" s="96" t="inlineStr">
@@ -8584,7 +8584,7 @@
         <v/>
       </c>
       <c r="S59" s="97">
-        <f>IF(COUNTIF($R$6:$R$247,R59)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R59)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T59" s="96" t="inlineStr">
@@ -8703,7 +8703,7 @@
         <v/>
       </c>
       <c r="S60" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R60)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R60)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T60" s="99" t="inlineStr">
@@ -8823,7 +8823,7 @@
         <v/>
       </c>
       <c r="S61" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R61)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R61)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T61" s="99" t="inlineStr">
@@ -8943,7 +8943,7 @@
         <v/>
       </c>
       <c r="S62" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R62)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R62)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T62" s="99" t="inlineStr">
@@ -9063,7 +9063,7 @@
         <v/>
       </c>
       <c r="S63" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R63)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R63)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T63" s="99" t="inlineStr"/>
@@ -9183,7 +9183,7 @@
         <v/>
       </c>
       <c r="S64" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R64)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R64)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T64" s="99" t="inlineStr">
@@ -9308,7 +9308,7 @@
         <v/>
       </c>
       <c r="S65" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R65)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R65)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T65" s="99" t="inlineStr">
@@ -9433,7 +9433,7 @@
         <v/>
       </c>
       <c r="S66" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R66)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R66)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T66" s="99" t="inlineStr">
@@ -9558,7 +9558,7 @@
         <v/>
       </c>
       <c r="S67" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R67)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R67)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T67" s="99" t="inlineStr">
@@ -9683,7 +9683,7 @@
         <v/>
       </c>
       <c r="S68" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R68)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R68)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T68" s="99" t="inlineStr">
@@ -9814,7 +9814,7 @@
         <v/>
       </c>
       <c r="S69" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R69)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R69)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T69" s="99" t="inlineStr">
@@ -9940,7 +9940,7 @@
         <v/>
       </c>
       <c r="S70" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R70)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R70)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T70" s="99" t="inlineStr">
@@ -10064,7 +10064,7 @@
         <v/>
       </c>
       <c r="S71" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R71)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R71)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T71" s="99" t="inlineStr">
@@ -10188,7 +10188,7 @@
         <v/>
       </c>
       <c r="S72" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R72)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R72)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T72" s="99" t="inlineStr">
@@ -10312,7 +10312,7 @@
         <v/>
       </c>
       <c r="S73" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R73)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R73)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T73" s="99" t="inlineStr">
@@ -10436,7 +10436,7 @@
         <v/>
       </c>
       <c r="S74" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R74)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R74)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T74" s="99" t="inlineStr">
@@ -10560,7 +10560,7 @@
         <v/>
       </c>
       <c r="S75" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R75)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R75)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T75" s="99" t="inlineStr">
@@ -10684,7 +10684,7 @@
         <v/>
       </c>
       <c r="S76" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R76)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R76)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T76" s="99" t="inlineStr">
@@ -10808,7 +10808,7 @@
         <v/>
       </c>
       <c r="S77" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R77)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R77)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T77" s="99" t="inlineStr">
@@ -10932,7 +10932,7 @@
         <v/>
       </c>
       <c r="S78" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R78)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R78)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T78" s="99" t="inlineStr">
@@ -11056,7 +11056,7 @@
         <v/>
       </c>
       <c r="S79" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R79)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R79)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T79" s="99" t="inlineStr">
@@ -11180,7 +11180,7 @@
         <v/>
       </c>
       <c r="S80" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R80)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R80)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T80" s="99" t="inlineStr">
@@ -11304,7 +11304,7 @@
         <v/>
       </c>
       <c r="S81" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R81)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R81)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T81" s="99" t="inlineStr">
@@ -11428,7 +11428,7 @@
         <v/>
       </c>
       <c r="S82" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R82)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R82)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T82" s="99" t="inlineStr">
@@ -11552,7 +11552,7 @@
         <v/>
       </c>
       <c r="S83" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R83)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R83)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T83" s="99" t="inlineStr">
@@ -11676,7 +11676,7 @@
         <v/>
       </c>
       <c r="S84" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R84)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R84)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T84" s="99" t="inlineStr">
@@ -11800,7 +11800,7 @@
         <v/>
       </c>
       <c r="S85" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R85)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R85)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T85" s="99" t="inlineStr">
@@ -11924,7 +11924,7 @@
         <v/>
       </c>
       <c r="S86" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R86)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R86)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T86" s="99" t="inlineStr">
@@ -12048,7 +12048,7 @@
         <v/>
       </c>
       <c r="S87" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R87)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R87)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T87" s="99" t="inlineStr">
@@ -12172,7 +12172,7 @@
         <v/>
       </c>
       <c r="S88" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R88)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R88)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T88" s="99" t="inlineStr">
@@ -12296,7 +12296,7 @@
         <v/>
       </c>
       <c r="S89" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R89)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R89)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T89" s="99" t="inlineStr">
@@ -12420,7 +12420,7 @@
         <v/>
       </c>
       <c r="S90" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R90)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R90)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T90" s="99" t="inlineStr">
@@ -12544,7 +12544,7 @@
         <v/>
       </c>
       <c r="S91" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R91)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R91)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T91" s="99" t="inlineStr">
@@ -12668,7 +12668,7 @@
         <v/>
       </c>
       <c r="S92" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R92)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R92)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T92" s="99" t="inlineStr">
@@ -12792,7 +12792,7 @@
         <v/>
       </c>
       <c r="S93" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R93)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R93)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T93" s="99" t="inlineStr">
@@ -12916,7 +12916,7 @@
         <v/>
       </c>
       <c r="S94" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R94)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R94)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T94" s="99" t="inlineStr">
@@ -13040,7 +13040,7 @@
         <v/>
       </c>
       <c r="S95" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R95)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R95)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T95" s="99" t="inlineStr">
@@ -13164,7 +13164,7 @@
         <v/>
       </c>
       <c r="S96" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R96)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R96)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T96" s="99" t="inlineStr">
@@ -13288,7 +13288,7 @@
         <v/>
       </c>
       <c r="S97" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R97)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R97)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T97" s="99" t="inlineStr">
@@ -13412,7 +13412,7 @@
         <v/>
       </c>
       <c r="S98" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R98)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R98)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T98" s="99" t="inlineStr">
@@ -13536,7 +13536,7 @@
         <v/>
       </c>
       <c r="S99" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R99)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R99)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T99" s="99" t="inlineStr">
@@ -13660,7 +13660,7 @@
         <v/>
       </c>
       <c r="S100" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R100)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R100)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T100" s="99" t="inlineStr">
@@ -13784,7 +13784,7 @@
         <v/>
       </c>
       <c r="S101" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R101)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R101)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T101" s="99" t="inlineStr">
@@ -13908,7 +13908,7 @@
         <v/>
       </c>
       <c r="S102" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R102)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R102)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T102" s="99" t="inlineStr">
@@ -14031,7 +14031,7 @@
         <v/>
       </c>
       <c r="S103" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R103)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R103)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T103" s="99" t="inlineStr">
@@ -14156,7 +14156,7 @@
         <v/>
       </c>
       <c r="S104" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R104)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R104)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T104" s="99" t="inlineStr">
@@ -14281,7 +14281,7 @@
         <v/>
       </c>
       <c r="S105" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R105)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R105)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T105" s="99" t="inlineStr">
@@ -14406,7 +14406,7 @@
         <v/>
       </c>
       <c r="S106" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R106)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R106)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T106" s="99" t="inlineStr">
@@ -14531,7 +14531,7 @@
         <v/>
       </c>
       <c r="S107" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R107)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R107)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T107" s="99" t="inlineStr">
@@ -14656,7 +14656,7 @@
         <v/>
       </c>
       <c r="S108" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R108)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R108)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T108" s="102" t="inlineStr">
@@ -14782,7 +14782,7 @@
         <v/>
       </c>
       <c r="S109" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R109)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R109)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T109" s="99" t="inlineStr">
@@ -14908,7 +14908,7 @@
         <v/>
       </c>
       <c r="S110" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R110)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R110)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T110" s="99" t="inlineStr">
@@ -15034,7 +15034,7 @@
         <v/>
       </c>
       <c r="S111" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R111)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R111)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T111" s="99" t="inlineStr">
@@ -15160,7 +15160,7 @@
         <v/>
       </c>
       <c r="S112" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R112)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R112)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T112" s="99" t="inlineStr">
@@ -15283,7 +15283,7 @@
         <v/>
       </c>
       <c r="S113" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R113)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R113)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T113" s="99" t="inlineStr">
@@ -15403,7 +15403,7 @@
         <v/>
       </c>
       <c r="S114" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R114)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R114)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T114" s="102" t="inlineStr">
@@ -15522,7 +15522,7 @@
         <v/>
       </c>
       <c r="S115" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R115)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R115)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T115" s="102" t="inlineStr">
@@ -15640,7 +15640,7 @@
         <v/>
       </c>
       <c r="S116" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R116)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R116)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T116" s="102" t="inlineStr">
@@ -15763,7 +15763,7 @@
         <v/>
       </c>
       <c r="S117" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R117)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R117)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T117" s="99" t="inlineStr">
@@ -15889,7 +15889,7 @@
         <v/>
       </c>
       <c r="S118" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R118)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R118)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T118" s="99" t="inlineStr">
@@ -16013,7 +16013,7 @@
         <v/>
       </c>
       <c r="S119" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R119)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R119)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T119" s="99" t="inlineStr">
@@ -16138,7 +16138,7 @@
         <v/>
       </c>
       <c r="S120" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R120)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R120)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T120" s="99" t="inlineStr">
@@ -16261,7 +16261,7 @@
         <v/>
       </c>
       <c r="S121" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R121)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R121)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T121" s="99" t="inlineStr">
@@ -16386,7 +16386,7 @@
         <v/>
       </c>
       <c r="S122" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R122)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R122)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T122" s="99" t="inlineStr">
@@ -16509,7 +16509,7 @@
         <v/>
       </c>
       <c r="S123" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R123)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R123)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T123" s="99" t="inlineStr">
@@ -16632,7 +16632,7 @@
         <v/>
       </c>
       <c r="S124" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R124)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R124)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T124" s="99" t="inlineStr">
@@ -16755,7 +16755,7 @@
         <v/>
       </c>
       <c r="S125" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R125)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R125)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T125" s="99" t="inlineStr">
@@ -16878,7 +16878,7 @@
         <v/>
       </c>
       <c r="S126" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R126)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R126)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T126" s="99" t="inlineStr">
@@ -17001,7 +17001,7 @@
         <v/>
       </c>
       <c r="S127" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R127)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R127)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T127" s="99" t="inlineStr">
@@ -17124,7 +17124,7 @@
         <v/>
       </c>
       <c r="S128" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R128)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R128)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T128" s="99" t="inlineStr">
@@ -17247,7 +17247,7 @@
         <v/>
       </c>
       <c r="S129" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R129)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R129)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T129" s="99" t="inlineStr">
@@ -17370,7 +17370,7 @@
         <v/>
       </c>
       <c r="S130" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R130)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R130)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T130" s="99" t="inlineStr">
@@ -17493,7 +17493,7 @@
         <v/>
       </c>
       <c r="S131" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R131)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R131)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T131" s="99" t="inlineStr">
@@ -17616,7 +17616,7 @@
         <v/>
       </c>
       <c r="S132" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R132)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R132)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T132" s="99" t="inlineStr">
@@ -17740,7 +17740,7 @@
         <v/>
       </c>
       <c r="S133" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R133)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R133)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T133" s="99" t="inlineStr">
@@ -17863,7 +17863,7 @@
         <v/>
       </c>
       <c r="S134" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R134)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R134)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T134" s="99" t="inlineStr">
@@ -17986,7 +17986,7 @@
         <v/>
       </c>
       <c r="S135" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R135)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R135)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T135" s="99" t="inlineStr">
@@ -18112,7 +18112,7 @@
         <v/>
       </c>
       <c r="S136" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R136)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R136)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T136" s="99" t="inlineStr">
@@ -18238,7 +18238,7 @@
         <v/>
       </c>
       <c r="S137" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R137)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R137)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T137" s="99" t="inlineStr">
@@ -18364,7 +18364,7 @@
         <v/>
       </c>
       <c r="S138" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R138)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R138)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T138" s="99" t="inlineStr">
@@ -18490,7 +18490,7 @@
         <v/>
       </c>
       <c r="S139" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R139)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R139)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T139" s="99" t="inlineStr">
@@ -18616,7 +18616,7 @@
         <v/>
       </c>
       <c r="S140" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R140)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R140)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T140" s="99" t="inlineStr">
@@ -18742,7 +18742,7 @@
         <v/>
       </c>
       <c r="S141" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R141)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R141)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T141" s="99" t="inlineStr">
@@ -18868,7 +18868,7 @@
         <v/>
       </c>
       <c r="S142" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R142)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R142)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T142" s="99" t="inlineStr">
@@ -18994,7 +18994,7 @@
         <v/>
       </c>
       <c r="S143" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R143)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R143)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T143" s="99" t="inlineStr">
@@ -19120,7 +19120,7 @@
         <v/>
       </c>
       <c r="S144" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R144)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R144)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T144" s="99" t="inlineStr">
@@ -19246,7 +19246,7 @@
         <v/>
       </c>
       <c r="S145" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R145)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R145)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T145" s="99" t="inlineStr">
@@ -19372,7 +19372,7 @@
         <v/>
       </c>
       <c r="S146" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R146)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R146)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T146" s="99" t="inlineStr">
@@ -19498,7 +19498,7 @@
         <v/>
       </c>
       <c r="S147" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R147)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R147)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T147" s="99" t="inlineStr">
@@ -19624,7 +19624,7 @@
         <v/>
       </c>
       <c r="S148" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R148)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R148)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T148" s="99" t="inlineStr">
@@ -19750,7 +19750,7 @@
         <v/>
       </c>
       <c r="S149" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R149)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R149)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T149" s="99" t="inlineStr">
@@ -19876,7 +19876,7 @@
         <v/>
       </c>
       <c r="S150" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R150)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R150)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T150" s="99" t="inlineStr">
@@ -20002,7 +20002,7 @@
         <v/>
       </c>
       <c r="S151" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R151)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R151)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T151" s="99" t="inlineStr">
@@ -20128,7 +20128,7 @@
         <v/>
       </c>
       <c r="S152" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R152)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R152)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T152" s="99" t="inlineStr">
@@ -20254,7 +20254,7 @@
         <v/>
       </c>
       <c r="S153" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R153)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R153)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T153" s="99" t="inlineStr">
@@ -20380,7 +20380,7 @@
         <v/>
       </c>
       <c r="S154" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R154)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R154)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T154" s="99" t="inlineStr">
@@ -20506,7 +20506,7 @@
         <v/>
       </c>
       <c r="S155" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R155)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R155)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T155" s="99" t="inlineStr">
@@ -20632,7 +20632,7 @@
         <v/>
       </c>
       <c r="S156" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R156)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R156)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T156" s="99" t="inlineStr">
@@ -20758,7 +20758,7 @@
         <v/>
       </c>
       <c r="S157" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R157)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R157)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T157" s="99" t="inlineStr">
@@ -20884,7 +20884,7 @@
         <v/>
       </c>
       <c r="S158" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R158)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R158)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T158" s="99" t="inlineStr">
@@ -21010,7 +21010,7 @@
         <v/>
       </c>
       <c r="S159" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R159)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R159)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T159" s="99" t="inlineStr">
@@ -21136,7 +21136,7 @@
         <v/>
       </c>
       <c r="S160" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R160)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R160)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T160" s="99" t="inlineStr">
@@ -21262,7 +21262,7 @@
         <v/>
       </c>
       <c r="S161" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R161)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R161)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T161" s="99" t="inlineStr">
@@ -21388,7 +21388,7 @@
         <v/>
       </c>
       <c r="S162" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R162)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R162)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T162" s="99" t="inlineStr">
@@ -21514,7 +21514,7 @@
         <v/>
       </c>
       <c r="S163" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R163)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R163)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T163" s="99" t="inlineStr">
@@ -21640,7 +21640,7 @@
         <v/>
       </c>
       <c r="S164" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R164)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R164)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T164" s="99" t="inlineStr">
@@ -21766,7 +21766,7 @@
         <v/>
       </c>
       <c r="S165" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R165)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R165)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T165" s="99" t="inlineStr">
@@ -21892,7 +21892,7 @@
         <v/>
       </c>
       <c r="S166" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R166)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R166)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T166" s="99" t="inlineStr">
@@ -22018,7 +22018,7 @@
         <v/>
       </c>
       <c r="S167" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R167)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R167)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T167" s="99" t="inlineStr">
@@ -22144,7 +22144,7 @@
         <v/>
       </c>
       <c r="S168" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R168)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R168)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T168" s="99" t="inlineStr">
@@ -22270,7 +22270,7 @@
         <v/>
       </c>
       <c r="S169" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R169)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R169)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T169" s="99" t="inlineStr">
@@ -22396,7 +22396,7 @@
         <v/>
       </c>
       <c r="S170" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R170)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R170)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T170" s="99" t="inlineStr">
@@ -22522,7 +22522,7 @@
         <v/>
       </c>
       <c r="S171" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R171)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R171)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T171" s="99" t="inlineStr">
@@ -22645,7 +22645,7 @@
         <v/>
       </c>
       <c r="S172" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R172)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R172)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T172" s="99" t="inlineStr">
@@ -22768,7 +22768,7 @@
         <v/>
       </c>
       <c r="S173" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R173)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R173)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T173" s="99" t="inlineStr">
@@ -22892,7 +22892,7 @@
         <v/>
       </c>
       <c r="S174" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R174)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R174)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T174" s="99" t="inlineStr">
@@ -23016,7 +23016,7 @@
         <v/>
       </c>
       <c r="S175" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R175)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R175)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T175" s="99" t="inlineStr">
@@ -23140,7 +23140,7 @@
         <v/>
       </c>
       <c r="S176" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R176)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R176)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T176" s="99" t="inlineStr">
@@ -23264,7 +23264,7 @@
         <v/>
       </c>
       <c r="S177" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R177)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R177)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T177" s="99" t="inlineStr">
@@ -23388,7 +23388,7 @@
         <v/>
       </c>
       <c r="S178" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R178)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R178)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T178" s="99" t="inlineStr">
@@ -23513,7 +23513,7 @@
         <v/>
       </c>
       <c r="S179" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R179)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R179)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T179" s="99" t="inlineStr">
@@ -23636,7 +23636,7 @@
         <v/>
       </c>
       <c r="S180" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R180)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R180)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T180" s="99" t="inlineStr">
@@ -23760,7 +23760,7 @@
         <v/>
       </c>
       <c r="S181" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R181)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R181)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T181" s="99" t="inlineStr">
@@ -23883,7 +23883,7 @@
         <v/>
       </c>
       <c r="S182" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R182)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R182)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T182" s="99" t="inlineStr">
@@ -24006,7 +24006,7 @@
         <v/>
       </c>
       <c r="S183" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R183)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R183)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T183" s="99" t="inlineStr">
@@ -24130,7 +24130,7 @@
         <v/>
       </c>
       <c r="S184" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R184)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R184)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T184" s="99" t="inlineStr">
@@ -24255,7 +24255,7 @@
         <v/>
       </c>
       <c r="S185" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R185)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R185)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T185" s="99" t="inlineStr">
@@ -24379,7 +24379,7 @@
         <v/>
       </c>
       <c r="S186" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R186)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R186)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T186" s="99" t="inlineStr">
@@ -24503,7 +24503,7 @@
         <v/>
       </c>
       <c r="S187" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R187)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R187)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T187" s="99" t="inlineStr">
@@ -24627,7 +24627,7 @@
         <v/>
       </c>
       <c r="S188" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R188)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R188)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T188" s="99" t="inlineStr">
@@ -24751,7 +24751,7 @@
         <v/>
       </c>
       <c r="S189" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R189)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R189)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T189" s="99" t="inlineStr">
@@ -24875,7 +24875,7 @@
         <v/>
       </c>
       <c r="S190" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R190)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R190)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T190" s="99" t="inlineStr">
@@ -24999,7 +24999,7 @@
         <v/>
       </c>
       <c r="S191" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R191)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R191)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T191" s="99" t="inlineStr">
@@ -25122,7 +25122,7 @@
         <v/>
       </c>
       <c r="S192" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R192)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R192)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T192" s="99" t="inlineStr">
@@ -25246,7 +25246,7 @@
         <v/>
       </c>
       <c r="S193" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R193)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R193)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T193" s="99" t="inlineStr">
@@ -25369,7 +25369,7 @@
         <v/>
       </c>
       <c r="S194" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R194)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R194)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T194" s="99" t="inlineStr">
@@ -25492,7 +25492,7 @@
         <v/>
       </c>
       <c r="S195" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R195)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R195)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T195" s="99" t="inlineStr">
@@ -25616,7 +25616,7 @@
         <v/>
       </c>
       <c r="S196" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R196)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R196)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T196" s="99" t="inlineStr">
@@ -25739,7 +25739,7 @@
         <v/>
       </c>
       <c r="S197" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R197)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R197)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T197" s="99" t="inlineStr">
@@ -25862,7 +25862,7 @@
         <v/>
       </c>
       <c r="S198" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R198)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R198)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T198" s="99" t="inlineStr">
@@ -25985,7 +25985,7 @@
         <v/>
       </c>
       <c r="S199" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R199)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R199)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T199" s="99" t="inlineStr">
@@ -26108,7 +26108,7 @@
         <v/>
       </c>
       <c r="S200" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R200)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R200)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T200" s="99" t="inlineStr">
@@ -26231,7 +26231,7 @@
         <v/>
       </c>
       <c r="S201" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R201)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R201)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T201" s="99" t="inlineStr">
@@ -26354,7 +26354,7 @@
         <v/>
       </c>
       <c r="S202" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R202)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R202)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T202" s="99" t="inlineStr">
@@ -26477,7 +26477,7 @@
         <v/>
       </c>
       <c r="S203" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R203)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R203)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T203" s="99" t="inlineStr">
@@ -26600,7 +26600,7 @@
         <v/>
       </c>
       <c r="S204" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R204)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R204)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T204" s="99" t="inlineStr">
@@ -26724,7 +26724,7 @@
         <v/>
       </c>
       <c r="S205" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R205)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R205)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T205" s="99" t="inlineStr">
@@ -26848,7 +26848,7 @@
         <v/>
       </c>
       <c r="S206" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R206)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R206)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T206" s="99" t="inlineStr">
@@ -26971,7 +26971,7 @@
         <v/>
       </c>
       <c r="S207" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R207)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R207)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T207" s="99" t="inlineStr">
@@ -27094,7 +27094,7 @@
         <v/>
       </c>
       <c r="S208" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R208)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R208)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T208" s="99" t="inlineStr">
@@ -27217,7 +27217,7 @@
         <v/>
       </c>
       <c r="S209" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R209)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R209)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T209" s="99" t="inlineStr">
@@ -27340,7 +27340,7 @@
         <v/>
       </c>
       <c r="S210" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R210)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R210)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T210" s="99" t="inlineStr">
@@ -27463,7 +27463,7 @@
         <v/>
       </c>
       <c r="S211" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R211)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R211)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T211" s="99" t="inlineStr">
@@ -27586,7 +27586,7 @@
         <v/>
       </c>
       <c r="S212" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R212)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R212)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T212" s="99" t="inlineStr">
@@ -27709,7 +27709,7 @@
         <v/>
       </c>
       <c r="S213" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R213)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R213)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T213" s="99" t="inlineStr">
@@ -27832,7 +27832,7 @@
         <v/>
       </c>
       <c r="S214" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R214)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R214)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T214" s="99" t="inlineStr">
@@ -27955,7 +27955,7 @@
         <v/>
       </c>
       <c r="S215" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R215)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R215)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T215" s="99" t="inlineStr">
@@ -28078,7 +28078,7 @@
         <v/>
       </c>
       <c r="S216" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R216)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R216)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T216" s="99" t="inlineStr">
@@ -28201,7 +28201,7 @@
         <v/>
       </c>
       <c r="S217" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R217)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R217)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T217" s="99" t="inlineStr">
@@ -28325,7 +28325,7 @@
         <v/>
       </c>
       <c r="S218" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R218)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R218)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T218" s="99" t="inlineStr">
@@ -28448,7 +28448,7 @@
         <v/>
       </c>
       <c r="S219" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R219)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R219)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T219" s="99" t="inlineStr">
@@ -28571,7 +28571,7 @@
         <v/>
       </c>
       <c r="S220" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R220)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R220)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T220" s="99" t="inlineStr">
@@ -28694,7 +28694,7 @@
         <v/>
       </c>
       <c r="S221" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R221)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R221)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T221" s="99" t="inlineStr">
@@ -28817,7 +28817,7 @@
         <v/>
       </c>
       <c r="S222" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R222)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R222)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T222" s="99" t="inlineStr">
@@ -28940,7 +28940,7 @@
         <v/>
       </c>
       <c r="S223" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R223)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R223)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T223" s="99" t="inlineStr">
@@ -29063,7 +29063,7 @@
         <v/>
       </c>
       <c r="S224" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R224)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R224)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T224" s="99" t="inlineStr">
@@ -29186,7 +29186,7 @@
         <v/>
       </c>
       <c r="S225" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R225)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R225)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T225" s="99" t="inlineStr">
@@ -29309,7 +29309,7 @@
         <v/>
       </c>
       <c r="S226" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R226)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R226)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T226" s="99" t="inlineStr">
@@ -29432,7 +29432,7 @@
         <v/>
       </c>
       <c r="S227" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R227)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R227)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T227" s="99" t="inlineStr">
@@ -29555,7 +29555,7 @@
         <v/>
       </c>
       <c r="S228" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R228)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R228)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T228" s="99" t="inlineStr">
@@ -29678,7 +29678,7 @@
         <v/>
       </c>
       <c r="S229" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R229)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R229)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T229" s="99" t="inlineStr">
@@ -29801,7 +29801,7 @@
         <v/>
       </c>
       <c r="S230" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R230)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R230)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T230" s="99" t="inlineStr">
@@ -29925,7 +29925,7 @@
         <v/>
       </c>
       <c r="S231" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R231)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R231)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T231" s="102" t="inlineStr">
@@ -30048,7 +30048,7 @@
         <v/>
       </c>
       <c r="S232" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R232)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R232)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T232" s="102" t="inlineStr">
@@ -30168,7 +30168,7 @@
         <v/>
       </c>
       <c r="S233" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R233)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R233)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U233" s="102" t="inlineStr">
@@ -30284,7 +30284,7 @@
         <v/>
       </c>
       <c r="S234" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R234)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R234)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U234" s="102" t="inlineStr">
@@ -30400,7 +30400,7 @@
         <v/>
       </c>
       <c r="S235" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R235)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R235)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U235" s="102" t="inlineStr">
@@ -30516,7 +30516,7 @@
         <v/>
       </c>
       <c r="S236" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R236)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R236)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U236" s="102" t="inlineStr">
@@ -30632,7 +30632,7 @@
         <v/>
       </c>
       <c r="S237" s="103">
-        <f>IF(COUNTIF($R$6:$R$247,R237)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R237)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U237" s="102" t="inlineStr">
@@ -30749,7 +30749,7 @@
         <v/>
       </c>
       <c r="S238" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R238)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R238)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T238" s="99" t="inlineStr">
@@ -30872,7 +30872,7 @@
         <v/>
       </c>
       <c r="S239" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R239)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R239)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T239" s="99" t="inlineStr">
@@ -30991,7 +30991,7 @@
         <v/>
       </c>
       <c r="S240" s="72">
-        <f>IF(COUNTIF($R$6:$R$247,R240)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R240)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T240" s="99" t="inlineStr">
@@ -31110,7 +31110,7 @@
         <v/>
       </c>
       <c r="S241" s="99">
-        <f>IF(COUNTIF($R$6:$R$247,R241)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R241)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T241" s="99" t="inlineStr">
@@ -31231,7 +31231,7 @@
         <v/>
       </c>
       <c r="S242" s="99">
-        <f>IF(COUNTIF($R$6:$R$247,R242)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R242)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T242" s="99" t="inlineStr">
@@ -31353,7 +31353,7 @@
         <v/>
       </c>
       <c r="S243" s="99">
-        <f>IF(COUNTIF($R$6:$R$247,R243)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R243)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T243" s="99" t="inlineStr">
@@ -31475,7 +31475,7 @@
         <v/>
       </c>
       <c r="S244" s="99">
-        <f>IF(COUNTIF($R$6:$R$247,R244)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R244)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T244" s="99" t="inlineStr">
@@ -31597,7 +31597,7 @@
         <v/>
       </c>
       <c r="S245" s="99">
-        <f>IF(COUNTIF($R$6:$R$247,R245)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R245)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T245" s="99" t="inlineStr">
@@ -31719,7 +31719,7 @@
         <v/>
       </c>
       <c r="S246" s="99">
-        <f>IF(COUNTIF($R$6:$R$247,R246)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R246)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T246" s="99" t="inlineStr">
@@ -31841,7 +31841,7 @@
         <v/>
       </c>
       <c r="S247" s="99">
-        <f>IF(COUNTIF($R$6:$R$247,R247)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$248,R247)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T247" s="99" t="inlineStr">
@@ -31876,8 +31876,129 @@
         </is>
       </c>
     </row>
+    <row r="248" ht="255" customHeight="1" s="129">
+      <c r="A248" s="99" t="inlineStr">
+        <is>
+          <t>ENV-OPENWORLD-TOWER02</t>
+        </is>
+      </c>
+      <c r="B248" s="72" t="inlineStr">
+        <is>
+          <t>开放世界 塔2 施工高楼 70×50m</t>
+        </is>
+      </c>
+      <c r="C248" s="72" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="D248" s="99" t="inlineStr">
+        <is>
+          <t>environment_kit_3d</t>
+        </is>
+      </c>
+      <c r="E248" s="99" t="inlineStr">
+        <is>
+          <t>open_world_tower_02</t>
+        </is>
+      </c>
+      <c r="F248" s="99" t="inlineStr">
+        <is>
+          <t>building_source</t>
+        </is>
+      </c>
+      <c r="G248" s="99" t="n"/>
+      <c r="H248" s="99" t="inlineStr">
+        <is>
+          <t>Top3D / Blender Z-up</t>
+        </is>
+      </c>
+      <c r="I248" s="99" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="J248" s="72" t="inlineStr">
+        <is>
+          <t>开放世界独立建筑，与主塔平级</t>
+        </is>
+      </c>
+      <c r="K248" s="99" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L248" s="99" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M248" s="99" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N248" s="99" t="inlineStr">
+        <is>
+          <t>主体70×50m；20层，层高4.2m为参考图推定；62独立包；4角色公共色盘；灰色屋顶</t>
+        </is>
+      </c>
+      <c r="O248" s="99" t="inlineStr">
+        <is>
+          <t>assets/art/environments/open_world/source/tower_02/v001/塔2_施工高楼_70x50m_v001.blend</t>
+        </is>
+      </c>
+      <c r="P248" s="99" t="inlineStr">
+        <is>
+          <t>用户参考图；docs/v0.1/development/2026-09-29_openworld_tower02_source.md</t>
+        </is>
+      </c>
+      <c r="Q248" s="72" t="inlineStr">
+        <is>
+          <t>塔2;施工高楼;塔吊;脚手架;灰色屋顶</t>
+        </is>
+      </c>
+      <c r="R248" s="99">
+        <f>LOWER(TRIM(C248)&amp;"|"&amp;TRIM(D248)&amp;"|"&amp;TRIM(E248)&amp;"|"&amp;TRIM(F248)&amp;"|"&amp;TRIM(H248)&amp;"|"&amp;TRIM(I248))</f>
+        <v/>
+      </c>
+      <c r="S248" s="99">
+        <f>IF(COUNTIF($R$6:$R$248,R248)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T248" s="99" t="inlineStr">
+        <is>
+          <t>e29fb41ba7a1ba9c498d5fe293498aa8e6f95f95e5dd38beb1e139ba39eac90e</t>
+        </is>
+      </c>
+      <c r="U248" s="72" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V248" s="99" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="W248" s="72" t="inlineStr">
+        <is>
+          <t>用户提供参考图，仅据图建模</t>
+        </is>
+      </c>
+      <c r="X248" s="72" t="inlineStr">
+        <is>
+          <t>塔2</t>
+        </is>
+      </c>
+      <c r="Y248" s="72" t="inlineStr">
+        <is>
+          <t>仅Blender原始文件；未导出GLB、未接入Godot、无碰撞/LOD。高度为美术推定，不继承主塔玩法层高。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:X240"/>
+  <autoFilter ref="A5:Y248"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X2"/>
     <mergeCell ref="A3:X3"/>
@@ -31899,13 +32020,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C247" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="C6:C248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" operator="between">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K247" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="K6:K248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" operator="between">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L247" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="L6:L248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" operator="between">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -45368,7 +45489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.808590000000001" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="68" min="1" max="1"/>
@@ -46320,6 +46441,43 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>v0.1.24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>新增Blender建筑源</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>关卡场景 / 开放世界</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ENV-OPENWORLD-TOWER02 塔2：70×50m，62包，灰色顶面。</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>仅源资产完成；运行时未接入。</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>

--- a/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
+++ b/assets/registry/ledgers/ShellStorm2_场景账本_v001.xlsx
@@ -24,12 +24,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_ \¥* #,##0.00_ ;_ \¥* -#,##0.00_ ;_ \¥* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ \¥* #,##0_ ;_ \¥* -#,##0_ ;_ \¥* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -564,7 +565,7 @@
     <xf numFmtId="168" fontId="26" fillId="11" borderId="21"/>
     <xf numFmtId="9" fontId="26" fillId="11" borderId="21"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -945,6 +946,12 @@
       <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="17" fillId="11" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1466,22 +1473,22 @@
     </row>
     <row r="6" ht="42" customFormat="1" customHeight="1" s="69">
       <c r="A6" s="74">
-        <f>=COUNTA(资产主表!$A$6:$A$248)</f>
+        <f>COUNTA(资产主表!$A$6:$A$249)</f>
         <v/>
       </c>
       <c r="B6" s="72" t="inlineStr"/>
       <c r="C6" s="74">
-        <f>=COUNTIF(资产主表!$K$6:$K$248,"已完成")+COUNTIF(资产主表!$K$6:$K$248,"原型已接入")+COUNTIF(资产主表!$K$6:$K$248,"正式美术已接入")+COUNTIF(资产主表!$K$6:$K$248,"已优化并正式接入")+COUNTIF(资产主表!$K$6:$K$248,"Blender源已完成")+COUNTIF(资产主表!$K$6:$K$248,"已导入；优化完成")+COUNTIF(资产主表!$K$6:$K$248,"白模源已完成；QA PASS")</f>
+        <f>COUNTIF(资产主表!$K$6:$K$249,"已完成")+COUNTIF(资产主表!$K$6:$K$249,"原型已接入")+COUNTIF(资产主表!$K$6:$K$249,"正式美术已接入")+COUNTIF(资产主表!$K$6:$K$249,"已优化并正式接入")+COUNTIF(资产主表!$K$6:$K$249,"Blender源已完成")+COUNTIF(资产主表!$K$6:$K$249,"已导入；优化完成")+COUNTIF(资产主表!$K$6:$K$249,"白模源已完成；QA PASS")</f>
         <v/>
       </c>
       <c r="D6" s="72" t="inlineStr"/>
       <c r="E6" s="74">
-        <f>=COUNTIF(资产主表!$K$6:$K$248,"待制作")+COUNTIF(资产主表!$K$6:$K$248,"程序占位")</f>
+        <f>COUNTIF(资产主表!$K$6:$K$249,"待制作")+COUNTIF(资产主表!$K$6:$K$249,"程序占位")</f>
         <v/>
       </c>
       <c r="F6" s="72" t="inlineStr"/>
       <c r="G6" s="74">
-        <f>=COUNTIF(资产主表!$S$6:$S$248,"重复")</f>
+        <f>COUNTIF(资产主表!$S$6:$S$249,"重复")</f>
         <v/>
       </c>
       <c r="H6" s="72" t="inlineStr"/>
@@ -1550,11 +1557,11 @@
         </is>
       </c>
       <c r="B10" s="79">
-        <f>=COUNTIF(资产主表!$C$6:$C$248,A10)</f>
+        <f>COUNTIF(资产主表!$C$6:$C$249,A10)</f>
         <v/>
       </c>
       <c r="C10" s="79">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$248=A10)*((资产主表!$K$6:$K$248="已完成")+(资产主表!$K$6:$K$248="原型已接入")+(资产主表!$K$6:$K$248="正式美术已接入")+(资产主表!$K$6:$K$248="已优化并正式接入")+(资产主表!$K$6:$K$248="Blender源已完成")+(资产主表!$K$6:$K$248="已导入；优化完成")+(资产主表!$K$6:$K$248="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT((资产主表!$C$6:$C$249=A10)*((资产主表!$K$6:$K$249="已完成")+(资产主表!$K$6:$K$249="原型已接入")+(资产主表!$K$6:$K$249="正式美术已接入")+(资产主表!$K$6:$K$249="已优化并正式接入")+(资产主表!$K$6:$K$249="Blender源已完成")+(资产主表!$K$6:$K$249="已导入；优化完成")+(资产主表!$K$6:$K$249="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D10" s="79" t="inlineStr"/>
@@ -1572,11 +1579,11 @@
         </is>
       </c>
       <c r="B11" s="79">
-        <f>=COUNTIF(资产主表!$C$6:$C$248,A11)</f>
+        <f>COUNTIF(资产主表!$C$6:$C$249,A11)</f>
         <v/>
       </c>
       <c r="C11" s="79">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$248=A11)*((资产主表!$K$6:$K$248="已完成")+(资产主表!$K$6:$K$248="原型已接入")+(资产主表!$K$6:$K$248="正式美术已接入")+(资产主表!$K$6:$K$248="已优化并正式接入")+(资产主表!$K$6:$K$248="Blender源已完成")+(资产主表!$K$6:$K$248="已导入；优化完成")+(资产主表!$K$6:$K$248="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT((资产主表!$C$6:$C$249=A11)*((资产主表!$K$6:$K$249="已完成")+(资产主表!$K$6:$K$249="原型已接入")+(资产主表!$K$6:$K$249="正式美术已接入")+(资产主表!$K$6:$K$249="已优化并正式接入")+(资产主表!$K$6:$K$249="Blender源已完成")+(资产主表!$K$6:$K$249="已导入；优化完成")+(资产主表!$K$6:$K$249="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D11" s="79" t="inlineStr"/>
@@ -1594,11 +1601,11 @@
         </is>
       </c>
       <c r="B12" s="79">
-        <f>=COUNTIF(资产主表!$C$6:$C$248,A12)</f>
+        <f>COUNTIF(资产主表!$C$6:$C$249,A12)</f>
         <v/>
       </c>
       <c r="C12" s="79">
-        <f>=SUMPRODUCT((资产主表!$C$6:$C$248=A12)*((资产主表!$K$6:$K$248="已完成")+(资产主表!$K$6:$K$248="原型已接入")+(资产主表!$K$6:$K$248="正式美术已接入")+(资产主表!$K$6:$K$248="已优化并正式接入")+(资产主表!$K$6:$K$248="Blender源已完成")+(资产主表!$K$6:$K$248="已导入；优化完成")+(资产主表!$K$6:$K$248="白模源已完成；QA PASS")))</f>
+        <f>SUMPRODUCT((资产主表!$C$6:$C$249=A12)*((资产主表!$K$6:$K$249="已完成")+(资产主表!$K$6:$K$249="原型已接入")+(资产主表!$K$6:$K$249="正式美术已接入")+(资产主表!$K$6:$K$249="已优化并正式接入")+(资产主表!$K$6:$K$249="Blender源已完成")+(资产主表!$K$6:$K$249="已导入；优化完成")+(资产主表!$K$6:$K$249="白模源已完成；QA PASS")))</f>
         <v/>
       </c>
       <c r="D12" s="79" t="inlineStr"/>
@@ -2184,7 +2191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y248"/>
+  <dimension ref="A1:Y249"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.808590000000001" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="25" customWidth="1" style="68" min="1" max="1"/>
@@ -2460,7 +2467,7 @@
         <v/>
       </c>
       <c r="S6" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R6)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R6)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T6" s="80" t="inlineStr"/>
@@ -2567,7 +2574,7 @@
         <v/>
       </c>
       <c r="S7" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R7)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R7)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T7" s="80" t="inlineStr"/>
@@ -2674,7 +2681,7 @@
         <v/>
       </c>
       <c r="S8" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R8)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R8)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T8" s="80" t="inlineStr"/>
@@ -2781,7 +2788,7 @@
         <v/>
       </c>
       <c r="S9" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R9)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R9)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T9" s="80" t="inlineStr"/>
@@ -2888,7 +2895,7 @@
         <v/>
       </c>
       <c r="S10" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R10)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R10)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T10" s="80" t="inlineStr"/>
@@ -2995,7 +3002,7 @@
         <v/>
       </c>
       <c r="S11" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R11)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R11)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T11" s="80" t="inlineStr"/>
@@ -3102,7 +3109,7 @@
         <v/>
       </c>
       <c r="S12" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R12)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R12)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T12" s="80" t="inlineStr"/>
@@ -3209,7 +3216,7 @@
         <v/>
       </c>
       <c r="S13" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R13)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R13)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T13" s="80" t="inlineStr"/>
@@ -3316,7 +3323,7 @@
         <v/>
       </c>
       <c r="S14" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R14)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R14)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T14" s="80" t="inlineStr"/>
@@ -3423,7 +3430,7 @@
         <v/>
       </c>
       <c r="S15" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R15)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R15)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T15" s="80" t="inlineStr"/>
@@ -3530,7 +3537,7 @@
         <v/>
       </c>
       <c r="S16" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R16)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R16)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T16" s="80" t="inlineStr"/>
@@ -3637,7 +3644,7 @@
         <v/>
       </c>
       <c r="S17" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R17)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R17)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T17" s="80" t="inlineStr"/>
@@ -3744,7 +3751,7 @@
         <v/>
       </c>
       <c r="S18" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R18)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R18)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T18" s="80" t="inlineStr"/>
@@ -3851,7 +3858,7 @@
         <v/>
       </c>
       <c r="S19" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R19)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R19)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T19" s="80" t="inlineStr"/>
@@ -3958,7 +3965,7 @@
         <v/>
       </c>
       <c r="S20" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R20)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R20)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T20" s="80" t="inlineStr"/>
@@ -4065,7 +4072,7 @@
         <v/>
       </c>
       <c r="S21" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R21)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R21)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T21" s="80" t="inlineStr"/>
@@ -4172,7 +4179,7 @@
         <v/>
       </c>
       <c r="S22" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R22)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R22)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T22" s="80" t="inlineStr"/>
@@ -4279,7 +4286,7 @@
         <v/>
       </c>
       <c r="S23" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R23)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R23)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T23" s="80" t="inlineStr"/>
@@ -4386,7 +4393,7 @@
         <v/>
       </c>
       <c r="S24" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R24)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R24)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T24" s="80" t="inlineStr"/>
@@ -4493,7 +4500,7 @@
         <v/>
       </c>
       <c r="S25" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R25)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R25)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T25" s="80" t="inlineStr"/>
@@ -4600,7 +4607,7 @@
         <v/>
       </c>
       <c r="S26" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R26)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R26)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T26" s="80" t="inlineStr"/>
@@ -4707,7 +4714,7 @@
         <v/>
       </c>
       <c r="S27" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R27)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R27)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T27" s="80" t="inlineStr"/>
@@ -4814,7 +4821,7 @@
         <v/>
       </c>
       <c r="S28" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R28)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R28)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T28" s="80" t="inlineStr"/>
@@ -4921,7 +4928,7 @@
         <v/>
       </c>
       <c r="S29" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R29)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R29)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T29" s="80" t="inlineStr"/>
@@ -5028,7 +5035,7 @@
         <v/>
       </c>
       <c r="S30" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R30)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R30)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T30" s="80" t="inlineStr"/>
@@ -5135,7 +5142,7 @@
         <v/>
       </c>
       <c r="S31" s="80">
-        <f>IF(COUNTIF($R$6:$R$248,R31)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R31)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T31" s="80" t="inlineStr"/>
@@ -5254,7 +5261,7 @@
         <v/>
       </c>
       <c r="S32" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R32)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R32)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T32" s="96" t="inlineStr">
@@ -5377,7 +5384,7 @@
         <v/>
       </c>
       <c r="S33" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R33)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R33)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T33" s="99" t="inlineStr">
@@ -5500,7 +5507,7 @@
         <v/>
       </c>
       <c r="S34" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R34)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R34)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T34" s="99" t="inlineStr">
@@ -5623,7 +5630,7 @@
         <v/>
       </c>
       <c r="S35" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R35)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R35)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T35" s="99" t="inlineStr">
@@ -5746,7 +5753,7 @@
         <v/>
       </c>
       <c r="S36" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R36)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R36)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T36" s="96" t="inlineStr">
@@ -5870,7 +5877,7 @@
         <v/>
       </c>
       <c r="S37" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R37)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R37)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T37" s="99" t="inlineStr">
@@ -5993,7 +6000,7 @@
         <v/>
       </c>
       <c r="S38" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R38)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R38)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T38" s="99" t="inlineStr">
@@ -6112,7 +6119,7 @@
         <v/>
       </c>
       <c r="S39" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R39)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R39)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T39" s="96" t="inlineStr">
@@ -6235,7 +6242,7 @@
         <v/>
       </c>
       <c r="S40" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R40)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R40)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T40" s="99" t="inlineStr">
@@ -6358,7 +6365,7 @@
         <v/>
       </c>
       <c r="S41" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R41)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R41)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T41" s="99" t="inlineStr">
@@ -6481,7 +6488,7 @@
         <v/>
       </c>
       <c r="S42" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R42)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R42)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T42" s="99" t="inlineStr">
@@ -6604,7 +6611,7 @@
         <v/>
       </c>
       <c r="S43" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R43)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R43)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T43" s="99" t="inlineStr">
@@ -6727,7 +6734,7 @@
         <v/>
       </c>
       <c r="S44" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R44)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R44)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T44" s="96" t="inlineStr">
@@ -6851,7 +6858,7 @@
         <v/>
       </c>
       <c r="S45" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R45)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R45)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T45" s="99" t="inlineStr">
@@ -6974,7 +6981,7 @@
         <v/>
       </c>
       <c r="S46" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R46)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R46)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T46" s="99" t="inlineStr">
@@ -7097,7 +7104,7 @@
         <v/>
       </c>
       <c r="S47" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R47)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R47)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T47" s="99" t="inlineStr">
@@ -7220,7 +7227,7 @@
         <v/>
       </c>
       <c r="S48" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R48)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R48)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T48" s="99" t="inlineStr">
@@ -7340,7 +7347,7 @@
         <v/>
       </c>
       <c r="S49" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R49)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R49)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T49" s="99" t="inlineStr">
@@ -7463,7 +7470,7 @@
         <v/>
       </c>
       <c r="S50" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R50)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R50)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T50" s="99" t="inlineStr">
@@ -7587,7 +7594,7 @@
         <v/>
       </c>
       <c r="S51" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R51)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R51)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T51" s="99" t="inlineStr">
@@ -7710,7 +7717,7 @@
         <v/>
       </c>
       <c r="S52" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R52)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R52)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T52" s="96" t="inlineStr">
@@ -7834,7 +7841,7 @@
         <v/>
       </c>
       <c r="S53" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R53)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R53)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T53" s="96" t="inlineStr">
@@ -7957,7 +7964,7 @@
         <v/>
       </c>
       <c r="S54" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R54)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R54)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T54" s="96" t="inlineStr">
@@ -8086,7 +8093,7 @@
         <v/>
       </c>
       <c r="S55" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R55)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R55)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T55" s="96" t="inlineStr">
@@ -8213,7 +8220,7 @@
         <v/>
       </c>
       <c r="S56" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R56)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R56)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T56" s="96" t="inlineStr">
@@ -8336,7 +8343,7 @@
         <v/>
       </c>
       <c r="S57" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R57)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R57)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T57" s="96" t="inlineStr">
@@ -8461,7 +8468,7 @@
         <v/>
       </c>
       <c r="S58" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R58)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R58)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T58" s="96" t="inlineStr">
@@ -8584,7 +8591,7 @@
         <v/>
       </c>
       <c r="S59" s="97">
-        <f>IF(COUNTIF($R$6:$R$248,R59)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R59)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T59" s="96" t="inlineStr">
@@ -8703,7 +8710,7 @@
         <v/>
       </c>
       <c r="S60" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R60)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R60)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T60" s="99" t="inlineStr">
@@ -8823,7 +8830,7 @@
         <v/>
       </c>
       <c r="S61" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R61)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R61)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T61" s="99" t="inlineStr">
@@ -8943,7 +8950,7 @@
         <v/>
       </c>
       <c r="S62" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R62)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R62)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T62" s="99" t="inlineStr">
@@ -9063,7 +9070,7 @@
         <v/>
       </c>
       <c r="S63" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R63)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R63)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T63" s="99" t="inlineStr"/>
@@ -9183,7 +9190,7 @@
         <v/>
       </c>
       <c r="S64" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R64)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R64)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T64" s="99" t="inlineStr">
@@ -9308,7 +9315,7 @@
         <v/>
       </c>
       <c r="S65" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R65)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R65)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T65" s="99" t="inlineStr">
@@ -9433,7 +9440,7 @@
         <v/>
       </c>
       <c r="S66" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R66)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R66)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T66" s="99" t="inlineStr">
@@ -9558,7 +9565,7 @@
         <v/>
       </c>
       <c r="S67" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R67)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R67)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T67" s="99" t="inlineStr">
@@ -9683,7 +9690,7 @@
         <v/>
       </c>
       <c r="S68" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R68)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R68)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T68" s="99" t="inlineStr">
@@ -9814,7 +9821,7 @@
         <v/>
       </c>
       <c r="S69" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R69)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R69)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T69" s="99" t="inlineStr">
@@ -9940,7 +9947,7 @@
         <v/>
       </c>
       <c r="S70" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R70)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R70)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T70" s="99" t="inlineStr">
@@ -10064,7 +10071,7 @@
         <v/>
       </c>
       <c r="S71" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R71)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R71)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T71" s="99" t="inlineStr">
@@ -10188,7 +10195,7 @@
         <v/>
       </c>
       <c r="S72" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R72)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R72)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T72" s="99" t="inlineStr">
@@ -10312,7 +10319,7 @@
         <v/>
       </c>
       <c r="S73" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R73)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R73)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T73" s="99" t="inlineStr">
@@ -10436,7 +10443,7 @@
         <v/>
       </c>
       <c r="S74" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R74)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R74)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T74" s="99" t="inlineStr">
@@ -10560,7 +10567,7 @@
         <v/>
       </c>
       <c r="S75" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R75)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R75)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T75" s="99" t="inlineStr">
@@ -10684,7 +10691,7 @@
         <v/>
       </c>
       <c r="S76" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R76)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R76)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T76" s="99" t="inlineStr">
@@ -10808,7 +10815,7 @@
         <v/>
       </c>
       <c r="S77" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R77)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R77)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T77" s="99" t="inlineStr">
@@ -10932,7 +10939,7 @@
         <v/>
       </c>
       <c r="S78" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R78)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R78)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T78" s="99" t="inlineStr">
@@ -11056,7 +11063,7 @@
         <v/>
       </c>
       <c r="S79" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R79)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R79)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T79" s="99" t="inlineStr">
@@ -11180,7 +11187,7 @@
         <v/>
       </c>
       <c r="S80" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R80)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R80)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T80" s="99" t="inlineStr">
@@ -11304,7 +11311,7 @@
         <v/>
       </c>
       <c r="S81" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R81)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R81)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T81" s="99" t="inlineStr">
@@ -11428,7 +11435,7 @@
         <v/>
       </c>
       <c r="S82" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R82)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R82)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T82" s="99" t="inlineStr">
@@ -11552,7 +11559,7 @@
         <v/>
       </c>
       <c r="S83" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R83)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R83)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T83" s="99" t="inlineStr">
@@ -11676,7 +11683,7 @@
         <v/>
       </c>
       <c r="S84" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R84)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R84)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T84" s="99" t="inlineStr">
@@ -11800,7 +11807,7 @@
         <v/>
       </c>
       <c r="S85" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R85)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R85)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T85" s="99" t="inlineStr">
@@ -11924,7 +11931,7 @@
         <v/>
       </c>
       <c r="S86" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R86)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R86)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T86" s="99" t="inlineStr">
@@ -12048,7 +12055,7 @@
         <v/>
       </c>
       <c r="S87" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R87)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R87)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T87" s="99" t="inlineStr">
@@ -12172,7 +12179,7 @@
         <v/>
       </c>
       <c r="S88" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R88)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R88)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T88" s="99" t="inlineStr">
@@ -12296,7 +12303,7 @@
         <v/>
       </c>
       <c r="S89" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R89)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R89)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T89" s="99" t="inlineStr">
@@ -12420,7 +12427,7 @@
         <v/>
       </c>
       <c r="S90" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R90)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R90)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T90" s="99" t="inlineStr">
@@ -12544,7 +12551,7 @@
         <v/>
       </c>
       <c r="S91" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R91)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R91)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T91" s="99" t="inlineStr">
@@ -12668,7 +12675,7 @@
         <v/>
       </c>
       <c r="S92" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R92)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R92)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T92" s="99" t="inlineStr">
@@ -12792,7 +12799,7 @@
         <v/>
       </c>
       <c r="S93" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R93)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R93)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T93" s="99" t="inlineStr">
@@ -12916,7 +12923,7 @@
         <v/>
       </c>
       <c r="S94" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R94)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R94)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T94" s="99" t="inlineStr">
@@ -13040,7 +13047,7 @@
         <v/>
       </c>
       <c r="S95" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R95)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R95)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T95" s="99" t="inlineStr">
@@ -13164,7 +13171,7 @@
         <v/>
       </c>
       <c r="S96" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R96)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R96)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T96" s="99" t="inlineStr">
@@ -13288,7 +13295,7 @@
         <v/>
       </c>
       <c r="S97" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R97)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R97)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T97" s="99" t="inlineStr">
@@ -13412,7 +13419,7 @@
         <v/>
       </c>
       <c r="S98" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R98)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R98)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T98" s="99" t="inlineStr">
@@ -13536,7 +13543,7 @@
         <v/>
       </c>
       <c r="S99" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R99)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R99)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T99" s="99" t="inlineStr">
@@ -13660,7 +13667,7 @@
         <v/>
       </c>
       <c r="S100" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R100)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R100)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T100" s="99" t="inlineStr">
@@ -13784,7 +13791,7 @@
         <v/>
       </c>
       <c r="S101" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R101)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R101)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T101" s="99" t="inlineStr">
@@ -13908,7 +13915,7 @@
         <v/>
       </c>
       <c r="S102" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R102)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R102)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T102" s="99" t="inlineStr">
@@ -14031,7 +14038,7 @@
         <v/>
       </c>
       <c r="S103" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R103)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R103)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T103" s="99" t="inlineStr">
@@ -14156,7 +14163,7 @@
         <v/>
       </c>
       <c r="S104" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R104)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R104)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T104" s="99" t="inlineStr">
@@ -14281,7 +14288,7 @@
         <v/>
       </c>
       <c r="S105" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R105)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R105)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T105" s="99" t="inlineStr">
@@ -14406,7 +14413,7 @@
         <v/>
       </c>
       <c r="S106" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R106)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R106)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T106" s="99" t="inlineStr">
@@ -14531,7 +14538,7 @@
         <v/>
       </c>
       <c r="S107" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R107)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R107)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T107" s="99" t="inlineStr">
@@ -14656,7 +14663,7 @@
         <v/>
       </c>
       <c r="S108" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R108)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R108)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T108" s="102" t="inlineStr">
@@ -14782,7 +14789,7 @@
         <v/>
       </c>
       <c r="S109" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R109)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R109)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T109" s="99" t="inlineStr">
@@ -14908,7 +14915,7 @@
         <v/>
       </c>
       <c r="S110" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R110)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R110)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T110" s="99" t="inlineStr">
@@ -15034,7 +15041,7 @@
         <v/>
       </c>
       <c r="S111" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R111)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R111)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T111" s="99" t="inlineStr">
@@ -15160,7 +15167,7 @@
         <v/>
       </c>
       <c r="S112" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R112)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R112)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T112" s="99" t="inlineStr">
@@ -15283,7 +15290,7 @@
         <v/>
       </c>
       <c r="S113" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R113)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R113)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T113" s="99" t="inlineStr">
@@ -15403,7 +15410,7 @@
         <v/>
       </c>
       <c r="S114" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R114)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R114)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T114" s="102" t="inlineStr">
@@ -15522,7 +15529,7 @@
         <v/>
       </c>
       <c r="S115" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R115)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R115)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T115" s="102" t="inlineStr">
@@ -15640,7 +15647,7 @@
         <v/>
       </c>
       <c r="S116" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R116)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R116)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T116" s="102" t="inlineStr">
@@ -15763,7 +15770,7 @@
         <v/>
       </c>
       <c r="S117" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R117)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R117)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T117" s="99" t="inlineStr">
@@ -15889,7 +15896,7 @@
         <v/>
       </c>
       <c r="S118" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R118)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R118)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T118" s="99" t="inlineStr">
@@ -16013,7 +16020,7 @@
         <v/>
       </c>
       <c r="S119" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R119)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R119)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T119" s="99" t="inlineStr">
@@ -16138,7 +16145,7 @@
         <v/>
       </c>
       <c r="S120" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R120)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R120)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T120" s="99" t="inlineStr">
@@ -16261,7 +16268,7 @@
         <v/>
       </c>
       <c r="S121" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R121)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R121)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T121" s="99" t="inlineStr">
@@ -16386,7 +16393,7 @@
         <v/>
       </c>
       <c r="S122" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R122)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R122)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T122" s="99" t="inlineStr">
@@ -16509,7 +16516,7 @@
         <v/>
       </c>
       <c r="S123" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R123)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R123)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T123" s="99" t="inlineStr">
@@ -16632,7 +16639,7 @@
         <v/>
       </c>
       <c r="S124" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R124)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R124)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T124" s="99" t="inlineStr">
@@ -16755,7 +16762,7 @@
         <v/>
       </c>
       <c r="S125" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R125)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R125)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T125" s="99" t="inlineStr">
@@ -16878,7 +16885,7 @@
         <v/>
       </c>
       <c r="S126" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R126)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R126)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T126" s="99" t="inlineStr">
@@ -17001,7 +17008,7 @@
         <v/>
       </c>
       <c r="S127" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R127)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R127)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T127" s="99" t="inlineStr">
@@ -17124,7 +17131,7 @@
         <v/>
       </c>
       <c r="S128" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R128)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R128)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T128" s="99" t="inlineStr">
@@ -17247,7 +17254,7 @@
         <v/>
       </c>
       <c r="S129" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R129)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R129)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T129" s="99" t="inlineStr">
@@ -17370,7 +17377,7 @@
         <v/>
       </c>
       <c r="S130" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R130)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R130)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T130" s="99" t="inlineStr">
@@ -17493,7 +17500,7 @@
         <v/>
       </c>
       <c r="S131" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R131)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R131)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T131" s="99" t="inlineStr">
@@ -17616,7 +17623,7 @@
         <v/>
       </c>
       <c r="S132" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R132)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R132)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T132" s="99" t="inlineStr">
@@ -17740,7 +17747,7 @@
         <v/>
       </c>
       <c r="S133" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R133)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R133)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T133" s="99" t="inlineStr">
@@ -17863,7 +17870,7 @@
         <v/>
       </c>
       <c r="S134" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R134)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R134)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T134" s="99" t="inlineStr">
@@ -17986,7 +17993,7 @@
         <v/>
       </c>
       <c r="S135" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R135)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R135)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T135" s="99" t="inlineStr">
@@ -18112,7 +18119,7 @@
         <v/>
       </c>
       <c r="S136" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R136)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R136)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T136" s="99" t="inlineStr">
@@ -18238,7 +18245,7 @@
         <v/>
       </c>
       <c r="S137" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R137)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R137)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T137" s="99" t="inlineStr">
@@ -18364,7 +18371,7 @@
         <v/>
       </c>
       <c r="S138" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R138)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R138)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T138" s="99" t="inlineStr">
@@ -18490,7 +18497,7 @@
         <v/>
       </c>
       <c r="S139" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R139)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R139)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T139" s="99" t="inlineStr">
@@ -18616,7 +18623,7 @@
         <v/>
       </c>
       <c r="S140" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R140)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R140)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T140" s="99" t="inlineStr">
@@ -18742,7 +18749,7 @@
         <v/>
       </c>
       <c r="S141" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R141)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R141)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T141" s="99" t="inlineStr">
@@ -18868,7 +18875,7 @@
         <v/>
       </c>
       <c r="S142" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R142)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R142)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T142" s="99" t="inlineStr">
@@ -18994,7 +19001,7 @@
         <v/>
       </c>
       <c r="S143" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R143)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R143)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T143" s="99" t="inlineStr">
@@ -19120,7 +19127,7 @@
         <v/>
       </c>
       <c r="S144" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R144)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R144)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T144" s="99" t="inlineStr">
@@ -19246,7 +19253,7 @@
         <v/>
       </c>
       <c r="S145" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R145)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R145)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T145" s="99" t="inlineStr">
@@ -19372,7 +19379,7 @@
         <v/>
       </c>
       <c r="S146" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R146)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R146)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T146" s="99" t="inlineStr">
@@ -19498,7 +19505,7 @@
         <v/>
       </c>
       <c r="S147" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R147)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R147)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T147" s="99" t="inlineStr">
@@ -19624,7 +19631,7 @@
         <v/>
       </c>
       <c r="S148" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R148)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R148)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T148" s="99" t="inlineStr">
@@ -19750,7 +19757,7 @@
         <v/>
       </c>
       <c r="S149" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R149)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R149)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T149" s="99" t="inlineStr">
@@ -19876,7 +19883,7 @@
         <v/>
       </c>
       <c r="S150" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R150)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R150)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T150" s="99" t="inlineStr">
@@ -20002,7 +20009,7 @@
         <v/>
       </c>
       <c r="S151" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R151)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R151)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T151" s="99" t="inlineStr">
@@ -20128,7 +20135,7 @@
         <v/>
       </c>
       <c r="S152" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R152)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R152)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T152" s="99" t="inlineStr">
@@ -20254,7 +20261,7 @@
         <v/>
       </c>
       <c r="S153" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R153)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R153)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T153" s="99" t="inlineStr">
@@ -20380,7 +20387,7 @@
         <v/>
       </c>
       <c r="S154" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R154)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R154)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T154" s="99" t="inlineStr">
@@ -20506,7 +20513,7 @@
         <v/>
       </c>
       <c r="S155" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R155)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R155)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T155" s="99" t="inlineStr">
@@ -20632,7 +20639,7 @@
         <v/>
       </c>
       <c r="S156" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R156)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R156)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T156" s="99" t="inlineStr">
@@ -20758,7 +20765,7 @@
         <v/>
       </c>
       <c r="S157" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R157)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R157)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T157" s="99" t="inlineStr">
@@ -20884,7 +20891,7 @@
         <v/>
       </c>
       <c r="S158" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R158)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R158)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T158" s="99" t="inlineStr">
@@ -21010,7 +21017,7 @@
         <v/>
       </c>
       <c r="S159" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R159)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R159)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T159" s="99" t="inlineStr">
@@ -21136,7 +21143,7 @@
         <v/>
       </c>
       <c r="S160" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R160)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R160)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T160" s="99" t="inlineStr">
@@ -21262,7 +21269,7 @@
         <v/>
       </c>
       <c r="S161" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R161)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R161)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T161" s="99" t="inlineStr">
@@ -21388,7 +21395,7 @@
         <v/>
       </c>
       <c r="S162" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R162)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R162)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T162" s="99" t="inlineStr">
@@ -21514,7 +21521,7 @@
         <v/>
       </c>
       <c r="S163" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R163)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R163)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T163" s="99" t="inlineStr">
@@ -21640,7 +21647,7 @@
         <v/>
       </c>
       <c r="S164" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R164)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R164)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T164" s="99" t="inlineStr">
@@ -21766,7 +21773,7 @@
         <v/>
       </c>
       <c r="S165" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R165)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R165)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T165" s="99" t="inlineStr">
@@ -21892,7 +21899,7 @@
         <v/>
       </c>
       <c r="S166" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R166)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R166)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T166" s="99" t="inlineStr">
@@ -22018,7 +22025,7 @@
         <v/>
       </c>
       <c r="S167" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R167)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R167)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T167" s="99" t="inlineStr">
@@ -22144,7 +22151,7 @@
         <v/>
       </c>
       <c r="S168" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R168)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R168)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T168" s="99" t="inlineStr">
@@ -22270,7 +22277,7 @@
         <v/>
       </c>
       <c r="S169" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R169)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R169)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T169" s="99" t="inlineStr">
@@ -22396,7 +22403,7 @@
         <v/>
       </c>
       <c r="S170" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R170)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R170)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T170" s="99" t="inlineStr">
@@ -22522,7 +22529,7 @@
         <v/>
       </c>
       <c r="S171" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R171)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R171)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T171" s="99" t="inlineStr">
@@ -22645,7 +22652,7 @@
         <v/>
       </c>
       <c r="S172" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R172)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R172)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T172" s="99" t="inlineStr">
@@ -22768,7 +22775,7 @@
         <v/>
       </c>
       <c r="S173" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R173)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R173)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T173" s="99" t="inlineStr">
@@ -22892,7 +22899,7 @@
         <v/>
       </c>
       <c r="S174" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R174)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R174)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T174" s="99" t="inlineStr">
@@ -23016,7 +23023,7 @@
         <v/>
       </c>
       <c r="S175" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R175)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R175)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T175" s="99" t="inlineStr">
@@ -23140,7 +23147,7 @@
         <v/>
       </c>
       <c r="S176" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R176)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R176)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T176" s="99" t="inlineStr">
@@ -23264,7 +23271,7 @@
         <v/>
       </c>
       <c r="S177" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R177)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R177)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T177" s="99" t="inlineStr">
@@ -23388,7 +23395,7 @@
         <v/>
       </c>
       <c r="S178" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R178)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R178)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T178" s="99" t="inlineStr">
@@ -23513,7 +23520,7 @@
         <v/>
       </c>
       <c r="S179" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R179)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R179)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T179" s="99" t="inlineStr">
@@ -23636,7 +23643,7 @@
         <v/>
       </c>
       <c r="S180" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R180)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R180)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T180" s="99" t="inlineStr">
@@ -23760,7 +23767,7 @@
         <v/>
       </c>
       <c r="S181" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R181)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R181)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T181" s="99" t="inlineStr">
@@ -23883,7 +23890,7 @@
         <v/>
       </c>
       <c r="S182" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R182)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R182)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T182" s="99" t="inlineStr">
@@ -24006,7 +24013,7 @@
         <v/>
       </c>
       <c r="S183" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R183)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R183)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T183" s="99" t="inlineStr">
@@ -24130,7 +24137,7 @@
         <v/>
       </c>
       <c r="S184" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R184)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R184)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T184" s="99" t="inlineStr">
@@ -24255,7 +24262,7 @@
         <v/>
       </c>
       <c r="S185" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R185)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R185)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T185" s="99" t="inlineStr">
@@ -24379,7 +24386,7 @@
         <v/>
       </c>
       <c r="S186" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R186)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R186)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T186" s="99" t="inlineStr">
@@ -24503,7 +24510,7 @@
         <v/>
       </c>
       <c r="S187" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R187)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R187)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T187" s="99" t="inlineStr">
@@ -24627,7 +24634,7 @@
         <v/>
       </c>
       <c r="S188" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R188)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R188)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T188" s="99" t="inlineStr">
@@ -24751,7 +24758,7 @@
         <v/>
       </c>
       <c r="S189" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R189)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R189)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T189" s="99" t="inlineStr">
@@ -24875,7 +24882,7 @@
         <v/>
       </c>
       <c r="S190" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R190)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R190)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T190" s="99" t="inlineStr">
@@ -24999,7 +25006,7 @@
         <v/>
       </c>
       <c r="S191" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R191)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R191)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T191" s="99" t="inlineStr">
@@ -25122,7 +25129,7 @@
         <v/>
       </c>
       <c r="S192" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R192)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R192)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T192" s="99" t="inlineStr">
@@ -25246,7 +25253,7 @@
         <v/>
       </c>
       <c r="S193" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R193)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R193)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T193" s="99" t="inlineStr">
@@ -25369,7 +25376,7 @@
         <v/>
       </c>
       <c r="S194" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R194)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R194)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T194" s="99" t="inlineStr">
@@ -25492,7 +25499,7 @@
         <v/>
       </c>
       <c r="S195" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R195)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R195)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T195" s="99" t="inlineStr">
@@ -25616,7 +25623,7 @@
         <v/>
       </c>
       <c r="S196" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R196)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R196)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T196" s="99" t="inlineStr">
@@ -25739,7 +25746,7 @@
         <v/>
       </c>
       <c r="S197" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R197)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R197)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T197" s="99" t="inlineStr">
@@ -25862,7 +25869,7 @@
         <v/>
       </c>
       <c r="S198" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R198)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R198)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T198" s="99" t="inlineStr">
@@ -25985,7 +25992,7 @@
         <v/>
       </c>
       <c r="S199" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R199)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R199)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T199" s="99" t="inlineStr">
@@ -26108,7 +26115,7 @@
         <v/>
       </c>
       <c r="S200" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R200)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R200)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T200" s="99" t="inlineStr">
@@ -26231,7 +26238,7 @@
         <v/>
       </c>
       <c r="S201" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R201)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R201)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T201" s="99" t="inlineStr">
@@ -26354,7 +26361,7 @@
         <v/>
       </c>
       <c r="S202" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R202)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R202)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T202" s="99" t="inlineStr">
@@ -26477,7 +26484,7 @@
         <v/>
       </c>
       <c r="S203" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R203)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R203)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T203" s="99" t="inlineStr">
@@ -26600,7 +26607,7 @@
         <v/>
       </c>
       <c r="S204" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R204)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R204)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T204" s="99" t="inlineStr">
@@ -26724,7 +26731,7 @@
         <v/>
       </c>
       <c r="S205" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R205)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R205)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T205" s="99" t="inlineStr">
@@ -26848,7 +26855,7 @@
         <v/>
       </c>
       <c r="S206" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R206)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R206)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T206" s="99" t="inlineStr">
@@ -26971,7 +26978,7 @@
         <v/>
       </c>
       <c r="S207" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R207)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R207)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T207" s="99" t="inlineStr">
@@ -27094,7 +27101,7 @@
         <v/>
       </c>
       <c r="S208" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R208)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R208)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T208" s="99" t="inlineStr">
@@ -27217,7 +27224,7 @@
         <v/>
       </c>
       <c r="S209" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R209)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R209)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T209" s="99" t="inlineStr">
@@ -27340,7 +27347,7 @@
         <v/>
       </c>
       <c r="S210" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R210)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R210)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T210" s="99" t="inlineStr">
@@ -27463,7 +27470,7 @@
         <v/>
       </c>
       <c r="S211" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R211)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R211)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T211" s="99" t="inlineStr">
@@ -27586,7 +27593,7 @@
         <v/>
       </c>
       <c r="S212" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R212)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R212)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T212" s="99" t="inlineStr">
@@ -27709,7 +27716,7 @@
         <v/>
       </c>
       <c r="S213" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R213)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R213)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T213" s="99" t="inlineStr">
@@ -27832,7 +27839,7 @@
         <v/>
       </c>
       <c r="S214" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R214)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R214)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T214" s="99" t="inlineStr">
@@ -27955,7 +27962,7 @@
         <v/>
       </c>
       <c r="S215" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R215)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R215)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T215" s="99" t="inlineStr">
@@ -28078,7 +28085,7 @@
         <v/>
       </c>
       <c r="S216" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R216)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R216)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T216" s="99" t="inlineStr">
@@ -28201,7 +28208,7 @@
         <v/>
       </c>
       <c r="S217" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R217)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R217)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T217" s="99" t="inlineStr">
@@ -28325,7 +28332,7 @@
         <v/>
       </c>
       <c r="S218" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R218)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R218)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T218" s="99" t="inlineStr">
@@ -28448,7 +28455,7 @@
         <v/>
       </c>
       <c r="S219" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R219)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R219)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T219" s="99" t="inlineStr">
@@ -28571,7 +28578,7 @@
         <v/>
       </c>
       <c r="S220" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R220)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R220)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T220" s="99" t="inlineStr">
@@ -28694,7 +28701,7 @@
         <v/>
       </c>
       <c r="S221" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R221)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R221)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T221" s="99" t="inlineStr">
@@ -28817,7 +28824,7 @@
         <v/>
       </c>
       <c r="S222" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R222)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R222)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T222" s="99" t="inlineStr">
@@ -28940,7 +28947,7 @@
         <v/>
       </c>
       <c r="S223" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R223)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R223)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T223" s="99" t="inlineStr">
@@ -29063,7 +29070,7 @@
         <v/>
       </c>
       <c r="S224" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R224)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R224)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T224" s="99" t="inlineStr">
@@ -29186,7 +29193,7 @@
         <v/>
       </c>
       <c r="S225" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R225)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R225)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T225" s="99" t="inlineStr">
@@ -29309,7 +29316,7 @@
         <v/>
       </c>
       <c r="S226" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R226)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R226)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T226" s="99" t="inlineStr">
@@ -29432,7 +29439,7 @@
         <v/>
       </c>
       <c r="S227" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R227)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R227)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T227" s="99" t="inlineStr">
@@ -29555,7 +29562,7 @@
         <v/>
       </c>
       <c r="S228" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R228)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R228)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T228" s="99" t="inlineStr">
@@ -29678,7 +29685,7 @@
         <v/>
       </c>
       <c r="S229" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R229)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R229)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T229" s="99" t="inlineStr">
@@ -29801,7 +29808,7 @@
         <v/>
       </c>
       <c r="S230" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R230)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R230)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T230" s="99" t="inlineStr">
@@ -29925,7 +29932,7 @@
         <v/>
       </c>
       <c r="S231" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R231)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R231)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T231" s="102" t="inlineStr">
@@ -30048,7 +30055,7 @@
         <v/>
       </c>
       <c r="S232" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R232)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R232)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T232" s="102" t="inlineStr">
@@ -30168,7 +30175,7 @@
         <v/>
       </c>
       <c r="S233" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R233)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R233)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U233" s="102" t="inlineStr">
@@ -30284,7 +30291,7 @@
         <v/>
       </c>
       <c r="S234" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R234)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R234)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U234" s="102" t="inlineStr">
@@ -30400,7 +30407,7 @@
         <v/>
       </c>
       <c r="S235" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R235)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R235)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U235" s="102" t="inlineStr">
@@ -30516,7 +30523,7 @@
         <v/>
       </c>
       <c r="S236" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R236)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R236)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U236" s="102" t="inlineStr">
@@ -30632,7 +30639,7 @@
         <v/>
       </c>
       <c r="S237" s="103">
-        <f>IF(COUNTIF($R$6:$R$248,R237)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R237)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="U237" s="102" t="inlineStr">
@@ -30749,7 +30756,7 @@
         <v/>
       </c>
       <c r="S238" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R238)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R238)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T238" s="99" t="inlineStr">
@@ -30872,7 +30879,7 @@
         <v/>
       </c>
       <c r="S239" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R239)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R239)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T239" s="99" t="inlineStr">
@@ -30991,7 +30998,7 @@
         <v/>
       </c>
       <c r="S240" s="72">
-        <f>IF(COUNTIF($R$6:$R$248,R240)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R240)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T240" s="99" t="inlineStr">
@@ -31110,7 +31117,7 @@
         <v/>
       </c>
       <c r="S241" s="99">
-        <f>IF(COUNTIF($R$6:$R$248,R241)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R241)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T241" s="99" t="inlineStr">
@@ -31231,7 +31238,7 @@
         <v/>
       </c>
       <c r="S242" s="99">
-        <f>IF(COUNTIF($R$6:$R$248,R242)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R242)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T242" s="99" t="inlineStr">
@@ -31353,7 +31360,7 @@
         <v/>
       </c>
       <c r="S243" s="99">
-        <f>IF(COUNTIF($R$6:$R$248,R243)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R243)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T243" s="99" t="inlineStr">
@@ -31475,7 +31482,7 @@
         <v/>
       </c>
       <c r="S244" s="99">
-        <f>IF(COUNTIF($R$6:$R$248,R244)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R244)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T244" s="99" t="inlineStr">
@@ -31597,7 +31604,7 @@
         <v/>
       </c>
       <c r="S245" s="99">
-        <f>IF(COUNTIF($R$6:$R$248,R245)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R245)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T245" s="99" t="inlineStr">
@@ -31719,7 +31726,7 @@
         <v/>
       </c>
       <c r="S246" s="99">
-        <f>IF(COUNTIF($R$6:$R$248,R246)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R246)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T246" s="99" t="inlineStr">
@@ -31841,7 +31848,7 @@
         <v/>
       </c>
       <c r="S247" s="99">
-        <f>IF(COUNTIF($R$6:$R$248,R247)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R247)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T247" s="99" t="inlineStr">
@@ -31935,17 +31942,17 @@
       </c>
       <c r="M248" s="99" t="inlineStr">
         <is>
-          <t>v001</t>
+          <t>v003</t>
         </is>
       </c>
       <c r="N248" s="99" t="inlineStr">
         <is>
-          <t>主体70×50m；20层，层高4.2m为参考图推定；62独立包；4角色公共色盘；灰色屋顶</t>
+          <t>主体70×50m；92独立资产包；灰色屋顶、错层楼板与高低立柱；3台塔吊各自独立合集，每台7组成件；4角色公共色盘</t>
         </is>
       </c>
       <c r="O248" s="99" t="inlineStr">
         <is>
-          <t>assets/art/environments/open_world/source/tower_02/v001/塔2_施工高楼_70x50m_v001.blend</t>
+          <t>assets/art/environments/open_world/source/tower_02/v003/塔2_施工高楼_70x50m_v003.blend</t>
         </is>
       </c>
       <c r="P248" s="99" t="inlineStr">
@@ -31955,7 +31962,7 @@
       </c>
       <c r="Q248" s="72" t="inlineStr">
         <is>
-          <t>塔2;施工高楼;塔吊;脚手架;灰色屋顶</t>
+          <t>塔2;施工高楼;塔吊独立合集;错层屋顶;灰色顶面;v003</t>
         </is>
       </c>
       <c r="R248" s="99">
@@ -31963,12 +31970,12 @@
         <v/>
       </c>
       <c r="S248" s="99">
-        <f>IF(COUNTIF($R$6:$R$248,R248)&gt;1,"重复","唯一")</f>
+        <f>IF(COUNTIF($R$6:$R$249,R248)&gt;1,"重复","唯一")</f>
         <v/>
       </c>
       <c r="T248" s="99" t="inlineStr">
         <is>
-          <t>e29fb41ba7a1ba9c498d5fe293498aa8e6f95f95e5dd38beb1e139ba39eac90e</t>
+          <t>9c56a7e489416230c460063c3b5a84b2cfed8d9c43cec05a20638e5e3d84b4c8</t>
         </is>
       </c>
       <c r="U248" s="72" t="inlineStr">
@@ -31976,10 +31983,8 @@
           <t>Codex</t>
         </is>
       </c>
-      <c r="V248" s="99" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
+      <c r="V248" s="130" t="n">
+        <v>46295</v>
       </c>
       <c r="W248" s="72" t="inlineStr">
         <is>
@@ -31993,7 +31998,126 @@
       </c>
       <c r="Y248" s="72" t="inlineStr">
         <is>
-          <t>仅Blender原始文件；未导出GLB、未接入Godot、无碰撞/LOD。高度为美术推定，不继承主塔玩法层高。</t>
+          <t>Blender原始文件已完成；3台塔吊为各自独立合集。未导出GLB、未接入Godot、未制作碰撞/LOD。</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="255" customHeight="1" s="129">
+      <c r="A249" s="99" t="inlineStr">
+        <is>
+          <t>ENV-OPENWORLD-TOWER03</t>
+        </is>
+      </c>
+      <c r="B249" s="72" t="inlineStr">
+        <is>
+          <t>开放世界 塔楼03 设备天台办公楼 70×44m</t>
+        </is>
+      </c>
+      <c r="C249" s="72" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="D249" s="99" t="inlineStr">
+        <is>
+          <t>environment_kit_3d</t>
+        </is>
+      </c>
+      <c r="E249" s="99" t="inlineStr">
+        <is>
+          <t>open_world_tower_03</t>
+        </is>
+      </c>
+      <c r="F249" s="99" t="inlineStr">
+        <is>
+          <t>building_source</t>
+        </is>
+      </c>
+      <c r="G249" s="99" t="n"/>
+      <c r="H249" s="99" t="inlineStr">
+        <is>
+          <t>Top3D / Blender Z-up</t>
+        </is>
+      </c>
+      <c r="I249" s="99" t="inlineStr">
+        <is>
+          <t>office_rooftop</t>
+        </is>
+      </c>
+      <c r="J249" s="72" t="inlineStr">
+        <is>
+          <t>开放世界独立塔楼，与主塔、塔2平级</t>
+        </is>
+      </c>
+      <c r="K249" s="99" t="inlineStr">
+        <is>
+          <t>Blender源已完成</t>
+        </is>
+      </c>
+      <c r="L249" s="99" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M249" s="99" t="inlineStr">
+        <is>
+          <t>v001</t>
+        </is>
+      </c>
+      <c r="N249" s="99" t="inlineStr">
+        <is>
+          <t>主体70×44m；屋顶高40m、机房高8m；217独立资产包；天台双层机房、风机、风管、通信桅杆和卫星天线</t>
+        </is>
+      </c>
+      <c r="O249" s="99" t="inlineStr">
+        <is>
+          <t>assets/art/environments/open_world/source/tower_03/v001/塔楼03_设备天台办公楼_v001.blend</t>
+        </is>
+      </c>
+      <c r="P249" s="99" t="inlineStr">
+        <is>
+          <t>用户参考图1（天台布局）及图2（整体结构）；assets/art/environments/open_world/source/tower_03/v001/catalog.json</t>
+        </is>
+      </c>
+      <c r="Q249" s="72" t="inlineStr">
+        <is>
+          <t>塔楼03;设备天台;办公楼;风机;风管;通信桅杆;卫星天线;70×44m</t>
+        </is>
+      </c>
+      <c r="R249" s="99">
+        <f>LOWER(TRIM(C249)&amp;"|"&amp;TRIM(D249)&amp;"|"&amp;TRIM(E249)&amp;"|"&amp;TRIM(F249)&amp;"|"&amp;TRIM(H249)&amp;"|"&amp;TRIM(I249))</f>
+        <v/>
+      </c>
+      <c r="S249" s="99">
+        <f>IF(COUNTIF($R$6:$R$249,R249)&gt;1,"重复","唯一")</f>
+        <v/>
+      </c>
+      <c r="T249" s="99" t="inlineStr">
+        <is>
+          <t>91b2f8f7d7ccfd483e76799e4b0a7573492b1741021eb3f7b34e5bfc24ec631e</t>
+        </is>
+      </c>
+      <c r="U249" s="72" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="V249" s="130" t="n">
+        <v>46295</v>
+      </c>
+      <c r="W249" s="72" t="inlineStr">
+        <is>
+          <t>用户提供参考图，仅据图建模</t>
+        </is>
+      </c>
+      <c r="X249" s="72" t="inlineStr">
+        <is>
+          <t>塔楼03</t>
+        </is>
+      </c>
+      <c r="Y249" s="72" t="inlineStr">
+        <is>
+          <t>仅Blender原始文件；按用户确认尺寸制作。未导出GLB、未接入Godot、未制作碰撞/LOD。</t>
         </is>
       </c>
     </row>
@@ -32020,13 +32144,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="C6:C249" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"角色,敌人,武器,道具,场景,场景道具,基地资产包,UI,特效,音频"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="K6:K249" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待制作,程序占位,已完成,原型已接入,弃用,旧资产已从正式基地移除,正式美术已接入,已优化并正式接入,Blender源已完成,已导入；优化完成,已从运行场景移除,白盒组件"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" operator="between">
+    <dataValidation sqref="L6:L249" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -45489,7 +45613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.808590000000001" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="68" min="1" max="1"/>
@@ -46442,41 +46566,68 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>v0.1.24</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>新增Blender建筑源</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>关卡场景 / 开放世界</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>ENV-OPENWORLD-TOWER02 塔2：70×50m，62包，灰色顶面。</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="0" t="inlineStr">
         <is>
           <t>仅源资产完成；运行时未接入。</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>Codex</t>
         </is>
       </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>v0.1.25</t>
+        </is>
+      </c>
+      <c r="B31" s="131" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>复原开放世界塔楼登记</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>关卡场景 / Blender源</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>塔2更新至v003并恢复塔楼03 v001源文件登记；仅Blender源，未登记运行时Prefab。</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="n"/>
+      <c r="G31" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
